--- a/docs/hoang-huy-phat/sosach2023/BAO_CAO_CONG_NO_HHP_2023.xlsx
+++ b/docs/hoang-huy-phat/sosach2023/BAO_CAO_CONG_NO_HHP_2023.xlsx
@@ -576,17 +576,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Hải Thanh</t>
+          <t>Lê Thị Thu Ba</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>99568668</v>
+        <v>120703208</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>99568668</v>
+        <v>120703208</v>
       </c>
     </row>
     <row r="10">
@@ -608,17 +608,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lê Thị Thu Ba</t>
+          <t>Nguyễn Thị Hải Thanh</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>120703208</v>
+        <v>99568668</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>120703208</v>
+        <v>99568668</v>
       </c>
     </row>
     <row r="12">
@@ -688,81 +688,81 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cửa Hàng Nhật An</t>
+          <t>Đặng Thị Luyến</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>53345488</v>
+        <v>152002192</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>53345488</v>
+        <v>152002192</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lê Thị Chanh</t>
+          <t>CÔNG TY ĐIỆN LỰC GIA LAI</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>198072703</v>
+        <v>4191000</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>198072703</v>
+        <v>4191000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CÔNG TY ĐIỆN LỰC GIA LAI</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4191000</v>
+        <v>53903780</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>4191000</v>
+        <v>53903780</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
+          <t>Cửa Hàng Nhật An</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>53903780</v>
+        <v>53345488</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>53903780</v>
+        <v>53345488</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Đặng Thị Luyến</t>
+          <t>Lê Thị Chanh</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>152002192</v>
+        <v>198072703</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>152002192</v>
+        <v>198072703</v>
       </c>
     </row>
     <row r="21">
@@ -944,33 +944,33 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN DAILYMART</t>
+          <t>TRẦN THANH HẢI</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>68022735</v>
+        <v>95699723</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>68022735</v>
+        <v>95699723</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TRẦN THANH HẢI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN DAILYMART</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>95699723</v>
+        <v>68022735</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>95699723</v>
+        <v>68022735</v>
       </c>
     </row>
     <row r="34">
@@ -1088,209 +1088,209 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TẠP HÓA KHÁNH HÀ</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẢI ANH TIẾN</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>23601721</v>
+        <v>86188966</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>23601721</v>
+        <v>86188966</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Huỳnh Văn Định</t>
+          <t>TẠP HÓA KHÁNH HÀ</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>77476395</v>
+        <v>23601721</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>77476395</v>
+        <v>23601721</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Tạp Hóa Hoàng Phát</t>
+          <t>Huỳnh Văn Định</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>16962352</v>
+        <v>77476395</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>16962352</v>
+        <v>77476395</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Hà Thị Thúy An</t>
+          <t>Tạp Hóa Hoàng Phát</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>77418077</v>
+        <v>16962352</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>77418077</v>
+        <v>16962352</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẢI ANH TIẾN</t>
+          <t>Hà Thị Thúy An</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>86188966</v>
+        <v>77418077</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>86188966</v>
+        <v>77418077</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TẠP HÓA THÙY LINH</t>
+          <t>VŨ TRỌNG PHƯƠNG</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>42317063</v>
+        <v>57397069</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>42317063</v>
+        <v>57397069</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>VŨ TRỌNG PHƯƠNG</t>
+          <t>TẠP HÓA THÙY LINH</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>57397069</v>
+        <v>42317063</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>57397069</v>
+        <v>42317063</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Lê Thị Tuyết Anh</t>
+          <t>TẠP PHẨM KHÁNH AN</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>75481879</v>
+        <v>2964343</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>75481879</v>
+        <v>2964343</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH TRẦN VĂN THỨC</t>
+          <t>NGUYỄN THỊ THẢO</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>77438398</v>
+        <v>41052529</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>77438398</v>
+        <v>41052529</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ THẢO</t>
+          <t>HỘ KINH DOAN ĐẶNG THỊ DIỄM</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>41052529</v>
+        <v>5578462</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>41052529</v>
+        <v>5578462</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HỘ KINH DOAN ĐẶNG THỊ DIỄM</t>
+          <t>HỘ KINH DOANH TRẦN VĂN THỨC</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>5578462</v>
+        <v>77438398</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>5578462</v>
+        <v>77438398</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TẠP PHẨM KHÁNH AN</t>
+          <t>Lê Thị Tuyết Anh</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2964343</v>
+        <v>75481879</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>2964343</v>
+        <v>75481879</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ THANH HƯƠNG</t>
+          <t>HỘ KINH DOANH TẠP HÓA NGỌC TÀI</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>76418221</v>
+        <v>80077301</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>76418221</v>
+        <v>80077301</v>
       </c>
     </row>
     <row r="54">
@@ -1312,17 +1312,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH TẠP HÓA NGỌC TÀI</t>
+          <t>HỘ KINH DOANH NGUYỄN THỊ THANH HƯƠNG</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>80077301</v>
+        <v>76418221</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>80077301</v>
+        <v>76418221</v>
       </c>
     </row>
     <row r="56">
@@ -1344,33 +1344,33 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ SƯƠNG</t>
+          <t>Cửa Hàng Mua Bán Tạp Hóa Và Dụng Cụ Gia Đình Ngọc Hân</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>57136188</v>
+        <v>118850900</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>57136188</v>
+        <v>118850900</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cửa Hàng Mua Bán Tạp Hóa Và Dụng Cụ Gia Đình Ngọc Hân</t>
+          <t>NGUYỄN THỊ SƯƠNG</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>118850900</v>
+        <v>57136188</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>118850900</v>
+        <v>57136188</v>
       </c>
     </row>
     <row r="59">
@@ -1536,33 +1536,33 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH PHAN THỊ ÁNH NHUNG</t>
+          <t>DOANH NGHIỆP TƯ NHÂN KEN</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>16661853</v>
+        <v>3988330</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>16661853</v>
+        <v>3988330</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN KEN</t>
+          <t>HỘ KINH DOANH PHAN THỊ ÁNH NHUNG</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3988330</v>
+        <v>16661853</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>3988330</v>
+        <v>16661853</v>
       </c>
     </row>
     <row r="71">
@@ -1584,33 +1584,33 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PHAN XUÂN TUẤN</t>
+          <t>Nguyễn Văn Vũ</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>32843778</v>
+        <v>44446971</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>32843778</v>
+        <v>44446971</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Vũ</t>
+          <t>PHAN XUÂN TUẤN</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>44446971</v>
+        <v>32843778</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>44446971</v>
+        <v>32843778</v>
       </c>
     </row>
     <row r="74">
@@ -1632,17 +1632,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ẨM THỰC CÔ DUYÊN</t>
+          <t>CÔNG TY BẢO HIỂM BIDV BẮC TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>18177736</v>
+        <v>143713599</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>18177736</v>
+        <v>143713599</v>
       </c>
     </row>
     <row r="76">
@@ -1664,49 +1664,49 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CÔNG TY BẢO HIỂM BIDV BẮC TÂY NGUYÊN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ẨM THỰC CÔ DUYÊN</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>143713599</v>
+        <v>18177736</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>143713599</v>
+        <v>18177736</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TẠP HÓA SƠN THƯƠNG</t>
+          <t>PHẠM THỊ THU TRANG</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>137958045</v>
+        <v>65479968</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>137958045</v>
+        <v>65479968</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PHẠM THỊ THU TRANG</t>
+          <t>TẠP HÓA SƠN THƯƠNG</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>65479968</v>
+        <v>137958045</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>65479968</v>
+        <v>137958045</v>
       </c>
     </row>
     <row r="80">
@@ -1728,33 +1728,33 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI GIA LAI</t>
+          <t>TẠP HÓA BỐN PHƯƠNG</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>52635998</v>
+        <v>9172417</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>52635998</v>
+        <v>9172417</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TẠP HÓA BỐN PHƯƠNG</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI GIA LAI</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>9172417</v>
+        <v>52635998</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>9172417</v>
+        <v>52635998</v>
       </c>
     </row>
     <row r="83">
@@ -2064,97 +2064,97 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>TẠP HÓA HỒNG NHUNG</t>
+          <t>Đàm Văn Tú</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>12402720</v>
+        <v>202030757</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>12402720</v>
+        <v>202030757</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Lương Thị Liễu</t>
+          <t>TẠP HÓA HỒNG NHUNG</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>112580783</v>
+        <v>12402720</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>112580783</v>
+        <v>12402720</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Hà Thị Ánh Thu</t>
+          <t>Lương Thị Liễu</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>31768870</v>
+        <v>112580783</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>31768870</v>
+        <v>112580783</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Đàm Văn Tú</t>
+          <t>Hà Thị Ánh Thu</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>202030757</v>
+        <v>31768870</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>202030757</v>
+        <v>31768870</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Đinh Văn Phúc</t>
+          <t>Đậu Đức Hào</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>106849534</v>
+        <v>238603563</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>106849534</v>
+        <v>238603563</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Đậu Đức Hào</t>
+          <t>Đinh Văn Phúc</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>238603563</v>
+        <v>106849534</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>238603563</v>
+        <v>106849534</v>
       </c>
     </row>
     <row r="108">
@@ -2176,33 +2176,33 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Đoàn Hữu Minh</t>
+          <t>DOANH NGHIỆP TƯ NHÂN HỒNG BIÊN</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>113495115</v>
+        <v>5741340</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>113495115</v>
+        <v>5741340</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN HỒNG BIÊN</t>
+          <t>Đoàn Hữu Minh</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>5741340</v>
+        <v>113495115</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>5741340</v>
+        <v>113495115</v>
       </c>
     </row>
     <row r="111">
@@ -2224,193 +2224,193 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Hồ Văn Thành</t>
+          <t>Ngô Võ Đan</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>113593552</v>
+        <v>113453838</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>113593552</v>
+        <v>113453838</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Dương Thị Hiếu</t>
+          <t>Lê Xuân Cường</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>289806522</v>
+        <v>92364509</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>289806522</v>
+        <v>92364509</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Hà Trịnh Quốc Việt</t>
+          <t>Hồ Văn Thành</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>209257274</v>
+        <v>113593552</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>209257274</v>
+        <v>113593552</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Huỳnh Thị Trúc Ly</t>
+          <t>Hà Trịnh Quốc Việt</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>172721649</v>
+        <v>209257274</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>172721649</v>
+        <v>209257274</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN NGÓI NÂU GIA LAI</t>
+          <t>Dương Thị Hiếu</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>62216706</v>
+        <v>289806522</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>62216706</v>
+        <v>289806522</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ngô Võ Đan</t>
+          <t>CÔNG TY CỔ PHẦN NGÓI NÂU GIA LAI</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>113453838</v>
+        <v>62216706</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>113453838</v>
+        <v>62216706</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Tú</t>
+          <t>Nguyễn Minh Tứ</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>169458458</v>
+        <v>132486797</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>169458458</v>
+        <v>132486797</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Duy</t>
+          <t>Nguyễn Minh Tú</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>241451470</v>
+        <v>169458458</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>241451470</v>
+        <v>169458458</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Hoàng Chí Công</t>
+          <t>Nguyễn Minh Duy</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>147289986</v>
+        <v>241451470</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>147289986</v>
+        <v>241451470</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Lê Xuân Cường</t>
+          <t>Huỳnh Thị Trúc Ly</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>92364509</v>
+        <v>172721649</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>92364509</v>
+        <v>172721649</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Lê Văn Mẫn</t>
+          <t>Hoàng Chí Công</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>235395239</v>
+        <v>147289986</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>235395239</v>
+        <v>147289986</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Tứ</t>
+          <t>Lê Văn Mẫn</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>132486797</v>
+        <v>235395239</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>132486797</v>
+        <v>235395239</v>
       </c>
     </row>
     <row r="124">
@@ -2432,161 +2432,161 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Lê Văn Bằng</t>
+          <t>Nguyễn Hữu Thành</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>132937416</v>
+        <v>260454151</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>132937416</v>
+        <v>260454151</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Nguyễn Hữu Thành</t>
+          <t>Lê Văn Bằng</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>260454151</v>
+        <v>132937416</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>260454151</v>
+        <v>132937416</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thu Hằng</t>
+          <t>Nguyễn Văn Dương</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>155155639</v>
+        <v>187691183</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>155155639</v>
+        <v>187691183</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Mai Hoàng Thiện Châu</t>
+          <t>Nguyễn Thị Đăng Loan</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>166626778</v>
+        <v>173086396</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>166626778</v>
+        <v>173086396</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Đăng Loan</t>
+          <t>Nguyễn Trịnh Minh Hoàng</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>173086396</v>
+        <v>209281321</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>173086396</v>
+        <v>209281321</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Nguyễn Quốc Đạt</t>
+          <t>Nguyễn Thị Thu Hằng</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>241448995</v>
+        <v>155155639</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>241448995</v>
+        <v>155155639</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Dương</t>
+          <t>Mai Hoàng Thiện Châu</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>187691183</v>
+        <v>166626778</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>187691183</v>
+        <v>166626778</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Nguyễn Trường Sơn</t>
+          <t>Nguyễn Quốc Đạt</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>107795444</v>
+        <v>241448995</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>107795444</v>
+        <v>241448995</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Minh Tâm</t>
+          <t>QUÁCH THỊ THÚY NGA</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>190953225</v>
+        <v>19762931</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>190953225</v>
+        <v>19762931</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Hiền</t>
+          <t>PHAN THỊ ÁNH LỸ</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>153063249</v>
+        <v>18342199</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>153063249</v>
+        <v>18342199</v>
       </c>
     </row>
     <row r="135">
@@ -2608,209 +2608,209 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PHAN THỊ ÁNH LỸ</t>
+          <t>Nguyễn Thị Hiền</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>18342199</v>
+        <v>153063249</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>18342199</v>
+        <v>153063249</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>QUÁCH THỊ THÚY NGA</t>
+          <t>Nguyễn Thị Minh Tâm</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>19762931</v>
+        <v>190953225</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>19762931</v>
+        <v>190953225</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Nguyễn Trịnh Minh Hoàng</t>
+          <t>Nguyễn Trường Sơn</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>209281321</v>
+        <v>107795444</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>209281321</v>
+        <v>107795444</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Nguyễn Nam Hồng</t>
+          <t>SUI NGỌC LAN</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>161914097</v>
+        <v>12232763</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>161914097</v>
+        <v>12232763</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH VÕ VĂN NGỌ</t>
+          <t>TẠP HÓA THÌN</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>66782415</v>
+        <v>9754668</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>66782415</v>
+        <v>9754668</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>TẠP HÓA NĂM THI</t>
+          <t>HỘ KINH DOANH VÕ VĂN NGỌ</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>46344956</v>
+        <v>66782415</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>46344956</v>
+        <v>66782415</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TẠP HÓA THÌN</t>
+          <t>Nguyễn Nam Hồng</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>9754668</v>
+        <v>161914097</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>9754668</v>
+        <v>161914097</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>SUI NGỌC LAN</t>
+          <t>TẠP HÓA NĂM THI</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>12232763</v>
+        <v>46344956</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>12232763</v>
+        <v>46344956</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Hoàng Tú</t>
+          <t>Trịnh Tân</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>199955071</v>
+        <v>206613852</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>199955071</v>
+        <v>206613852</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Phạm Hồng Công</t>
+          <t>Trịnh Thị Sinh</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>130483375</v>
+        <v>152557899</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>130483375</v>
+        <v>152557899</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Trần Bích Hải</t>
+          <t>Võ Chí Hà</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>114345439</v>
+        <v>112601232</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>114345439</v>
+        <v>112601232</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Trần Quý Đức</t>
+          <t>Nguyễn Trịnh Tố Ngân</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>169963096</v>
+        <v>130495163</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
       </c>
       <c r="D147" t="n">
-        <v>169963096</v>
+        <v>130495163</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Trần Thị Tuyết Nhung</t>
+          <t>TẠP HÓA BỬU HIỀN</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>132827967</v>
+        <v>61435252</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>132827967</v>
+        <v>61435252</v>
       </c>
     </row>
     <row r="149">
@@ -2832,129 +2832,129 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Trịnh Tân</t>
+          <t>LÊ THỊ MỸ PHƯƠNG</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>206613852</v>
+        <v>43179190</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>206613852</v>
+        <v>43179190</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Trịnh Thị Sinh</t>
+          <t>Trần Thị Tuyết Nhung</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>152557899</v>
+        <v>132827967</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>152557899</v>
+        <v>132827967</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Võ Chí Hà</t>
+          <t>Phạm Hồng Công</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>112601232</v>
+        <v>130483375</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>112601232</v>
+        <v>130483375</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Nguyễn Trịnh Tố Ngân</t>
+          <t>Phan Thanh Hoàng</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>130495163</v>
+        <v>116130899</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>130495163</v>
+        <v>116130899</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>TẠP HÓA BỬU HIỀN</t>
+          <t>Đỗ Trịnh Công</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>61435252</v>
+        <v>152180951</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>61435252</v>
+        <v>152180951</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>LÊ THỊ MỸ PHƯƠNG</t>
+          <t>Vũ Thị Việt Hằng</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>43179190</v>
+        <v>165336925</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>43179190</v>
+        <v>165336925</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Phan Thanh Hoàng</t>
+          <t>Võ Văn Vũ</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>116130899</v>
+        <v>112039110</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>116130899</v>
+        <v>112039110</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Đỗ Trịnh Công</t>
+          <t>Vương Trường Giang</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>152180951</v>
+        <v>111832426</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>152180951</v>
+        <v>111832426</v>
       </c>
     </row>
     <row r="158">
@@ -2976,49 +2976,49 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Vương Trường Giang</t>
+          <t>Hoàng Tú</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>111832426</v>
+        <v>199955071</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>111832426</v>
+        <v>199955071</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Võ Văn Vũ</t>
+          <t>Trần Bích Hải</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>112039110</v>
+        <v>114345439</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>112039110</v>
+        <v>114345439</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Vũ Thị Việt Hằng</t>
+          <t>Trần Quý Đức</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>165336925</v>
+        <v>169963096</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>165336925</v>
+        <v>169963096</v>
       </c>
     </row>
     <row r="162">
@@ -3040,193 +3040,193 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>NGUYỄN VĂN CÔNG</t>
+          <t>Phan Thị Thùy Mỵ</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>94306512</v>
+        <v>113837653</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>94306512</v>
+        <v>113837653</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Kpă Vũ Mạnh Long</t>
+          <t>HUỲNH ĐỨC AN</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>109286964</v>
+        <v>54719280</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
       </c>
       <c r="D164" t="n">
-        <v>109286964</v>
+        <v>54719280</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>HUỲNH ĐỨC AN</t>
+          <t>Kpă Vũ Mạnh Long</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>54719280</v>
+        <v>109286964</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>54719280</v>
+        <v>109286964</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Phan Thị Thùy Mỵ</t>
+          <t>NGUYỄN VĂN CÔNG</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>113837653</v>
+        <v>94306512</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>113837653</v>
+        <v>94306512</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Nguyễn Lê Hậu</t>
+          <t>Trịnh Thị Luận</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>260476999</v>
+        <v>168619647</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>260476999</v>
+        <v>168619647</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Trịnh Thị Luận</t>
+          <t>Dương Thị Thông</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>168619647</v>
+        <v>243833248</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>168619647</v>
+        <v>243833248</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Dương Thị Thông</t>
+          <t>Huỳnh Thị Cúc</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>243833248</v>
+        <v>248582520</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
       </c>
       <c r="D169" t="n">
-        <v>243833248</v>
+        <v>248582520</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Phan Công Thiện</t>
+          <t>Nguyễn Lê Hậu</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>112632349</v>
+        <v>260476999</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
       </c>
       <c r="D170" t="n">
-        <v>112632349</v>
+        <v>260476999</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Nguyễn Thúc Bảo</t>
+          <t>Phan Công Thiện</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>111954346</v>
+        <v>112632349</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>111954346</v>
+        <v>112632349</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Huỳnh Thị Cúc</t>
+          <t>Nguyễn Thúc Bảo</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>248582520</v>
+        <v>111954346</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>248582520</v>
+        <v>111954346</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Dương Nô</t>
+          <t>Ngô Đức Thuận</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>111439059</v>
+        <v>131567122</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>111439059</v>
+        <v>131567122</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Ngô Đức Thuận</t>
+          <t>Nguyễn Văn Theo</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>131567122</v>
+        <v>93332200</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>131567122</v>
+        <v>93332200</v>
       </c>
     </row>
     <row r="175">
@@ -3248,753 +3248,753 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Mai Thị Kim Loan</t>
+          <t>Đinh Biên Thùy</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>144859608</v>
+        <v>142784458</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
       </c>
       <c r="D176" t="n">
-        <v>144859608</v>
+        <v>142784458</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Theo</t>
+          <t>Trần Trung Hiếu</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>93332200</v>
+        <v>19665288</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
       </c>
       <c r="D177" t="n">
-        <v>93332200</v>
+        <v>19665288</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Trịnh Lê Hưng</t>
+          <t>Dương Nô</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>208830345</v>
+        <v>111439059</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
       </c>
       <c r="D178" t="n">
-        <v>208830345</v>
+        <v>111439059</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Đinh Biên Thùy</t>
+          <t>Trịnh Lê Hưng</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>142784458</v>
+        <v>208830345</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>142784458</v>
+        <v>208830345</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Trần Trung Hiếu</t>
+          <t>Đinh Thiện Ân</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>19665288</v>
+        <v>114697559</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>19665288</v>
+        <v>114697559</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Đinh Thiện Ân</t>
+          <t>Mai Thị Kim Loan</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>114697559</v>
+        <v>144859608</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>114697559</v>
+        <v>144859608</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Trung</t>
+          <t>PHẠM NGUYỄN LONG THÀNH</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>34317000</v>
+        <v>40290318</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>34317000</v>
+        <v>40290318</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Trần Văn Hiệu</t>
+          <t>Mai Văn Tân</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>58075244</v>
+        <v>149513069</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>58075244</v>
+        <v>149513069</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PHẠM THỊ THU SA</t>
+          <t>Nguyễn Thị Thanh Hương</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>72713516</v>
+        <v>292651315</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>72713516</v>
+        <v>292651315</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Đồng Thị Thanh</t>
+          <t>Lê Văn Hưng</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>75303891</v>
+        <v>95596343</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>75303891</v>
+        <v>95596343</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Lại Thị Hà</t>
+          <t>Hà Thị Hiếu</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>91139305</v>
+        <v>94706437</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>91139305</v>
+        <v>94706437</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thu</t>
+          <t>Đỗ Thành Vinh</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>56904595</v>
+        <v>113695752</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>56904595</v>
+        <v>113695752</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Mai Văn Tân</t>
+          <t>Phạm Thị Mỹ Hạnh</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>149513069</v>
+        <v>225080985</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>149513069</v>
+        <v>225080985</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Đỗ Thị Bích Hương</t>
+          <t>NGUYỄN THỊ TẠO</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>220668611</v>
+        <v>56632668</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>220668611</v>
+        <v>56632668</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>LƯU THỊ THUỲ</t>
+          <t>CAO MẠNH HÙNG</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>96882946</v>
+        <v>93965037</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>96882946</v>
+        <v>93965037</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Trần Thị Thu Hồng</t>
+          <t>LÊ THỊ MỸ LOAN</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>103684279</v>
+        <v>69945287</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>103684279</v>
+        <v>69945287</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Dương Minh Ngọc</t>
+          <t>NGUYỄN THỊ LINH GIANG</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>73225572</v>
+        <v>89714754</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>73225572</v>
+        <v>89714754</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Hoàng Anh Thương</t>
+          <t>TRẦN TIẾN DŨNG</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>67529025</v>
+        <v>37058364</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
       </c>
       <c r="D193" t="n">
-        <v>67529025</v>
+        <v>37058364</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ LINH GIANG</t>
+          <t>BÙI XUÂN NAM</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>89714754</v>
+        <v>93355244</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
       </c>
       <c r="D194" t="n">
-        <v>89714754</v>
+        <v>93355244</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Nhà Thuốc Linh</t>
+          <t>Trần Văn Hiệu</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>19459440</v>
+        <v>58075244</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>19459440</v>
+        <v>58075244</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TRẦN TIẾN DŨNG</t>
+          <t>PHẠM THỊ THU SA</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>37058364</v>
+        <v>72713516</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>37058364</v>
+        <v>72713516</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>BÙI XUÂN NAM</t>
+          <t>Nguyễn Văn Trung</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>93355244</v>
+        <v>34317000</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>93355244</v>
+        <v>34317000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TRẦN THỊ THU HÀ</t>
+          <t>Đỗ Thị Bích Hương</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>55746047</v>
+        <v>220668611</v>
       </c>
       <c r="C198" t="n">
         <v>0</v>
       </c>
       <c r="D198" t="n">
-        <v>55746047</v>
+        <v>220668611</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Trần Minh Chung</t>
+          <t>Nhà Thuốc Linh</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>55283301</v>
+        <v>19459440</v>
       </c>
       <c r="C199" t="n">
         <v>0</v>
       </c>
       <c r="D199" t="n">
-        <v>55283301</v>
+        <v>19459440</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Đỗ Thị Hồng Nhung</t>
+          <t>Tạp Hóa Thùy Linh</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>222153462</v>
+        <v>72053019</v>
       </c>
       <c r="C200" t="n">
         <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>222153462</v>
+        <v>72053019</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Tạp Hóa Thùy Linh</t>
+          <t>Đỗ Thị Hồng Nhung</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>72053019</v>
+        <v>222153462</v>
       </c>
       <c r="C201" t="n">
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>72053019</v>
+        <v>222153462</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>LÊ THỊ MỸ LOAN</t>
+          <t>Trần Minh Chung</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>69945287</v>
+        <v>55283301</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>69945287</v>
+        <v>55283301</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>TRẦN THỊ THU HƯƠNG</t>
+          <t>TRẦN THỊ THU HÀ</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>33034001</v>
+        <v>55746047</v>
       </c>
       <c r="C203" t="n">
         <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>33034001</v>
+        <v>55746047</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thanh Hương</t>
+          <t>Nguyễn Thị Thu</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>292651315</v>
+        <v>56904595</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>292651315</v>
+        <v>56904595</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>CAO MẠNH HÙNG</t>
+          <t>Lại Thị Hà</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>93965037</v>
+        <v>91139305</v>
       </c>
       <c r="C205" t="n">
         <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>93965037</v>
+        <v>91139305</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ TẠO</t>
+          <t>LƯU THỊ THUỲ</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>56632668</v>
+        <v>96882946</v>
       </c>
       <c r="C206" t="n">
         <v>0</v>
       </c>
       <c r="D206" t="n">
-        <v>56632668</v>
+        <v>96882946</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Phạm Thị Mỹ Hạnh</t>
+          <t>TRẦN THỊ THU HƯƠNG</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>225080985</v>
+        <v>33034001</v>
       </c>
       <c r="C207" t="n">
         <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>225080985</v>
+        <v>33034001</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Đỗ Thành Vinh</t>
+          <t>Hoàng Anh Thương</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>113695752</v>
+        <v>67529025</v>
       </c>
       <c r="C208" t="n">
         <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>113695752</v>
+        <v>67529025</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Hà Thị Hiếu</t>
+          <t>TẠP HÓA NHƯ THỦY</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>94706437</v>
+        <v>57550578</v>
       </c>
       <c r="C209" t="n">
         <v>0</v>
       </c>
       <c r="D209" t="n">
-        <v>94706437</v>
+        <v>57550578</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Lê Văn Hưng</t>
+          <t>Phan Thị Ánh Mỹ</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>95596343</v>
+        <v>240243282</v>
       </c>
       <c r="C210" t="n">
         <v>0</v>
       </c>
       <c r="D210" t="n">
-        <v>95596343</v>
+        <v>240243282</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>TẠP HÓA NHƯ THỦY</t>
+          <t>Dương Minh Ngọc</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>57550578</v>
+        <v>73225572</v>
       </c>
       <c r="C211" t="n">
         <v>0</v>
       </c>
       <c r="D211" t="n">
-        <v>57550578</v>
+        <v>73225572</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Phan Thị Ánh Mỹ</t>
+          <t>Hộ Kinh Doanh Đồng Thị Thanh</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>240243282</v>
+        <v>75303891</v>
       </c>
       <c r="C212" t="n">
         <v>0</v>
       </c>
       <c r="D212" t="n">
-        <v>240243282</v>
+        <v>75303891</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>PHẠM NGUYỄN LONG THÀNH</t>
+          <t>Trần Thị Thu Hồng</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>40290318</v>
+        <v>103684279</v>
       </c>
       <c r="C213" t="n">
         <v>0</v>
       </c>
       <c r="D213" t="n">
-        <v>40290318</v>
+        <v>103684279</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Vũ Thị Thu Hường</t>
+          <t>TRỊNH HOÀNG SƠN</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>100927438</v>
+        <v>147169661</v>
       </c>
       <c r="C214" t="n">
         <v>0</v>
       </c>
       <c r="D214" t="n">
-        <v>100927438</v>
+        <v>147169661</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Nương</t>
+          <t>Lâm Ngọc Đào</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>37600124</v>
+        <v>133099188</v>
       </c>
       <c r="C215" t="n">
         <v>0</v>
       </c>
       <c r="D215" t="n">
-        <v>37600124</v>
+        <v>133099188</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Trần Thị Lan Thi</t>
+          <t>Hoàng Thị Thanh Hương</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>93448010</v>
+        <v>55259900</v>
       </c>
       <c r="C216" t="n">
         <v>0</v>
       </c>
       <c r="D216" t="n">
-        <v>93448010</v>
+        <v>55259900</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Lê Tiến Hậu</t>
+          <t>Vũ Thị Thu Hường</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>130810220</v>
+        <v>100927438</v>
       </c>
       <c r="C217" t="n">
         <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>130810220</v>
+        <v>100927438</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Nguyễn Đức Thiên</t>
+          <t>Trần Thị Lan Thi</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>93567284</v>
+        <v>93448010</v>
       </c>
       <c r="C218" t="n">
         <v>0</v>
       </c>
       <c r="D218" t="n">
-        <v>93567284</v>
+        <v>93448010</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH KHIÊN LÀNH</t>
+          <t>Lê Tiến Hậu</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>75158369</v>
+        <v>130810220</v>
       </c>
       <c r="C219" t="n">
         <v>0</v>
       </c>
       <c r="D219" t="n">
-        <v>75158369</v>
+        <v>130810220</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH ĐẶNG THỊ DIỄM</t>
+          <t>Nguyễn Đức Thiên</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>75977935</v>
+        <v>93567284</v>
       </c>
       <c r="C220" t="n">
         <v>0</v>
       </c>
       <c r="D220" t="n">
-        <v>75977935</v>
+        <v>93567284</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Hoàng Thị Thanh Hương</t>
+          <t>Hộ Kinh Doanh Hồ Thị Thanh Hiền</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>55259900</v>
+        <v>72565656</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
       </c>
       <c r="D221" t="n">
-        <v>55259900</v>
+        <v>72565656</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Hồ Thị Thanh Hiền</t>
+          <t>Đặng Kim Hùng</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>72565656</v>
+        <v>72633979</v>
       </c>
       <c r="C222" t="n">
         <v>0</v>
       </c>
       <c r="D222" t="n">
-        <v>72565656</v>
+        <v>72633979</v>
       </c>
     </row>
     <row r="223">
@@ -4032,145 +4032,145 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Võ Văn Thành</t>
+          <t>Nguyễn Thị Nương</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>37061399</v>
+        <v>37600124</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>37061399</v>
+        <v>37600124</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Thới Thị Bích Hà</t>
+          <t>LÂM MINH HOÀNG</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>96073251</v>
+        <v>75323336</v>
       </c>
       <c r="C226" t="n">
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>96073251</v>
+        <v>75323336</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Đàm Đình Ngữ</t>
+          <t>Võ Văn Thành</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>105797354</v>
+        <v>37061399</v>
       </c>
       <c r="C227" t="n">
         <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>105797354</v>
+        <v>37061399</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Tường Vi</t>
+          <t>HỘ KINH DOANH KHIÊN LÀNH</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>37203656</v>
+        <v>75158369</v>
       </c>
       <c r="C228" t="n">
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>37203656</v>
+        <v>75158369</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Đặng Kim Hùng</t>
+          <t>HỘ KINH DOANH ĐẶNG THỊ DIỄM</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>72633979</v>
+        <v>75977935</v>
       </c>
       <c r="C229" t="n">
         <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>72633979</v>
+        <v>75977935</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>LÂM MINH HOÀNG</t>
+          <t>Thới Thị Bích Hà</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>75323336</v>
+        <v>96073251</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>75323336</v>
+        <v>96073251</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Lâm Ngọc Đào</t>
+          <t>Nguyễn Thị Tường Vi</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>133099188</v>
+        <v>37203656</v>
       </c>
       <c r="C231" t="n">
         <v>0</v>
       </c>
       <c r="D231" t="n">
-        <v>133099188</v>
+        <v>37203656</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>TRỊNH HOÀNG SƠN</t>
+          <t>Đàm Đình Ngữ</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>147169661</v>
+        <v>105797354</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
       </c>
       <c r="D232" t="n">
-        <v>147169661</v>
+        <v>105797354</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Phạm Văn Minh</t>
+          <t>TẠP HÓA CÚC</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>129316036</v>
+        <v>77778421</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
       </c>
       <c r="D233" t="n">
-        <v>129316036</v>
+        <v>77778421</v>
       </c>
     </row>
     <row r="234">
@@ -4208,65 +4208,65 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>TẠP HÓA CÚC</t>
+          <t>Trần Bích Hả</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>77778421</v>
+        <v>18502560</v>
       </c>
       <c r="C236" t="n">
         <v>0</v>
       </c>
       <c r="D236" t="n">
-        <v>77778421</v>
+        <v>18502560</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Trần Bích Hả</t>
+          <t>Phạm Văn Minh</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>18502560</v>
+        <v>129316036</v>
       </c>
       <c r="C237" t="n">
         <v>0</v>
       </c>
       <c r="D237" t="n">
-        <v>18502560</v>
+        <v>129316036</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>HỒ TRỌNG DUY</t>
+          <t>PHOTOCOPY - VĂN PHÒNG PHẨM - TẠP HÓA MAI LAN</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>37879130</v>
+        <v>59869441</v>
       </c>
       <c r="C238" t="n">
         <v>0</v>
       </c>
       <c r="D238" t="n">
-        <v>37879130</v>
+        <v>59869441</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>PHOTOCOPY - VĂN PHÒNG PHẨM - TẠP HÓA MAI LAN</t>
+          <t>HỒ TRỌNG DUY</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>59869441</v>
+        <v>37879130</v>
       </c>
       <c r="C239" t="n">
         <v>0</v>
       </c>
       <c r="D239" t="n">
-        <v>59869441</v>
+        <v>37879130</v>
       </c>
     </row>
     <row r="240">
@@ -4304,49 +4304,49 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Hoàng Thị Thu Hương</t>
+          <t>Nguyễn Thị Kim Tuyến</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>45800482</v>
+        <v>56971830</v>
       </c>
       <c r="C242" t="n">
         <v>0</v>
       </c>
       <c r="D242" t="n">
-        <v>45800482</v>
+        <v>56971830</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Kim Tuyến</t>
+          <t>Sui Ngọc Lan</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>56971830</v>
+        <v>17926173</v>
       </c>
       <c r="C243" t="n">
         <v>0</v>
       </c>
       <c r="D243" t="n">
-        <v>56971830</v>
+        <v>17926173</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Sui Ngọc Lan</t>
+          <t>Hoàng Thị Thu Hương</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>17926173</v>
+        <v>45800482</v>
       </c>
       <c r="C244" t="n">
         <v>0</v>
       </c>
       <c r="D244" t="n">
-        <v>17926173</v>
+        <v>45800482</v>
       </c>
     </row>
     <row r="245">
@@ -4720,33 +4720,33 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Cty TNHH MTV SXTMDV Nhật Vĩnh</t>
+          <t>Công Ty TNHH Bel Việt Nam</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>18981000</v>
+        <v>17143056</v>
       </c>
       <c r="C268" t="n">
         <v>0</v>
       </c>
       <c r="D268" t="n">
-        <v>18981000</v>
+        <v>17143056</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Bel Việt Nam</t>
+          <t>Cty TNHH MTV SXTMDV Nhật Vĩnh</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>17143056</v>
+        <v>18981000</v>
       </c>
       <c r="C269" t="n">
         <v>0</v>
       </c>
       <c r="D269" t="n">
-        <v>17143056</v>
+        <v>18981000</v>
       </c>
     </row>
     <row r="270">
@@ -4784,33 +4784,33 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Tổng Công Ty Hàng Không Việt Nam- CTCP- Chi Nhánh Việt Nam</t>
+          <t>Phan Thị Ánh Lũy</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>5400194</v>
+        <v>69261630</v>
       </c>
       <c r="C272" t="n">
         <v>0</v>
       </c>
       <c r="D272" t="n">
-        <v>5400194</v>
+        <v>69261630</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Phan Thị Ánh Lũy</t>
+          <t>Tổng Công Ty Hàng Không Việt Nam- CTCP- Chi Nhánh Việt Nam</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>69261630</v>
+        <v>5400194</v>
       </c>
       <c r="C273" t="n">
         <v>0</v>
       </c>
       <c r="D273" t="n">
-        <v>69261630</v>
+        <v>5400194</v>
       </c>
     </row>
     <row r="274">
@@ -4832,17 +4832,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Hồ Minh Ngân</t>
+          <t>Nguyễn Mạnh</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>71035603</v>
+        <v>114537266</v>
       </c>
       <c r="C275" t="n">
         <v>0</v>
       </c>
       <c r="D275" t="n">
-        <v>71035603</v>
+        <v>114537266</v>
       </c>
     </row>
     <row r="276">
@@ -4864,49 +4864,49 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Nguyễn Mạnh</t>
+          <t>Hồ Minh Ngân</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>114537266</v>
+        <v>71035603</v>
       </c>
       <c r="C277" t="n">
         <v>0</v>
       </c>
       <c r="D277" t="n">
-        <v>114537266</v>
+        <v>71035603</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Trần Phương Thảo</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN WIN FOODS GIA LAI</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>146118433</v>
+        <v>19643904</v>
       </c>
       <c r="C278" t="n">
         <v>0</v>
       </c>
       <c r="D278" t="n">
-        <v>146118433</v>
+        <v>19643904</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN WIN FOODS GIA LAI</t>
+          <t>Phan Thị Lâm</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>19643904</v>
+        <v>104212766</v>
       </c>
       <c r="C279" t="n">
         <v>0</v>
       </c>
       <c r="D279" t="n">
-        <v>19643904</v>
+        <v>104212766</v>
       </c>
     </row>
     <row r="280">
@@ -4944,17 +4944,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Phan Thị Lâm</t>
+          <t>Trần Phương Thảo</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>104212766</v>
+        <v>146118433</v>
       </c>
       <c r="C282" t="n">
         <v>0</v>
       </c>
       <c r="D282" t="n">
-        <v>104212766</v>
+        <v>146118433</v>
       </c>
     </row>
     <row r="283">
@@ -5008,65 +5008,65 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Lê Thị Hồng Hà</t>
+          <t>Đoàn Thị Hồng Vân</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>88381672</v>
+        <v>128445286</v>
       </c>
       <c r="C286" t="n">
         <v>0</v>
       </c>
       <c r="D286" t="n">
-        <v>88381672</v>
+        <v>128445286</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Đoàn Thị Hồng Vân</t>
+          <t>Lê Thị Hồng Hà</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>128445286</v>
+        <v>88381672</v>
       </c>
       <c r="C287" t="n">
         <v>0</v>
       </c>
       <c r="D287" t="n">
-        <v>128445286</v>
+        <v>88381672</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Phạm Thị Thu Sương</t>
+          <t>Văn Phòng Phẩm- Tạp Hóa Bảy</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>114003953</v>
+        <v>18981000</v>
       </c>
       <c r="C288" t="n">
         <v>0</v>
       </c>
       <c r="D288" t="n">
-        <v>114003953</v>
+        <v>18981000</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Văn Phòng Phẩm- Tạp Hóa Bảy</t>
+          <t>Phạm Thị Thu Sương</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>18981000</v>
+        <v>114003953</v>
       </c>
       <c r="C289" t="n">
         <v>0</v>
       </c>
       <c r="D289" t="n">
-        <v>18981000</v>
+        <v>114003953</v>
       </c>
     </row>
     <row r="290">
@@ -5104,17 +5104,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>BỆNH VIỆN ĐA KHOA TỈNH GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN PRETZLE VIABLE</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>7916651</v>
+        <v>3534369</v>
       </c>
       <c r="C292" t="n">
         <v>0</v>
       </c>
       <c r="D292" t="n">
-        <v>7916651</v>
+        <v>3534369</v>
       </c>
     </row>
     <row r="293">
@@ -5136,17 +5136,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN PRETZLE VIABLE</t>
+          <t>BỆNH VIỆN ĐA KHOA TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>3534369</v>
+        <v>7916651</v>
       </c>
       <c r="C294" t="n">
         <v>0</v>
       </c>
       <c r="D294" t="n">
-        <v>3534369</v>
+        <v>7916651</v>
       </c>
     </row>
     <row r="295">
@@ -5232,33 +5232,33 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Đỗ Hà Trang</t>
+          <t>PHAN THỊ ÁNH MỸ</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>39601148</v>
+        <v>5956200</v>
       </c>
       <c r="C300" t="n">
         <v>0</v>
       </c>
       <c r="D300" t="n">
-        <v>39601148</v>
+        <v>5956200</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>PHAN THỊ ÁNH MỸ</t>
+          <t>Đỗ Hà Trang</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>5956200</v>
+        <v>39601148</v>
       </c>
       <c r="C301" t="n">
         <v>0</v>
       </c>
       <c r="D301" t="n">
-        <v>5956200</v>
+        <v>39601148</v>
       </c>
     </row>
     <row r="302">
@@ -5304,7 +5304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D228"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5354,3620 +5354,1249 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Ngoại thương Việt Nam</t>
+          <t>CÔNG TY TNHH BEL VIỆT NAM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3200627</v>
+        <v>8246551436</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3200627</v>
+        <v>8246551436</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BEL VIỆT NAM</t>
+          <t>Ngân hàng TMCP Ngoại thương Việt Nam</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8246551436</v>
+        <v>3200627</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>8246551436</v>
+        <v>3200627</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN NƯỚC GIẢI KHÁT SANEST KHÁNH HÒA</t>
+          <t>CÔNG TY CỔ PHẦN VIỆT NAM KỸ NGHỆ SÚC SẢN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50214269701</v>
+        <v>24575429136</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>50214269701</v>
+        <v>24575429136</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THỰC PHẨM CHOLIMEX</t>
+          <t>CÔNG TY CỔ PHẦN NƯỚC GIẢI KHÁT SANEST KHÁNH HÒA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24617486040</v>
+        <v>50214269701</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>24617486040</v>
+        <v>50214269701</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lxe Đức</t>
+          <t>CÔNG TY CỔ PHẦN THỰC PHẨM CHOLIMEX</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>24617486040</v>
       </c>
       <c r="C7" t="n">
-        <v>37923850</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-37923850</v>
+        <v>24617486040</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN VIỆT NAM KỸ NGHỆ SÚC SẢN</t>
+          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Gia Lai </t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24575429136</v>
+        <v>1907972846</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>24575429136</v>
+        <v>1907972846</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Gia Lai </t>
+          <t>Vay VCB tt tiền hàng Cty CLM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1907972846</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2023410510</v>
       </c>
       <c r="D9" t="n">
-        <v>1907972846</v>
+        <v>-2023410510</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rút Bidv Cty nộp vào Vcb Cty</t>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 7 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1559501</v>
       </c>
       <c r="C10" t="n">
-        <v>64900000</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-64900000</v>
+        <v>1559501</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 7 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
+          <t>CÔNG TY CỔ PHẦN CẤP THOÁT NƯỚC GIA LAI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1559501</v>
+        <v>241533</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1559501</v>
+        <v>241533</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rút bidv Cty nộp vào Vcb Cty</t>
+          <t>Vay VCB tt tiền hàng Cty Yến</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52000000</v>
+        <v>10311253022</v>
       </c>
       <c r="D12" t="n">
-        <v>-52000000</v>
+        <v>-10311253022</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A Hào</t>
+          <t>CÔNG TY TNHH SẢN XUẤT - THƯƠNG MẠI VÀ DỊCH VỤ HỒNG AN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>55159335</v>
       </c>
       <c r="C13" t="n">
-        <v>39725396</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-39725396</v>
+        <v>55159335</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bel Hiếu</t>
+          <t>CÔNG TY TNHH NABATI VIỆT NAM</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>14155929868</v>
       </c>
       <c r="C14" t="n">
-        <v>50052989</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-50052989</v>
+        <v>14155929868</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bel Liễu</t>
+          <t>Vay VCB tt tiền hàng Cty VS+NBT</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42129449</v>
+        <v>1047059026</v>
       </c>
       <c r="D15" t="n">
-        <v>-42129449</v>
+        <v>-1047059026</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN CẤP THOÁT NƯỚC GIA LAI</t>
+          <t>Công ty Điện lực Gia Lai</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>241533</v>
+        <v>957344</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>241533</v>
+        <v>957344</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH SẢN XUẤT - THƯƠNG MẠI VÀ DỊCH VỤ HỒNG AN</t>
+          <t>Vay VCB tt tiền hàng Cty Vissan</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>55159335</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>2675384521</v>
       </c>
       <c r="D17" t="n">
-        <v>55159335</v>
+        <v>-2675384521</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NABATI VIỆT NAM</t>
+          <t>CÔNG TY CỔ PHẦN TRƯỜNG XUÂN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14155929868</v>
+        <v>12097000</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14155929868</v>
+        <v>12097000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nguyễn Trịnh Minh Huy theo số PC 10AA 0544165</t>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Gia Lai</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1175020</v>
       </c>
       <c r="C19" t="n">
-        <v>2226606</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>-2226606</v>
+        <v>1175020</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ktoan Dương</t>
+          <t>NGAN HANG TMCP CONG THUONG VIET NAM - CN GIA LAI</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>111352677</v>
       </c>
       <c r="C20" t="n">
-        <v>29697471</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>-29697471</v>
+        <v>111352677</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AL A Đạt</t>
+          <t>Vay VCB tt tiền hàng Cty Nbt</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>15896173</v>
+        <v>500842964</v>
       </c>
       <c r="D21" t="n">
-        <v>-15896173</v>
+        <v>-500842964</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AL A Mẫn</t>
+          <t>Vay VCB TT tiền hàng Cty Yến</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>18825871</v>
+        <v>1896095709</v>
       </c>
       <c r="D22" t="n">
-        <v>-18825871</v>
+        <v>-1896095709</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lxe An</t>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>20331967</v>
       </c>
       <c r="C23" t="n">
-        <v>33401000</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-33401000</v>
+        <v>20331967</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lxe Công</t>
+          <t>Vay VCB tt tiền hàng Cty VS</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>30248500</v>
+        <v>382900052</v>
       </c>
       <c r="D24" t="n">
-        <v>-30248500</v>
+        <v>-382900052</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Phụ xe Hồng</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ÂN PHÚ KON TUM</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>25716339</v>
       </c>
       <c r="C25" t="n">
-        <v>27999600</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-27999600</v>
+        <v>25716339</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lxe Danh</t>
+          <t>Vay VCB tt tiền hàng Cty Yến+VS+NBT</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>25432000</v>
+        <v>1481316545</v>
       </c>
       <c r="D26" t="n">
-        <v>-25432000</v>
+        <v>-1481316545</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ktoan Trang</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN QUẢN LÝ NỢ VÀ KHAI THÁC TÀI SẢN NGÂN HÀNG TMCP CÔNG THƯƠNG VIỆT NAM</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>3300000</v>
       </c>
       <c r="C27" t="n">
-        <v>26987500</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-26987500</v>
+        <v>3300000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lxe Tú Gà</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>33920000</v>
       </c>
       <c r="C28" t="n">
-        <v>33151000</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>-33151000</v>
+        <v>33920000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lxe Vịt</t>
+          <t>Vay VCB tt tiền hàng Cty Nabati</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>38023080</v>
+        <v>254121566</v>
       </c>
       <c r="D29" t="n">
-        <v>-38023080</v>
+        <v>-254121566</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ktoan Loan</t>
+          <t>Vay Vcb tt tiền hàng Cty Clm</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>4825000</v>
+        <v>526780035</v>
       </c>
       <c r="D30" t="n">
-        <v>-4825000</v>
+        <v>-526780035</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ktoan Ly</t>
+          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Gia Lai</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>2888600</v>
       </c>
       <c r="C31" t="n">
-        <v>27797500</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>-27797500</v>
+        <v>2888600</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SN Thành</t>
+          <t>CÔNG TY TNHH ĐĂNG KIỂM CAO NGUYÊN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>2053454</v>
       </c>
       <c r="C32" t="n">
-        <v>11041575</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>-11041575</v>
+        <v>2053454</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Thủ kho Duy</t>
+          <t>CÔNG TY CỔ PHẦN SOM TUM THAI</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>1555800</v>
       </c>
       <c r="C33" t="n">
-        <v>34591696</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>-34591696</v>
+        <v>1555800</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Lxe Trung</t>
+          <t>Công Ty Cổ Phần Bệnh Viện Đa Khoa Tâm Anh TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>31687194</v>
       </c>
       <c r="C34" t="n">
-        <v>16256000</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>-16256000</v>
+        <v>31687194</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SN Hiệp</t>
+          <t>CÔNG TY TNHH HTV MẠNH PHƯƠNG F&amp;B</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>26542336</v>
       </c>
       <c r="C35" t="n">
-        <v>8707696</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>-8707696</v>
+        <v>26542336</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ktoan Tâm</t>
+          <t>CHI NHÁNH CÔNG TY TNHH CHRISTIAN DIOR VIỆT NAM TẠI THÀNH PHỐ HỒ CHÍ MINH</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>11415000</v>
       </c>
       <c r="C36" t="n">
-        <v>8199750</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>-8199750</v>
+        <v>11415000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Công ty Điện lực Gia Lai</t>
+          <t>CÔNG TY CỔ PHẦN QUỐC TẾ TAM SƠN - CHI NHÁNH HCM</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>957344</v>
+        <v>62605000</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>957344</v>
+        <v>62605000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cty Hoàng Huy Phát theo số PC10AA0528678</t>
+          <t>Công ty TNHH Thuần Lý</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>18390000</v>
       </c>
       <c r="C38" t="n">
-        <v>243419</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>-243419</v>
+        <v>18390000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN TRƯỜNG XUÂN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DU LỊCH TÀU BẾN NGHÉ</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>12097000</v>
+        <v>3061300</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>12097000</v>
+        <v>3061300</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rút Bidv Cty nộp vào Bidv cn</t>
+          <t>CÔNG TY TNHH HAI DI LAO VIET NAM HOLDINGS - CHI NHÁNH THÀNH PHỐ HỒ CHÍ MINH</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>1309000</v>
       </c>
       <c r="C40" t="n">
-        <v>60000000</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>-60000000</v>
+        <v>1309000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lxe Lxe Công</t>
+          <t>Viettel Gia Lai- Chi nhánh Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>-3000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Lxe Lxe Danh</t>
+          <t>Vay VCB tt tiền hàng Cty VS= vay</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>3000000</v>
+        <v>532525085</v>
       </c>
       <c r="D42" t="n">
-        <v>-3000000</v>
+        <v>-532525085</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ktoan Loan</t>
+          <t>CÔNG TY TNHH MITRAMODE DUTA FASHINDO VIỆT NAM</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>16194000</v>
       </c>
       <c r="C43" t="n">
-        <v>14496100</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>-14496100</v>
+        <v>16194000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Gia Lai</t>
+          <t>Vay VCB tt tiền hàng Cty Nabati+VS</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1175020</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>301878328</v>
       </c>
       <c r="D44" t="n">
-        <v>1175020</v>
+        <v>-301878328</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NGAN HANG TMCP CONG THUONG VIET NAM - CN GIA LAI</t>
+          <t>Vay VCB tt tiền hàng Cty Bel</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>111352677</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>131227569</v>
       </c>
       <c r="D45" t="n">
-        <v>111352677</v>
+        <v>-131227569</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+          <t>CÔNG TY CỔ PHẦN ĐIỆN TỬ VIỄN THÔNG ÁNH DƯƠNG</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>20331967</v>
+        <v>2970000</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>20331967</v>
+        <v>2970000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>UNC TT tiền hàng Cty NBT</t>
+          <t>CÔNG TY BẢO HIỂM BƯU ĐIỆN GIA LAI</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>4770300</v>
       </c>
       <c r="C47" t="n">
-        <v>1000569970</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>-1000569970</v>
+        <v>4770300</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cty Hoàng Huy Phát</t>
+          <t>Vay Vcb tt tiền hàng Cty Yến</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>25752581</v>
+        <v>2034968400</v>
       </c>
       <c r="D48" t="n">
-        <v>-25752581</v>
+        <v>-2034968400</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ÂN PHÚ KON TUM</t>
+          <t>CÔNG TY TNHH MTV THƯƠNG MẠI &amp; DỊCH VỤ ẮC QUY DIỆN LIÊN</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25716339</v>
+        <v>3300000</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>25716339</v>
+        <v>3300000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PC 10AA0544165</t>
+          <t>Vay VCB TT tiền hàng CTY Nabati</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>1981909</v>
+        <v>955809765</v>
       </c>
       <c r="D50" t="n">
-        <v>-1981909</v>
+        <v>-955809765</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AL Mẫn</t>
+          <t>CÔNG TY TNHH MTV Ô TÔ TRƯỜNG HẢI GIA LAI</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>6418867</v>
       </c>
       <c r="C51" t="n">
-        <v>36495710</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>-36495710</v>
+        <v>6418867</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AL Đạt</t>
+          <t>Vay VCB TT tiền hàng CTY CLM</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>34336933</v>
+        <v>2576806319</v>
       </c>
       <c r="D52" t="n">
-        <v>-34336933</v>
+        <v>-2576806319</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN QUẢN LÝ NỢ VÀ KHAI THÁC TÀI SẢN NGÂN HÀNG TMCP CÔNG THƯƠNG VIỆT NAM</t>
+          <t>Vay VCB TT tiền hàng CTY Nabati VN</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3300000</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>725460393</v>
       </c>
       <c r="D53" t="n">
-        <v>3300000</v>
+        <v>-725460393</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CtY HHP theo số PC 10AA 0528678</t>
+          <t>Vay VCB TT tiền hàng CTY Yến SN</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>124715</v>
+        <v>2700000000</v>
       </c>
       <c r="D54" t="n">
-        <v>-124715</v>
+        <v>-2700000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CLM My</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MAY THÊU GIÀY AN PHƯỚC TẠI GIA LAI</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>2969400</v>
       </c>
       <c r="C55" t="n">
-        <v>36917629</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>-36917629</v>
+        <v>2969400</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CLM T.Hằng</t>
+          <t>Vay VCB TT tiền hàng CTY VISSAN</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>37974410</v>
+        <v>250151555</v>
       </c>
       <c r="D56" t="n">
-        <v>-37974410</v>
+        <v>-250151555</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CLM V.Hằng</t>
+          <t>CÔNG TY XĂNG DẦU NAM TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="C57" t="n">
-        <v>37344410</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>-37344410</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CLM Châu</t>
+          <t>CÔNG TY TNHH MTV Ô TÔ GIA LAI</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>1817430</v>
       </c>
       <c r="C58" t="n">
-        <v>55278612</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>-55278612</v>
+        <v>1817430</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
+          <t>CÔNG TY CỔ PHẦN THỜI TRANG VÀ MỸ PHẨM DUY ANH</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>33920000</v>
+        <v>35230000</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>33920000</v>
+        <v>35230000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KT Trang</t>
+          <t>Vay VCB TT tiền hàng CTY Yến</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>2970000</v>
+        <v>4714638720</v>
       </c>
       <c r="D60" t="n">
-        <v>-2970000</v>
+        <v>-4714638720</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Lxe Gà</t>
+          <t>TRUNG TÂM KINH DOANH VNPT - GIA LAI - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>4332900</v>
       </c>
       <c r="C61" t="n">
-        <v>2085000</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>-2085000</v>
+        <v>4332900</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>KT Dương</t>
+          <t>Vay VCB TT tiền hàng CTY Vissan</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>4418134</v>
+        <v>983516051</v>
       </c>
       <c r="D62" t="n">
-        <v>-4418134</v>
+        <v>-983516051</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>KT Ly</t>
+          <t>CHI NHÁNH CÔNG TY TNHH TRUYỀN HÌNH CÁP SAIGONTOURIST-TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>1610000</v>
       </c>
       <c r="C63" t="n">
-        <v>3641000</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>-3641000</v>
+        <v>1610000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KT Loan</t>
+          <t>CÔNG TY BẢO HIỂM BIDV BẮC TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>3230700</v>
       </c>
       <c r="C64" t="n">
-        <v>1978800</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>-1978800</v>
+        <v>3230700</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Gia Lai</t>
+          <t>Vay VCB TT tiền hàng cty Yến SN</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2888600</v>
+        <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>2755957600</v>
       </c>
       <c r="D65" t="n">
-        <v>2888600</v>
+        <v>-2755957600</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>UNC tt tiền hàng Cty Nabati</t>
+          <t>Vay VCB TT tiền hàng CLM</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>1030000000</v>
+        <v>714632644</v>
       </c>
       <c r="D66" t="n">
-        <v>-1030000000</v>
+        <v>-714632644</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Rút bidv cty nộp vào vcb cty</t>
+          <t>Vay VCB TT tiền hàng Vissan</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>44000000</v>
+        <v>911224575</v>
       </c>
       <c r="D67" t="n">
-        <v>-44000000</v>
+        <v>-911224575</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ck banking tt tiền hàng Cty Bel</t>
+          <t>NGAN HANG TMCP CONG THUONG VIET NAM - 50098|CN GIA LAI</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>159543182</v>
       </c>
       <c r="C68" t="n">
-        <v>318040283</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>-318040283</v>
+        <v>159543182</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cty CLM</t>
+          <t>Vay VCB TT tiền hàng CTY Visssan</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>76700346</v>
+        <v>240489903</v>
       </c>
       <c r="D69" t="n">
-        <v>-76700346</v>
+        <v>-240489903</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cty Bel</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HÀ ĐỨC VINH</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>5200000</v>
       </c>
       <c r="C70" t="n">
-        <v>47786490</v>
+        <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>-47786490</v>
+        <v>5200000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Nguyễn Trịnh Minh Huy theo số PC10AA0544165</t>
+          <t>CÔNG TY CỔ PHẦN SÁCH VÀ THIẾT BỊ TRƯỜNG HỌC GIA LAI</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="C71" t="n">
-        <v>4173097</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>-4173097</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN BẢO THUẬN</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>4390000</v>
       </c>
       <c r="C72" t="n">
-        <v>25917581</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>-25917581</v>
+        <v>4390000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>theo số PC10AA0528678</t>
+          <t>CÔNG TY TNHH THU PHÍ TỰ ĐỘNG VETC</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>8963000</v>
       </c>
       <c r="C73" t="n">
-        <v>77503</v>
+        <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>-77503</v>
+        <v>8963000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐĂNG KIỂM CAO NGUYÊN</t>
+          <t>CÔNG TY BẢO HIỂM VIETINBANK BẮC TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2053454</v>
+        <v>1681000</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>2053454</v>
+        <v>1681000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN SOM TUM THAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN AN PHÁT LỘC GIA LAI</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1555800</v>
+        <v>2866000</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>1555800</v>
+        <v>2866000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Công Ty Cổ Phần Bệnh Viện Đa Khoa Tâm Anh TP. Hồ Chí Minh</t>
+          <t>Vay VCB TT tiền hàng CTY CLM A : 272,950,420 + CLM B : 11,360,232 + VS : 167,379,844đ</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>31687194</v>
+        <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>451690496</v>
       </c>
       <c r="D76" t="n">
-        <v>31687194</v>
+        <v>-451690496</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cty HHP</t>
+          <t>Vay VCB TT tiền hàng CTY VS</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>24688252</v>
+        <v>254815217</v>
       </c>
       <c r="D77" t="n">
-        <v>-24688252</v>
+        <v>-254815217</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Lxe Tú Vịt</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THẾ HỆ MỚI GIA LAI</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>11712950</v>
       </c>
       <c r="C78" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>-2000000</v>
+        <v>11712950</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HTV MẠNH PHƯƠNG F&amp;B</t>
+          <t>Vay VCB TT tiền hàng Cty CLM</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>26542336</v>
+        <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>279542523</v>
       </c>
       <c r="D79" t="n">
-        <v>26542336</v>
+        <v>-279542523</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Bel Thông</t>
+          <t>CN CÔNG TY CP PHÁT TRIỂN PHẦN MỀM ASIA TẠI ĐÀ NẴNG</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>14000000</v>
       </c>
       <c r="C80" t="n">
-        <v>4977594</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>-4977594</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN QUỐC TẾ TAM SƠN - CHI NHÁNH HCM</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>62605000</v>
-      </c>
-      <c r="C81" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" t="n">
-        <v>62605000</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH CÔNG TY TNHH CHRISTIAN DIOR VIỆT NAM TẠI THÀNH PHỐ HỒ CHÍ MINH</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>11415000</v>
-      </c>
-      <c r="C82" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" t="n">
-        <v>11415000</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Bel Hào</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>0</v>
-      </c>
-      <c r="C83" t="n">
-        <v>11608630</v>
-      </c>
-      <c r="D83" t="n">
-        <v>-11608630</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Công ty TNHH Thuần Lý</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>18390000</v>
-      </c>
-      <c r="C84" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" t="n">
-        <v>18390000</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DU LỊCH TÀU BẾN NGHÉ</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>3061300</v>
-      </c>
-      <c r="C85" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" t="n">
-        <v>3061300</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH HAI DI LAO VIET NAM HOLDINGS - CHI NHÁNH THÀNH PHỐ HỒ CHÍ MINH</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>1309000</v>
-      </c>
-      <c r="C86" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" t="n">
-        <v>1309000</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Viettel Gia Lai- Chi nhánh Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>0</v>
-      </c>
-      <c r="C87" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Cty HHP theo số PC10AA0528678</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>0</v>
-      </c>
-      <c r="C88" t="n">
-        <v>50780</v>
-      </c>
-      <c r="D88" t="n">
-        <v>-50780</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MITRAMODE DUTA FASHINDO VIỆT NAM</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>16194000</v>
-      </c>
-      <c r="C89" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" t="n">
-        <v>16194000</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐIỆN TỬ VIỄN THÔNG ÁNH DƯƠNG</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>2970000</v>
-      </c>
-      <c r="C90" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" t="n">
-        <v>2970000</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>CÔNG TY BẢO HIỂM BƯU ĐIỆN GIA LAI</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>4770300</v>
-      </c>
-      <c r="C91" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" t="n">
-        <v>4770300</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Thu phi BDSD 05/2023, So TK: 110649896789, SDT: 0983827174</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
-      <c r="C92" t="n">
-        <v>19800</v>
-      </c>
-      <c r="D92" t="n">
-        <v>-19800</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MTV THƯƠNG MẠI &amp; DỊCH VỤ ẮC QUY DIỆN LIÊN</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="C93" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" t="n">
-        <v>3300000</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Nộp vào TK VCB CTY</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>0</v>
-      </c>
-      <c r="C94" t="n">
-        <v>84000000</v>
-      </c>
-      <c r="D94" t="n">
-        <v>-84000000</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>CLM</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>0</v>
-      </c>
-      <c r="C95" t="n">
-        <v>48072960</v>
-      </c>
-      <c r="D95" t="n">
-        <v>-48072960</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Tháng 4/2023</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
-      <c r="C96" t="n">
-        <v>47687794</v>
-      </c>
-      <c r="D96" t="n">
-        <v>-47687794</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>T4/2023</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>0</v>
-      </c>
-      <c r="C97" t="n">
-        <v>33110451</v>
-      </c>
-      <c r="D97" t="n">
-        <v>-33110451</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Thông</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>0</v>
-      </c>
-      <c r="C98" t="n">
-        <v>77147878</v>
-      </c>
-      <c r="D98" t="n">
-        <v>-77147878</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Châu</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>0</v>
-      </c>
-      <c r="C99" t="n">
-        <v>123995134</v>
-      </c>
-      <c r="D99" t="n">
-        <v>-123995134</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>My</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>0</v>
-      </c>
-      <c r="C100" t="n">
-        <v>65936228</v>
-      </c>
-      <c r="D100" t="n">
-        <v>-65936228</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>T.Hằng</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>0</v>
-      </c>
-      <c r="C101" t="n">
-        <v>58111051</v>
-      </c>
-      <c r="D101" t="n">
-        <v>-58111051</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>V.Hằng</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>0</v>
-      </c>
-      <c r="C102" t="n">
-        <v>58559990</v>
-      </c>
-      <c r="D102" t="n">
-        <v>-58559990</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>UNC nộp tiền BHXH CTY CLM  T5/2023(HHP)</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>0</v>
-      </c>
-      <c r="C103" t="n">
-        <v>6409728</v>
-      </c>
-      <c r="D103" t="n">
-        <v>-6409728</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>UNC nộp tiền BHXH CTY  T5/2023(HHP)</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>0</v>
-      </c>
-      <c r="C104" t="n">
-        <v>26233381</v>
-      </c>
-      <c r="D104" t="n">
-        <v>-26233381</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>68 Tạ Quang Bửu</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>0</v>
-      </c>
-      <c r="C105" t="n">
-        <v>296099</v>
-      </c>
-      <c r="D105" t="n">
-        <v>-296099</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>HHP</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>0</v>
-      </c>
-      <c r="C106" t="n">
-        <v>87477551</v>
-      </c>
-      <c r="D106" t="n">
-        <v>-87477551</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MTV Ô TÔ TRƯỜNG HẢI GIA LAI</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>6418867</v>
-      </c>
-      <c r="C107" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" t="n">
-        <v>6418867</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>A.Mẫn</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>0</v>
-      </c>
-      <c r="C108" t="n">
-        <v>33589782</v>
-      </c>
-      <c r="D108" t="n">
-        <v>-33589782</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>A.Đạt</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>0</v>
-      </c>
-      <c r="C109" t="n">
-        <v>23112288</v>
-      </c>
-      <c r="D109" t="n">
-        <v>-23112288</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>&gt; T5/2023</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>0</v>
-      </c>
-      <c r="C110" t="n">
-        <v>2681091</v>
-      </c>
-      <c r="D110" t="n">
-        <v>-2681091</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>0</v>
-      </c>
-      <c r="C111" t="n">
-        <v>5011914</v>
-      </c>
-      <c r="D111" t="n">
-        <v>-5011914</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>0</v>
-      </c>
-      <c r="C112" t="n">
-        <v>301000000</v>
-      </c>
-      <c r="D112" t="n">
-        <v>-301000000</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>CK Banking TT tiền hàng CTY Vissan</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>0</v>
-      </c>
-      <c r="C113" t="n">
-        <v>1608867217</v>
-      </c>
-      <c r="D113" t="n">
-        <v>-1608867217</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Rút tiền từ TK BIDV CTY  Nộp tiền vào VCB CTY</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>0</v>
-      </c>
-      <c r="C114" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="D114" t="n">
-        <v>-50000000</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>LX Hồng</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>0</v>
-      </c>
-      <c r="C115" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="D115" t="n">
-        <v>-4000000</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>LX Đức</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>0</v>
-      </c>
-      <c r="C116" t="n">
-        <v>25000000</v>
-      </c>
-      <c r="D116" t="n">
-        <v>-25000000</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Thu phi BDSD 06/2023, So TK: 110649896789, SDT: 0983827174</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>0</v>
-      </c>
-      <c r="C117" t="n">
-        <v>19800</v>
-      </c>
-      <c r="D117" t="n">
-        <v>-19800</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Liễu</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>0</v>
-      </c>
-      <c r="C118" t="n">
-        <v>54432655</v>
-      </c>
-      <c r="D118" t="n">
-        <v>-54432655</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Hiếu</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>0</v>
-      </c>
-      <c r="C119" t="n">
-        <v>50598860</v>
-      </c>
-      <c r="D119" t="n">
-        <v>-50598860</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Hào</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>0</v>
-      </c>
-      <c r="C120" t="n">
-        <v>58242184</v>
-      </c>
-      <c r="D120" t="n">
-        <v>-58242184</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>PC10AA0544165 Nguyễn Trịnh Minh Huy</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>0</v>
-      </c>
-      <c r="C121" t="n">
-        <v>3606741</v>
-      </c>
-      <c r="D121" t="n">
-        <v>-3606741</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Ck Banking TT tiền hàng CTY Vissan</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>0</v>
-      </c>
-      <c r="C122" t="n">
-        <v>83727900</v>
-      </c>
-      <c r="D122" t="n">
-        <v>-83727900</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Tiền trách nhiệm T3,23</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>0</v>
-      </c>
-      <c r="C123" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="D123" t="n">
-        <v>-1800000</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Thiện Ân</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>0</v>
-      </c>
-      <c r="C124" t="n">
-        <v>3392000</v>
-      </c>
-      <c r="D124" t="n">
-        <v>-3392000</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Anh Đạt</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>0</v>
-      </c>
-      <c r="C125" t="n">
-        <v>9435415</v>
-      </c>
-      <c r="D125" t="n">
-        <v>-9435415</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Anh Mẫn</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>0</v>
-      </c>
-      <c r="C126" t="n">
-        <v>10774635</v>
-      </c>
-      <c r="D126" t="n">
-        <v>-10774635</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Hiệp</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>0</v>
-      </c>
-      <c r="C127" t="n">
-        <v>15183888</v>
-      </c>
-      <c r="D127" t="n">
-        <v>-15183888</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Thành</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>0</v>
-      </c>
-      <c r="C128" t="n">
-        <v>17899030</v>
-      </c>
-      <c r="D128" t="n">
-        <v>-17899030</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Công</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>0</v>
-      </c>
-      <c r="C129" t="n">
-        <v>46375000</v>
-      </c>
-      <c r="D129" t="n">
-        <v>-46375000</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Hồng</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>0</v>
-      </c>
-      <c r="C130" t="n">
-        <v>32617000</v>
-      </c>
-      <c r="D130" t="n">
-        <v>-32617000</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Trang</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>0</v>
-      </c>
-      <c r="C131" t="n">
-        <v>40335075</v>
-      </c>
-      <c r="D131" t="n">
-        <v>-40335075</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Đức</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>0</v>
-      </c>
-      <c r="C132" t="n">
-        <v>16729000</v>
-      </c>
-      <c r="D132" t="n">
-        <v>-16729000</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>An</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>0</v>
-      </c>
-      <c r="C133" t="n">
-        <v>23005045</v>
-      </c>
-      <c r="D133" t="n">
-        <v>-23005045</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MAY THÊU GIÀY AN PHƯỚC TẠI GIA LAI</t>
-        </is>
-      </c>
-      <c r="B134" t="n">
-        <v>2969400</v>
-      </c>
-      <c r="C134" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" t="n">
-        <v>2969400</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Tú (Vịt)</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>0</v>
-      </c>
-      <c r="C135" t="n">
-        <v>10005125</v>
-      </c>
-      <c r="D135" t="n">
-        <v>-10005125</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Ly</t>
-        </is>
-      </c>
-      <c r="B136" t="n">
-        <v>0</v>
-      </c>
-      <c r="C136" t="n">
-        <v>36313175</v>
-      </c>
-      <c r="D136" t="n">
-        <v>-36313175</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Minh Tú</t>
-        </is>
-      </c>
-      <c r="B137" t="n">
-        <v>0</v>
-      </c>
-      <c r="C137" t="n">
-        <v>10049125</v>
-      </c>
-      <c r="D137" t="n">
-        <v>-10049125</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Dương</t>
-        </is>
-      </c>
-      <c r="B138" t="n">
-        <v>0</v>
-      </c>
-      <c r="C138" t="n">
-        <v>36933504</v>
-      </c>
-      <c r="D138" t="n">
-        <v>-36933504</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Duy</t>
-        </is>
-      </c>
-      <c r="B139" t="n">
-        <v>0</v>
-      </c>
-      <c r="C139" t="n">
-        <v>43271675</v>
-      </c>
-      <c r="D139" t="n">
-        <v>-43271675</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Thịnh (ck Tâm)</t>
-        </is>
-      </c>
-      <c r="B140" t="n">
-        <v>0</v>
-      </c>
-      <c r="C140" t="n">
-        <v>12385000</v>
-      </c>
-      <c r="D140" t="n">
-        <v>-12385000</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>HĐ 13059</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>0</v>
-      </c>
-      <c r="C141" t="n">
-        <v>164828</v>
-      </c>
-      <c r="D141" t="n">
-        <v>-164828</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>CÔNG TY XĂNG DẦU NAM TÂY NGUYÊN</t>
-        </is>
-      </c>
-      <c r="B142" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C142" t="n">
-        <v>0</v>
-      </c>
-      <c r="D142" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>CK Banking TT tiền hàng CTY Nabati</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>0</v>
-      </c>
-      <c r="C143" t="n">
-        <v>466895546</v>
-      </c>
-      <c r="D143" t="n">
-        <v>-466895546</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>HHP đợt 1</t>
-        </is>
-      </c>
-      <c r="B144" t="n">
-        <v>0</v>
-      </c>
-      <c r="C144" t="n">
-        <v>26024185</v>
-      </c>
-      <c r="D144" t="n">
-        <v>-26024185</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN THỜI TRANG VÀ MỸ PHẨM DUY ANH</t>
-        </is>
-      </c>
-      <c r="B145" t="n">
-        <v>35230000</v>
-      </c>
-      <c r="C145" t="n">
-        <v>0</v>
-      </c>
-      <c r="D145" t="n">
-        <v>35230000</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Rút tiền Bidv CTY nộp tiền vào Bidv CN</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>0</v>
-      </c>
-      <c r="C146" t="n">
-        <v>26000000</v>
-      </c>
-      <c r="D146" t="n">
-        <v>-26000000</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MTV Ô TÔ GIA LAI</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>1817430</v>
-      </c>
-      <c r="C147" t="n">
-        <v>0</v>
-      </c>
-      <c r="D147" t="n">
-        <v>1817430</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>CK Banking TT Tiền hàng CTY Vissan</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>0</v>
-      </c>
-      <c r="C148" t="n">
-        <v>192655628</v>
-      </c>
-      <c r="D148" t="n">
-        <v>-192655628</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Thu phi BDSD 07/2023, So TK: 110649896789, SDT: 0983827174</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>0</v>
-      </c>
-      <c r="C149" t="n">
-        <v>19800</v>
-      </c>
-      <c r="D149" t="n">
-        <v>-19800</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>A.Hào</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>0</v>
-      </c>
-      <c r="C150" t="n">
-        <v>19577832</v>
-      </c>
-      <c r="D150" t="n">
-        <v>-19577832</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>A Hiếu</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>0</v>
-      </c>
-      <c r="C151" t="n">
-        <v>13172215</v>
-      </c>
-      <c r="D151" t="n">
-        <v>-13172215</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>121/6 Lê Đại Hành</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>0</v>
-      </c>
-      <c r="C152" t="n">
-        <v>2844337</v>
-      </c>
-      <c r="D152" t="n">
-        <v>-2844337</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>LX Tào Hồng</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>0</v>
-      </c>
-      <c r="C153" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D153" t="n">
-        <v>-2000000</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Ân</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>0</v>
-      </c>
-      <c r="C154" t="n">
-        <v>29934000</v>
-      </c>
-      <c r="D154" t="n">
-        <v>-29934000</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Tú (gà)</t>
-        </is>
-      </c>
-      <c r="B155" t="n">
-        <v>0</v>
-      </c>
-      <c r="C155" t="n">
-        <v>9689025</v>
-      </c>
-      <c r="D155" t="n">
-        <v>-9689025</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Vịt</t>
-        </is>
-      </c>
-      <c r="B156" t="n">
-        <v>0</v>
-      </c>
-      <c r="C156" t="n">
-        <v>19330050</v>
-      </c>
-      <c r="D156" t="n">
-        <v>-19330050</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>TRUNG TÂM KINH DOANH VNPT - GIA LAI - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>4332900</v>
-      </c>
-      <c r="C157" t="n">
-        <v>0</v>
-      </c>
-      <c r="D157" t="n">
-        <v>4332900</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Thịnh</t>
-        </is>
-      </c>
-      <c r="B158" t="n">
-        <v>0</v>
-      </c>
-      <c r="C158" t="n">
-        <v>12385000</v>
-      </c>
-      <c r="D158" t="n">
-        <v>-12385000</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Mẫn</t>
-        </is>
-      </c>
-      <c r="B159" t="n">
-        <v>0</v>
-      </c>
-      <c r="C159" t="n">
-        <v>24229806</v>
-      </c>
-      <c r="D159" t="n">
-        <v>-24229806</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Đạt</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>0</v>
-      </c>
-      <c r="C160" t="n">
-        <v>22700559</v>
-      </c>
-      <c r="D160" t="n">
-        <v>-22700559</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>CK Bangking TT tiền CTY Vissan</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>0</v>
-      </c>
-      <c r="C161" t="n">
-        <v>138127317</v>
-      </c>
-      <c r="D161" t="n">
-        <v>-138127317</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH CÔNG TY TNHH TRUYỀN HÌNH CÁP SAIGONTOURIST-TỈNH GIA LAI</t>
-        </is>
-      </c>
-      <c r="B162" t="n">
-        <v>1610000</v>
-      </c>
-      <c r="C162" t="n">
-        <v>0</v>
-      </c>
-      <c r="D162" t="n">
-        <v>1610000</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>CK BanKing TT tiền hàng CTY Nabati VN</t>
-        </is>
-      </c>
-      <c r="B163" t="n">
-        <v>0</v>
-      </c>
-      <c r="C163" t="n">
-        <v>202588776</v>
-      </c>
-      <c r="D163" t="n">
-        <v>-202588776</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Đợt 1</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>0</v>
-      </c>
-      <c r="C164" t="n">
-        <v>89802895</v>
-      </c>
-      <c r="D164" t="n">
-        <v>-89802895</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>CK Banking TT Tiền hang CTY Vissan</t>
-        </is>
-      </c>
-      <c r="B165" t="n">
-        <v>0</v>
-      </c>
-      <c r="C165" t="n">
-        <v>213536112</v>
-      </c>
-      <c r="D165" t="n">
-        <v>-213536112</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>CÔNG TY BẢO HIỂM BIDV BẮC TÂY NGUYÊN</t>
-        </is>
-      </c>
-      <c r="B166" t="n">
-        <v>3230700</v>
-      </c>
-      <c r="C166" t="n">
-        <v>0</v>
-      </c>
-      <c r="D166" t="n">
-        <v>3230700</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>ck Banking TT tiền hàng CY Nabati</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>0</v>
-      </c>
-      <c r="C167" t="n">
-        <v>306255816</v>
-      </c>
-      <c r="D167" t="n">
-        <v>-306255816</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Thu phi BDSD 08/2023, So TK: 110649896789, SDT: 0983827174</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>0</v>
-      </c>
-      <c r="C168" t="n">
-        <v>19800</v>
-      </c>
-      <c r="D168" t="n">
-        <v>-19800</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>CK Baking TT tiền hàng Cty Vissan</t>
-        </is>
-      </c>
-      <c r="B169" t="n">
-        <v>0</v>
-      </c>
-      <c r="C169" t="n">
-        <v>46144948</v>
-      </c>
-      <c r="D169" t="n">
-        <v>-46144948</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Loan</t>
-        </is>
-      </c>
-      <c r="B170" t="n">
-        <v>0</v>
-      </c>
-      <c r="C170" t="n">
-        <v>69569308</v>
-      </c>
-      <c r="D170" t="n">
-        <v>-69569308</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>V, Hằng</t>
-        </is>
-      </c>
-      <c r="B171" t="n">
-        <v>0</v>
-      </c>
-      <c r="C171" t="n">
-        <v>14694202</v>
-      </c>
-      <c r="D171" t="n">
-        <v>-14694202</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Nguyễn Trịnh Minh Huy</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>0</v>
-      </c>
-      <c r="C172" t="n">
-        <v>2792237</v>
-      </c>
-      <c r="D172" t="n">
-        <v>-2792237</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>CK Banking TT tiền hàng CTY  Nabati</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>0</v>
-      </c>
-      <c r="C173" t="n">
-        <v>214038893</v>
-      </c>
-      <c r="D173" t="n">
-        <v>-214038893</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Gà</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>0</v>
-      </c>
-      <c r="C174" t="n">
-        <v>9689025</v>
-      </c>
-      <c r="D174" t="n">
-        <v>-9689025</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Tâm</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>0</v>
-      </c>
-      <c r="C175" t="n">
-        <v>23952025</v>
-      </c>
-      <c r="D175" t="n">
-        <v>-23952025</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Rút tiền từ TK Bidv Cty nộp tiền vào TK VCB Cty</t>
-        </is>
-      </c>
-      <c r="B176" t="n">
-        <v>0</v>
-      </c>
-      <c r="C176" t="n">
-        <v>44000000</v>
-      </c>
-      <c r="D176" t="n">
-        <v>-44000000</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>CK Banking TT tiền hàng CTY Nabati VN</t>
-        </is>
-      </c>
-      <c r="B177" t="n">
-        <v>0</v>
-      </c>
-      <c r="C177" t="n">
-        <v>223071516</v>
-      </c>
-      <c r="D177" t="n">
-        <v>-223071516</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>CK BanKing TT tiền hàng CTY Vissan</t>
-        </is>
-      </c>
-      <c r="B178" t="n">
-        <v>0</v>
-      </c>
-      <c r="C178" t="n">
-        <v>28320317</v>
-      </c>
-      <c r="D178" t="n">
-        <v>-28320317</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>LX Tú Gà</t>
-        </is>
-      </c>
-      <c r="B179" t="n">
-        <v>0</v>
-      </c>
-      <c r="C179" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D179" t="n">
-        <v>-3000000</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Ck Banking TT tiền hàng Cty Nabati</t>
-        </is>
-      </c>
-      <c r="B180" t="n">
-        <v>0</v>
-      </c>
-      <c r="C180" t="n">
-        <v>351687215</v>
-      </c>
-      <c r="D180" t="n">
-        <v>-351687215</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>CK Banking TT tiền hàng Cty Vissan</t>
-        </is>
-      </c>
-      <c r="B181" t="n">
-        <v>0</v>
-      </c>
-      <c r="C181" t="n">
-        <v>104362604</v>
-      </c>
-      <c r="D181" t="n">
-        <v>-104362604</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>nước suối</t>
-        </is>
-      </c>
-      <c r="B182" t="n">
-        <v>0</v>
-      </c>
-      <c r="C182" t="n">
-        <v>20565160</v>
-      </c>
-      <c r="D182" t="n">
-        <v>-20565160</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>đơn 01</t>
-        </is>
-      </c>
-      <c r="B183" t="n">
-        <v>0</v>
-      </c>
-      <c r="C183" t="n">
-        <v>303648611</v>
-      </c>
-      <c r="D183" t="n">
-        <v>-303648611</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>đơn 02</t>
-        </is>
-      </c>
-      <c r="B184" t="n">
-        <v>0</v>
-      </c>
-      <c r="C184" t="n">
-        <v>102814181</v>
-      </c>
-      <c r="D184" t="n">
-        <v>-102814181</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>UNC Tiền LX Tú Gà mượn tiền Cô Lý</t>
-        </is>
-      </c>
-      <c r="B185" t="n">
-        <v>0</v>
-      </c>
-      <c r="C185" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="D185" t="n">
-        <v>-15000000</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>T8/2023</t>
-        </is>
-      </c>
-      <c r="B186" t="n">
-        <v>0</v>
-      </c>
-      <c r="C186" t="n">
-        <v>36173113</v>
-      </c>
-      <c r="D186" t="n">
-        <v>-36173113</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>NGAN HANG TMCP CONG THUONG VIET NAM - 50098|CN GIA LAI</t>
-        </is>
-      </c>
-      <c r="B187" t="n">
-        <v>159543182</v>
-      </c>
-      <c r="C187" t="n">
-        <v>0</v>
-      </c>
-      <c r="D187" t="n">
-        <v>159543182</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Thu phi BDSD 09/2023, So TK: 110649896789, SDT: 0983827174</t>
-        </is>
-      </c>
-      <c r="B188" t="n">
-        <v>0</v>
-      </c>
-      <c r="C188" t="n">
-        <v>19800</v>
-      </c>
-      <c r="D188" t="n">
-        <v>-19800</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>ck Banking TT tiền hàng CTY Nabati</t>
-        </is>
-      </c>
-      <c r="B189" t="n">
-        <v>0</v>
-      </c>
-      <c r="C189" t="n">
-        <v>476961280</v>
-      </c>
-      <c r="D189" t="n">
-        <v>-476961280</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Việt Hằng</t>
-        </is>
-      </c>
-      <c r="B190" t="n">
-        <v>0</v>
-      </c>
-      <c r="C190" t="n">
-        <v>17714336</v>
-      </c>
-      <c r="D190" t="n">
-        <v>-17714336</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Thu Hằng</t>
-        </is>
-      </c>
-      <c r="B191" t="n">
-        <v>0</v>
-      </c>
-      <c r="C191" t="n">
-        <v>45272606</v>
-      </c>
-      <c r="D191" t="n">
-        <v>-45272606</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>CK Bankin TT tiền Cty Vissan</t>
-        </is>
-      </c>
-      <c r="B192" t="n">
-        <v>0</v>
-      </c>
-      <c r="C192" t="n">
-        <v>129039464</v>
-      </c>
-      <c r="D192" t="n">
-        <v>-129039464</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>HHP  Ly</t>
-        </is>
-      </c>
-      <c r="B193" t="n">
-        <v>0</v>
-      </c>
-      <c r="C193" t="n">
-        <v>8728000</v>
-      </c>
-      <c r="D193" t="n">
-        <v>-8728000</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Tú Vịt</t>
-        </is>
-      </c>
-      <c r="B194" t="n">
-        <v>0</v>
-      </c>
-      <c r="C194" t="n">
-        <v>9229000</v>
-      </c>
-      <c r="D194" t="n">
-        <v>-9229000</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Tú  Gà</t>
-        </is>
-      </c>
-      <c r="B195" t="n">
-        <v>0</v>
-      </c>
-      <c r="C195" t="n">
-        <v>5321000</v>
-      </c>
-      <c r="D195" t="n">
-        <v>-5321000</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>ck Banking TT tiền hàng CTY Vissan</t>
-        </is>
-      </c>
-      <c r="B196" t="n">
-        <v>0</v>
-      </c>
-      <c r="C196" t="n">
-        <v>152212138</v>
-      </c>
-      <c r="D196" t="n">
-        <v>-152212138</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Thu phi duy tri dich vu IB 09/2023</t>
-        </is>
-      </c>
-      <c r="B197" t="n">
-        <v>0</v>
-      </c>
-      <c r="C197" t="n">
-        <v>38500</v>
-      </c>
-      <c r="D197" t="n">
-        <v>-38500</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>"UNC tiền Samplinh đội CLM : T4/23 : 16,160,000
-+ T5/23: 1,960,000
-+T6/23: 6,860,000"</t>
-        </is>
-      </c>
-      <c r="B198" t="n">
-        <v>0</v>
-      </c>
-      <c r="C198" t="n">
-        <v>13742000</v>
-      </c>
-      <c r="D198" t="n">
-        <v>-13742000</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>PC10AA0544165</t>
-        </is>
-      </c>
-      <c r="B199" t="n">
-        <v>0</v>
-      </c>
-      <c r="C199" t="n">
-        <v>6369219</v>
-      </c>
-      <c r="D199" t="n">
-        <v>-6369219</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN SÁCH VÀ THIẾT BỊ TRƯỜNG HỌC GIA LAI</t>
-        </is>
-      </c>
-      <c r="B200" t="n">
-        <v>800000</v>
-      </c>
-      <c r="C200" t="n">
-        <v>0</v>
-      </c>
-      <c r="D200" t="n">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HÀ ĐỨC VINH</t>
-        </is>
-      </c>
-      <c r="B201" t="n">
-        <v>5200000</v>
-      </c>
-      <c r="C201" t="n">
-        <v>0</v>
-      </c>
-      <c r="D201" t="n">
-        <v>5200000</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Chi tiền lương tháng 8</t>
-        </is>
-      </c>
-      <c r="B202" t="n">
-        <v>0</v>
-      </c>
-      <c r="C202" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D202" t="n">
-        <v>-2000000</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>CK BanKing TT tiền hàng CTY Visssan</t>
-        </is>
-      </c>
-      <c r="B203" t="n">
-        <v>0</v>
-      </c>
-      <c r="C203" t="n">
-        <v>106826491</v>
-      </c>
-      <c r="D203" t="n">
-        <v>-106826491</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN BẢO THUẬN</t>
-        </is>
-      </c>
-      <c r="B204" t="n">
-        <v>4390000</v>
-      </c>
-      <c r="C204" t="n">
-        <v>0</v>
-      </c>
-      <c r="D204" t="n">
-        <v>4390000</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Thu phi BDSD 10/2023, So TK: 110649896789, SDT: 0983827174</t>
-        </is>
-      </c>
-      <c r="B205" t="n">
-        <v>0</v>
-      </c>
-      <c r="C205" t="n">
-        <v>19800</v>
-      </c>
-      <c r="D205" t="n">
-        <v>-19800</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THU PHÍ TỰ ĐỘNG VETC</t>
-        </is>
-      </c>
-      <c r="B206" t="n">
-        <v>8963000</v>
-      </c>
-      <c r="C206" t="n">
-        <v>0</v>
-      </c>
-      <c r="D206" t="n">
-        <v>8963000</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Anh Đức</t>
-        </is>
-      </c>
-      <c r="B207" t="n">
-        <v>0</v>
-      </c>
-      <c r="C207" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="D207" t="n">
-        <v>-5000000</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Việt Hằng 
-( đã ck bổ sung tiền lương T8/2023 : 260,385đ)"</t>
-        </is>
-      </c>
-      <c r="B208" t="n">
-        <v>0</v>
-      </c>
-      <c r="C208" t="n">
-        <v>15989587</v>
-      </c>
-      <c r="D208" t="n">
-        <v>-15989587</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Lâm</t>
-        </is>
-      </c>
-      <c r="B209" t="n">
-        <v>0</v>
-      </c>
-      <c r="C209" t="n">
-        <v>18172990</v>
-      </c>
-      <c r="D209" t="n">
-        <v>-18172990</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>CK Banking TT tiền hàng CTY Visan</t>
-        </is>
-      </c>
-      <c r="B210" t="n">
-        <v>0</v>
-      </c>
-      <c r="C210" t="n">
-        <v>37089805</v>
-      </c>
-      <c r="D210" t="n">
-        <v>-37089805</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>A. Đạt</t>
-        </is>
-      </c>
-      <c r="B211" t="n">
-        <v>0</v>
-      </c>
-      <c r="C211" t="n">
-        <v>11499415</v>
-      </c>
-      <c r="D211" t="n">
-        <v>-11499415</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>CÔNG TY BẢO HIỂM VIETINBANK BẮC TÂY NGUYÊN</t>
-        </is>
-      </c>
-      <c r="B212" t="n">
-        <v>1681000</v>
-      </c>
-      <c r="C212" t="n">
-        <v>0</v>
-      </c>
-      <c r="D212" t="n">
-        <v>1681000</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>TT tiền hàng CTY Yến SN</t>
-        </is>
-      </c>
-      <c r="B213" t="n">
-        <v>0</v>
-      </c>
-      <c r="C213" t="n">
-        <v>4000125480</v>
-      </c>
-      <c r="D213" t="n">
-        <v>-4000125480</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN AN PHÁT LỘC GIA LAI</t>
-        </is>
-      </c>
-      <c r="B214" t="n">
-        <v>2866000</v>
-      </c>
-      <c r="C214" t="n">
-        <v>0</v>
-      </c>
-      <c r="D214" t="n">
-        <v>2866000</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Tú (Gà )</t>
-        </is>
-      </c>
-      <c r="B215" t="n">
-        <v>0</v>
-      </c>
-      <c r="C215" t="n">
-        <v>6233000</v>
-      </c>
-      <c r="D215" t="n">
-        <v>-6233000</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Tú (Vịt )</t>
-        </is>
-      </c>
-      <c r="B216" t="n">
-        <v>0</v>
-      </c>
-      <c r="C216" t="n">
-        <v>9229000</v>
-      </c>
-      <c r="D216" t="n">
-        <v>-9229000</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Chi tiền lương tháng 9</t>
-        </is>
-      </c>
-      <c r="B217" t="n">
-        <v>0</v>
-      </c>
-      <c r="C217" t="n">
-        <v>11976000</v>
-      </c>
-      <c r="D217" t="n">
-        <v>-11976000</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Thu phi duy tri dich vu IB 10/2023</t>
-        </is>
-      </c>
-      <c r="B218" t="n">
-        <v>0</v>
-      </c>
-      <c r="C218" t="n">
-        <v>38500</v>
-      </c>
-      <c r="D218" t="n">
-        <v>-38500</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>GS Viên CLM</t>
-        </is>
-      </c>
-      <c r="B219" t="n">
-        <v>0</v>
-      </c>
-      <c r="C219" t="n">
-        <v>6860000</v>
-      </c>
-      <c r="D219" t="n">
-        <v>-6860000</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THẾ HỆ MỚI GIA LAI</t>
-        </is>
-      </c>
-      <c r="B220" t="n">
-        <v>11712950</v>
-      </c>
-      <c r="C220" t="n">
-        <v>0</v>
-      </c>
-      <c r="D220" t="n">
-        <v>11712950</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Lãi tất toán</t>
-        </is>
-      </c>
-      <c r="B221" t="n">
-        <v>0</v>
-      </c>
-      <c r="C221" t="n">
-        <v>5139967</v>
-      </c>
-      <c r="D221" t="n">
-        <v>-5139967</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>CK Banking TT tiền đơn hàng Nước Suối</t>
-        </is>
-      </c>
-      <c r="B222" t="n">
-        <v>0</v>
-      </c>
-      <c r="C222" t="n">
-        <v>19977584</v>
-      </c>
-      <c r="D222" t="n">
-        <v>-19977584</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>Thu phi BDSD 11/2023, So TK: 110649896789, SDT: 0983827174</t>
-        </is>
-      </c>
-      <c r="B223" t="n">
-        <v>0</v>
-      </c>
-      <c r="C223" t="n">
-        <v>19800</v>
-      </c>
-      <c r="D223" t="n">
-        <v>-19800</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>CK Banking TT CTY Visssan</t>
-        </is>
-      </c>
-      <c r="B224" t="n">
-        <v>0</v>
-      </c>
-      <c r="C224" t="n">
-        <v>82709210</v>
-      </c>
-      <c r="D224" t="n">
-        <v>-82709210</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>CN CÔNG TY CP PHÁT TRIỂN PHẦN MỀM ASIA TẠI ĐÀ NẴNG</t>
-        </is>
-      </c>
-      <c r="B225" t="n">
         <v>14000000</v>
-      </c>
-      <c r="C225" t="n">
-        <v>0</v>
-      </c>
-      <c r="D225" t="n">
-        <v>14000000</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Phước</t>
-        </is>
-      </c>
-      <c r="B226" t="n">
-        <v>0</v>
-      </c>
-      <c r="C226" t="n">
-        <v>19000000</v>
-      </c>
-      <c r="D226" t="n">
-        <v>-19000000</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Hằng</t>
-        </is>
-      </c>
-      <c r="B227" t="n">
-        <v>0</v>
-      </c>
-      <c r="C227" t="n">
-        <v>19824202</v>
-      </c>
-      <c r="D227" t="n">
-        <v>-19824202</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>CK Banking TT tiền hàng CYT NBT</t>
-        </is>
-      </c>
-      <c r="B228" t="n">
-        <v>0</v>
-      </c>
-      <c r="C228" t="n">
-        <v>370952084</v>
-      </c>
-      <c r="D228" t="n">
-        <v>-370952084</v>
       </c>
     </row>
   </sheetData>

--- a/docs/hoang-huy-phat/sosach2023/BAO_CAO_CONG_NO_HHP_2023.xlsx
+++ b/docs/hoang-huy-phat/sosach2023/BAO_CAO_CONG_NO_HHP_2023.xlsx
@@ -480,33 +480,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Hoa</t>
+          <t>CÔNG TY TNHH NHƯ HOA TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>303101385</v>
+        <v>149170604</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>303101385</v>
+        <v>149170604</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NHƯ HOA TÂY NGUYÊN</t>
+          <t>Nguyễn Thị Hoa</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>149170604</v>
+        <v>303101385</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>149170604</v>
+        <v>303101385</v>
       </c>
     </row>
     <row r="5">
@@ -576,17 +576,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lê Thị Thu Ba</t>
+          <t>Nguyễn Thị Hải Thanh</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>120703208</v>
+        <v>99568668</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>120703208</v>
+        <v>99568668</v>
       </c>
     </row>
     <row r="10">
@@ -608,17 +608,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Hải Thanh</t>
+          <t>Bùi Thị Dung</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>99568668</v>
+        <v>195398686</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>99568668</v>
+        <v>195398686</v>
       </c>
     </row>
     <row r="12">
@@ -640,33 +640,33 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ KIM HƯƠNG</t>
+          <t>Lê Thị Thu Ba</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31301277</v>
+        <v>120703208</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>31301277</v>
+        <v>120703208</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bùi Thị Dung</t>
+          <t>NGUYỄN THỊ KIM HƯƠNG</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>195398686</v>
+        <v>31301277</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>195398686</v>
+        <v>31301277</v>
       </c>
     </row>
     <row r="15">
@@ -688,81 +688,81 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Đặng Thị Luyến</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>152002192</v>
+        <v>53903780</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>152002192</v>
+        <v>53903780</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CÔNG TY ĐIỆN LỰC GIA LAI</t>
+          <t>Cửa Hàng Nhật An</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4191000</v>
+        <v>53345488</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4191000</v>
+        <v>53345488</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
+          <t>Lê Thị Chanh</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53903780</v>
+        <v>198072703</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>53903780</v>
+        <v>198072703</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cửa Hàng Nhật An</t>
+          <t>Đặng Thị Luyến</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>53345488</v>
+        <v>152002192</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>53345488</v>
+        <v>152002192</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lê Thị Chanh</t>
+          <t>CÔNG TY ĐIỆN LỰC GIA LAI</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>198072703</v>
+        <v>4191000</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>198072703</v>
+        <v>4191000</v>
       </c>
     </row>
     <row r="21">
@@ -800,33 +800,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lê Thị Xuân</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI NGỌC HOA</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>134005420</v>
+        <v>16524465</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>134005420</v>
+        <v>16524465</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI NGỌC HOA</t>
+          <t>Lê Thị Xuân</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16524465</v>
+        <v>134005420</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>16524465</v>
+        <v>134005420</v>
       </c>
     </row>
     <row r="25">
@@ -1088,145 +1088,145 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẢI ANH TIẾN</t>
+          <t>Huỳnh Văn Định</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>86188966</v>
+        <v>77476395</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>86188966</v>
+        <v>77476395</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TẠP HÓA KHÁNH HÀ</t>
+          <t>Tạp Hóa Hoàng Phát</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>23601721</v>
+        <v>16962352</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>23601721</v>
+        <v>16962352</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Huỳnh Văn Định</t>
+          <t>Hà Thị Thúy An</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>77476395</v>
+        <v>77418077</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>77476395</v>
+        <v>77418077</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tạp Hóa Hoàng Phát</t>
+          <t>TẠP HÓA KHÁNH HÀ</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>16962352</v>
+        <v>23601721</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>16962352</v>
+        <v>23601721</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hà Thị Thúy An</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẢI ANH TIẾN</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>77418077</v>
+        <v>86188966</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>77418077</v>
+        <v>86188966</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VŨ TRỌNG PHƯƠNG</t>
+          <t>TẠP HÓA THÙY LINH</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>57397069</v>
+        <v>42317063</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>57397069</v>
+        <v>42317063</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TẠP HÓA THÙY LINH</t>
+          <t>VŨ TRỌNG PHƯƠNG</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>42317063</v>
+        <v>57397069</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>42317063</v>
+        <v>57397069</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TẠP PHẨM KHÁNH AN</t>
+          <t>HỘ KINH DOANH TRẦN VĂN THỨC</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2964343</v>
+        <v>77438398</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>2964343</v>
+        <v>77438398</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ THẢO</t>
+          <t>TẠP PHẨM KHÁNH AN</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>41052529</v>
+        <v>2964343</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>41052529</v>
+        <v>2964343</v>
       </c>
     </row>
     <row r="50">
@@ -1248,17 +1248,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH TRẦN VĂN THỨC</t>
+          <t>NGUYỄN THỊ THẢO</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>77438398</v>
+        <v>41052529</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>77438398</v>
+        <v>41052529</v>
       </c>
     </row>
     <row r="52">
@@ -1280,33 +1280,33 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH TẠP HÓA NGỌC TÀI</t>
+          <t>NGUYỄN THỊ THÌN</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>80077301</v>
+        <v>27381529</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>80077301</v>
+        <v>27381529</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ THÌN</t>
+          <t>HỘ KINH DOANH TẠP HÓA NGỌC TÀI</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>27381529</v>
+        <v>80077301</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>27381529</v>
+        <v>80077301</v>
       </c>
     </row>
     <row r="55">
@@ -1536,33 +1536,33 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN KEN</t>
+          <t>HỘ KINH DOANH PHAN THỊ ÁNH NHUNG</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3988330</v>
+        <v>16661853</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>3988330</v>
+        <v>16661853</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH PHAN THỊ ÁNH NHUNG</t>
+          <t>DOANH NGHIỆP TƯ NHÂN KEN</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>16661853</v>
+        <v>3988330</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>16661853</v>
+        <v>3988330</v>
       </c>
     </row>
     <row r="71">
@@ -1584,33 +1584,33 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Vũ</t>
+          <t>PHAN XUÂN TUẤN</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>44446971</v>
+        <v>32843778</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>44446971</v>
+        <v>32843778</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PHAN XUÂN TUẤN</t>
+          <t>Nguyễn Văn Vũ</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>32843778</v>
+        <v>44446971</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>32843778</v>
+        <v>44446971</v>
       </c>
     </row>
     <row r="74">
@@ -1632,65 +1632,65 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CÔNG TY BẢO HIỂM BIDV BẮC TÂY NGUYÊN</t>
+          <t>Như Ý</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>143713599</v>
+        <v>3262813</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>143713599</v>
+        <v>3262813</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Như Ý</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ẨM THỰC CÔ DUYÊN</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3262813</v>
+        <v>18177736</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>3262813</v>
+        <v>18177736</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ẨM THỰC CÔ DUYÊN</t>
+          <t>CÔNG TY BẢO HIỂM BIDV BẮC TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>18177736</v>
+        <v>143713599</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>18177736</v>
+        <v>143713599</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PHẠM THỊ THU TRANG</t>
+          <t>ĐINH VĂN CƯỜNG</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>65479968</v>
+        <v>100594786</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>65479968</v>
+        <v>100594786</v>
       </c>
     </row>
     <row r="79">
@@ -1712,49 +1712,49 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ĐINH VĂN CƯỜNG</t>
+          <t>PHẠM THỊ THU TRANG</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>100594786</v>
+        <v>65479968</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>100594786</v>
+        <v>65479968</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TẠP HÓA BỐN PHƯƠNG</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI GIA LAI</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>9172417</v>
+        <v>52635998</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>9172417</v>
+        <v>52635998</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI GIA LAI</t>
+          <t>TẠP HÓA BỐN PHƯƠNG</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>52635998</v>
+        <v>9172417</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>52635998</v>
+        <v>9172417</v>
       </c>
     </row>
     <row r="83">
@@ -2048,1217 +2048,1217 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Đặng Thị Kim Liễu</t>
+          <t>Đàm Văn Tú</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>168991911</v>
+        <v>202030757</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>168991911</v>
+        <v>202030757</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Đàm Văn Tú</t>
+          <t>TẠP HÓA HỒNG NHUNG</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>202030757</v>
+        <v>12402720</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>202030757</v>
+        <v>12402720</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>TẠP HÓA HỒNG NHUNG</t>
+          <t>Hà Thị Ánh Thu</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>12402720</v>
+        <v>31768870</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>12402720</v>
+        <v>31768870</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Lương Thị Liễu</t>
+          <t>Đặng Thị Kim Liễu</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>112580783</v>
+        <v>168991911</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>112580783</v>
+        <v>168991911</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Hà Thị Ánh Thu</t>
+          <t>Lương Thị Liễu</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>31768870</v>
+        <v>112580783</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>31768870</v>
+        <v>112580783</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Đậu Đức Hào</t>
+          <t>Đoàn Hữu Minh</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>238603563</v>
+        <v>113495115</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>238603563</v>
+        <v>113495115</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Đinh Văn Phúc</t>
+          <t>DOANH NGHIỆP TƯ NHÂN HỒNG BIÊN</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>106849534</v>
+        <v>5741340</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>106849534</v>
+        <v>5741340</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>TRẦN KIM HUẾ</t>
+          <t>Đinh Văn Phúc</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>193931531</v>
+        <v>106849534</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>193931531</v>
+        <v>106849534</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN HỒNG BIÊN</t>
+          <t>Văn Thị Trang</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>5741340</v>
+        <v>64511283</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>5741340</v>
+        <v>64511283</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Đoàn Hữu Minh</t>
+          <t>Đậu Đức Hào</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>113495115</v>
+        <v>238603563</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>113495115</v>
+        <v>238603563</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Văn Thị Trang</t>
+          <t>TRẦN KIM HUẾ</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>64511283</v>
+        <v>193931531</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>64511283</v>
+        <v>193931531</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ngô Võ Đan</t>
+          <t>CÔNG TY CỔ PHẦN NGÓI NÂU GIA LAI</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>113453838</v>
+        <v>62216706</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>113453838</v>
+        <v>62216706</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Lê Xuân Cường</t>
+          <t>Huỳnh Thị Trúc Ly</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>92364509</v>
+        <v>172721649</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>92364509</v>
+        <v>172721649</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Hồ Văn Thành</t>
+          <t>Hoàng Chí Công</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>113593552</v>
+        <v>147289986</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>113593552</v>
+        <v>147289986</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Hà Trịnh Quốc Việt</t>
+          <t>Nguyễn Thị Tâm</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>209257274</v>
+        <v>167005238</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>209257274</v>
+        <v>167005238</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Dương Thị Hiếu</t>
+          <t>Nguyễn Minh Tứ</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>289806522</v>
+        <v>132486797</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>289806522</v>
+        <v>132486797</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN NGÓI NÂU GIA LAI</t>
+          <t>Nguyễn Hữu Thành</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>62216706</v>
+        <v>260454151</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>62216706</v>
+        <v>260454151</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Tứ</t>
+          <t>Lê Văn Mẫn</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>132486797</v>
+        <v>235395239</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>132486797</v>
+        <v>235395239</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Tú</t>
+          <t>Lê Văn Bằng</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>169458458</v>
+        <v>132937416</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>169458458</v>
+        <v>132937416</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Duy</t>
+          <t>Nguyễn Minh Tú</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>241451470</v>
+        <v>169458458</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>241451470</v>
+        <v>169458458</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Huỳnh Thị Trúc Ly</t>
+          <t>Hà Trịnh Quốc Việt</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>172721649</v>
+        <v>209257274</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>172721649</v>
+        <v>209257274</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Hoàng Chí Công</t>
+          <t>Hồ Văn Thành</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>147289986</v>
+        <v>113593552</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>147289986</v>
+        <v>113593552</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Lê Văn Mẫn</t>
+          <t>Dương Thị Hiếu</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>235395239</v>
+        <v>289806522</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>235395239</v>
+        <v>289806522</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Tâm</t>
+          <t>Ngô Võ Đan</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>167005238</v>
+        <v>113453838</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>167005238</v>
+        <v>113453838</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Nguyễn Hữu Thành</t>
+          <t>Nguyễn Minh Duy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>260454151</v>
+        <v>241451470</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>260454151</v>
+        <v>241451470</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Lê Văn Bằng</t>
+          <t>Lê Xuân Cường</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>132937416</v>
+        <v>92364509</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>132937416</v>
+        <v>92364509</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Dương</t>
+          <t>Nguyễn Thị Thu Hằng</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>187691183</v>
+        <v>155155639</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>187691183</v>
+        <v>155155639</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Đăng Loan</t>
+          <t>QUÁCH THỊ THÚY NGA</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>173086396</v>
+        <v>19762931</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>173086396</v>
+        <v>19762931</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Nguyễn Trịnh Minh Hoàng</t>
+          <t>TẠP HÓA THÌN</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>209281321</v>
+        <v>9754668</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>209281321</v>
+        <v>9754668</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thu Hằng</t>
+          <t>PHAN THỊ ÁNH LỸ</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>155155639</v>
+        <v>18342199</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>155155639</v>
+        <v>18342199</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Mai Hoàng Thiện Châu</t>
+          <t>SUI NGỌC LAN</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>166626778</v>
+        <v>12232763</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>166626778</v>
+        <v>12232763</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Nguyễn Quốc Đạt</t>
+          <t>Nguyễn Thị Minh Tâm</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>241448995</v>
+        <v>190953225</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>241448995</v>
+        <v>190953225</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>QUÁCH THỊ THÚY NGA</t>
+          <t>Nguyễn Trường Sơn</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>19762931</v>
+        <v>107795444</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>19762931</v>
+        <v>107795444</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PHAN THỊ ÁNH LỸ</t>
+          <t>Nguyễn Hồng Ý</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>18342199</v>
+        <v>225945739</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>18342199</v>
+        <v>225945739</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Nguyễn Hồng Ý</t>
+          <t>Nguyễn Thị Hiền</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>225945739</v>
+        <v>153063249</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>225945739</v>
+        <v>153063249</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Hiền</t>
+          <t>Nguyễn Thị Đăng Loan</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>153063249</v>
+        <v>173086396</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>153063249</v>
+        <v>173086396</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Minh Tâm</t>
+          <t>Nguyễn Văn Dương</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>190953225</v>
+        <v>187691183</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>190953225</v>
+        <v>187691183</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Nguyễn Trường Sơn</t>
+          <t>Mai Hoàng Thiện Châu</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>107795444</v>
+        <v>166626778</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>107795444</v>
+        <v>166626778</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SUI NGỌC LAN</t>
+          <t>Nguyễn Trịnh Minh Hoàng</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>12232763</v>
+        <v>209281321</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>12232763</v>
+        <v>209281321</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TẠP HÓA THÌN</t>
+          <t>HỘ KINH DOANH VÕ VĂN NGỌ</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>9754668</v>
+        <v>66782415</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>9754668</v>
+        <v>66782415</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH VÕ VĂN NGỌ</t>
+          <t>TẠP HÓA NĂM THI</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>66782415</v>
+        <v>46344956</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>66782415</v>
+        <v>46344956</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Nguyễn Nam Hồng</t>
+          <t>Nguyễn Quốc Đạt</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>161914097</v>
+        <v>241448995</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>161914097</v>
+        <v>241448995</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TẠP HÓA NĂM THI</t>
+          <t>Nguyễn Nam Hồng</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>46344956</v>
+        <v>161914097</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>46344956</v>
+        <v>161914097</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Trịnh Tân</t>
+          <t>Trần Bích Hải</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>206613852</v>
+        <v>114345439</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>206613852</v>
+        <v>114345439</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Trịnh Thị Sinh</t>
+          <t>Phạm Hồng Công</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>152557899</v>
+        <v>130483375</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>152557899</v>
+        <v>130483375</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Võ Chí Hà</t>
+          <t>Phan Thanh Hoàng</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>112601232</v>
+        <v>116130899</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>112601232</v>
+        <v>116130899</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Nguyễn Trịnh Tố Ngân</t>
+          <t>Trần Thị Tuyết Nhung</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>130495163</v>
+        <v>132827967</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
       </c>
       <c r="D147" t="n">
-        <v>130495163</v>
+        <v>132827967</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>TẠP HÓA BỬU HIỀN</t>
+          <t>Trần Quý Đức</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>61435252</v>
+        <v>169963096</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>61435252</v>
+        <v>169963096</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Trịnh Lê Hiệp</t>
+          <t>Vương Trường Giang</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>260140118</v>
+        <v>111832426</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>260140118</v>
+        <v>111832426</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>LÊ THỊ MỸ PHƯƠNG</t>
+          <t>Bùi Văn Lực</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>43179190</v>
+        <v>243611717</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>43179190</v>
+        <v>243611717</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Trần Thị Tuyết Nhung</t>
+          <t>Hoàng Tú</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>132827967</v>
+        <v>199955071</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>132827967</v>
+        <v>199955071</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Phạm Hồng Công</t>
+          <t>Võ Văn Vũ</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>130483375</v>
+        <v>112039110</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>130483375</v>
+        <v>112039110</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Phan Thanh Hoàng</t>
+          <t>Đỗ Trịnh Công</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>116130899</v>
+        <v>152180951</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>116130899</v>
+        <v>152180951</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Đỗ Trịnh Công</t>
+          <t>Vũ Thị Việt Hằng</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>152180951</v>
+        <v>165336925</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>152180951</v>
+        <v>165336925</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Vũ Thị Việt Hằng</t>
+          <t>Trịnh Lê Hiệp</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>165336925</v>
+        <v>260140118</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>165336925</v>
+        <v>260140118</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Võ Văn Vũ</t>
+          <t>Nguyễn Trịnh Tố Ngân</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>112039110</v>
+        <v>130495163</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>112039110</v>
+        <v>130495163</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Vương Trường Giang</t>
+          <t>TẠP HÓA BỬU HIỀN</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>111832426</v>
+        <v>61435252</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>111832426</v>
+        <v>61435252</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Bùi Văn Lực</t>
+          <t>LÊ THỊ MỸ PHƯƠNG</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>243611717</v>
+        <v>43179190</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>243611717</v>
+        <v>43179190</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Hoàng Tú</t>
+          <t>Trịnh Tân</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>199955071</v>
+        <v>206613852</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>199955071</v>
+        <v>206613852</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Trần Bích Hải</t>
+          <t>Trịnh Thị Sinh</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>114345439</v>
+        <v>152557899</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>114345439</v>
+        <v>152557899</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Trần Quý Đức</t>
+          <t>Võ Chí Hà</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>169963096</v>
+        <v>112601232</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>169963096</v>
+        <v>112601232</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Ngô Văn Bằng</t>
+          <t>Nguyễn Thúc Bảo</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>111936480</v>
+        <v>111954346</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>111936480</v>
+        <v>111954346</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Phan Thị Thùy Mỵ</t>
+          <t>NGUYỄN VĂN CÔNG</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>113837653</v>
+        <v>94306512</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>113837653</v>
+        <v>94306512</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>HUỲNH ĐỨC AN</t>
+          <t>Phan Công Thiện</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>54719280</v>
+        <v>112632349</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
       </c>
       <c r="D164" t="n">
-        <v>54719280</v>
+        <v>112632349</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Kpă Vũ Mạnh Long</t>
+          <t>Nguyễn Lê Hậu</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>109286964</v>
+        <v>260476999</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>109286964</v>
+        <v>260476999</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>NGUYỄN VĂN CÔNG</t>
+          <t>Dương Thị Thông</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>94306512</v>
+        <v>243833248</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>94306512</v>
+        <v>243833248</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Trịnh Thị Luận</t>
+          <t>Phan Thị Thùy Mỵ</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>168619647</v>
+        <v>113837653</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>168619647</v>
+        <v>113837653</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Dương Thị Thông</t>
+          <t>Ngô Văn Bằng</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>243833248</v>
+        <v>111936480</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>243833248</v>
+        <v>111936480</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Huỳnh Thị Cúc</t>
+          <t>Trịnh Thị Luận</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>248582520</v>
+        <v>168619647</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
       </c>
       <c r="D169" t="n">
-        <v>248582520</v>
+        <v>168619647</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Nguyễn Lê Hậu</t>
+          <t>HUỲNH ĐỨC AN</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>260476999</v>
+        <v>54719280</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
       </c>
       <c r="D170" t="n">
-        <v>260476999</v>
+        <v>54719280</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Phan Công Thiện</t>
+          <t>Huỳnh Thị Cúc</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>112632349</v>
+        <v>248582520</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>112632349</v>
+        <v>248582520</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Nguyễn Thúc Bảo</t>
+          <t>Kpă Vũ Mạnh Long</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>111954346</v>
+        <v>109286964</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>111954346</v>
+        <v>109286964</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Ngô Đức Thuận</t>
+          <t>Mai Thị Kim Loan</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>131567122</v>
+        <v>144859608</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>131567122</v>
+        <v>144859608</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Theo</t>
+          <t>Dương Nô</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>93332200</v>
+        <v>111439059</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>93332200</v>
+        <v>111439059</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ĐINH VĂN VIÊN</t>
+          <t>Ngô Đức Thuận</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>51415511</v>
+        <v>131567122</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
       </c>
       <c r="D175" t="n">
-        <v>51415511</v>
+        <v>131567122</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Đinh Biên Thùy</t>
+          <t>ĐINH VĂN VIÊN</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>142784458</v>
+        <v>51415511</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
       </c>
       <c r="D176" t="n">
-        <v>142784458</v>
+        <v>51415511</v>
       </c>
     </row>
     <row r="177">
@@ -3280,65 +3280,65 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Dương Nô</t>
+          <t>Đinh Thiện Ân</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>111439059</v>
+        <v>114697559</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
       </c>
       <c r="D178" t="n">
-        <v>111439059</v>
+        <v>114697559</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Trịnh Lê Hưng</t>
+          <t>Nguyễn Văn Theo</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>208830345</v>
+        <v>93332200</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>208830345</v>
+        <v>93332200</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Đinh Thiện Ân</t>
+          <t>Trịnh Lê Hưng</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>114697559</v>
+        <v>208830345</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>114697559</v>
+        <v>208830345</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Mai Thị Kim Loan</t>
+          <t>Đinh Biên Thùy</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>144859608</v>
+        <v>142784458</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>144859608</v>
+        <v>142784458</v>
       </c>
     </row>
     <row r="182">
@@ -3360,913 +3360,913 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Mai Văn Tân</t>
+          <t>Hộ Kinh Doanh Đồng Thị Thanh</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>149513069</v>
+        <v>75303891</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>149513069</v>
+        <v>75303891</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thanh Hương</t>
+          <t>Lại Thị Hà</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>292651315</v>
+        <v>91139305</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>292651315</v>
+        <v>91139305</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Lê Văn Hưng</t>
+          <t>Phan Thị Ánh Mỹ</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>95596343</v>
+        <v>240243282</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>95596343</v>
+        <v>240243282</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Hà Thị Hiếu</t>
+          <t>Nguyễn Thị Thanh Hương</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>94706437</v>
+        <v>292651315</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>94706437</v>
+        <v>292651315</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Đỗ Thành Vinh</t>
+          <t>Hà Thị Hiếu</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>113695752</v>
+        <v>94706437</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>113695752</v>
+        <v>94706437</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Phạm Thị Mỹ Hạnh</t>
+          <t>Mai Văn Tân</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>225080985</v>
+        <v>149513069</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>225080985</v>
+        <v>149513069</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ TẠO</t>
+          <t>Lê Văn Hưng</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>56632668</v>
+        <v>95596343</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>56632668</v>
+        <v>95596343</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>CAO MẠNH HÙNG</t>
+          <t>LÊ THỊ MỸ LOAN</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>93965037</v>
+        <v>69945287</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>93965037</v>
+        <v>69945287</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>LÊ THỊ MỸ LOAN</t>
+          <t>NGUYỄN THỊ TẠO</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>69945287</v>
+        <v>56632668</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>69945287</v>
+        <v>56632668</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ LINH GIANG</t>
+          <t>CAO MẠNH HÙNG</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>89714754</v>
+        <v>93965037</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>89714754</v>
+        <v>93965037</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>TRẦN TIẾN DŨNG</t>
+          <t>Đỗ Thành Vinh</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>37058364</v>
+        <v>113695752</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
       </c>
       <c r="D193" t="n">
-        <v>37058364</v>
+        <v>113695752</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>BÙI XUÂN NAM</t>
+          <t>Phạm Thị Mỹ Hạnh</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>93355244</v>
+        <v>225080985</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
       </c>
       <c r="D194" t="n">
-        <v>93355244</v>
+        <v>225080985</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Trần Văn Hiệu</t>
+          <t>Tạp Hóa Thùy Linh</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>58075244</v>
+        <v>72053019</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>58075244</v>
+        <v>72053019</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PHẠM THỊ THU SA</t>
+          <t>Đỗ Thị Hồng Nhung</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>72713516</v>
+        <v>222153462</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>72713516</v>
+        <v>222153462</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Trung</t>
+          <t>Trần Minh Chung</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>34317000</v>
+        <v>55283301</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>34317000</v>
+        <v>55283301</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Đỗ Thị Bích Hương</t>
+          <t>LƯU THỊ THUỲ</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>220668611</v>
+        <v>96882946</v>
       </c>
       <c r="C198" t="n">
         <v>0</v>
       </c>
       <c r="D198" t="n">
-        <v>220668611</v>
+        <v>96882946</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Nhà Thuốc Linh</t>
+          <t>Đỗ Thị Bích Hương</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>19459440</v>
+        <v>220668611</v>
       </c>
       <c r="C199" t="n">
         <v>0</v>
       </c>
       <c r="D199" t="n">
-        <v>19459440</v>
+        <v>220668611</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Tạp Hóa Thùy Linh</t>
+          <t>Nhà Thuốc Linh</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>72053019</v>
+        <v>19459440</v>
       </c>
       <c r="C200" t="n">
         <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>72053019</v>
+        <v>19459440</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Đỗ Thị Hồng Nhung</t>
+          <t>TRẦN THỊ THU HÀ</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>222153462</v>
+        <v>55746047</v>
       </c>
       <c r="C201" t="n">
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>222153462</v>
+        <v>55746047</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Trần Minh Chung</t>
+          <t>BÙI XUÂN NAM</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>55283301</v>
+        <v>93355244</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>55283301</v>
+        <v>93355244</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>TRẦN THỊ THU HÀ</t>
+          <t>TRẦN TIẾN DŨNG</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>55746047</v>
+        <v>37058364</v>
       </c>
       <c r="C203" t="n">
         <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>55746047</v>
+        <v>37058364</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thu</t>
+          <t>TRẦN THỊ THU HƯƠNG</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>56904595</v>
+        <v>33034001</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>56904595</v>
+        <v>33034001</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Lại Thị Hà</t>
+          <t>TẠP HÓA NHƯ THỦY</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>91139305</v>
+        <v>57550578</v>
       </c>
       <c r="C205" t="n">
         <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>91139305</v>
+        <v>57550578</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>LƯU THỊ THUỲ</t>
+          <t>Trần Thị Thu Hồng</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>96882946</v>
+        <v>103684279</v>
       </c>
       <c r="C206" t="n">
         <v>0</v>
       </c>
       <c r="D206" t="n">
-        <v>96882946</v>
+        <v>103684279</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TRẦN THỊ THU HƯƠNG</t>
+          <t>Dương Minh Ngọc</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>33034001</v>
+        <v>73225572</v>
       </c>
       <c r="C207" t="n">
         <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>33034001</v>
+        <v>73225572</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Hoàng Anh Thương</t>
+          <t>NGUYỄN THỊ LINH GIANG</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>67529025</v>
+        <v>89714754</v>
       </c>
       <c r="C208" t="n">
         <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>67529025</v>
+        <v>89714754</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>TẠP HÓA NHƯ THỦY</t>
+          <t>Hoàng Anh Thương</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>57550578</v>
+        <v>67529025</v>
       </c>
       <c r="C209" t="n">
         <v>0</v>
       </c>
       <c r="D209" t="n">
-        <v>57550578</v>
+        <v>67529025</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Phan Thị Ánh Mỹ</t>
+          <t>Trần Văn Hiệu</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>240243282</v>
+        <v>58075244</v>
       </c>
       <c r="C210" t="n">
         <v>0</v>
       </c>
       <c r="D210" t="n">
-        <v>240243282</v>
+        <v>58075244</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Dương Minh Ngọc</t>
+          <t>Nguyễn Thị Thu</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>73225572</v>
+        <v>56904595</v>
       </c>
       <c r="C211" t="n">
         <v>0</v>
       </c>
       <c r="D211" t="n">
-        <v>73225572</v>
+        <v>56904595</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Đồng Thị Thanh</t>
+          <t>Nguyễn Văn Trung</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>75303891</v>
+        <v>34317000</v>
       </c>
       <c r="C212" t="n">
         <v>0</v>
       </c>
       <c r="D212" t="n">
-        <v>75303891</v>
+        <v>34317000</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Trần Thị Thu Hồng</t>
+          <t>PHẠM THỊ THU SA</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>103684279</v>
+        <v>72713516</v>
       </c>
       <c r="C213" t="n">
         <v>0</v>
       </c>
       <c r="D213" t="n">
-        <v>103684279</v>
+        <v>72713516</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TRỊNH HOÀNG SƠN</t>
+          <t>HỘ KINH DOANH ĐẶNG THỊ DIỄM</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>147169661</v>
+        <v>75977935</v>
       </c>
       <c r="C214" t="n">
         <v>0</v>
       </c>
       <c r="D214" t="n">
-        <v>147169661</v>
+        <v>75977935</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Lâm Ngọc Đào</t>
+          <t>HỘ KINH DOANH KHIÊN LÀNH</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>133099188</v>
+        <v>75158369</v>
       </c>
       <c r="C215" t="n">
         <v>0</v>
       </c>
       <c r="D215" t="n">
-        <v>133099188</v>
+        <v>75158369</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Hoàng Thị Thanh Hương</t>
+          <t>Lê Tiến Hậu</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>55259900</v>
+        <v>130810220</v>
       </c>
       <c r="C216" t="n">
         <v>0</v>
       </c>
       <c r="D216" t="n">
-        <v>55259900</v>
+        <v>130810220</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Vũ Thị Thu Hường</t>
+          <t>Nguyễn Đức Thiên</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>100927438</v>
+        <v>93567284</v>
       </c>
       <c r="C217" t="n">
         <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>100927438</v>
+        <v>93567284</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Trần Thị Lan Thi</t>
+          <t>Hộ Kinh Doanh Hồ Thị Thanh Hiền</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>93448010</v>
+        <v>72565656</v>
       </c>
       <c r="C218" t="n">
         <v>0</v>
       </c>
       <c r="D218" t="n">
-        <v>93448010</v>
+        <v>72565656</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Lê Tiến Hậu</t>
+          <t>Hoàng Thị Thanh Hương</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>130810220</v>
+        <v>55259900</v>
       </c>
       <c r="C219" t="n">
         <v>0</v>
       </c>
       <c r="D219" t="n">
-        <v>130810220</v>
+        <v>55259900</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Nguyễn Đức Thiên</t>
+          <t>LÂM MINH HOÀNG</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>93567284</v>
+        <v>75323336</v>
       </c>
       <c r="C220" t="n">
         <v>0</v>
       </c>
       <c r="D220" t="n">
-        <v>93567284</v>
+        <v>75323336</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Hồ Thị Thanh Hiền</t>
+          <t>Nguyễn Thị Nương</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>72565656</v>
+        <v>37600124</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
       </c>
       <c r="D221" t="n">
-        <v>72565656</v>
+        <v>37600124</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Đặng Kim Hùng</t>
+          <t>Trịnh Lê Đông</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>72633979</v>
+        <v>208483355</v>
       </c>
       <c r="C222" t="n">
         <v>0</v>
       </c>
       <c r="D222" t="n">
-        <v>72633979</v>
+        <v>208483355</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VIỄN THÔNG T&amp;T GIA LAI</t>
+          <t>Đặng Kim Hùng</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>5148768</v>
+        <v>72633979</v>
       </c>
       <c r="C223" t="n">
         <v>0</v>
       </c>
       <c r="D223" t="n">
-        <v>5148768</v>
+        <v>72633979</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Trịnh Lê Đông</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VIỄN THÔNG T&amp;T GIA LAI</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>208483355</v>
+        <v>5148768</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>208483355</v>
+        <v>5148768</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Nương</t>
+          <t>Võ Văn Thành</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>37600124</v>
+        <v>37061399</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>37600124</v>
+        <v>37061399</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>LÂM MINH HOÀNG</t>
+          <t>Thới Thị Bích Hà</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>75323336</v>
+        <v>96073251</v>
       </c>
       <c r="C226" t="n">
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>75323336</v>
+        <v>96073251</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Võ Văn Thành</t>
+          <t>Trần Thị Lan Thi</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>37061399</v>
+        <v>93448010</v>
       </c>
       <c r="C227" t="n">
         <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>37061399</v>
+        <v>93448010</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH KHIÊN LÀNH</t>
+          <t>TRỊNH HOÀNG SƠN</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>75158369</v>
+        <v>147169661</v>
       </c>
       <c r="C228" t="n">
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>75158369</v>
+        <v>147169661</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH ĐẶNG THỊ DIỄM</t>
+          <t>Lâm Ngọc Đào</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>75977935</v>
+        <v>133099188</v>
       </c>
       <c r="C229" t="n">
         <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>75977935</v>
+        <v>133099188</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Thới Thị Bích Hà</t>
+          <t>Vũ Thị Thu Hường</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>96073251</v>
+        <v>100927438</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>96073251</v>
+        <v>100927438</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Tường Vi</t>
+          <t>Đàm Đình Ngữ</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>37203656</v>
+        <v>105797354</v>
       </c>
       <c r="C231" t="n">
         <v>0</v>
       </c>
       <c r="D231" t="n">
-        <v>37203656</v>
+        <v>105797354</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Đàm Đình Ngữ</t>
+          <t>Nguyễn Thị Tường Vi</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>105797354</v>
+        <v>37203656</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
       </c>
       <c r="D232" t="n">
-        <v>105797354</v>
+        <v>37203656</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>TẠP HÓA CÚC</t>
+          <t>Phạm Văn Minh</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>77778421</v>
+        <v>129316036</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
       </c>
       <c r="D233" t="n">
-        <v>77778421</v>
+        <v>129316036</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ KIM LIÊN</t>
+          <t>Trần Bích Hả</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>95603094</v>
+        <v>18502560</v>
       </c>
       <c r="C234" t="n">
         <v>0</v>
       </c>
       <c r="D234" t="n">
-        <v>95603094</v>
+        <v>18502560</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>TẠP HÓA THÙY TRANG</t>
+          <t>NGUYỄN THỊ KIM LIÊN</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>56131277</v>
+        <v>95603094</v>
       </c>
       <c r="C235" t="n">
         <v>0</v>
       </c>
       <c r="D235" t="n">
-        <v>56131277</v>
+        <v>95603094</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Trần Bích Hả</t>
+          <t>TẠP HÓA CÚC</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>18502560</v>
+        <v>77778421</v>
       </c>
       <c r="C236" t="n">
         <v>0</v>
       </c>
       <c r="D236" t="n">
-        <v>18502560</v>
+        <v>77778421</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Phạm Văn Minh</t>
+          <t>TẠP HÓA THÙY TRANG</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>129316036</v>
+        <v>56131277</v>
       </c>
       <c r="C237" t="n">
         <v>0</v>
       </c>
       <c r="D237" t="n">
-        <v>129316036</v>
+        <v>56131277</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>PHOTOCOPY - VĂN PHÒNG PHẨM - TẠP HÓA MAI LAN</t>
+          <t>HỒ TRỌNG DUY</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>59869441</v>
+        <v>37879130</v>
       </c>
       <c r="C238" t="n">
         <v>0</v>
       </c>
       <c r="D238" t="n">
-        <v>59869441</v>
+        <v>37879130</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>HỒ TRỌNG DUY</t>
+          <t>PHOTOCOPY - VĂN PHÒNG PHẨM - TẠP HÓA MAI LAN</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>37879130</v>
+        <v>59869441</v>
       </c>
       <c r="C239" t="n">
         <v>0</v>
       </c>
       <c r="D239" t="n">
-        <v>37879130</v>
+        <v>59869441</v>
       </c>
     </row>
     <row r="240">
@@ -4720,33 +4720,33 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Bel Việt Nam</t>
+          <t>Cty TNHH MTV SXTMDV Nhật Vĩnh</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>17143056</v>
+        <v>18981000</v>
       </c>
       <c r="C268" t="n">
         <v>0</v>
       </c>
       <c r="D268" t="n">
-        <v>17143056</v>
+        <v>18981000</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Cty TNHH MTV SXTMDV Nhật Vĩnh</t>
+          <t>Công Ty TNHH Bel Việt Nam</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>18981000</v>
+        <v>17143056</v>
       </c>
       <c r="C269" t="n">
         <v>0</v>
       </c>
       <c r="D269" t="n">
-        <v>18981000</v>
+        <v>17143056</v>
       </c>
     </row>
     <row r="270">
@@ -4832,17 +4832,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Nguyễn Mạnh</t>
+          <t>Hồ Minh Ngân</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>114537266</v>
+        <v>71035603</v>
       </c>
       <c r="C275" t="n">
         <v>0</v>
       </c>
       <c r="D275" t="n">
-        <v>114537266</v>
+        <v>71035603</v>
       </c>
     </row>
     <row r="276">
@@ -4864,97 +4864,97 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Hồ Minh Ngân</t>
+          <t>Nguyễn Mạnh</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>71035603</v>
+        <v>114537266</v>
       </c>
       <c r="C277" t="n">
         <v>0</v>
       </c>
       <c r="D277" t="n">
-        <v>71035603</v>
+        <v>114537266</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN WIN FOODS GIA LAI</t>
+          <t>Nguyễn Thành Phước</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>19643904</v>
+        <v>17073698</v>
       </c>
       <c r="C278" t="n">
         <v>0</v>
       </c>
       <c r="D278" t="n">
-        <v>19643904</v>
+        <v>17073698</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Phan Thị Lâm</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN WIN FOODS GIA LAI</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>104212766</v>
+        <v>19643904</v>
       </c>
       <c r="C279" t="n">
         <v>0</v>
       </c>
       <c r="D279" t="n">
-        <v>104212766</v>
+        <v>19643904</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Nguyễn Tấn Đức</t>
+          <t>Trần Phương Thảo</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>53502403</v>
+        <v>146118433</v>
       </c>
       <c r="C280" t="n">
         <v>0</v>
       </c>
       <c r="D280" t="n">
-        <v>53502403</v>
+        <v>146118433</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Nguyễn Thành Phước</t>
+          <t>Phan Thị Lâm</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>17073698</v>
+        <v>104212766</v>
       </c>
       <c r="C281" t="n">
         <v>0</v>
       </c>
       <c r="D281" t="n">
-        <v>17073698</v>
+        <v>104212766</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Trần Phương Thảo</t>
+          <t>Nguyễn Tấn Đức</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>146118433</v>
+        <v>53502403</v>
       </c>
       <c r="C282" t="n">
         <v>0</v>
       </c>
       <c r="D282" t="n">
-        <v>146118433</v>
+        <v>53502403</v>
       </c>
     </row>
     <row r="283">
@@ -5008,33 +5008,33 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Đoàn Thị Hồng Vân</t>
+          <t>Lê Thị Hồng Hà</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>128445286</v>
+        <v>88381672</v>
       </c>
       <c r="C286" t="n">
         <v>0</v>
       </c>
       <c r="D286" t="n">
-        <v>128445286</v>
+        <v>88381672</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Lê Thị Hồng Hà</t>
+          <t>Đoàn Thị Hồng Vân</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>88381672</v>
+        <v>128445286</v>
       </c>
       <c r="C287" t="n">
         <v>0</v>
       </c>
       <c r="D287" t="n">
-        <v>88381672</v>
+        <v>128445286</v>
       </c>
     </row>
     <row r="288">
@@ -5120,33 +5120,33 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Một Thành Viên Minh Hà Gia Lai</t>
+          <t>BỆNH VIỆN ĐA KHOA TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>19212077</v>
+        <v>7916651</v>
       </c>
       <c r="C293" t="n">
         <v>0</v>
       </c>
       <c r="D293" t="n">
-        <v>19212077</v>
+        <v>7916651</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>BỆNH VIỆN ĐA KHOA TỈNH GIA LAI</t>
+          <t>Công Ty TNHH Một Thành Viên Minh Hà Gia Lai</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>7916651</v>
+        <v>19212077</v>
       </c>
       <c r="C294" t="n">
         <v>0</v>
       </c>
       <c r="D294" t="n">
-        <v>7916651</v>
+        <v>19212077</v>
       </c>
     </row>
     <row r="295">
@@ -5354,33 +5354,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BEL VIỆT NAM</t>
+          <t>Ngân hàng TMCP Ngoại thương Việt Nam</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8246551436</v>
+        <v>3200627</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8246551436</v>
+        <v>3200627</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Ngoại thương Việt Nam</t>
+          <t>CÔNG TY TNHH BEL VIỆT NAM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3200627</v>
+        <v>8246551436</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>3200627</v>
+        <v>8246551436</v>
       </c>
     </row>
     <row r="5">
@@ -5450,33 +5450,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty CLM</t>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 7 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1559501</v>
       </c>
       <c r="C9" t="n">
-        <v>2023410510</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-2023410510</v>
+        <v>1559501</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 7 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
+          <t>Vay VCB tt tiền hàng Cty CLM</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1559501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2023410510</v>
       </c>
       <c r="D10" t="n">
-        <v>1559501</v>
+        <v>-2023410510</v>
       </c>
     </row>
     <row r="11">
@@ -5498,97 +5498,97 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty Yến</t>
+          <t>CÔNG TY TNHH SẢN XUẤT - THƯƠNG MẠI VÀ DỊCH VỤ HỒNG AN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>55159335</v>
       </c>
       <c r="C12" t="n">
-        <v>10311253022</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-10311253022</v>
+        <v>55159335</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH SẢN XUẤT - THƯƠNG MẠI VÀ DỊCH VỤ HỒNG AN</t>
+          <t>Vay VCB tt tiền hàng Cty Yến</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>55159335</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>10311253022</v>
       </c>
       <c r="D13" t="n">
-        <v>55159335</v>
+        <v>-10311253022</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NABATI VIỆT NAM</t>
+          <t>Vay VCB tt tiền hàng Cty VS+NBT</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14155929868</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1047059026</v>
       </c>
       <c r="D14" t="n">
-        <v>14155929868</v>
+        <v>-1047059026</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty VS+NBT</t>
+          <t>CÔNG TY TNHH NABATI VIỆT NAM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>14155929868</v>
       </c>
       <c r="C15" t="n">
-        <v>1047059026</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-1047059026</v>
+        <v>14155929868</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Công ty Điện lực Gia Lai</t>
+          <t>Vay VCB tt tiền hàng Cty Vissan</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>957344</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2675384521</v>
       </c>
       <c r="D16" t="n">
-        <v>957344</v>
+        <v>-2675384521</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty Vissan</t>
+          <t>Công ty Điện lực Gia Lai</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>957344</v>
       </c>
       <c r="C17" t="n">
-        <v>2675384521</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-2675384521</v>
+        <v>957344</v>
       </c>
     </row>
     <row r="18">
@@ -5658,33 +5658,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Vay VCB TT tiền hàng Cty Yến</t>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>20331967</v>
       </c>
       <c r="C22" t="n">
-        <v>1896095709</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>-1896095709</v>
+        <v>20331967</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+          <t>Vay VCB TT tiền hàng Cty Yến</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>20331967</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1896095709</v>
       </c>
       <c r="D23" t="n">
-        <v>20331967</v>
+        <v>-1896095709</v>
       </c>
     </row>
     <row r="24">
@@ -5882,33 +5882,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH CHRISTIAN DIOR VIỆT NAM TẠI THÀNH PHỐ HỒ CHÍ MINH</t>
+          <t>CÔNG TY CỔ PHẦN QUỐC TẾ TAM SƠN - CHI NHÁNH HCM</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>11415000</v>
+        <v>62605000</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>11415000</v>
+        <v>62605000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN QUỐC TẾ TAM SƠN - CHI NHÁNH HCM</t>
+          <t>CHI NHÁNH CÔNG TY TNHH CHRISTIAN DIOR VIỆT NAM TẠI THÀNH PHỐ HỒ CHÍ MINH</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>62605000</v>
+        <v>11415000</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>62605000</v>
+        <v>11415000</v>
       </c>
     </row>
     <row r="38">
@@ -6426,33 +6426,33 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HÀ ĐỨC VINH</t>
+          <t>CÔNG TY CỔ PHẦN SÁCH VÀ THIẾT BỊ TRƯỜNG HỌC GIA LAI</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>5200000</v>
+        <v>800000</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>5200000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN SÁCH VÀ THIẾT BỊ TRƯỜNG HỌC GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HÀ ĐỨC VINH</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>800000</v>
+        <v>5200000</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>800000</v>
+        <v>5200000</v>
       </c>
     </row>
     <row r="72">

--- a/docs/hoang-huy-phat/sosach2023/BAO_CAO_CONG_NO_HHP_2023.xlsx
+++ b/docs/hoang-huy-phat/sosach2023/BAO_CAO_CONG_NO_HHP_2023.xlsx
@@ -480,33 +480,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NHƯ HOA TÂY NGUYÊN</t>
+          <t>Nguyễn Thị Hoa</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>149170604</v>
+        <v>303101385</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>149170604</v>
+        <v>303101385</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Hoa</t>
+          <t>CÔNG TY TNHH NHƯ HOA TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>303101385</v>
+        <v>149170604</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>303101385</v>
+        <v>149170604</v>
       </c>
     </row>
     <row r="5">
@@ -576,17 +576,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Hải Thanh</t>
+          <t>Lê Thị Thu Ba</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>99568668</v>
+        <v>120703208</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>99568668</v>
+        <v>120703208</v>
       </c>
     </row>
     <row r="10">
@@ -608,17 +608,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bùi Thị Dung</t>
+          <t>Nguyễn Thị Hải Thanh</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>195398686</v>
+        <v>99568668</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>195398686</v>
+        <v>99568668</v>
       </c>
     </row>
     <row r="12">
@@ -640,33 +640,33 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lê Thị Thu Ba</t>
+          <t>NGUYỄN THỊ KIM HƯƠNG</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>120703208</v>
+        <v>31301277</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>120703208</v>
+        <v>31301277</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ KIM HƯƠNG</t>
+          <t>Bùi Thị Dung</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31301277</v>
+        <v>195398686</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>31301277</v>
+        <v>195398686</v>
       </c>
     </row>
     <row r="15">
@@ -688,81 +688,81 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
+          <t>Đặng Thị Luyến</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>53903780</v>
+        <v>152002192</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>53903780</v>
+        <v>152002192</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cửa Hàng Nhật An</t>
+          <t>CÔNG TY ĐIỆN LỰC GIA LAI</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>53345488</v>
+        <v>4191000</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>53345488</v>
+        <v>4191000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lê Thị Chanh</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>198072703</v>
+        <v>53903780</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>198072703</v>
+        <v>53903780</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Đặng Thị Luyến</t>
+          <t>Cửa Hàng Nhật An</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>152002192</v>
+        <v>53345488</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>152002192</v>
+        <v>53345488</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CÔNG TY ĐIỆN LỰC GIA LAI</t>
+          <t>Lê Thị Chanh</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4191000</v>
+        <v>198072703</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>4191000</v>
+        <v>198072703</v>
       </c>
     </row>
     <row r="21">
@@ -800,33 +800,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI NGỌC HOA</t>
+          <t>Lê Thị Xuân</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16524465</v>
+        <v>134005420</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>16524465</v>
+        <v>134005420</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lê Thị Xuân</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI NGỌC HOA</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>134005420</v>
+        <v>16524465</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>134005420</v>
+        <v>16524465</v>
       </c>
     </row>
     <row r="25">
@@ -1088,145 +1088,145 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Huỳnh Văn Định</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẢI ANH TIẾN</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>77476395</v>
+        <v>86188966</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>77476395</v>
+        <v>86188966</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tạp Hóa Hoàng Phát</t>
+          <t>TẠP HÓA KHÁNH HÀ</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>16962352</v>
+        <v>23601721</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>16962352</v>
+        <v>23601721</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Hà Thị Thúy An</t>
+          <t>Huỳnh Văn Định</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>77418077</v>
+        <v>77476395</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>77418077</v>
+        <v>77476395</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TẠP HÓA KHÁNH HÀ</t>
+          <t>Tạp Hóa Hoàng Phát</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>23601721</v>
+        <v>16962352</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>23601721</v>
+        <v>16962352</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẢI ANH TIẾN</t>
+          <t>Hà Thị Thúy An</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>86188966</v>
+        <v>77418077</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>86188966</v>
+        <v>77418077</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TẠP HÓA THÙY LINH</t>
+          <t>VŨ TRỌNG PHƯƠNG</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>42317063</v>
+        <v>57397069</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>42317063</v>
+        <v>57397069</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>VŨ TRỌNG PHƯƠNG</t>
+          <t>TẠP HÓA THÙY LINH</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>57397069</v>
+        <v>42317063</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>57397069</v>
+        <v>42317063</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH TRẦN VĂN THỨC</t>
+          <t>TẠP PHẨM KHÁNH AN</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>77438398</v>
+        <v>2964343</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>77438398</v>
+        <v>2964343</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TẠP PHẨM KHÁNH AN</t>
+          <t>NGUYỄN THỊ THẢO</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2964343</v>
+        <v>41052529</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>2964343</v>
+        <v>41052529</v>
       </c>
     </row>
     <row r="50">
@@ -1248,17 +1248,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ THẢO</t>
+          <t>HỘ KINH DOANH TRẦN VĂN THỨC</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>41052529</v>
+        <v>77438398</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>41052529</v>
+        <v>77438398</v>
       </c>
     </row>
     <row r="52">
@@ -1280,33 +1280,33 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ THÌN</t>
+          <t>HỘ KINH DOANH TẠP HÓA NGỌC TÀI</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>27381529</v>
+        <v>80077301</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>27381529</v>
+        <v>80077301</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH TẠP HÓA NGỌC TÀI</t>
+          <t>NGUYỄN THỊ THÌN</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>80077301</v>
+        <v>27381529</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>80077301</v>
+        <v>27381529</v>
       </c>
     </row>
     <row r="55">
@@ -1536,33 +1536,33 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH PHAN THỊ ÁNH NHUNG</t>
+          <t>DOANH NGHIỆP TƯ NHÂN KEN</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>16661853</v>
+        <v>3988330</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>16661853</v>
+        <v>3988330</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN KEN</t>
+          <t>HỘ KINH DOANH PHAN THỊ ÁNH NHUNG</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3988330</v>
+        <v>16661853</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>3988330</v>
+        <v>16661853</v>
       </c>
     </row>
     <row r="71">
@@ -1584,33 +1584,33 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PHAN XUÂN TUẤN</t>
+          <t>Nguyễn Văn Vũ</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>32843778</v>
+        <v>44446971</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>32843778</v>
+        <v>44446971</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Vũ</t>
+          <t>PHAN XUÂN TUẤN</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>44446971</v>
+        <v>32843778</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>44446971</v>
+        <v>32843778</v>
       </c>
     </row>
     <row r="74">
@@ -1632,65 +1632,65 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Như Ý</t>
+          <t>CÔNG TY BẢO HIỂM BIDV BẮC TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3262813</v>
+        <v>143713599</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>3262813</v>
+        <v>143713599</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ẨM THỰC CÔ DUYÊN</t>
+          <t>Như Ý</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>18177736</v>
+        <v>3262813</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>18177736</v>
+        <v>3262813</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CÔNG TY BẢO HIỂM BIDV BẮC TÂY NGUYÊN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ẨM THỰC CÔ DUYÊN</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>143713599</v>
+        <v>18177736</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>143713599</v>
+        <v>18177736</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ĐINH VĂN CƯỜNG</t>
+          <t>PHẠM THỊ THU TRANG</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>100594786</v>
+        <v>65479968</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>100594786</v>
+        <v>65479968</v>
       </c>
     </row>
     <row r="79">
@@ -1712,49 +1712,49 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PHẠM THỊ THU TRANG</t>
+          <t>ĐINH VĂN CƯỜNG</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>65479968</v>
+        <v>100594786</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>65479968</v>
+        <v>100594786</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI GIA LAI</t>
+          <t>TẠP HÓA BỐN PHƯƠNG</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>52635998</v>
+        <v>9172417</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>52635998</v>
+        <v>9172417</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TẠP HÓA BỐN PHƯƠNG</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI GIA LAI</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>9172417</v>
+        <v>52635998</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>9172417</v>
+        <v>52635998</v>
       </c>
     </row>
     <row r="83">
@@ -2048,1217 +2048,1217 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Đàm Văn Tú</t>
+          <t>Đặng Thị Kim Liễu</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>202030757</v>
+        <v>168991911</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>202030757</v>
+        <v>168991911</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>TẠP HÓA HỒNG NHUNG</t>
+          <t>Đàm Văn Tú</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>12402720</v>
+        <v>202030757</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>12402720</v>
+        <v>202030757</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Hà Thị Ánh Thu</t>
+          <t>TẠP HÓA HỒNG NHUNG</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>31768870</v>
+        <v>12402720</v>
       </c>
       <c r="C103" t="n">
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>31768870</v>
+        <v>12402720</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Đặng Thị Kim Liễu</t>
+          <t>Lương Thị Liễu</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>168991911</v>
+        <v>112580783</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>168991911</v>
+        <v>112580783</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Lương Thị Liễu</t>
+          <t>Hà Thị Ánh Thu</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>112580783</v>
+        <v>31768870</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>112580783</v>
+        <v>31768870</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Đoàn Hữu Minh</t>
+          <t>Đậu Đức Hào</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>113495115</v>
+        <v>238603563</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>113495115</v>
+        <v>238603563</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN HỒNG BIÊN</t>
+          <t>Đinh Văn Phúc</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>5741340</v>
+        <v>106849534</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>5741340</v>
+        <v>106849534</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Đinh Văn Phúc</t>
+          <t>TRẦN KIM HUẾ</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>106849534</v>
+        <v>193931531</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>106849534</v>
+        <v>193931531</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Văn Thị Trang</t>
+          <t>DOANH NGHIỆP TƯ NHÂN HỒNG BIÊN</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>64511283</v>
+        <v>5741340</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>64511283</v>
+        <v>5741340</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Đậu Đức Hào</t>
+          <t>Đoàn Hữu Minh</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>238603563</v>
+        <v>113495115</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>238603563</v>
+        <v>113495115</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>TRẦN KIM HUẾ</t>
+          <t>Văn Thị Trang</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>193931531</v>
+        <v>64511283</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>193931531</v>
+        <v>64511283</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN NGÓI NÂU GIA LAI</t>
+          <t>Ngô Võ Đan</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>62216706</v>
+        <v>113453838</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>62216706</v>
+        <v>113453838</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Huỳnh Thị Trúc Ly</t>
+          <t>Lê Xuân Cường</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>172721649</v>
+        <v>92364509</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>172721649</v>
+        <v>92364509</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Hoàng Chí Công</t>
+          <t>Hồ Văn Thành</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>147289986</v>
+        <v>113593552</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>147289986</v>
+        <v>113593552</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Tâm</t>
+          <t>Hà Trịnh Quốc Việt</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>167005238</v>
+        <v>209257274</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>167005238</v>
+        <v>209257274</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Tứ</t>
+          <t>Dương Thị Hiếu</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>132486797</v>
+        <v>289806522</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>132486797</v>
+        <v>289806522</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Nguyễn Hữu Thành</t>
+          <t>CÔNG TY CỔ PHẦN NGÓI NÂU GIA LAI</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>260454151</v>
+        <v>62216706</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>260454151</v>
+        <v>62216706</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Lê Văn Mẫn</t>
+          <t>Nguyễn Minh Tứ</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>235395239</v>
+        <v>132486797</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>235395239</v>
+        <v>132486797</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Lê Văn Bằng</t>
+          <t>Nguyễn Minh Tú</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>132937416</v>
+        <v>169458458</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>132937416</v>
+        <v>169458458</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Tú</t>
+          <t>Nguyễn Minh Duy</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>169458458</v>
+        <v>241451470</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>169458458</v>
+        <v>241451470</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Hà Trịnh Quốc Việt</t>
+          <t>Huỳnh Thị Trúc Ly</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>209257274</v>
+        <v>172721649</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>209257274</v>
+        <v>172721649</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Hồ Văn Thành</t>
+          <t>Hoàng Chí Công</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>113593552</v>
+        <v>147289986</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>113593552</v>
+        <v>147289986</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Dương Thị Hiếu</t>
+          <t>Lê Văn Mẫn</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>289806522</v>
+        <v>235395239</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>289806522</v>
+        <v>235395239</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Ngô Võ Đan</t>
+          <t>Nguyễn Thị Tâm</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>113453838</v>
+        <v>167005238</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>113453838</v>
+        <v>167005238</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Duy</t>
+          <t>Nguyễn Hữu Thành</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>241451470</v>
+        <v>260454151</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>241451470</v>
+        <v>260454151</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Lê Xuân Cường</t>
+          <t>Lê Văn Bằng</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>92364509</v>
+        <v>132937416</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>92364509</v>
+        <v>132937416</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thu Hằng</t>
+          <t>Nguyễn Văn Dương</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>155155639</v>
+        <v>187691183</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>155155639</v>
+        <v>187691183</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>QUÁCH THỊ THÚY NGA</t>
+          <t>Nguyễn Thị Đăng Loan</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>19762931</v>
+        <v>173086396</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>19762931</v>
+        <v>173086396</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TẠP HÓA THÌN</t>
+          <t>Nguyễn Trịnh Minh Hoàng</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>9754668</v>
+        <v>209281321</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>9754668</v>
+        <v>209281321</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PHAN THỊ ÁNH LỸ</t>
+          <t>Nguyễn Thị Thu Hằng</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>18342199</v>
+        <v>155155639</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>18342199</v>
+        <v>155155639</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SUI NGỌC LAN</t>
+          <t>Mai Hoàng Thiện Châu</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>12232763</v>
+        <v>166626778</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>12232763</v>
+        <v>166626778</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Minh Tâm</t>
+          <t>Nguyễn Quốc Đạt</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>190953225</v>
+        <v>241448995</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>190953225</v>
+        <v>241448995</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Nguyễn Trường Sơn</t>
+          <t>QUÁCH THỊ THÚY NGA</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>107795444</v>
+        <v>19762931</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>107795444</v>
+        <v>19762931</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Nguyễn Hồng Ý</t>
+          <t>PHAN THỊ ÁNH LỸ</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>225945739</v>
+        <v>18342199</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>225945739</v>
+        <v>18342199</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Hiền</t>
+          <t>Nguyễn Hồng Ý</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>153063249</v>
+        <v>225945739</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>153063249</v>
+        <v>225945739</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Đăng Loan</t>
+          <t>Nguyễn Thị Hiền</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>173086396</v>
+        <v>153063249</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>173086396</v>
+        <v>153063249</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Dương</t>
+          <t>Nguyễn Thị Minh Tâm</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>187691183</v>
+        <v>190953225</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>187691183</v>
+        <v>190953225</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Mai Hoàng Thiện Châu</t>
+          <t>Nguyễn Trường Sơn</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>166626778</v>
+        <v>107795444</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>166626778</v>
+        <v>107795444</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Nguyễn Trịnh Minh Hoàng</t>
+          <t>SUI NGỌC LAN</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>209281321</v>
+        <v>12232763</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>209281321</v>
+        <v>12232763</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH VÕ VĂN NGỌ</t>
+          <t>TẠP HÓA THÌN</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>66782415</v>
+        <v>9754668</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>66782415</v>
+        <v>9754668</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>TẠP HÓA NĂM THI</t>
+          <t>HỘ KINH DOANH VÕ VĂN NGỌ</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>46344956</v>
+        <v>66782415</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>46344956</v>
+        <v>66782415</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Nguyễn Quốc Đạt</t>
+          <t>Nguyễn Nam Hồng</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>241448995</v>
+        <v>161914097</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>241448995</v>
+        <v>161914097</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Nguyễn Nam Hồng</t>
+          <t>TẠP HÓA NĂM THI</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>161914097</v>
+        <v>46344956</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>161914097</v>
+        <v>46344956</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Trần Bích Hải</t>
+          <t>Trịnh Tân</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>114345439</v>
+        <v>206613852</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>114345439</v>
+        <v>206613852</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Phạm Hồng Công</t>
+          <t>Trịnh Thị Sinh</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>130483375</v>
+        <v>152557899</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>130483375</v>
+        <v>152557899</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Phan Thanh Hoàng</t>
+          <t>Võ Chí Hà</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>116130899</v>
+        <v>112601232</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>116130899</v>
+        <v>112601232</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Trần Thị Tuyết Nhung</t>
+          <t>Nguyễn Trịnh Tố Ngân</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>132827967</v>
+        <v>130495163</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
       </c>
       <c r="D147" t="n">
-        <v>132827967</v>
+        <v>130495163</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Trần Quý Đức</t>
+          <t>TẠP HÓA BỬU HIỀN</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>169963096</v>
+        <v>61435252</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>169963096</v>
+        <v>61435252</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Vương Trường Giang</t>
+          <t>Trịnh Lê Hiệp</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>111832426</v>
+        <v>260140118</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>111832426</v>
+        <v>260140118</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Bùi Văn Lực</t>
+          <t>LÊ THỊ MỸ PHƯƠNG</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>243611717</v>
+        <v>43179190</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>243611717</v>
+        <v>43179190</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Hoàng Tú</t>
+          <t>Trần Thị Tuyết Nhung</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>199955071</v>
+        <v>132827967</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>199955071</v>
+        <v>132827967</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Võ Văn Vũ</t>
+          <t>Phạm Hồng Công</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>112039110</v>
+        <v>130483375</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>112039110</v>
+        <v>130483375</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Đỗ Trịnh Công</t>
+          <t>Phan Thanh Hoàng</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>152180951</v>
+        <v>116130899</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>152180951</v>
+        <v>116130899</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Vũ Thị Việt Hằng</t>
+          <t>Đỗ Trịnh Công</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>165336925</v>
+        <v>152180951</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>165336925</v>
+        <v>152180951</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Trịnh Lê Hiệp</t>
+          <t>Vũ Thị Việt Hằng</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>260140118</v>
+        <v>165336925</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>260140118</v>
+        <v>165336925</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Nguyễn Trịnh Tố Ngân</t>
+          <t>Võ Văn Vũ</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>130495163</v>
+        <v>112039110</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>130495163</v>
+        <v>112039110</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TẠP HÓA BỬU HIỀN</t>
+          <t>Vương Trường Giang</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>61435252</v>
+        <v>111832426</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>61435252</v>
+        <v>111832426</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>LÊ THỊ MỸ PHƯƠNG</t>
+          <t>Bùi Văn Lực</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>43179190</v>
+        <v>243611717</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>43179190</v>
+        <v>243611717</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Trịnh Tân</t>
+          <t>Hoàng Tú</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>206613852</v>
+        <v>199955071</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>206613852</v>
+        <v>199955071</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Trịnh Thị Sinh</t>
+          <t>Trần Bích Hải</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>152557899</v>
+        <v>114345439</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>152557899</v>
+        <v>114345439</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Võ Chí Hà</t>
+          <t>Trần Quý Đức</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>112601232</v>
+        <v>169963096</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>112601232</v>
+        <v>169963096</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Nguyễn Thúc Bảo</t>
+          <t>Ngô Văn Bằng</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>111954346</v>
+        <v>111936480</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>111954346</v>
+        <v>111936480</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>NGUYỄN VĂN CÔNG</t>
+          <t>Phan Thị Thùy Mỵ</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>94306512</v>
+        <v>113837653</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>94306512</v>
+        <v>113837653</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Phan Công Thiện</t>
+          <t>HUỲNH ĐỨC AN</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>112632349</v>
+        <v>54719280</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
       </c>
       <c r="D164" t="n">
-        <v>112632349</v>
+        <v>54719280</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Nguyễn Lê Hậu</t>
+          <t>Kpă Vũ Mạnh Long</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>260476999</v>
+        <v>109286964</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>260476999</v>
+        <v>109286964</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Dương Thị Thông</t>
+          <t>NGUYỄN VĂN CÔNG</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>243833248</v>
+        <v>94306512</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>243833248</v>
+        <v>94306512</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Phan Thị Thùy Mỵ</t>
+          <t>Trịnh Thị Luận</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>113837653</v>
+        <v>168619647</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>113837653</v>
+        <v>168619647</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Ngô Văn Bằng</t>
+          <t>Dương Thị Thông</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>111936480</v>
+        <v>243833248</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>111936480</v>
+        <v>243833248</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Trịnh Thị Luận</t>
+          <t>Huỳnh Thị Cúc</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>168619647</v>
+        <v>248582520</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
       </c>
       <c r="D169" t="n">
-        <v>168619647</v>
+        <v>248582520</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>HUỲNH ĐỨC AN</t>
+          <t>Nguyễn Lê Hậu</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>54719280</v>
+        <v>260476999</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
       </c>
       <c r="D170" t="n">
-        <v>54719280</v>
+        <v>260476999</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Huỳnh Thị Cúc</t>
+          <t>Phan Công Thiện</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>248582520</v>
+        <v>112632349</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>248582520</v>
+        <v>112632349</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Kpă Vũ Mạnh Long</t>
+          <t>Nguyễn Thúc Bảo</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>109286964</v>
+        <v>111954346</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>109286964</v>
+        <v>111954346</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Mai Thị Kim Loan</t>
+          <t>Ngô Đức Thuận</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>144859608</v>
+        <v>131567122</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>144859608</v>
+        <v>131567122</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Dương Nô</t>
+          <t>Nguyễn Văn Theo</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>111439059</v>
+        <v>93332200</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>111439059</v>
+        <v>93332200</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Ngô Đức Thuận</t>
+          <t>ĐINH VĂN VIÊN</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>131567122</v>
+        <v>51415511</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
       </c>
       <c r="D175" t="n">
-        <v>131567122</v>
+        <v>51415511</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ĐINH VĂN VIÊN</t>
+          <t>Đinh Biên Thùy</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>51415511</v>
+        <v>142784458</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
       </c>
       <c r="D176" t="n">
-        <v>51415511</v>
+        <v>142784458</v>
       </c>
     </row>
     <row r="177">
@@ -3280,65 +3280,65 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Đinh Thiện Ân</t>
+          <t>Dương Nô</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>114697559</v>
+        <v>111439059</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
       </c>
       <c r="D178" t="n">
-        <v>114697559</v>
+        <v>111439059</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Theo</t>
+          <t>Trịnh Lê Hưng</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>93332200</v>
+        <v>208830345</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>93332200</v>
+        <v>208830345</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Trịnh Lê Hưng</t>
+          <t>Đinh Thiện Ân</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>208830345</v>
+        <v>114697559</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>208830345</v>
+        <v>114697559</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Đinh Biên Thùy</t>
+          <t>Mai Thị Kim Loan</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>142784458</v>
+        <v>144859608</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>142784458</v>
+        <v>144859608</v>
       </c>
     </row>
     <row r="182">
@@ -3360,913 +3360,913 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Đồng Thị Thanh</t>
+          <t>Mai Văn Tân</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>75303891</v>
+        <v>149513069</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>75303891</v>
+        <v>149513069</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Lại Thị Hà</t>
+          <t>Nguyễn Thị Thanh Hương</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>91139305</v>
+        <v>292651315</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>91139305</v>
+        <v>292651315</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Phan Thị Ánh Mỹ</t>
+          <t>Lê Văn Hưng</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>240243282</v>
+        <v>95596343</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>240243282</v>
+        <v>95596343</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thanh Hương</t>
+          <t>Hà Thị Hiếu</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>292651315</v>
+        <v>94706437</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>292651315</v>
+        <v>94706437</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Hà Thị Hiếu</t>
+          <t>Đỗ Thành Vinh</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>94706437</v>
+        <v>113695752</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>94706437</v>
+        <v>113695752</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Mai Văn Tân</t>
+          <t>Phạm Thị Mỹ Hạnh</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>149513069</v>
+        <v>225080985</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>149513069</v>
+        <v>225080985</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Lê Văn Hưng</t>
+          <t>NGUYỄN THỊ TẠO</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>95596343</v>
+        <v>56632668</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>95596343</v>
+        <v>56632668</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>LÊ THỊ MỸ LOAN</t>
+          <t>CAO MẠNH HÙNG</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>69945287</v>
+        <v>93965037</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>69945287</v>
+        <v>93965037</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ TẠO</t>
+          <t>LÊ THỊ MỸ LOAN</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>56632668</v>
+        <v>69945287</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>56632668</v>
+        <v>69945287</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>CAO MẠNH HÙNG</t>
+          <t>NGUYỄN THỊ LINH GIANG</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>93965037</v>
+        <v>89714754</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>93965037</v>
+        <v>89714754</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Đỗ Thành Vinh</t>
+          <t>TRẦN TIẾN DŨNG</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>113695752</v>
+        <v>37058364</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
       </c>
       <c r="D193" t="n">
-        <v>113695752</v>
+        <v>37058364</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Phạm Thị Mỹ Hạnh</t>
+          <t>BÙI XUÂN NAM</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>225080985</v>
+        <v>93355244</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
       </c>
       <c r="D194" t="n">
-        <v>225080985</v>
+        <v>93355244</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Tạp Hóa Thùy Linh</t>
+          <t>Trần Văn Hiệu</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>72053019</v>
+        <v>58075244</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>72053019</v>
+        <v>58075244</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Đỗ Thị Hồng Nhung</t>
+          <t>PHẠM THỊ THU SA</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>222153462</v>
+        <v>72713516</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>222153462</v>
+        <v>72713516</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Trần Minh Chung</t>
+          <t>Nguyễn Văn Trung</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>55283301</v>
+        <v>34317000</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>55283301</v>
+        <v>34317000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>LƯU THỊ THUỲ</t>
+          <t>Đỗ Thị Bích Hương</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>96882946</v>
+        <v>220668611</v>
       </c>
       <c r="C198" t="n">
         <v>0</v>
       </c>
       <c r="D198" t="n">
-        <v>96882946</v>
+        <v>220668611</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Đỗ Thị Bích Hương</t>
+          <t>Nhà Thuốc Linh</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>220668611</v>
+        <v>19459440</v>
       </c>
       <c r="C199" t="n">
         <v>0</v>
       </c>
       <c r="D199" t="n">
-        <v>220668611</v>
+        <v>19459440</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Nhà Thuốc Linh</t>
+          <t>Tạp Hóa Thùy Linh</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>19459440</v>
+        <v>72053019</v>
       </c>
       <c r="C200" t="n">
         <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>19459440</v>
+        <v>72053019</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TRẦN THỊ THU HÀ</t>
+          <t>Đỗ Thị Hồng Nhung</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>55746047</v>
+        <v>222153462</v>
       </c>
       <c r="C201" t="n">
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>55746047</v>
+        <v>222153462</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>BÙI XUÂN NAM</t>
+          <t>Trần Minh Chung</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>93355244</v>
+        <v>55283301</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>93355244</v>
+        <v>55283301</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>TRẦN TIẾN DŨNG</t>
+          <t>TRẦN THỊ THU HÀ</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>37058364</v>
+        <v>55746047</v>
       </c>
       <c r="C203" t="n">
         <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>37058364</v>
+        <v>55746047</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>TRẦN THỊ THU HƯƠNG</t>
+          <t>Nguyễn Thị Thu</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>33034001</v>
+        <v>56904595</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>33034001</v>
+        <v>56904595</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>TẠP HÓA NHƯ THỦY</t>
+          <t>Lại Thị Hà</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>57550578</v>
+        <v>91139305</v>
       </c>
       <c r="C205" t="n">
         <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>57550578</v>
+        <v>91139305</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Trần Thị Thu Hồng</t>
+          <t>LƯU THỊ THUỲ</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>103684279</v>
+        <v>96882946</v>
       </c>
       <c r="C206" t="n">
         <v>0</v>
       </c>
       <c r="D206" t="n">
-        <v>103684279</v>
+        <v>96882946</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Dương Minh Ngọc</t>
+          <t>TRẦN THỊ THU HƯƠNG</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>73225572</v>
+        <v>33034001</v>
       </c>
       <c r="C207" t="n">
         <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>73225572</v>
+        <v>33034001</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ LINH GIANG</t>
+          <t>Hoàng Anh Thương</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>89714754</v>
+        <v>67529025</v>
       </c>
       <c r="C208" t="n">
         <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>89714754</v>
+        <v>67529025</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Hoàng Anh Thương</t>
+          <t>TẠP HÓA NHƯ THỦY</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>67529025</v>
+        <v>57550578</v>
       </c>
       <c r="C209" t="n">
         <v>0</v>
       </c>
       <c r="D209" t="n">
-        <v>67529025</v>
+        <v>57550578</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Trần Văn Hiệu</t>
+          <t>Phan Thị Ánh Mỹ</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>58075244</v>
+        <v>240243282</v>
       </c>
       <c r="C210" t="n">
         <v>0</v>
       </c>
       <c r="D210" t="n">
-        <v>58075244</v>
+        <v>240243282</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thu</t>
+          <t>Dương Minh Ngọc</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>56904595</v>
+        <v>73225572</v>
       </c>
       <c r="C211" t="n">
         <v>0</v>
       </c>
       <c r="D211" t="n">
-        <v>56904595</v>
+        <v>73225572</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Trung</t>
+          <t>Hộ Kinh Doanh Đồng Thị Thanh</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>34317000</v>
+        <v>75303891</v>
       </c>
       <c r="C212" t="n">
         <v>0</v>
       </c>
       <c r="D212" t="n">
-        <v>34317000</v>
+        <v>75303891</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>PHẠM THỊ THU SA</t>
+          <t>Trần Thị Thu Hồng</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>72713516</v>
+        <v>103684279</v>
       </c>
       <c r="C213" t="n">
         <v>0</v>
       </c>
       <c r="D213" t="n">
-        <v>72713516</v>
+        <v>103684279</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH ĐẶNG THỊ DIỄM</t>
+          <t>TRỊNH HOÀNG SƠN</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>75977935</v>
+        <v>147169661</v>
       </c>
       <c r="C214" t="n">
         <v>0</v>
       </c>
       <c r="D214" t="n">
-        <v>75977935</v>
+        <v>147169661</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH KHIÊN LÀNH</t>
+          <t>Lâm Ngọc Đào</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>75158369</v>
+        <v>133099188</v>
       </c>
       <c r="C215" t="n">
         <v>0</v>
       </c>
       <c r="D215" t="n">
-        <v>75158369</v>
+        <v>133099188</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Lê Tiến Hậu</t>
+          <t>Hoàng Thị Thanh Hương</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>130810220</v>
+        <v>55259900</v>
       </c>
       <c r="C216" t="n">
         <v>0</v>
       </c>
       <c r="D216" t="n">
-        <v>130810220</v>
+        <v>55259900</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Nguyễn Đức Thiên</t>
+          <t>Vũ Thị Thu Hường</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>93567284</v>
+        <v>100927438</v>
       </c>
       <c r="C217" t="n">
         <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>93567284</v>
+        <v>100927438</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Hồ Thị Thanh Hiền</t>
+          <t>Trần Thị Lan Thi</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>72565656</v>
+        <v>93448010</v>
       </c>
       <c r="C218" t="n">
         <v>0</v>
       </c>
       <c r="D218" t="n">
-        <v>72565656</v>
+        <v>93448010</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Hoàng Thị Thanh Hương</t>
+          <t>Lê Tiến Hậu</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>55259900</v>
+        <v>130810220</v>
       </c>
       <c r="C219" t="n">
         <v>0</v>
       </c>
       <c r="D219" t="n">
-        <v>55259900</v>
+        <v>130810220</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>LÂM MINH HOÀNG</t>
+          <t>Nguyễn Đức Thiên</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>75323336</v>
+        <v>93567284</v>
       </c>
       <c r="C220" t="n">
         <v>0</v>
       </c>
       <c r="D220" t="n">
-        <v>75323336</v>
+        <v>93567284</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Nương</t>
+          <t>Hộ Kinh Doanh Hồ Thị Thanh Hiền</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>37600124</v>
+        <v>72565656</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
       </c>
       <c r="D221" t="n">
-        <v>37600124</v>
+        <v>72565656</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Trịnh Lê Đông</t>
+          <t>Đặng Kim Hùng</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>208483355</v>
+        <v>72633979</v>
       </c>
       <c r="C222" t="n">
         <v>0</v>
       </c>
       <c r="D222" t="n">
-        <v>208483355</v>
+        <v>72633979</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Đặng Kim Hùng</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VIỄN THÔNG T&amp;T GIA LAI</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>72633979</v>
+        <v>5148768</v>
       </c>
       <c r="C223" t="n">
         <v>0</v>
       </c>
       <c r="D223" t="n">
-        <v>72633979</v>
+        <v>5148768</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VIỄN THÔNG T&amp;T GIA LAI</t>
+          <t>Trịnh Lê Đông</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>5148768</v>
+        <v>208483355</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>5148768</v>
+        <v>208483355</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Võ Văn Thành</t>
+          <t>Nguyễn Thị Nương</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>37061399</v>
+        <v>37600124</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>37061399</v>
+        <v>37600124</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Thới Thị Bích Hà</t>
+          <t>LÂM MINH HOÀNG</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>96073251</v>
+        <v>75323336</v>
       </c>
       <c r="C226" t="n">
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>96073251</v>
+        <v>75323336</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Trần Thị Lan Thi</t>
+          <t>Võ Văn Thành</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>93448010</v>
+        <v>37061399</v>
       </c>
       <c r="C227" t="n">
         <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>93448010</v>
+        <v>37061399</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>TRỊNH HOÀNG SƠN</t>
+          <t>HỘ KINH DOANH KHIÊN LÀNH</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>147169661</v>
+        <v>75158369</v>
       </c>
       <c r="C228" t="n">
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>147169661</v>
+        <v>75158369</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Lâm Ngọc Đào</t>
+          <t>HỘ KINH DOANH ĐẶNG THỊ DIỄM</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>133099188</v>
+        <v>75977935</v>
       </c>
       <c r="C229" t="n">
         <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>133099188</v>
+        <v>75977935</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Vũ Thị Thu Hường</t>
+          <t>Thới Thị Bích Hà</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>100927438</v>
+        <v>96073251</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>100927438</v>
+        <v>96073251</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Đàm Đình Ngữ</t>
+          <t>Nguyễn Thị Tường Vi</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>105797354</v>
+        <v>37203656</v>
       </c>
       <c r="C231" t="n">
         <v>0</v>
       </c>
       <c r="D231" t="n">
-        <v>105797354</v>
+        <v>37203656</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Tường Vi</t>
+          <t>Đàm Đình Ngữ</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>37203656</v>
+        <v>105797354</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
       </c>
       <c r="D232" t="n">
-        <v>37203656</v>
+        <v>105797354</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Phạm Văn Minh</t>
+          <t>TẠP HÓA CÚC</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>129316036</v>
+        <v>77778421</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
       </c>
       <c r="D233" t="n">
-        <v>129316036</v>
+        <v>77778421</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Trần Bích Hả</t>
+          <t>NGUYỄN THỊ KIM LIÊN</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>18502560</v>
+        <v>95603094</v>
       </c>
       <c r="C234" t="n">
         <v>0</v>
       </c>
       <c r="D234" t="n">
-        <v>18502560</v>
+        <v>95603094</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ KIM LIÊN</t>
+          <t>TẠP HÓA THÙY TRANG</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>95603094</v>
+        <v>56131277</v>
       </c>
       <c r="C235" t="n">
         <v>0</v>
       </c>
       <c r="D235" t="n">
-        <v>95603094</v>
+        <v>56131277</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>TẠP HÓA CÚC</t>
+          <t>Trần Bích Hả</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>77778421</v>
+        <v>18502560</v>
       </c>
       <c r="C236" t="n">
         <v>0</v>
       </c>
       <c r="D236" t="n">
-        <v>77778421</v>
+        <v>18502560</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>TẠP HÓA THÙY TRANG</t>
+          <t>Phạm Văn Minh</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>56131277</v>
+        <v>129316036</v>
       </c>
       <c r="C237" t="n">
         <v>0</v>
       </c>
       <c r="D237" t="n">
-        <v>56131277</v>
+        <v>129316036</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>HỒ TRỌNG DUY</t>
+          <t>PHOTOCOPY - VĂN PHÒNG PHẨM - TẠP HÓA MAI LAN</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>37879130</v>
+        <v>59869441</v>
       </c>
       <c r="C238" t="n">
         <v>0</v>
       </c>
       <c r="D238" t="n">
-        <v>37879130</v>
+        <v>59869441</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>PHOTOCOPY - VĂN PHÒNG PHẨM - TẠP HÓA MAI LAN</t>
+          <t>HỒ TRỌNG DUY</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>59869441</v>
+        <v>37879130</v>
       </c>
       <c r="C239" t="n">
         <v>0</v>
       </c>
       <c r="D239" t="n">
-        <v>59869441</v>
+        <v>37879130</v>
       </c>
     </row>
     <row r="240">
@@ -4720,33 +4720,33 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Cty TNHH MTV SXTMDV Nhật Vĩnh</t>
+          <t>Công Ty TNHH Bel Việt Nam</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>18981000</v>
+        <v>17143056</v>
       </c>
       <c r="C268" t="n">
         <v>0</v>
       </c>
       <c r="D268" t="n">
-        <v>18981000</v>
+        <v>17143056</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Bel Việt Nam</t>
+          <t>Cty TNHH MTV SXTMDV Nhật Vĩnh</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>17143056</v>
+        <v>18981000</v>
       </c>
       <c r="C269" t="n">
         <v>0</v>
       </c>
       <c r="D269" t="n">
-        <v>17143056</v>
+        <v>18981000</v>
       </c>
     </row>
     <row r="270">
@@ -4832,17 +4832,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Hồ Minh Ngân</t>
+          <t>Nguyễn Mạnh</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>71035603</v>
+        <v>114537266</v>
       </c>
       <c r="C275" t="n">
         <v>0</v>
       </c>
       <c r="D275" t="n">
-        <v>71035603</v>
+        <v>114537266</v>
       </c>
     </row>
     <row r="276">
@@ -4864,97 +4864,97 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Nguyễn Mạnh</t>
+          <t>Hồ Minh Ngân</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>114537266</v>
+        <v>71035603</v>
       </c>
       <c r="C277" t="n">
         <v>0</v>
       </c>
       <c r="D277" t="n">
-        <v>114537266</v>
+        <v>71035603</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Nguyễn Thành Phước</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN WIN FOODS GIA LAI</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>17073698</v>
+        <v>19643904</v>
       </c>
       <c r="C278" t="n">
         <v>0</v>
       </c>
       <c r="D278" t="n">
-        <v>17073698</v>
+        <v>19643904</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN WIN FOODS GIA LAI</t>
+          <t>Phan Thị Lâm</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>19643904</v>
+        <v>104212766</v>
       </c>
       <c r="C279" t="n">
         <v>0</v>
       </c>
       <c r="D279" t="n">
-        <v>19643904</v>
+        <v>104212766</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Trần Phương Thảo</t>
+          <t>Nguyễn Tấn Đức</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>146118433</v>
+        <v>53502403</v>
       </c>
       <c r="C280" t="n">
         <v>0</v>
       </c>
       <c r="D280" t="n">
-        <v>146118433</v>
+        <v>53502403</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Phan Thị Lâm</t>
+          <t>Nguyễn Thành Phước</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>104212766</v>
+        <v>17073698</v>
       </c>
       <c r="C281" t="n">
         <v>0</v>
       </c>
       <c r="D281" t="n">
-        <v>104212766</v>
+        <v>17073698</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Nguyễn Tấn Đức</t>
+          <t>Trần Phương Thảo</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>53502403</v>
+        <v>146118433</v>
       </c>
       <c r="C282" t="n">
         <v>0</v>
       </c>
       <c r="D282" t="n">
-        <v>53502403</v>
+        <v>146118433</v>
       </c>
     </row>
     <row r="283">
@@ -5008,33 +5008,33 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Lê Thị Hồng Hà</t>
+          <t>Đoàn Thị Hồng Vân</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>88381672</v>
+        <v>128445286</v>
       </c>
       <c r="C286" t="n">
         <v>0</v>
       </c>
       <c r="D286" t="n">
-        <v>88381672</v>
+        <v>128445286</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Đoàn Thị Hồng Vân</t>
+          <t>Lê Thị Hồng Hà</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>128445286</v>
+        <v>88381672</v>
       </c>
       <c r="C287" t="n">
         <v>0</v>
       </c>
       <c r="D287" t="n">
-        <v>128445286</v>
+        <v>88381672</v>
       </c>
     </row>
     <row r="288">
@@ -5120,33 +5120,33 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>BỆNH VIỆN ĐA KHOA TỈNH GIA LAI</t>
+          <t>Công Ty TNHH Một Thành Viên Minh Hà Gia Lai</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>7916651</v>
+        <v>19212077</v>
       </c>
       <c r="C293" t="n">
         <v>0</v>
       </c>
       <c r="D293" t="n">
-        <v>7916651</v>
+        <v>19212077</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Một Thành Viên Minh Hà Gia Lai</t>
+          <t>BỆNH VIỆN ĐA KHOA TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>19212077</v>
+        <v>7916651</v>
       </c>
       <c r="C294" t="n">
         <v>0</v>
       </c>
       <c r="D294" t="n">
-        <v>19212077</v>
+        <v>7916651</v>
       </c>
     </row>
     <row r="295">
@@ -5354,33 +5354,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Ngoại thương Việt Nam</t>
+          <t>CÔNG TY TNHH BEL VIỆT NAM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3200627</v>
+        <v>8246551436</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3200627</v>
+        <v>8246551436</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BEL VIỆT NAM</t>
+          <t>Ngân hàng TMCP Ngoại thương Việt Nam</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8246551436</v>
+        <v>3200627</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>8246551436</v>
+        <v>3200627</v>
       </c>
     </row>
     <row r="5">
@@ -5450,33 +5450,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 7 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
+          <t>Vay VCB tt tiền hàng Cty CLM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1559501</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2023410510</v>
       </c>
       <c r="D9" t="n">
-        <v>1559501</v>
+        <v>-2023410510</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty CLM</t>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 7 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1559501</v>
       </c>
       <c r="C10" t="n">
-        <v>2023410510</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-2023410510</v>
+        <v>1559501</v>
       </c>
     </row>
     <row r="11">
@@ -5498,97 +5498,97 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH SẢN XUẤT - THƯƠNG MẠI VÀ DỊCH VỤ HỒNG AN</t>
+          <t>Vay VCB tt tiền hàng Cty Yến</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55159335</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>10311253022</v>
       </c>
       <c r="D12" t="n">
-        <v>55159335</v>
+        <v>-10311253022</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty Yến</t>
+          <t>CÔNG TY TNHH SẢN XUẤT - THƯƠNG MẠI VÀ DỊCH VỤ HỒNG AN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>55159335</v>
       </c>
       <c r="C13" t="n">
-        <v>10311253022</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-10311253022</v>
+        <v>55159335</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty VS+NBT</t>
+          <t>CÔNG TY TNHH NABATI VIỆT NAM</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>14155929868</v>
       </c>
       <c r="C14" t="n">
-        <v>1047059026</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-1047059026</v>
+        <v>14155929868</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NABATI VIỆT NAM</t>
+          <t>Vay VCB tt tiền hàng Cty VS+NBT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14155929868</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1047059026</v>
       </c>
       <c r="D15" t="n">
-        <v>14155929868</v>
+        <v>-1047059026</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty Vissan</t>
+          <t>Công ty Điện lực Gia Lai</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>957344</v>
       </c>
       <c r="C16" t="n">
-        <v>2675384521</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>-2675384521</v>
+        <v>957344</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Công ty Điện lực Gia Lai</t>
+          <t>Vay VCB tt tiền hàng Cty Vissan</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>957344</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>2675384521</v>
       </c>
       <c r="D17" t="n">
-        <v>957344</v>
+        <v>-2675384521</v>
       </c>
     </row>
     <row r="18">
@@ -5658,33 +5658,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+          <t>Vay VCB TT tiền hàng Cty Yến</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20331967</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1896095709</v>
       </c>
       <c r="D22" t="n">
-        <v>20331967</v>
+        <v>-1896095709</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Vay VCB TT tiền hàng Cty Yến</t>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>20331967</v>
       </c>
       <c r="C23" t="n">
-        <v>1896095709</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-1896095709</v>
+        <v>20331967</v>
       </c>
     </row>
     <row r="24">
@@ -5882,33 +5882,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN QUỐC TẾ TAM SƠN - CHI NHÁNH HCM</t>
+          <t>CHI NHÁNH CÔNG TY TNHH CHRISTIAN DIOR VIỆT NAM TẠI THÀNH PHỐ HỒ CHÍ MINH</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>62605000</v>
+        <v>11415000</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>62605000</v>
+        <v>11415000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH CHRISTIAN DIOR VIỆT NAM TẠI THÀNH PHỐ HỒ CHÍ MINH</t>
+          <t>CÔNG TY CỔ PHẦN QUỐC TẾ TAM SƠN - CHI NHÁNH HCM</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>11415000</v>
+        <v>62605000</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>11415000</v>
+        <v>62605000</v>
       </c>
     </row>
     <row r="38">
@@ -6426,33 +6426,33 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN SÁCH VÀ THIẾT BỊ TRƯỜNG HỌC GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HÀ ĐỨC VINH</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>800000</v>
+        <v>5200000</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>800000</v>
+        <v>5200000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HÀ ĐỨC VINH</t>
+          <t>CÔNG TY CỔ PHẦN SÁCH VÀ THIẾT BỊ TRƯỜNG HỌC GIA LAI</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>5200000</v>
+        <v>800000</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>5200000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="72">

--- a/docs/hoang-huy-phat/sosach2023/BAO_CAO_CONG_NO_HHP_2023.xlsx
+++ b/docs/hoang-huy-phat/sosach2023/BAO_CAO_CONG_NO_HHP_2023.xlsx
@@ -464,17 +464,19 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>98424342419</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>98424342419</v>
       </c>
     </row>
     <row r="3">
@@ -672,65 +674,65 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Khánh Hà</t>
+          <t>CÔNG TY ĐIỆN LỰC GIA LAI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>174239731</v>
+        <v>4191000</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>174239731</v>
+        <v>4191000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Đặng Thị Luyến</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>152002192</v>
+        <v>53903780</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>152002192</v>
+        <v>53903780</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CÔNG TY ĐIỆN LỰC GIA LAI</t>
+          <t>Khánh Hà</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4191000</v>
+        <v>174239731</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4191000</v>
+        <v>174239731</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
+          <t>Đặng Thị Luyến</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53903780</v>
+        <v>152002192</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>53903780</v>
+        <v>152002192</v>
       </c>
     </row>
     <row r="19">
@@ -1072,49 +1074,49 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Trần Thanh Lương</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẢI ANH TIẾN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>77768432</v>
+        <v>86188966</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>77768432</v>
+        <v>86188966</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẢI ANH TIẾN</t>
+          <t>Hà Thị Thúy An</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>86188966</v>
+        <v>77418077</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>86188966</v>
+        <v>77418077</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TẠP HÓA KHÁNH HÀ</t>
+          <t>Tạp Hóa Hoàng Phát</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>23601721</v>
+        <v>16962352</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>23601721</v>
+        <v>16962352</v>
       </c>
     </row>
     <row r="43">
@@ -1136,129 +1138,129 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tạp Hóa Hoàng Phát</t>
+          <t>TẠP HÓA KHÁNH HÀ</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>16962352</v>
+        <v>23601721</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>16962352</v>
+        <v>23601721</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hà Thị Thúy An</t>
+          <t>Trần Thanh Lương</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>77418077</v>
+        <v>77768432</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>77418077</v>
+        <v>77768432</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VŨ TRỌNG PHƯƠNG</t>
+          <t>TẠP HÓA THÙY LINH</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>57397069</v>
+        <v>42317063</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>57397069</v>
+        <v>42317063</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TẠP HÓA THÙY LINH</t>
+          <t>VŨ TRỌNG PHƯƠNG</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>42317063</v>
+        <v>57397069</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>42317063</v>
+        <v>57397069</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TẠP PHẨM KHÁNH AN</t>
+          <t>HỘ KINH DOANH TRẦN VĂN THỨC</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2964343</v>
+        <v>77438398</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>2964343</v>
+        <v>77438398</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ THẢO</t>
+          <t>HỘ KINH DOAN ĐẶNG THỊ DIỄM</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>41052529</v>
+        <v>5578462</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>41052529</v>
+        <v>5578462</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HỘ KINH DOAN ĐẶNG THỊ DIỄM</t>
+          <t>NGUYỄN THỊ THẢO</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5578462</v>
+        <v>41052529</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>5578462</v>
+        <v>41052529</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH TRẦN VĂN THỨC</t>
+          <t>TẠP PHẨM KHÁNH AN</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>77438398</v>
+        <v>2964343</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>77438398</v>
+        <v>2964343</v>
       </c>
     </row>
     <row r="52">
@@ -1280,65 +1282,65 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH TẠP HÓA NGỌC TÀI</t>
+          <t>NGUYỄN THỊ THÌN</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>80077301</v>
+        <v>27381529</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>80077301</v>
+        <v>27381529</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ THÌN</t>
+          <t>HỘ KINH DOANH TẠP HÓA NGỌC TÀI</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>27381529</v>
+        <v>80077301</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>27381529</v>
+        <v>80077301</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ THANH HƯƠNG</t>
+          <t>HỘ KINH DOANH NGUYỄN THỊ BÍCH THUẬN</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>76418221</v>
+        <v>95198734</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>76418221</v>
+        <v>95198734</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ BÍCH THUẬN</t>
+          <t>HỘ KINH DOANH NGUYỄN THỊ THANH HƯƠNG</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>95198734</v>
+        <v>76418221</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>95198734</v>
+        <v>76418221</v>
       </c>
     </row>
     <row r="57">
@@ -1536,33 +1538,33 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN KEN</t>
+          <t>HỘ KINH DOANH PHAN THỊ ÁNH NHUNG</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3988330</v>
+        <v>16661853</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>3988330</v>
+        <v>16661853</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH PHAN THỊ ÁNH NHUNG</t>
+          <t>DOANH NGHIỆP TƯ NHÂN KEN</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>16661853</v>
+        <v>3988330</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>16661853</v>
+        <v>3988330</v>
       </c>
     </row>
     <row r="71">
@@ -1584,33 +1586,33 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Vũ</t>
+          <t>PHAN XUÂN TUẤN</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>44446971</v>
+        <v>32843778</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>44446971</v>
+        <v>32843778</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PHAN XUÂN TUẤN</t>
+          <t>Nguyễn Văn Vũ</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>32843778</v>
+        <v>44446971</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>32843778</v>
+        <v>44446971</v>
       </c>
     </row>
     <row r="74">
@@ -1632,65 +1634,65 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CÔNG TY BẢO HIỂM BIDV BẮC TÂY NGUYÊN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ẨM THỰC CÔ DUYÊN</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>143713599</v>
+        <v>18177736</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>143713599</v>
+        <v>18177736</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Như Ý</t>
+          <t>CÔNG TY BẢO HIỂM BIDV BẮC TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3262813</v>
+        <v>143713599</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>3262813</v>
+        <v>143713599</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ẨM THỰC CÔ DUYÊN</t>
+          <t>Như Ý</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>18177736</v>
+        <v>3262813</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>18177736</v>
+        <v>3262813</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PHẠM THỊ THU TRANG</t>
+          <t>ĐINH VĂN CƯỜNG</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>65479968</v>
+        <v>100594786</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>65479968</v>
+        <v>100594786</v>
       </c>
     </row>
     <row r="79">
@@ -1712,49 +1714,49 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ĐINH VĂN CƯỜNG</t>
+          <t>PHẠM THỊ THU TRANG</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>100594786</v>
+        <v>65479968</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>100594786</v>
+        <v>65479968</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TẠP HÓA BỐN PHƯƠNG</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI GIA LAI</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>9172417</v>
+        <v>52635998</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>9172417</v>
+        <v>52635998</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI GIA LAI</t>
+          <t>TẠP HÓA BỐN PHƯƠNG</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>52635998</v>
+        <v>9172417</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>52635998</v>
+        <v>9172417</v>
       </c>
     </row>
     <row r="83">
@@ -1984,33 +1986,33 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TM-DV HIẾU ĐỨC</t>
+          <t>HỒ VĂN CÔNG</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>15771280</v>
+        <v>70075802</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>15771280</v>
+        <v>70075802</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>HỒ VĂN CÔNG</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TM-DV HIẾU ĐỨC</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>70075802</v>
+        <v>15771280</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>70075802</v>
+        <v>15771280</v>
       </c>
     </row>
     <row r="99">
@@ -2048,33 +2050,33 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Đặng Thị Kim Liễu</t>
+          <t>Hà Thị Ánh Thu</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>168991911</v>
+        <v>31768870</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>168991911</v>
+        <v>31768870</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Đàm Văn Tú</t>
+          <t>Lương Thị Liễu</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>202030757</v>
+        <v>112580783</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>202030757</v>
+        <v>112580783</v>
       </c>
     </row>
     <row r="103">
@@ -2096,65 +2098,65 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Lương Thị Liễu</t>
+          <t>Đàm Văn Tú</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>112580783</v>
+        <v>202030757</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>112580783</v>
+        <v>202030757</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Hà Thị Ánh Thu</t>
+          <t>Đặng Thị Kim Liễu</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>31768870</v>
+        <v>168991911</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>31768870</v>
+        <v>168991911</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Đậu Đức Hào</t>
+          <t>Văn Thị Trang</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>238603563</v>
+        <v>64511283</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>238603563</v>
+        <v>64511283</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Đinh Văn Phúc</t>
+          <t>DOANH NGHIỆP TƯ NHÂN HỒNG BIÊN</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>106849534</v>
+        <v>5741340</v>
       </c>
       <c r="C107" t="n">
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>106849534</v>
+        <v>5741340</v>
       </c>
     </row>
     <row r="108">
@@ -2176,369 +2178,369 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN HỒNG BIÊN</t>
+          <t>Đoàn Hữu Minh</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>5741340</v>
+        <v>113495115</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>5741340</v>
+        <v>113495115</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Đoàn Hữu Minh</t>
+          <t>Đậu Đức Hào</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>113495115</v>
+        <v>238603563</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>113495115</v>
+        <v>238603563</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Văn Thị Trang</t>
+          <t>Đinh Văn Phúc</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>64511283</v>
+        <v>106849534</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>64511283</v>
+        <v>106849534</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ngô Võ Đan</t>
+          <t>Hà Trịnh Quốc Việt</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>113453838</v>
+        <v>209257274</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>113453838</v>
+        <v>209257274</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Lê Xuân Cường</t>
+          <t>Dương Thị Hiếu</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>92364509</v>
+        <v>289806522</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>92364509</v>
+        <v>289806522</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Hồ Văn Thành</t>
+          <t>CÔNG TY CỔ PHẦN NGÓI NÂU GIA LAI</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>113593552</v>
+        <v>62216706</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>113593552</v>
+        <v>62216706</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Hà Trịnh Quốc Việt</t>
+          <t>Hồ Văn Thành</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>209257274</v>
+        <v>113593552</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>209257274</v>
+        <v>113593552</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Dương Thị Hiếu</t>
+          <t>Nguyễn Minh Duy</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>289806522</v>
+        <v>241451470</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>289806522</v>
+        <v>241451470</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN NGÓI NÂU GIA LAI</t>
+          <t>Lê Xuân Cường</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>62216706</v>
+        <v>92364509</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>62216706</v>
+        <v>92364509</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Tứ</t>
+          <t>Huỳnh Thị Trúc Ly</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>132486797</v>
+        <v>172721649</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>132486797</v>
+        <v>172721649</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Tú</t>
+          <t>Hoàng Chí Công</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>169458458</v>
+        <v>147289986</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>169458458</v>
+        <v>147289986</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Duy</t>
+          <t>Lê Văn Mẫn</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>241451470</v>
+        <v>235395239</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>241451470</v>
+        <v>235395239</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Huỳnh Thị Trúc Ly</t>
+          <t>Lê Văn Bằng</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>172721649</v>
+        <v>132937416</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>172721649</v>
+        <v>132937416</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Hoàng Chí Công</t>
+          <t>Nguyễn Hữu Thành</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>147289986</v>
+        <v>260454151</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>147289986</v>
+        <v>260454151</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Lê Văn Mẫn</t>
+          <t>Nguyễn Thị Tâm</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>235395239</v>
+        <v>167005238</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>235395239</v>
+        <v>167005238</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Tâm</t>
+          <t>Nguyễn Minh Tứ</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>167005238</v>
+        <v>132486797</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>167005238</v>
+        <v>132486797</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Nguyễn Hữu Thành</t>
+          <t>Nguyễn Minh Tú</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>260454151</v>
+        <v>169458458</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>260454151</v>
+        <v>169458458</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Lê Văn Bằng</t>
+          <t>Ngô Võ Đan</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>132937416</v>
+        <v>113453838</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>132937416</v>
+        <v>113453838</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Dương</t>
+          <t>Nguyễn Thị Đăng Loan</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>187691183</v>
+        <v>173086396</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>187691183</v>
+        <v>173086396</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Đăng Loan</t>
+          <t>Nguyễn Thị Thu Hằng</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>173086396</v>
+        <v>155155639</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>173086396</v>
+        <v>155155639</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Nguyễn Trịnh Minh Hoàng</t>
+          <t>Mai Hoàng Thiện Châu</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>209281321</v>
+        <v>166626778</v>
       </c>
       <c r="C129" t="n">
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>209281321</v>
+        <v>166626778</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thu Hằng</t>
+          <t>Nguyễn Văn Dương</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>155155639</v>
+        <v>187691183</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>155155639</v>
+        <v>187691183</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Mai Hoàng Thiện Châu</t>
+          <t>Nguyễn Trịnh Minh Hoàng</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>166626778</v>
+        <v>209281321</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>166626778</v>
+        <v>209281321</v>
       </c>
     </row>
     <row r="132">
@@ -2560,513 +2562,513 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>QUÁCH THỊ THÚY NGA</t>
+          <t>Nguyễn Nam Hồng</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>19762931</v>
+        <v>161914097</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>19762931</v>
+        <v>161914097</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PHAN THỊ ÁNH LỸ</t>
+          <t>HỘ KINH DOANH VÕ VĂN NGỌ</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>18342199</v>
+        <v>66782415</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>18342199</v>
+        <v>66782415</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Nguyễn Hồng Ý</t>
+          <t>TẠP HÓA NĂM THI</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>225945739</v>
+        <v>46344956</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>225945739</v>
+        <v>46344956</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Hiền</t>
+          <t>TẠP HÓA THÌN</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>153063249</v>
+        <v>9754668</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>153063249</v>
+        <v>9754668</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Minh Tâm</t>
+          <t>SUI NGỌC LAN</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>190953225</v>
+        <v>12232763</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>190953225</v>
+        <v>12232763</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Nguyễn Trường Sơn</t>
+          <t>QUÁCH THỊ THÚY NGA</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>107795444</v>
+        <v>19762931</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>107795444</v>
+        <v>19762931</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SUI NGỌC LAN</t>
+          <t>PHAN THỊ ÁNH LỸ</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>12232763</v>
+        <v>18342199</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>12232763</v>
+        <v>18342199</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TẠP HÓA THÌN</t>
+          <t>Nguyễn Hồng Ý</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>9754668</v>
+        <v>225945739</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>9754668</v>
+        <v>225945739</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH VÕ VĂN NGỌ</t>
+          <t>Nguyễn Thị Hiền</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>66782415</v>
+        <v>153063249</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>66782415</v>
+        <v>153063249</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Nguyễn Nam Hồng</t>
+          <t>Nguyễn Thị Minh Tâm</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>161914097</v>
+        <v>190953225</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>161914097</v>
+        <v>190953225</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TẠP HÓA NĂM THI</t>
+          <t>Nguyễn Trường Sơn</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>46344956</v>
+        <v>107795444</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>46344956</v>
+        <v>107795444</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Trịnh Tân</t>
+          <t>Hoàng Tú</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>206613852</v>
+        <v>199955071</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>206613852</v>
+        <v>199955071</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Trịnh Thị Sinh</t>
+          <t>Trần Quý Đức</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>152557899</v>
+        <v>169963096</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>152557899</v>
+        <v>169963096</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Võ Chí Hà</t>
+          <t>Trần Bích Hải</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>112601232</v>
+        <v>114345439</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>112601232</v>
+        <v>114345439</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Nguyễn Trịnh Tố Ngân</t>
+          <t>Phạm Hồng Công</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>130495163</v>
+        <v>130483375</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
       </c>
       <c r="D147" t="n">
-        <v>130495163</v>
+        <v>130483375</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>TẠP HÓA BỬU HIỀN</t>
+          <t>Phan Thanh Hoàng</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>61435252</v>
+        <v>116130899</v>
       </c>
       <c r="C148" t="n">
         <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>61435252</v>
+        <v>116130899</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Trịnh Lê Hiệp</t>
+          <t>Đỗ Trịnh Công</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>260140118</v>
+        <v>152180951</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>260140118</v>
+        <v>152180951</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>LÊ THỊ MỸ PHƯƠNG</t>
+          <t>Vũ Thị Việt Hằng</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>43179190</v>
+        <v>165336925</v>
       </c>
       <c r="C150" t="n">
         <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>43179190</v>
+        <v>165336925</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Trần Thị Tuyết Nhung</t>
+          <t>Võ Văn Vũ</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>132827967</v>
+        <v>112039110</v>
       </c>
       <c r="C151" t="n">
         <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>132827967</v>
+        <v>112039110</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Phạm Hồng Công</t>
+          <t>Vương Trường Giang</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>130483375</v>
+        <v>111832426</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>130483375</v>
+        <v>111832426</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Phan Thanh Hoàng</t>
+          <t>Bùi Văn Lực</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>116130899</v>
+        <v>243611717</v>
       </c>
       <c r="C153" t="n">
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>116130899</v>
+        <v>243611717</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Đỗ Trịnh Công</t>
+          <t>Trần Thị Tuyết Nhung</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>152180951</v>
+        <v>132827967</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>152180951</v>
+        <v>132827967</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Vũ Thị Việt Hằng</t>
+          <t>LÊ THỊ MỸ PHƯƠNG</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>165336925</v>
+        <v>43179190</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>165336925</v>
+        <v>43179190</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Võ Văn Vũ</t>
+          <t>TẠP HÓA BỬU HIỀN</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>112039110</v>
+        <v>61435252</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>112039110</v>
+        <v>61435252</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Vương Trường Giang</t>
+          <t>Nguyễn Trịnh Tố Ngân</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>111832426</v>
+        <v>130495163</v>
       </c>
       <c r="C157" t="n">
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>111832426</v>
+        <v>130495163</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Bùi Văn Lực</t>
+          <t>Võ Chí Hà</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>243611717</v>
+        <v>112601232</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>243611717</v>
+        <v>112601232</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Hoàng Tú</t>
+          <t>Trịnh Thị Sinh</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>199955071</v>
+        <v>152557899</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>199955071</v>
+        <v>152557899</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Trần Bích Hải</t>
+          <t>Trịnh Tân</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>114345439</v>
+        <v>206613852</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>114345439</v>
+        <v>206613852</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Trần Quý Đức</t>
+          <t>Trịnh Lê Hiệp</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>169963096</v>
+        <v>260140118</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>169963096</v>
+        <v>260140118</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Ngô Văn Bằng</t>
+          <t>Nguyễn Lê Hậu</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>111936480</v>
+        <v>260476999</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>111936480</v>
+        <v>260476999</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Phan Thị Thùy Mỵ</t>
+          <t>Dương Thị Thông</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>113837653</v>
+        <v>243833248</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>113837653</v>
+        <v>243833248</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>HUỲNH ĐỨC AN</t>
+          <t>NGUYỄN VĂN CÔNG</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>54719280</v>
+        <v>94306512</v>
       </c>
       <c r="C164" t="n">
         <v>0</v>
       </c>
       <c r="D164" t="n">
-        <v>54719280</v>
+        <v>94306512</v>
       </c>
     </row>
     <row r="165">
@@ -3088,817 +3090,817 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>NGUYỄN VĂN CÔNG</t>
+          <t>Phan Công Thiện</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>94306512</v>
+        <v>112632349</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>94306512</v>
+        <v>112632349</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Trịnh Thị Luận</t>
+          <t>Nguyễn Thúc Bảo</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>168619647</v>
+        <v>111954346</v>
       </c>
       <c r="C167" t="n">
         <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>168619647</v>
+        <v>111954346</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Dương Thị Thông</t>
+          <t>Huỳnh Thị Cúc</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>243833248</v>
+        <v>248582520</v>
       </c>
       <c r="C168" t="n">
         <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>243833248</v>
+        <v>248582520</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Huỳnh Thị Cúc</t>
+          <t>Ngô Văn Bằng</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>248582520</v>
+        <v>111936480</v>
       </c>
       <c r="C169" t="n">
         <v>0</v>
       </c>
       <c r="D169" t="n">
-        <v>248582520</v>
+        <v>111936480</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Nguyễn Lê Hậu</t>
+          <t>HUỲNH ĐỨC AN</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>260476999</v>
+        <v>54719280</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
       </c>
       <c r="D170" t="n">
-        <v>260476999</v>
+        <v>54719280</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Phan Công Thiện</t>
+          <t>Phan Thị Thùy Mỵ</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>112632349</v>
+        <v>113837653</v>
       </c>
       <c r="C171" t="n">
         <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>112632349</v>
+        <v>113837653</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Nguyễn Thúc Bảo</t>
+          <t>Trịnh Thị Luận</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>111954346</v>
+        <v>168619647</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>111954346</v>
+        <v>168619647</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Ngô Đức Thuận</t>
+          <t>ĐINH VĂN VIÊN</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>131567122</v>
+        <v>51415511</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>131567122</v>
+        <v>51415511</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Theo</t>
+          <t>Ngô Đức Thuận</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>93332200</v>
+        <v>131567122</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>93332200</v>
+        <v>131567122</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ĐINH VĂN VIÊN</t>
+          <t>Mai Thị Kim Loan</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>51415511</v>
+        <v>144859608</v>
       </c>
       <c r="C175" t="n">
         <v>0</v>
       </c>
       <c r="D175" t="n">
-        <v>51415511</v>
+        <v>144859608</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Đinh Biên Thùy</t>
+          <t>Dương Nô</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>142784458</v>
+        <v>111439059</v>
       </c>
       <c r="C176" t="n">
         <v>0</v>
       </c>
       <c r="D176" t="n">
-        <v>142784458</v>
+        <v>111439059</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Trần Trung Hiếu</t>
+          <t>Nguyễn Văn Theo</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>19665288</v>
+        <v>93332200</v>
       </c>
       <c r="C177" t="n">
         <v>0</v>
       </c>
       <c r="D177" t="n">
-        <v>19665288</v>
+        <v>93332200</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Dương Nô</t>
+          <t>Trịnh Lê Hưng</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>111439059</v>
+        <v>208830345</v>
       </c>
       <c r="C178" t="n">
         <v>0</v>
       </c>
       <c r="D178" t="n">
-        <v>111439059</v>
+        <v>208830345</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Trịnh Lê Hưng</t>
+          <t>Đinh Thiện Ân</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>208830345</v>
+        <v>114697559</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>208830345</v>
+        <v>114697559</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Đinh Thiện Ân</t>
+          <t>Trần Trung Hiếu</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>114697559</v>
+        <v>19665288</v>
       </c>
       <c r="C180" t="n">
         <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>114697559</v>
+        <v>19665288</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Mai Thị Kim Loan</t>
+          <t>Đinh Biên Thùy</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>144859608</v>
+        <v>142784458</v>
       </c>
       <c r="C181" t="n">
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>144859608</v>
+        <v>142784458</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PHẠM NGUYỄN LONG THÀNH</t>
+          <t>Hộ Kinh Doanh Đồng Thị Thanh</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>40290318</v>
+        <v>75303891</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>40290318</v>
+        <v>75303891</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Mai Văn Tân</t>
+          <t>Trần Văn Hiệu</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>149513069</v>
+        <v>58075244</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>149513069</v>
+        <v>58075244</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thanh Hương</t>
+          <t>PHẠM THỊ THU SA</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>292651315</v>
+        <v>72713516</v>
       </c>
       <c r="C184" t="n">
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>292651315</v>
+        <v>72713516</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Lê Văn Hưng</t>
+          <t>Nguyễn Văn Trung</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>95596343</v>
+        <v>34317000</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>95596343</v>
+        <v>34317000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Hà Thị Hiếu</t>
+          <t>Nguyễn Thị Thu</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>94706437</v>
+        <v>56904595</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>94706437</v>
+        <v>56904595</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Đỗ Thành Vinh</t>
+          <t>Lại Thị Hà</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>113695752</v>
+        <v>91139305</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>113695752</v>
+        <v>91139305</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Phạm Thị Mỹ Hạnh</t>
+          <t>NGUYỄN THỊ TẠO</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>225080985</v>
+        <v>56632668</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>225080985</v>
+        <v>56632668</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ TẠO</t>
+          <t>Nguyễn Thị Thanh Hương</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>56632668</v>
+        <v>292651315</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>56632668</v>
+        <v>292651315</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>CAO MẠNH HÙNG</t>
+          <t>PHẠM NGUYỄN LONG THÀNH</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>93965037</v>
+        <v>40290318</v>
       </c>
       <c r="C190" t="n">
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>93965037</v>
+        <v>40290318</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>LÊ THỊ MỸ LOAN</t>
+          <t>Phan Thị Ánh Mỹ</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>69945287</v>
+        <v>240243282</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>69945287</v>
+        <v>240243282</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ LINH GIANG</t>
+          <t>TẠP HÓA NHƯ THỦY</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>89714754</v>
+        <v>57550578</v>
       </c>
       <c r="C192" t="n">
         <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>89714754</v>
+        <v>57550578</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>TRẦN TIẾN DŨNG</t>
+          <t>CAO MẠNH HÙNG</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>37058364</v>
+        <v>93965037</v>
       </c>
       <c r="C193" t="n">
         <v>0</v>
       </c>
       <c r="D193" t="n">
-        <v>37058364</v>
+        <v>93965037</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>BÙI XUÂN NAM</t>
+          <t>LÊ THỊ MỸ LOAN</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>93355244</v>
+        <v>69945287</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
       </c>
       <c r="D194" t="n">
-        <v>93355244</v>
+        <v>69945287</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Trần Văn Hiệu</t>
+          <t>Mai Văn Tân</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>58075244</v>
+        <v>149513069</v>
       </c>
       <c r="C195" t="n">
         <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>58075244</v>
+        <v>149513069</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PHẠM THỊ THU SA</t>
+          <t>Lê Văn Hưng</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>72713516</v>
+        <v>95596343</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>72713516</v>
+        <v>95596343</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Trung</t>
+          <t>Hà Thị Hiếu</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>34317000</v>
+        <v>94706437</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>34317000</v>
+        <v>94706437</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Đỗ Thị Bích Hương</t>
+          <t>Đỗ Thành Vinh</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>220668611</v>
+        <v>113695752</v>
       </c>
       <c r="C198" t="n">
         <v>0</v>
       </c>
       <c r="D198" t="n">
-        <v>220668611</v>
+        <v>113695752</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Nhà Thuốc Linh</t>
+          <t>Phạm Thị Mỹ Hạnh</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>19459440</v>
+        <v>225080985</v>
       </c>
       <c r="C199" t="n">
         <v>0</v>
       </c>
       <c r="D199" t="n">
-        <v>19459440</v>
+        <v>225080985</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Tạp Hóa Thùy Linh</t>
+          <t>TRẦN THỊ THU HƯƠNG</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>72053019</v>
+        <v>33034001</v>
       </c>
       <c r="C200" t="n">
         <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>72053019</v>
+        <v>33034001</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Đỗ Thị Hồng Nhung</t>
+          <t>Nhà Thuốc Linh</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>222153462</v>
+        <v>19459440</v>
       </c>
       <c r="C201" t="n">
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>222153462</v>
+        <v>19459440</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Trần Minh Chung</t>
+          <t>Tạp Hóa Thùy Linh</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>55283301</v>
+        <v>72053019</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>55283301</v>
+        <v>72053019</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>TRẦN THỊ THU HÀ</t>
+          <t>Đỗ Thị Hồng Nhung</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>55746047</v>
+        <v>222153462</v>
       </c>
       <c r="C203" t="n">
         <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>55746047</v>
+        <v>222153462</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thu</t>
+          <t>Trần Minh Chung</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>56904595</v>
+        <v>55283301</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>56904595</v>
+        <v>55283301</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Lại Thị Hà</t>
+          <t>TRẦN THỊ THU HÀ</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>91139305</v>
+        <v>55746047</v>
       </c>
       <c r="C205" t="n">
         <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>91139305</v>
+        <v>55746047</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>LƯU THỊ THUỲ</t>
+          <t>TRẦN TIẾN DŨNG</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>96882946</v>
+        <v>37058364</v>
       </c>
       <c r="C206" t="n">
         <v>0</v>
       </c>
       <c r="D206" t="n">
-        <v>96882946</v>
+        <v>37058364</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TRẦN THỊ THU HƯƠNG</t>
+          <t>BÙI XUÂN NAM</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>33034001</v>
+        <v>93355244</v>
       </c>
       <c r="C207" t="n">
         <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>33034001</v>
+        <v>93355244</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Hoàng Anh Thương</t>
+          <t>NGUYỄN THỊ LINH GIANG</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>67529025</v>
+        <v>89714754</v>
       </c>
       <c r="C208" t="n">
         <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>67529025</v>
+        <v>89714754</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>TẠP HÓA NHƯ THỦY</t>
+          <t>Hoàng Anh Thương</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>57550578</v>
+        <v>67529025</v>
       </c>
       <c r="C209" t="n">
         <v>0</v>
       </c>
       <c r="D209" t="n">
-        <v>57550578</v>
+        <v>67529025</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Phan Thị Ánh Mỹ</t>
+          <t>Dương Minh Ngọc</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>240243282</v>
+        <v>73225572</v>
       </c>
       <c r="C210" t="n">
         <v>0</v>
       </c>
       <c r="D210" t="n">
-        <v>240243282</v>
+        <v>73225572</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Dương Minh Ngọc</t>
+          <t>Trần Thị Thu Hồng</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>73225572</v>
+        <v>103684279</v>
       </c>
       <c r="C211" t="n">
         <v>0</v>
       </c>
       <c r="D211" t="n">
-        <v>73225572</v>
+        <v>103684279</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Đồng Thị Thanh</t>
+          <t>LƯU THỊ THUỲ</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>75303891</v>
+        <v>96882946</v>
       </c>
       <c r="C212" t="n">
         <v>0</v>
       </c>
       <c r="D212" t="n">
-        <v>75303891</v>
+        <v>96882946</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Trần Thị Thu Hồng</t>
+          <t>Đỗ Thị Bích Hương</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>103684279</v>
+        <v>220668611</v>
       </c>
       <c r="C213" t="n">
         <v>0</v>
       </c>
       <c r="D213" t="n">
-        <v>103684279</v>
+        <v>220668611</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TRỊNH HOÀNG SƠN</t>
+          <t>Nguyễn Đức Thiên</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>147169661</v>
+        <v>93567284</v>
       </c>
       <c r="C214" t="n">
         <v>0</v>
       </c>
       <c r="D214" t="n">
-        <v>147169661</v>
+        <v>93567284</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Lâm Ngọc Đào</t>
+          <t>Trần Thị Lan Thi</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>133099188</v>
+        <v>93448010</v>
       </c>
       <c r="C215" t="n">
         <v>0</v>
       </c>
       <c r="D215" t="n">
-        <v>133099188</v>
+        <v>93448010</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Hoàng Thị Thanh Hương</t>
+          <t>Lê Tiến Hậu</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>55259900</v>
+        <v>130810220</v>
       </c>
       <c r="C216" t="n">
         <v>0</v>
       </c>
       <c r="D216" t="n">
-        <v>55259900</v>
+        <v>130810220</v>
       </c>
     </row>
     <row r="217">
@@ -3920,81 +3922,81 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Trần Thị Lan Thi</t>
+          <t>Hộ Kinh Doanh Hồ Thị Thanh Hiền</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>93448010</v>
+        <v>72565656</v>
       </c>
       <c r="C218" t="n">
         <v>0</v>
       </c>
       <c r="D218" t="n">
-        <v>93448010</v>
+        <v>72565656</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Lê Tiến Hậu</t>
+          <t>Đàm Đình Ngữ</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>130810220</v>
+        <v>105797354</v>
       </c>
       <c r="C219" t="n">
         <v>0</v>
       </c>
       <c r="D219" t="n">
-        <v>130810220</v>
+        <v>105797354</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Nguyễn Đức Thiên</t>
+          <t>Thới Thị Bích Hà</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>93567284</v>
+        <v>96073251</v>
       </c>
       <c r="C220" t="n">
         <v>0</v>
       </c>
       <c r="D220" t="n">
-        <v>93567284</v>
+        <v>96073251</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Hồ Thị Thanh Hiền</t>
+          <t>Võ Văn Thành</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>72565656</v>
+        <v>37061399</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
       </c>
       <c r="D221" t="n">
-        <v>72565656</v>
+        <v>37061399</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Đặng Kim Hùng</t>
+          <t>Trịnh Lê Đông</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>72633979</v>
+        <v>208483355</v>
       </c>
       <c r="C222" t="n">
         <v>0</v>
       </c>
       <c r="D222" t="n">
-        <v>72633979</v>
+        <v>208483355</v>
       </c>
     </row>
     <row r="223">
@@ -4016,177 +4018,177 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Trịnh Lê Đông</t>
+          <t>Đặng Kim Hùng</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>208483355</v>
+        <v>72633979</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>208483355</v>
+        <v>72633979</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Nương</t>
+          <t>Nguyễn Thị Tường Vi</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>37600124</v>
+        <v>37203656</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>37600124</v>
+        <v>37203656</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>LÂM MINH HOÀNG</t>
+          <t>TRỊNH HOÀNG SƠN</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>75323336</v>
+        <v>147169661</v>
       </c>
       <c r="C226" t="n">
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>75323336</v>
+        <v>147169661</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Võ Văn Thành</t>
+          <t>Lâm Ngọc Đào</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>37061399</v>
+        <v>133099188</v>
       </c>
       <c r="C227" t="n">
         <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>37061399</v>
+        <v>133099188</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH KHIÊN LÀNH</t>
+          <t>HỘ KINH DOANH ĐẶNG THỊ DIỄM</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>75158369</v>
+        <v>75977935</v>
       </c>
       <c r="C228" t="n">
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>75158369</v>
+        <v>75977935</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH ĐẶNG THỊ DIỄM</t>
+          <t>Hoàng Thị Thanh Hương</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>75977935</v>
+        <v>55259900</v>
       </c>
       <c r="C229" t="n">
         <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>75977935</v>
+        <v>55259900</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Thới Thị Bích Hà</t>
+          <t>HỘ KINH DOANH KHIÊN LÀNH</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>96073251</v>
+        <v>75158369</v>
       </c>
       <c r="C230" t="n">
         <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>96073251</v>
+        <v>75158369</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Tường Vi</t>
+          <t>LÂM MINH HOÀNG</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>37203656</v>
+        <v>75323336</v>
       </c>
       <c r="C231" t="n">
         <v>0</v>
       </c>
       <c r="D231" t="n">
-        <v>37203656</v>
+        <v>75323336</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Đàm Đình Ngữ</t>
+          <t>Nguyễn Thị Nương</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>105797354</v>
+        <v>37600124</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
       </c>
       <c r="D232" t="n">
-        <v>105797354</v>
+        <v>37600124</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>TẠP HÓA CÚC</t>
+          <t>NGUYỄN THỊ KIM LIÊN</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>77778421</v>
+        <v>95603094</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
       </c>
       <c r="D233" t="n">
-        <v>77778421</v>
+        <v>95603094</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ KIM LIÊN</t>
+          <t>Trần Bích Hả</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>95603094</v>
+        <v>18502560</v>
       </c>
       <c r="C234" t="n">
         <v>0</v>
       </c>
       <c r="D234" t="n">
-        <v>95603094</v>
+        <v>18502560</v>
       </c>
     </row>
     <row r="235">
@@ -4208,33 +4210,33 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Trần Bích Hả</t>
+          <t>Phạm Văn Minh</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>18502560</v>
+        <v>129316036</v>
       </c>
       <c r="C236" t="n">
         <v>0</v>
       </c>
       <c r="D236" t="n">
-        <v>18502560</v>
+        <v>129316036</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Phạm Văn Minh</t>
+          <t>TẠP HÓA CÚC</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>129316036</v>
+        <v>77778421</v>
       </c>
       <c r="C237" t="n">
         <v>0</v>
       </c>
       <c r="D237" t="n">
-        <v>129316036</v>
+        <v>77778421</v>
       </c>
     </row>
     <row r="238">
@@ -4304,33 +4306,33 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Kim Tuyến</t>
+          <t>Sui Ngọc Lan</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>56971830</v>
+        <v>17926173</v>
       </c>
       <c r="C242" t="n">
         <v>0</v>
       </c>
       <c r="D242" t="n">
-        <v>56971830</v>
+        <v>17926173</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Sui Ngọc Lan</t>
+          <t>Nguyễn Thị Kim Tuyến</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>17926173</v>
+        <v>56971830</v>
       </c>
       <c r="C243" t="n">
         <v>0</v>
       </c>
       <c r="D243" t="n">
-        <v>17926173</v>
+        <v>56971830</v>
       </c>
     </row>
     <row r="244">
@@ -4512,33 +4514,33 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh An Bình</t>
+          <t>Bách Hóa Tổng Hợp Tư Tạo</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>37425850</v>
+        <v>18031613</v>
       </c>
       <c r="C255" t="n">
         <v>0</v>
       </c>
       <c r="D255" t="n">
-        <v>37425850</v>
+        <v>18031613</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Bách Hóa Tổng Hợp Tư Tạo</t>
+          <t>Hộ Kinh Doanh An Bình</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>18031613</v>
+        <v>37425850</v>
       </c>
       <c r="C256" t="n">
         <v>0</v>
       </c>
       <c r="D256" t="n">
-        <v>18031613</v>
+        <v>37425850</v>
       </c>
     </row>
     <row r="257">
@@ -5338,65 +5340,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV XĂNG DẦU BẮC TÂY NGUYÊN</t>
+          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>828943543</v>
+        <v>21791855</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>828943543</v>
+        <v>21791855</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BEL VIỆT NAM</t>
+          <t>CÔNG TY TNHH MTV XĂNG DẦU BẮC TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8246551436</v>
+        <v>830567693</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8246551436</v>
+        <v>830567693</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Ngoại thương Việt Nam</t>
+          <t>CÔNG TY TNHH BEL VIỆT NAM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3200627</v>
+        <v>8246551436</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>3200627</v>
+        <v>8246551436</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN VIỆT NAM KỸ NGHỆ SÚC SẢN</t>
+          <t>Ngân hàng TMCP Ngoại thương Việt Nam</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24575429136</v>
+        <v>3200627</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>24575429136</v>
+        <v>3200627</v>
       </c>
     </row>
     <row r="6">
@@ -5434,33 +5436,33 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Gia Lai </t>
+          <t>CÔNG TY CỔ PHẦN VIỆT NAM KỸ NGHỆ SÚC SẢN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1907972846</v>
+        <v>24575429136</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1907972846</v>
+        <v>24575429136</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty CLM</t>
+          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Gia Lai </t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1907972846</v>
       </c>
       <c r="C9" t="n">
-        <v>2023410510</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-2023410510</v>
+        <v>1907972846</v>
       </c>
     </row>
     <row r="10">
@@ -5482,33 +5484,33 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN CẤP THOÁT NƯỚC GIA LAI</t>
+          <t>Vay VCB tt tiền hàng Cty CLM</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>241533</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2023410510</v>
       </c>
       <c r="D11" t="n">
-        <v>241533</v>
+        <v>-2023410510</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty Yến</t>
+          <t>CÔNG TY CỔ PHẦN CẤP THOÁT NƯỚC GIA LAI</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>241533</v>
       </c>
       <c r="C12" t="n">
-        <v>10311253022</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-10311253022</v>
+        <v>241533</v>
       </c>
     </row>
     <row r="13">
@@ -5530,113 +5532,113 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NABATI VIỆT NAM</t>
+          <t>Vay VCB tt tiền hàng Cty Yến</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14155929868</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>10311253022</v>
       </c>
       <c r="D14" t="n">
-        <v>14155929868</v>
+        <v>-10311253022</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty VS+NBT</t>
+          <t>CÔNG TY TNHH NABATI VIỆT NAM</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>14155929868</v>
       </c>
       <c r="C15" t="n">
-        <v>1047059026</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-1047059026</v>
+        <v>14155929868</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Công ty Điện lực Gia Lai</t>
+          <t>Vay VCB tt tiền hàng Cty VS+NBT</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>957344</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1047059026</v>
       </c>
       <c r="D16" t="n">
-        <v>957344</v>
+        <v>-1047059026</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty Vissan</t>
+          <t>Công ty Điện lực Gia Lai</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>957344</v>
       </c>
       <c r="C17" t="n">
-        <v>2675384521</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-2675384521</v>
+        <v>957344</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN TRƯỜNG XUÂN</t>
+          <t>Vay VCB tt tiền hàng Cty Vissan</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12097000</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2675384521</v>
       </c>
       <c r="D18" t="n">
-        <v>12097000</v>
+        <v>-2675384521</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Gia Lai</t>
+          <t>CÔNG TY CỔ PHẦN TRƯỜNG XUÂN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1175020</v>
+        <v>12097000</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1175020</v>
+        <v>12097000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NGAN HANG TMCP CONG THUONG VIET NAM - CN GIA LAI</t>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Gia Lai</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>111352677</v>
+        <v>1175020</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>111352677</v>
+        <v>1175020</v>
       </c>
     </row>
     <row r="21">
@@ -5658,33 +5660,33 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Vay VCB TT tiền hàng Cty Yến</t>
+          <t>NGAN HANG TMCP CONG THUONG VIET NAM - CN GIA LAI</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>111352677</v>
       </c>
       <c r="C22" t="n">
-        <v>1896095709</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>-1896095709</v>
+        <v>111352677</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+          <t>Vay VCB TT tiền hàng Cty Yến</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>20331967</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1896095709</v>
       </c>
       <c r="D23" t="n">
-        <v>20331967</v>
+        <v>-1896095709</v>
       </c>
     </row>
     <row r="24">
@@ -6234,33 +6236,33 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV Ô TÔ GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN THỜI TRANG VÀ MỸ PHẨM DUY ANH</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1817430</v>
+        <v>35230000</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>1817430</v>
+        <v>35230000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THỜI TRANG VÀ MỸ PHẨM DUY ANH</t>
+          <t>CÔNG TY TNHH MTV Ô TÔ GIA LAI</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>35230000</v>
+        <v>1817430</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>35230000</v>
+        <v>1817430</v>
       </c>
     </row>
     <row r="60">
@@ -6426,33 +6428,33 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HÀ ĐỨC VINH</t>
+          <t>CÔNG TY CỔ PHẦN SÁCH VÀ THIẾT BỊ TRƯỜNG HỌC GIA LAI</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>5200000</v>
+        <v>800000</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>5200000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN SÁCH VÀ THIẾT BỊ TRƯỜNG HỌC GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HÀ ĐỨC VINH</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>800000</v>
+        <v>5200000</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>800000</v>
+        <v>5200000</v>
       </c>
     </row>
     <row r="72">
@@ -6478,13 +6480,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>8963000</v>
+        <v>8847000</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>8963000</v>
+        <v>8847000</v>
       </c>
     </row>
     <row r="74">

--- a/docs/hoang-huy-phat/sosach2023/BAO_CAO_CONG_NO_HHP_2023.xlsx
+++ b/docs/hoang-huy-phat/sosach2023/BAO_CAO_CONG_NO_HHP_2023.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KHACH_HANG_131" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NHA_CUNG_CAP_331" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="131 - Phải thu" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="331 - Phải trả" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,115 +432,134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D303"/>
+  <dimension ref="A1:E304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Đối tượng</t>
+          <t>Khách hàng</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>BÁN RA</t>
+          <t>Số dư đầu</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ĐÃ THU</t>
+          <t>Phát sinh Nợ (Bán)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DƯ CUỐI KỲ</t>
+          <t>Phát sinh Có (Thu)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Dư cuối</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Khách lẻ</t>
-        </is>
+      <c r="A2" t="n">
+        <v/>
       </c>
       <c r="B2" t="n">
-        <v>98424342419</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>98424342419</v>
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Hoa</t>
+          <t>CÔNG TY TNHH NHƯ HOA TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>303101385</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>149170604</v>
       </c>
       <c r="D3" t="n">
-        <v>303101385</v>
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>149170604</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NHƯ HOA TÂY NGUYÊN</t>
+          <t>Nguyễn Thị Hoa</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>149170604</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>303101385</v>
       </c>
       <c r="D4" t="n">
-        <v>149170604</v>
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>303101385</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN VĨNH HIỆP</t>
+          <t>sao kê Bidv 23.xls</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>489599374</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>489599374</v>
+        <v>3428218174</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-3428218174</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PHAN THỊ PHƯƠNG DUNG</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN VĨNH HIỆP</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>108771796</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>489599374</v>
       </c>
       <c r="D6" t="n">
-        <v>108771796</v>
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>489599374</v>
       </c>
     </row>
     <row r="7">
@@ -550,45 +569,54 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
         <v>118727461</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
       <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>118727461</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ LINH GIANG</t>
+          <t>PHAN THỊ PHƯƠNG DUNG</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>607200</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>108771796</v>
       </c>
       <c r="D8" t="n">
-        <v>607200</v>
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>108771796</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lê Thị Thu Ba</t>
+          <t>HỘ KINH DOANH NGUYỄN THỊ LINH GIANG</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>120703208</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>607200</v>
       </c>
       <c r="D9" t="n">
-        <v>120703208</v>
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>607200</v>
       </c>
     </row>
     <row r="10">
@@ -598,45 +626,54 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
         <v>73850617</v>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>73850617</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Hải Thanh</t>
+          <t>Lê Thị Thu Ba</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>99568668</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>120703208</v>
       </c>
       <c r="D11" t="n">
-        <v>99568668</v>
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>120703208</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NHÀ SÁCH VẠN TRÍ</t>
+          <t>Nguyễn Thị Hải Thanh</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2548744</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>99568668</v>
       </c>
       <c r="D12" t="n">
-        <v>2548744</v>
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>99568668</v>
       </c>
     </row>
     <row r="13">
@@ -646,541 +683,643 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
         <v>31301277</v>
       </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
       <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
         <v>31301277</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bùi Thị Dung</t>
+          <t>NHÀ SÁCH VẠN TRÍ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>195398686</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2548744</v>
       </c>
       <c r="D14" t="n">
-        <v>195398686</v>
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2548744</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CÔNG TY ĐIỆN LỰC GIA LAI</t>
+          <t>Bùi Thị Dung</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4191000</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>195398686</v>
       </c>
       <c r="D15" t="n">
-        <v>4191000</v>
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>195398686</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
+          <t>Khánh Hà</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>53903780</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>174239731</v>
       </c>
       <c r="D16" t="n">
-        <v>53903780</v>
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>174239731</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Khánh Hà</t>
+          <t>Đặng Thị Luyến</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>174239731</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>152002192</v>
       </c>
       <c r="D17" t="n">
-        <v>174239731</v>
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>152002192</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Đặng Thị Luyến</t>
+          <t>CÔNG TY ĐIỆN LỰC GIA LAI</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>152002192</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>4191000</v>
       </c>
       <c r="D18" t="n">
-        <v>152002192</v>
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4191000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cửa Hàng Nhật An</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>53345488</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>53903780</v>
       </c>
       <c r="D19" t="n">
-        <v>53345488</v>
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>53903780</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lê Thị Chanh</t>
+          <t>Cửa Hàng Nhật An</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>198072703</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>53345488</v>
       </c>
       <c r="D20" t="n">
-        <v>198072703</v>
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>53345488</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Trần Thị Anh Thư</t>
+          <t>Lê Thị Chanh</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>66979186</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>198072703</v>
       </c>
       <c r="D21" t="n">
-        <v>66979186</v>
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>198072703</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HTV MẠNH PHƯƠNG F&amp;B</t>
+          <t>Trần Thị Anh Thư</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1856854</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>66979186</v>
       </c>
       <c r="D22" t="n">
-        <v>1856854</v>
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>66979186</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lê Thị Xuân</t>
+          <t>CÔNG TY TNHH HTV MẠNH PHƯƠNG F&amp;B</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>134005420</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1856854</v>
       </c>
       <c r="D23" t="n">
-        <v>134005420</v>
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1856854</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI NGỌC HOA</t>
+          <t>Lê Thị Xuân</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16524465</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>134005420</v>
       </c>
       <c r="D24" t="n">
-        <v>16524465</v>
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>134005420</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CHI NHÁNH KHÁCH SẠN HOÀNG ANH GIA LAI</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI NGỌC HOA</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>69046765</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>16524465</v>
       </c>
       <c r="D25" t="n">
-        <v>69046765</v>
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>16524465</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Phạm Văn Hùng</t>
+          <t>CHI NHÁNH KHÁCH SẠN HOÀNG ANH GIA LAI</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>114535770</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>69046765</v>
       </c>
       <c r="D26" t="n">
-        <v>114535770</v>
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>69046765</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tống Thị Lan</t>
+          <t>Phạm Văn Hùng</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>75661056</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>114535770</v>
       </c>
       <c r="D27" t="n">
-        <v>75661056</v>
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>114535770</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mai Thị Thủy</t>
+          <t>Tống Thị Lan</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>92676236</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>75661056</v>
       </c>
       <c r="D28" t="n">
-        <v>92676236</v>
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>75661056</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VŨ THỊ THƯƠNG</t>
+          <t>Mai Thị Thủy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>73757627</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>92676236</v>
       </c>
       <c r="D29" t="n">
-        <v>73757627</v>
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>92676236</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HUỲNH THỊ VÂN</t>
+          <t>VŨ THỊ THƯƠNG</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>134522211</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>73757627</v>
       </c>
       <c r="D30" t="n">
-        <v>134522211</v>
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>73757627</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TRẦN THANH THUỶ</t>
+          <t>HUỲNH THỊ VÂN</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>238275640</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>134522211</v>
       </c>
       <c r="D31" t="n">
-        <v>238275640</v>
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>134522211</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TRẦN THANH HẢI</t>
+          <t>TRẦN THANH THUỶ</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>95699723</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>238275640</v>
       </c>
       <c r="D32" t="n">
-        <v>95699723</v>
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>238275640</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN DAILYMART</t>
+          <t>TRẦN THANH HẢI</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>68022735</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>95699723</v>
       </c>
       <c r="D33" t="n">
-        <v>68022735</v>
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>95699723</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TIẾN THỊNH GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN DAILYMART</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>24239063</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>68022735</v>
       </c>
       <c r="D34" t="n">
-        <v>24239063</v>
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>68022735</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CỬA HÀNG HỒNG NHUNG</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TIẾN THỊNH GIA LAI</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>57654872</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>24239063</v>
       </c>
       <c r="D35" t="n">
-        <v>57654872</v>
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>24239063</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN LÊ CANG ÂN</t>
+          <t>CỬA HÀNG HỒNG NHUNG</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>14815563</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>57654872</v>
       </c>
       <c r="D36" t="n">
-        <v>14815563</v>
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>57654872</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN NGUYỄN HIỆU GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN LÊ CANG ÂN</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>61130160</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>14815563</v>
       </c>
       <c r="D37" t="n">
-        <v>61130160</v>
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>14815563</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THỰC PHẨM CHOLIMEX</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN NGUYỄN HIỆU GIA LAI</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>776377752</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>61130160</v>
       </c>
       <c r="D38" t="n">
-        <v>776377752</v>
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>61130160</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BEL VIỆT NAM</t>
+          <t>CÔNG TY CỔ PHẦN THỰC PHẨM CHOLIMEX</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>162557801</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>776377752</v>
       </c>
       <c r="D39" t="n">
-        <v>162557801</v>
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>776377752</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẢI ANH TIẾN</t>
+          <t>CÔNG TY TNHH BEL VIỆT NAM</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>86188966</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>162557801</v>
       </c>
       <c r="D40" t="n">
-        <v>86188966</v>
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>162557801</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Hà Thị Thúy An</t>
+          <t>Tạp Hóa Hoàng Phát</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>77418077</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>16962352</v>
       </c>
       <c r="D41" t="n">
-        <v>77418077</v>
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>16962352</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tạp Hóa Hoàng Phát</t>
+          <t>Hà Thị Thúy An</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>16962352</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>77418077</v>
       </c>
       <c r="D42" t="n">
-        <v>16962352</v>
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>77418077</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Huỳnh Văn Định</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẢI ANH TIẾN</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>77476395</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>86188966</v>
       </c>
       <c r="D43" t="n">
-        <v>77476395</v>
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>86188966</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TẠP HÓA KHÁNH HÀ</t>
+          <t>Huỳnh Văn Định</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>23601721</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>77476395</v>
       </c>
       <c r="D44" t="n">
-        <v>23601721</v>
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>77476395</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Trần Thanh Lương</t>
+          <t>TẠP HÓA KHÁNH HÀ</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>77768432</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>23601721</v>
       </c>
       <c r="D45" t="n">
-        <v>77768432</v>
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>23601721</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TẠP HÓA THÙY LINH</t>
+          <t>Trần Thanh Lương</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>42317063</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>77768432</v>
       </c>
       <c r="D46" t="n">
-        <v>42317063</v>
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>77768432</v>
       </c>
     </row>
     <row r="47">
@@ -1190,29 +1329,35 @@
         </is>
       </c>
       <c r="B47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" t="n">
         <v>57397069</v>
       </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
       <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
         <v>57397069</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH TRẦN VĂN THỨC</t>
+          <t>TẠP HÓA THÙY LINH</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>77438398</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>42317063</v>
       </c>
       <c r="D48" t="n">
-        <v>77438398</v>
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>42317063</v>
       </c>
     </row>
     <row r="49">
@@ -1222,29 +1367,35 @@
         </is>
       </c>
       <c r="B49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" t="n">
         <v>5578462</v>
       </c>
-      <c r="C49" t="n">
-        <v>0</v>
-      </c>
       <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
         <v>5578462</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ THẢO</t>
+          <t>HỘ KINH DOANH TRẦN VĂN THỨC</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>41052529</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>77438398</v>
       </c>
       <c r="D50" t="n">
-        <v>41052529</v>
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>77438398</v>
       </c>
     </row>
     <row r="51">
@@ -1254,61 +1405,73 @@
         </is>
       </c>
       <c r="B51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" t="n">
         <v>2964343</v>
       </c>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
       <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
         <v>2964343</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Lê Thị Tuyết Anh</t>
+          <t>NGUYỄN THỊ THẢO</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>75481879</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>41052529</v>
       </c>
       <c r="D52" t="n">
-        <v>75481879</v>
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>41052529</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ THÌN</t>
+          <t>Lê Thị Tuyết Anh</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>27381529</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>75481879</v>
       </c>
       <c r="D53" t="n">
-        <v>27381529</v>
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>75481879</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH TẠP HÓA NGỌC TÀI</t>
+          <t>HỘ KINH DOANH NGUYỄN THỊ THANH HƯƠNG</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>80077301</v>
+        <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>76418221</v>
       </c>
       <c r="D54" t="n">
-        <v>80077301</v>
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>76418221</v>
       </c>
     </row>
     <row r="55">
@@ -1318,45 +1481,54 @@
         </is>
       </c>
       <c r="B55" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" t="n">
         <v>95198734</v>
       </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
       <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
         <v>95198734</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ THANH HƯƠNG</t>
+          <t>HỘ KINH DOANH TẠP HÓA NGỌC TÀI</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>76418221</v>
+        <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>80077301</v>
       </c>
       <c r="D56" t="n">
-        <v>76418221</v>
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>80077301</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cửa Hàng Mua Bán Tạp Hóa Và Dụng Cụ Gia Đình Ngọc Hân</t>
+          <t>NGUYỄN THỊ THÌN</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>118850900</v>
+        <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>27381529</v>
       </c>
       <c r="D57" t="n">
-        <v>118850900</v>
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>27381529</v>
       </c>
     </row>
     <row r="58">
@@ -1366,701 +1538,833 @@
         </is>
       </c>
       <c r="B58" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" t="n">
         <v>57136188</v>
       </c>
-      <c r="C58" t="n">
-        <v>0</v>
-      </c>
       <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
         <v>57136188</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN MINH PHƯƠNG</t>
+          <t>Cửa Hàng Mua Bán Tạp Hóa Và Dụng Cụ Gia Đình Ngọc Hân</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>93016476</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>118850900</v>
       </c>
       <c r="D59" t="n">
-        <v>93016476</v>
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>118850900</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ĐẶNG THỊ THỦY</t>
+          <t>HỘ KINH DOANH NGUYỄN MINH PHƯƠNG</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>112695734</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>93016476</v>
       </c>
       <c r="D60" t="n">
-        <v>112695734</v>
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>93016476</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN SẢN XUẤT THƯƠNG MẠI DỊCH VỤ MỘC GIA</t>
+          <t>ĐẶNG THỊ THỦY</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>63542833</v>
+        <v>0</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>112695734</v>
       </c>
       <c r="D61" t="n">
-        <v>63542833</v>
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>112695734</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Lê Quang Vinh</t>
+          <t>CÔNG TY CỔ PHẦN SẢN XUẤT THƯƠNG MẠI DỊCH VỤ MỘC GIA</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>144886746</v>
+        <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>63542833</v>
       </c>
       <c r="D62" t="n">
-        <v>144886746</v>
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>63542833</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CÔNG TY BẢO VIỆT GIA LAI</t>
+          <t>Lê Quang Vinh</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3661275</v>
+        <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>144886746</v>
       </c>
       <c r="D63" t="n">
-        <v>3661275</v>
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>144886746</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NABATI VIỆT NAM</t>
+          <t>CÔNG TY BẢO VIỆT GIA LAI</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>100290250</v>
+        <v>0</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>3661275</v>
       </c>
       <c r="D64" t="n">
-        <v>100290250</v>
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>3661275</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ĐỒNG THỊ TUYẾT</t>
+          <t>CÔNG TY TNHH NABATI VIỆT NAM</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>47802470</v>
+        <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>100290250</v>
       </c>
       <c r="D65" t="n">
-        <v>47802470</v>
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>100290250</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LÊ TUẤN HẢI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ĐỒNG THỊ TUYẾT</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>77202297</v>
+        <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>47802470</v>
       </c>
       <c r="D66" t="n">
-        <v>77202297</v>
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>47802470</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH PHẠM ĐÀO DẠ THẢO</t>
+          <t>LÊ TUẤN HẢI</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>44605161</v>
+        <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>77202297</v>
       </c>
       <c r="D67" t="n">
-        <v>44605161</v>
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>77202297</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LÊ THỊ LINH PHƯƠNG</t>
+          <t>HỘ KINH DOANH PHẠM ĐÀO DẠ THẢO</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>87455197</v>
+        <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>44605161</v>
       </c>
       <c r="D68" t="n">
-        <v>87455197</v>
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>44605161</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH PHAN THỊ ÁNH NHUNG</t>
+          <t>LÊ THỊ LINH PHƯƠNG</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>16661853</v>
+        <v>0</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>87455197</v>
       </c>
       <c r="D69" t="n">
-        <v>16661853</v>
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>87455197</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN KEN</t>
+          <t>HỘ KINH DOANH PHAN THỊ ÁNH NHUNG</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>3988330</v>
+        <v>0</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>16661853</v>
       </c>
       <c r="D70" t="n">
-        <v>3988330</v>
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>16661853</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV HOÀNG ANH QUÂN GIA LAI</t>
+          <t>DOANH NGHIỆP TƯ NHÂN KEN</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>10917528</v>
+        <v>0</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>3988330</v>
       </c>
       <c r="D71" t="n">
-        <v>10917528</v>
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>3988330</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PHAN XUÂN TUẤN</t>
+          <t>CÔNG TY TNHH MTV HOÀNG ANH QUÂN GIA LAI</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>32843778</v>
+        <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>10917528</v>
       </c>
       <c r="D72" t="n">
-        <v>32843778</v>
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>10917528</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Vũ</t>
+          <t>PHAN XUÂN TUẤN</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>44446971</v>
+        <v>0</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>32843778</v>
       </c>
       <c r="D73" t="n">
-        <v>44446971</v>
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>32843778</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GIÁM SÁT TRỊNH HOÀNG SƠN</t>
+          <t>Nguyễn Văn Vũ</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>44446971</v>
       </c>
       <c r="D74" t="n">
         <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>44446971</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ẨM THỰC CÔ DUYÊN</t>
+          <t>GIÁM SÁT TRỊNH HOÀNG SƠN</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>18177736</v>
+        <v>0</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>18177736</v>
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CÔNG TY BẢO HIỂM BIDV BẮC TÂY NGUYÊN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ẨM THỰC CÔ DUYÊN</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>143713599</v>
+        <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>18177736</v>
       </c>
       <c r="D76" t="n">
-        <v>143713599</v>
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>18177736</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Như Ý</t>
+          <t>CÔNG TY BẢO HIỂM BIDV BẮC TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3262813</v>
+        <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>143713599</v>
       </c>
       <c r="D77" t="n">
-        <v>3262813</v>
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>143713599</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ĐINH VĂN CƯỜNG</t>
+          <t>Như Ý</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>100594786</v>
+        <v>0</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>3262813</v>
       </c>
       <c r="D78" t="n">
-        <v>100594786</v>
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>3262813</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TẠP HÓA SƠN THƯƠNG</t>
+          <t>PHẠM THỊ THU TRANG</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>137958045</v>
+        <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>65479968</v>
       </c>
       <c r="D79" t="n">
-        <v>137958045</v>
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>65479968</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PHẠM THỊ THU TRANG</t>
+          <t>TẠP HÓA SƠN THƯƠNG</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>65479968</v>
+        <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>137958045</v>
       </c>
       <c r="D80" t="n">
-        <v>65479968</v>
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>137958045</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI GIA LAI</t>
+          <t>ĐINH VĂN CƯỜNG</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>52635998</v>
+        <v>0</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>100594786</v>
       </c>
       <c r="D81" t="n">
-        <v>52635998</v>
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>100594786</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TẠP HÓA BỐN PHƯƠNG</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI GIA LAI</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>9172417</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>52635998</v>
       </c>
       <c r="D82" t="n">
-        <v>9172417</v>
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>52635998</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PHAN THỊ NGỌC OANH</t>
+          <t>TẠP HÓA BỐN PHƯƠNG</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>81830212</v>
+        <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>9172417</v>
       </c>
       <c r="D83" t="n">
-        <v>81830212</v>
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>9172417</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Lê Vũ Thanh Nga</t>
+          <t>PHAN THỊ NGỌC OANH</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>42730686</v>
+        <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>81830212</v>
       </c>
       <c r="D84" t="n">
-        <v>42730686</v>
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>81830212</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TẠP HÓA HOÀNG PHÁT</t>
+          <t>Lê Vũ Thanh Nga</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>19384101</v>
+        <v>0</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>42730686</v>
       </c>
       <c r="D85" t="n">
-        <v>19384101</v>
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>42730686</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN NHÀ HÀNG HỒNG LUYẾN</t>
+          <t>TẠP HÓA HOÀNG PHÁT</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1351449</v>
+        <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>19384101</v>
       </c>
       <c r="D86" t="n">
-        <v>1351449</v>
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>19384101</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PHOTOCOPY - VĂN PHÒNG PHẨM - TẠP HÓA BẢY</t>
+          <t>DOANH NGHIỆP TƯ NHÂN NHÀ HÀNG HỒNG LUYẾN</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>35745235</v>
+        <v>0</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>1351449</v>
       </c>
       <c r="D87" t="n">
-        <v>35745235</v>
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1351449</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TRẦN THANH THỦY</t>
+          <t>PHOTOCOPY - VĂN PHÒNG PHẨM - TẠP HÓA BẢY</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>4055040</v>
+        <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>35745235</v>
       </c>
       <c r="D88" t="n">
-        <v>4055040</v>
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>35745235</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GIÁM SÁT ĐINH VĂN VIÊN</t>
+          <t>TRẦN THANH THỦY</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>4055040</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>4055040</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CỬA HÀNG NHẬT AN</t>
+          <t>GIÁM SÁT ĐINH VĂN VIÊN</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>38930264</v>
+        <v>0</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>38930264</v>
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV KIÊN NGUYỄN</t>
+          <t>CỬA HÀNG NHẬT AN</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2193686</v>
+        <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>38930264</v>
       </c>
       <c r="D91" t="n">
-        <v>2193686</v>
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>38930264</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH VĨNH HIỆP</t>
+          <t>CÔNG TY TNHH MTV KIÊN NGUYỄN</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>58793864</v>
+        <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>2193686</v>
       </c>
       <c r="D92" t="n">
-        <v>58793864</v>
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>2193686</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MỘT THÀNH VIÊN NGUYỄN HIỆU GIA LAI-DỊCH VỤ GIẢI TRÍ PARADISE</t>
+          <t>CÔNG TY TNHH VĨNH HIỆP</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>24918968</v>
+        <v>0</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>58793864</v>
       </c>
       <c r="D93" t="n">
-        <v>24918968</v>
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>58793864</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GIÁM SÁT HUỲNH ĐỨC AN</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MỘT THÀNH VIÊN NGUYỄN HIỆU GIA LAI-DỊCH VỤ GIẢI TRÍ PARADISE</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>24918968</v>
       </c>
       <c r="D94" t="n">
         <v>0</v>
+      </c>
+      <c r="E94" t="n">
+        <v>24918968</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Bách Hóa Tổng Hợp Sĩ Quỳnh</t>
+          <t>GIÁM SÁT HUỲNH ĐỨC AN</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>121490463</v>
+        <v>0</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>121490463</v>
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>TẠP HÓA PHẠM HỒNG QUÂN</t>
+          <t>Bách Hóa Tổng Hợp Sĩ Quỳnh</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>94704331</v>
+        <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>121490463</v>
       </c>
       <c r="D96" t="n">
-        <v>94704331</v>
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>121490463</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>HỒ VĂN CÔNG</t>
+          <t>TẠP HÓA PHẠM HỒNG QUÂN</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>70075802</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>94704331</v>
       </c>
       <c r="D97" t="n">
-        <v>70075802</v>
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>94704331</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TM-DV HIẾU ĐỨC</t>
+          <t>HỒ VĂN CÔNG</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>15771280</v>
+        <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>70075802</v>
       </c>
       <c r="D98" t="n">
-        <v>15771280</v>
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>70075802</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ĐẶC SẢN CÁ MEKONG THANH TRÚC - ĐỊA ĐIỂM KINH DOANH CÔNG TY TNHH MỘT THÀNH VIÊN VIỄN THÔNG T&amp;T GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TM-DV HIẾU ĐỨC</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>5713448</v>
+        <v>0</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>15771280</v>
       </c>
       <c r="D99" t="n">
-        <v>5713448</v>
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>15771280</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH THỦY HÒA</t>
+          <t>ĐẶC SẢN CÁ MEKONG THANH TRÚC - ĐỊA ĐIỂM KINH DOANH CÔNG TY TNHH MỘT THÀNH VIÊN VIỄN THÔNG T&amp;T GIA LAI</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>16944794</v>
+        <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>5713448</v>
       </c>
       <c r="D100" t="n">
-        <v>16944794</v>
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>5713448</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Hà Thị Ánh Thu</t>
+          <t>HỘ KINH DOANH THỦY HÒA</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>31768870</v>
+        <v>0</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>16944794</v>
       </c>
       <c r="D101" t="n">
-        <v>31768870</v>
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>16944794</v>
       </c>
     </row>
     <row r="102">
@@ -2070,1037 +2374,1232 @@
         </is>
       </c>
       <c r="B102" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" t="n">
         <v>112580783</v>
       </c>
-      <c r="C102" t="n">
-        <v>0</v>
-      </c>
       <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
         <v>112580783</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>TẠP HÓA HỒNG NHUNG</t>
+          <t>Đặng Thị Kim Liễu</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>12402720</v>
+        <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>168991911</v>
       </c>
       <c r="D103" t="n">
-        <v>12402720</v>
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>168991911</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Đàm Văn Tú</t>
+          <t>Hà Thị Ánh Thu</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>202030757</v>
+        <v>0</v>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>31768870</v>
       </c>
       <c r="D104" t="n">
-        <v>202030757</v>
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>31768870</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Đặng Thị Kim Liễu</t>
+          <t>Đàm Văn Tú</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>168991911</v>
+        <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>202030757</v>
       </c>
       <c r="D105" t="n">
-        <v>168991911</v>
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>202030757</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Văn Thị Trang</t>
+          <t>TẠP HÓA HỒNG NHUNG</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>64511283</v>
+        <v>0</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>12402720</v>
       </c>
       <c r="D106" t="n">
-        <v>64511283</v>
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>12402720</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN HỒNG BIÊN</t>
+          <t>Văn Thị Trang</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>5741340</v>
+        <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>64511283</v>
       </c>
       <c r="D107" t="n">
-        <v>5741340</v>
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
+        <v>64511283</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>TRẦN KIM HUẾ</t>
+          <t>Đinh Văn Phúc</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>193931531</v>
+        <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>106849534</v>
       </c>
       <c r="D108" t="n">
-        <v>193931531</v>
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
+        <v>106849534</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Đoàn Hữu Minh</t>
+          <t>Đậu Đức Hào</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>113495115</v>
+        <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>238603563</v>
       </c>
       <c r="D109" t="n">
-        <v>113495115</v>
+        <v>0</v>
+      </c>
+      <c r="E109" t="n">
+        <v>238603563</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Đậu Đức Hào</t>
+          <t>TRẦN KIM HUẾ</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>238603563</v>
+        <v>0</v>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>193931531</v>
       </c>
       <c r="D110" t="n">
-        <v>238603563</v>
+        <v>0</v>
+      </c>
+      <c r="E110" t="n">
+        <v>193931531</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Đinh Văn Phúc</t>
+          <t>Đoàn Hữu Minh</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>106849534</v>
+        <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>113495115</v>
       </c>
       <c r="D111" t="n">
-        <v>106849534</v>
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>113495115</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Hà Trịnh Quốc Việt</t>
+          <t>DOANH NGHIỆP TƯ NHÂN HỒNG BIÊN</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>209257274</v>
+        <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>5741340</v>
       </c>
       <c r="D112" t="n">
-        <v>209257274</v>
+        <v>0</v>
+      </c>
+      <c r="E112" t="n">
+        <v>5741340</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Dương Thị Hiếu</t>
+          <t>Hoàng Chí Công</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>289806522</v>
+        <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>147289986</v>
       </c>
       <c r="D113" t="n">
-        <v>289806522</v>
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
+        <v>147289986</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN NGÓI NÂU GIA LAI</t>
+          <t>Huỳnh Thị Trúc Ly</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>62216706</v>
+        <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>0</v>
+        <v>172721649</v>
       </c>
       <c r="D114" t="n">
-        <v>62216706</v>
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
+        <v>172721649</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Hồ Văn Thành</t>
+          <t>Lê Văn Mẫn</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>113593552</v>
+        <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>235395239</v>
       </c>
       <c r="D115" t="n">
-        <v>113593552</v>
+        <v>0</v>
+      </c>
+      <c r="E115" t="n">
+        <v>235395239</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Duy</t>
+          <t>Nguyễn Minh Tú</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>241451470</v>
+        <v>0</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>169458458</v>
       </c>
       <c r="D116" t="n">
-        <v>241451470</v>
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>169458458</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Lê Xuân Cường</t>
+          <t>CÔNG TY CỔ PHẦN NGÓI NÂU GIA LAI</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>92364509</v>
+        <v>0</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>62216706</v>
       </c>
       <c r="D117" t="n">
-        <v>92364509</v>
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>62216706</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Huỳnh Thị Trúc Ly</t>
+          <t>Dương Thị Hiếu</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>172721649</v>
+        <v>0</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>289806522</v>
       </c>
       <c r="D118" t="n">
-        <v>172721649</v>
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
+        <v>289806522</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Hoàng Chí Công</t>
+          <t>Hà Trịnh Quốc Việt</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>147289986</v>
+        <v>0</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>209257274</v>
       </c>
       <c r="D119" t="n">
-        <v>147289986</v>
+        <v>0</v>
+      </c>
+      <c r="E119" t="n">
+        <v>209257274</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Lê Văn Mẫn</t>
+          <t>Hồ Văn Thành</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>235395239</v>
+        <v>0</v>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>113593552</v>
       </c>
       <c r="D120" t="n">
-        <v>235395239</v>
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>113593552</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Lê Văn Bằng</t>
+          <t>Lê Xuân Cường</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>132937416</v>
+        <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>92364509</v>
       </c>
       <c r="D121" t="n">
-        <v>132937416</v>
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>92364509</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Nguyễn Hữu Thành</t>
+          <t>Ngô Võ Đan</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>260454151</v>
+        <v>0</v>
       </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>113453838</v>
       </c>
       <c r="D122" t="n">
-        <v>260454151</v>
+        <v>0</v>
+      </c>
+      <c r="E122" t="n">
+        <v>113453838</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Tâm</t>
+          <t>Nguyễn Minh Duy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>167005238</v>
+        <v>0</v>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>241451470</v>
       </c>
       <c r="D123" t="n">
-        <v>167005238</v>
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>241451470</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Tứ</t>
+          <t>Lê Văn Bằng</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>132486797</v>
+        <v>0</v>
       </c>
       <c r="C124" t="n">
-        <v>0</v>
+        <v>132937416</v>
       </c>
       <c r="D124" t="n">
-        <v>132486797</v>
+        <v>0</v>
+      </c>
+      <c r="E124" t="n">
+        <v>132937416</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Tú</t>
+          <t>Nguyễn Hữu Thành</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>169458458</v>
+        <v>0</v>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>260454151</v>
       </c>
       <c r="D125" t="n">
-        <v>169458458</v>
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
+        <v>260454151</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ngô Võ Đan</t>
+          <t>Nguyễn Thị Tâm</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>113453838</v>
+        <v>0</v>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>167005238</v>
       </c>
       <c r="D126" t="n">
-        <v>113453838</v>
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>167005238</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Đăng Loan</t>
+          <t>Nguyễn Minh Tứ</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>173086396</v>
+        <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>132486797</v>
       </c>
       <c r="D127" t="n">
-        <v>173086396</v>
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
+        <v>132486797</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thu Hằng</t>
+          <t>HỘ KINH DOANH VÕ VĂN NGỌ</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>155155639</v>
+        <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>66782415</v>
       </c>
       <c r="D128" t="n">
-        <v>155155639</v>
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>66782415</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Mai Hoàng Thiện Châu</t>
+          <t>TẠP HÓA NĂM THI</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>166626778</v>
+        <v>0</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>46344956</v>
       </c>
       <c r="D129" t="n">
-        <v>166626778</v>
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
+        <v>46344956</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Dương</t>
+          <t>Nguyễn Thị Thu Hằng</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>187691183</v>
+        <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>155155639</v>
       </c>
       <c r="D130" t="n">
-        <v>187691183</v>
+        <v>0</v>
+      </c>
+      <c r="E130" t="n">
+        <v>155155639</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Nguyễn Trịnh Minh Hoàng</t>
+          <t>TẠP HÓA THÌN</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>209281321</v>
+        <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>9754668</v>
       </c>
       <c r="D131" t="n">
-        <v>209281321</v>
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>9754668</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Nguyễn Quốc Đạt</t>
+          <t>Nguyễn Nam Hồng</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>241448995</v>
+        <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>161914097</v>
       </c>
       <c r="D132" t="n">
-        <v>241448995</v>
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
+        <v>161914097</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Nguyễn Nam Hồng</t>
+          <t>Nguyễn Quốc Đạt</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>161914097</v>
+        <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>241448995</v>
       </c>
       <c r="D133" t="n">
-        <v>161914097</v>
+        <v>0</v>
+      </c>
+      <c r="E133" t="n">
+        <v>241448995</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH VÕ VĂN NGỌ</t>
+          <t>Nguyễn Trịnh Minh Hoàng</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>66782415</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>0</v>
+        <v>209281321</v>
       </c>
       <c r="D134" t="n">
-        <v>66782415</v>
+        <v>0</v>
+      </c>
+      <c r="E134" t="n">
+        <v>209281321</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TẠP HÓA NĂM THI</t>
+          <t>Mai Hoàng Thiện Châu</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>46344956</v>
+        <v>0</v>
       </c>
       <c r="C135" t="n">
-        <v>0</v>
+        <v>166626778</v>
       </c>
       <c r="D135" t="n">
-        <v>46344956</v>
+        <v>0</v>
+      </c>
+      <c r="E135" t="n">
+        <v>166626778</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TẠP HÓA THÌN</t>
+          <t>Nguyễn Thị Đăng Loan</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>9754668</v>
+        <v>0</v>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>173086396</v>
       </c>
       <c r="D136" t="n">
-        <v>9754668</v>
+        <v>0</v>
+      </c>
+      <c r="E136" t="n">
+        <v>173086396</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SUI NGỌC LAN</t>
+          <t>Nguyễn Văn Dương</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>12232763</v>
+        <v>0</v>
       </c>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>187691183</v>
       </c>
       <c r="D137" t="n">
-        <v>12232763</v>
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
+        <v>187691183</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>QUÁCH THỊ THÚY NGA</t>
+          <t>SUI NGỌC LAN</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>19762931</v>
+        <v>0</v>
       </c>
       <c r="C138" t="n">
-        <v>0</v>
+        <v>12232763</v>
       </c>
       <c r="D138" t="n">
-        <v>19762931</v>
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>12232763</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PHAN THỊ ÁNH LỸ</t>
+          <t>QUÁCH THỊ THÚY NGA</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>18342199</v>
+        <v>0</v>
       </c>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>19762931</v>
       </c>
       <c r="D139" t="n">
-        <v>18342199</v>
+        <v>0</v>
+      </c>
+      <c r="E139" t="n">
+        <v>19762931</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Nguyễn Hồng Ý</t>
+          <t>Nguyễn Trường Sơn</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>225945739</v>
+        <v>0</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>107795444</v>
       </c>
       <c r="D140" t="n">
-        <v>225945739</v>
+        <v>0</v>
+      </c>
+      <c r="E140" t="n">
+        <v>107795444</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Hiền</t>
+          <t>Nguyễn Thị Minh Tâm</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>153063249</v>
+        <v>0</v>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>190953225</v>
       </c>
       <c r="D141" t="n">
-        <v>153063249</v>
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>190953225</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Minh Tâm</t>
+          <t>Nguyễn Thị Hiền</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>190953225</v>
+        <v>0</v>
       </c>
       <c r="C142" t="n">
-        <v>0</v>
+        <v>153063249</v>
       </c>
       <c r="D142" t="n">
-        <v>190953225</v>
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>153063249</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Nguyễn Trường Sơn</t>
+          <t>Nguyễn Hồng Ý</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>107795444</v>
+        <v>0</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>225945739</v>
       </c>
       <c r="D143" t="n">
-        <v>107795444</v>
+        <v>0</v>
+      </c>
+      <c r="E143" t="n">
+        <v>225945739</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Hoàng Tú</t>
+          <t>PHAN THỊ ÁNH LỸ</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>199955071</v>
+        <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>18342199</v>
       </c>
       <c r="D144" t="n">
-        <v>199955071</v>
+        <v>0</v>
+      </c>
+      <c r="E144" t="n">
+        <v>18342199</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Trần Quý Đức</t>
+          <t>Trịnh Tân</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>169963096</v>
+        <v>0</v>
       </c>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>206613852</v>
       </c>
       <c r="D145" t="n">
-        <v>169963096</v>
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
+        <v>206613852</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Trần Bích Hải</t>
+          <t>Trịnh Thị Sinh</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>114345439</v>
+        <v>0</v>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>152557899</v>
       </c>
       <c r="D146" t="n">
-        <v>114345439</v>
+        <v>0</v>
+      </c>
+      <c r="E146" t="n">
+        <v>152557899</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Phạm Hồng Công</t>
+          <t>Võ Chí Hà</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>130483375</v>
+        <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>112601232</v>
       </c>
       <c r="D147" t="n">
-        <v>130483375</v>
+        <v>0</v>
+      </c>
+      <c r="E147" t="n">
+        <v>112601232</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Phan Thanh Hoàng</t>
+          <t>LÊ THỊ MỸ PHƯƠNG</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>116130899</v>
+        <v>0</v>
       </c>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>43179190</v>
       </c>
       <c r="D148" t="n">
-        <v>116130899</v>
+        <v>0</v>
+      </c>
+      <c r="E148" t="n">
+        <v>43179190</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Đỗ Trịnh Công</t>
+          <t>Nguyễn Trịnh Tố Ngân</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>152180951</v>
+        <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>130495163</v>
       </c>
       <c r="D149" t="n">
-        <v>152180951</v>
+        <v>0</v>
+      </c>
+      <c r="E149" t="n">
+        <v>130495163</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Vũ Thị Việt Hằng</t>
+          <t>TẠP HÓA BỬU HIỀN</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>165336925</v>
+        <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>0</v>
+        <v>61435252</v>
       </c>
       <c r="D150" t="n">
-        <v>165336925</v>
+        <v>0</v>
+      </c>
+      <c r="E150" t="n">
+        <v>61435252</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Võ Văn Vũ</t>
+          <t>Trần Thị Tuyết Nhung</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>112039110</v>
+        <v>0</v>
       </c>
       <c r="C151" t="n">
-        <v>0</v>
+        <v>132827967</v>
       </c>
       <c r="D151" t="n">
-        <v>112039110</v>
+        <v>0</v>
+      </c>
+      <c r="E151" t="n">
+        <v>132827967</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Vương Trường Giang</t>
+          <t>Trịnh Lê Hiệp</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>111832426</v>
+        <v>0</v>
       </c>
       <c r="C152" t="n">
-        <v>0</v>
+        <v>260140118</v>
       </c>
       <c r="D152" t="n">
-        <v>111832426</v>
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
+        <v>260140118</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Bùi Văn Lực</t>
+          <t>Hoàng Tú</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>243611717</v>
+        <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>199955071</v>
       </c>
       <c r="D153" t="n">
-        <v>243611717</v>
+        <v>0</v>
+      </c>
+      <c r="E153" t="n">
+        <v>199955071</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Trần Thị Tuyết Nhung</t>
+          <t>Bùi Văn Lực</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>132827967</v>
+        <v>0</v>
       </c>
       <c r="C154" t="n">
-        <v>0</v>
+        <v>243611717</v>
       </c>
       <c r="D154" t="n">
-        <v>132827967</v>
+        <v>0</v>
+      </c>
+      <c r="E154" t="n">
+        <v>243611717</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>LÊ THỊ MỸ PHƯƠNG</t>
+          <t>Vương Trường Giang</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>43179190</v>
+        <v>0</v>
       </c>
       <c r="C155" t="n">
-        <v>0</v>
+        <v>111832426</v>
       </c>
       <c r="D155" t="n">
-        <v>43179190</v>
+        <v>0</v>
+      </c>
+      <c r="E155" t="n">
+        <v>111832426</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>TẠP HÓA BỬU HIỀN</t>
+          <t>Võ Văn Vũ</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>61435252</v>
+        <v>0</v>
       </c>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>112039110</v>
       </c>
       <c r="D156" t="n">
-        <v>61435252</v>
+        <v>0</v>
+      </c>
+      <c r="E156" t="n">
+        <v>112039110</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Nguyễn Trịnh Tố Ngân</t>
+          <t>Vũ Thị Việt Hằng</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>130495163</v>
+        <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>165336925</v>
       </c>
       <c r="D157" t="n">
-        <v>130495163</v>
+        <v>0</v>
+      </c>
+      <c r="E157" t="n">
+        <v>165336925</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Võ Chí Hà</t>
+          <t>Đỗ Trịnh Công</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>112601232</v>
+        <v>0</v>
       </c>
       <c r="C158" t="n">
-        <v>0</v>
+        <v>152180951</v>
       </c>
       <c r="D158" t="n">
-        <v>112601232</v>
+        <v>0</v>
+      </c>
+      <c r="E158" t="n">
+        <v>152180951</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Trịnh Thị Sinh</t>
+          <t>Phan Thanh Hoàng</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>152557899</v>
+        <v>0</v>
       </c>
       <c r="C159" t="n">
-        <v>0</v>
+        <v>116130899</v>
       </c>
       <c r="D159" t="n">
-        <v>152557899</v>
+        <v>0</v>
+      </c>
+      <c r="E159" t="n">
+        <v>116130899</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Trịnh Tân</t>
+          <t>Phạm Hồng Công</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>206613852</v>
+        <v>0</v>
       </c>
       <c r="C160" t="n">
-        <v>0</v>
+        <v>130483375</v>
       </c>
       <c r="D160" t="n">
-        <v>206613852</v>
+        <v>0</v>
+      </c>
+      <c r="E160" t="n">
+        <v>130483375</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Trịnh Lê Hiệp</t>
+          <t>Trần Bích Hải</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>260140118</v>
+        <v>0</v>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>114345439</v>
       </c>
       <c r="D161" t="n">
-        <v>260140118</v>
+        <v>0</v>
+      </c>
+      <c r="E161" t="n">
+        <v>114345439</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Nguyễn Lê Hậu</t>
+          <t>Trần Quý Đức</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>260476999</v>
+        <v>0</v>
       </c>
       <c r="C162" t="n">
-        <v>0</v>
+        <v>169963096</v>
       </c>
       <c r="D162" t="n">
-        <v>260476999</v>
+        <v>0</v>
+      </c>
+      <c r="E162" t="n">
+        <v>169963096</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Dương Thị Thông</t>
+          <t>Kpă Vũ Mạnh Long</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>243833248</v>
+        <v>0</v>
       </c>
       <c r="C163" t="n">
-        <v>0</v>
+        <v>109286964</v>
       </c>
       <c r="D163" t="n">
-        <v>243833248</v>
+        <v>0</v>
+      </c>
+      <c r="E163" t="n">
+        <v>109286964</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>NGUYỄN VĂN CÔNG</t>
+          <t>Ngô Văn Bằng</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>94306512</v>
+        <v>0</v>
       </c>
       <c r="C164" t="n">
-        <v>0</v>
+        <v>111936480</v>
       </c>
       <c r="D164" t="n">
-        <v>94306512</v>
+        <v>0</v>
+      </c>
+      <c r="E164" t="n">
+        <v>111936480</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Kpă Vũ Mạnh Long</t>
+          <t>HUỲNH ĐỨC AN</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>109286964</v>
+        <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>0</v>
+        <v>54719280</v>
       </c>
       <c r="D165" t="n">
-        <v>109286964</v>
+        <v>0</v>
+      </c>
+      <c r="E165" t="n">
+        <v>54719280</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Phan Công Thiện</t>
+          <t>Huỳnh Thị Cúc</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>112632349</v>
+        <v>0</v>
       </c>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>248582520</v>
       </c>
       <c r="D166" t="n">
-        <v>112632349</v>
+        <v>0</v>
+      </c>
+      <c r="E166" t="n">
+        <v>248582520</v>
       </c>
     </row>
     <row r="167">
@@ -3110,77 +3609,92 @@
         </is>
       </c>
       <c r="B167" t="n">
+        <v>0</v>
+      </c>
+      <c r="C167" t="n">
         <v>111954346</v>
       </c>
-      <c r="C167" t="n">
-        <v>0</v>
-      </c>
       <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="n">
         <v>111954346</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Huỳnh Thị Cúc</t>
+          <t>Phan Công Thiện</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>248582520</v>
+        <v>0</v>
       </c>
       <c r="C168" t="n">
-        <v>0</v>
+        <v>112632349</v>
       </c>
       <c r="D168" t="n">
-        <v>248582520</v>
+        <v>0</v>
+      </c>
+      <c r="E168" t="n">
+        <v>112632349</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Ngô Văn Bằng</t>
+          <t>Nguyễn Lê Hậu</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>111936480</v>
+        <v>0</v>
       </c>
       <c r="C169" t="n">
-        <v>0</v>
+        <v>260476999</v>
       </c>
       <c r="D169" t="n">
-        <v>111936480</v>
+        <v>0</v>
+      </c>
+      <c r="E169" t="n">
+        <v>260476999</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>HUỲNH ĐỨC AN</t>
+          <t>NGUYỄN VĂN CÔNG</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>54719280</v>
+        <v>0</v>
       </c>
       <c r="C170" t="n">
-        <v>0</v>
+        <v>94306512</v>
       </c>
       <c r="D170" t="n">
-        <v>54719280</v>
+        <v>0</v>
+      </c>
+      <c r="E170" t="n">
+        <v>94306512</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Phan Thị Thùy Mỵ</t>
+          <t>Dương Thị Thông</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>113837653</v>
+        <v>0</v>
       </c>
       <c r="C171" t="n">
-        <v>0</v>
+        <v>243833248</v>
       </c>
       <c r="D171" t="n">
-        <v>113837653</v>
+        <v>0</v>
+      </c>
+      <c r="E171" t="n">
+        <v>243833248</v>
       </c>
     </row>
     <row r="172">
@@ -3190,77 +3704,92 @@
         </is>
       </c>
       <c r="B172" t="n">
+        <v>0</v>
+      </c>
+      <c r="C172" t="n">
         <v>168619647</v>
       </c>
-      <c r="C172" t="n">
-        <v>0</v>
-      </c>
       <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="n">
         <v>168619647</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ĐINH VĂN VIÊN</t>
+          <t>Phan Thị Thùy Mỵ</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>51415511</v>
+        <v>0</v>
       </c>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>113837653</v>
       </c>
       <c r="D173" t="n">
-        <v>51415511</v>
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
+        <v>113837653</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Ngô Đức Thuận</t>
+          <t>Mai Thị Kim Loan</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>131567122</v>
+        <v>0</v>
       </c>
       <c r="C174" t="n">
-        <v>0</v>
+        <v>144859608</v>
       </c>
       <c r="D174" t="n">
-        <v>131567122</v>
+        <v>0</v>
+      </c>
+      <c r="E174" t="n">
+        <v>144859608</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Mai Thị Kim Loan</t>
+          <t>Dương Nô</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>144859608</v>
+        <v>0</v>
       </c>
       <c r="C175" t="n">
-        <v>0</v>
+        <v>111439059</v>
       </c>
       <c r="D175" t="n">
-        <v>144859608</v>
+        <v>0</v>
+      </c>
+      <c r="E175" t="n">
+        <v>111439059</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Dương Nô</t>
+          <t>Ngô Đức Thuận</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>111439059</v>
+        <v>0</v>
       </c>
       <c r="C176" t="n">
-        <v>0</v>
+        <v>131567122</v>
       </c>
       <c r="D176" t="n">
-        <v>111439059</v>
+        <v>0</v>
+      </c>
+      <c r="E176" t="n">
+        <v>131567122</v>
       </c>
     </row>
     <row r="177">
@@ -3270,29 +3799,35 @@
         </is>
       </c>
       <c r="B177" t="n">
+        <v>0</v>
+      </c>
+      <c r="C177" t="n">
         <v>93332200</v>
       </c>
-      <c r="C177" t="n">
-        <v>0</v>
-      </c>
       <c r="D177" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="n">
         <v>93332200</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Trịnh Lê Hưng</t>
+          <t>ĐINH VĂN VIÊN</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>208830345</v>
+        <v>0</v>
       </c>
       <c r="C178" t="n">
-        <v>0</v>
+        <v>51415511</v>
       </c>
       <c r="D178" t="n">
-        <v>208830345</v>
+        <v>0</v>
+      </c>
+      <c r="E178" t="n">
+        <v>51415511</v>
       </c>
     </row>
     <row r="179">
@@ -3302,12 +3837,15 @@
         </is>
       </c>
       <c r="B179" t="n">
+        <v>0</v>
+      </c>
+      <c r="C179" t="n">
         <v>114697559</v>
       </c>
-      <c r="C179" t="n">
-        <v>0</v>
-      </c>
       <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="n">
         <v>114697559</v>
       </c>
     </row>
@@ -3318,12 +3856,15 @@
         </is>
       </c>
       <c r="B180" t="n">
+        <v>0</v>
+      </c>
+      <c r="C180" t="n">
         <v>19665288</v>
       </c>
-      <c r="C180" t="n">
-        <v>0</v>
-      </c>
       <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="n">
         <v>19665288</v>
       </c>
     </row>
@@ -3334,237 +3875,282 @@
         </is>
       </c>
       <c r="B181" t="n">
+        <v>0</v>
+      </c>
+      <c r="C181" t="n">
         <v>142784458</v>
       </c>
-      <c r="C181" t="n">
-        <v>0</v>
-      </c>
       <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="n">
         <v>142784458</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Đồng Thị Thanh</t>
+          <t>Trịnh Lê Hưng</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>75303891</v>
+        <v>0</v>
       </c>
       <c r="C182" t="n">
-        <v>0</v>
+        <v>208830345</v>
       </c>
       <c r="D182" t="n">
-        <v>75303891</v>
+        <v>0</v>
+      </c>
+      <c r="E182" t="n">
+        <v>208830345</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Trần Văn Hiệu</t>
+          <t>NGUYỄN THỊ LINH GIANG</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>58075244</v>
+        <v>0</v>
       </c>
       <c r="C183" t="n">
-        <v>0</v>
+        <v>89714754</v>
       </c>
       <c r="D183" t="n">
-        <v>58075244</v>
+        <v>0</v>
+      </c>
+      <c r="E183" t="n">
+        <v>89714754</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PHẠM THỊ THU SA</t>
+          <t>TRẦN THỊ THU HƯƠNG</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>72713516</v>
+        <v>0</v>
       </c>
       <c r="C184" t="n">
-        <v>0</v>
+        <v>33034001</v>
       </c>
       <c r="D184" t="n">
-        <v>72713516</v>
+        <v>0</v>
+      </c>
+      <c r="E184" t="n">
+        <v>33034001</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Trung</t>
+          <t>Hoàng Anh Thương</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>34317000</v>
+        <v>0</v>
       </c>
       <c r="C185" t="n">
-        <v>0</v>
+        <v>67529025</v>
       </c>
       <c r="D185" t="n">
-        <v>34317000</v>
+        <v>0</v>
+      </c>
+      <c r="E185" t="n">
+        <v>67529025</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thu</t>
+          <t>Trần Thị Thu Hồng</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>56904595</v>
+        <v>0</v>
       </c>
       <c r="C186" t="n">
-        <v>0</v>
+        <v>103684279</v>
       </c>
       <c r="D186" t="n">
-        <v>56904595</v>
+        <v>0</v>
+      </c>
+      <c r="E186" t="n">
+        <v>103684279</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Lại Thị Hà</t>
+          <t>Dương Minh Ngọc</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>91139305</v>
+        <v>0</v>
       </c>
       <c r="C187" t="n">
-        <v>0</v>
+        <v>73225572</v>
       </c>
       <c r="D187" t="n">
-        <v>91139305</v>
+        <v>0</v>
+      </c>
+      <c r="E187" t="n">
+        <v>73225572</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ TẠO</t>
+          <t>Nhà Thuốc Linh</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>56632668</v>
+        <v>0</v>
       </c>
       <c r="C188" t="n">
-        <v>0</v>
+        <v>19459440</v>
       </c>
       <c r="D188" t="n">
-        <v>56632668</v>
+        <v>0</v>
+      </c>
+      <c r="E188" t="n">
+        <v>19459440</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thanh Hương</t>
+          <t>Tạp Hóa Thùy Linh</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>292651315</v>
+        <v>0</v>
       </c>
       <c r="C189" t="n">
-        <v>0</v>
+        <v>72053019</v>
       </c>
       <c r="D189" t="n">
-        <v>292651315</v>
+        <v>0</v>
+      </c>
+      <c r="E189" t="n">
+        <v>72053019</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>PHẠM NGUYỄN LONG THÀNH</t>
+          <t>Đỗ Thị Bích Hương</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>40290318</v>
+        <v>0</v>
       </c>
       <c r="C190" t="n">
-        <v>0</v>
+        <v>220668611</v>
       </c>
       <c r="D190" t="n">
-        <v>40290318</v>
+        <v>0</v>
+      </c>
+      <c r="E190" t="n">
+        <v>220668611</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Phan Thị Ánh Mỹ</t>
+          <t>TẠP HÓA NHƯ THỦY</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>240243282</v>
+        <v>0</v>
       </c>
       <c r="C191" t="n">
-        <v>0</v>
+        <v>57550578</v>
       </c>
       <c r="D191" t="n">
-        <v>240243282</v>
+        <v>0</v>
+      </c>
+      <c r="E191" t="n">
+        <v>57550578</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>TẠP HÓA NHƯ THỦY</t>
+          <t>LƯU THỊ THUỲ</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>57550578</v>
+        <v>0</v>
       </c>
       <c r="C192" t="n">
-        <v>0</v>
+        <v>96882946</v>
       </c>
       <c r="D192" t="n">
-        <v>57550578</v>
+        <v>0</v>
+      </c>
+      <c r="E192" t="n">
+        <v>96882946</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>CAO MẠNH HÙNG</t>
+          <t>Nguyễn Thị Thanh Hương</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>93965037</v>
+        <v>0</v>
       </c>
       <c r="C193" t="n">
-        <v>0</v>
+        <v>292651315</v>
       </c>
       <c r="D193" t="n">
-        <v>93965037</v>
+        <v>0</v>
+      </c>
+      <c r="E193" t="n">
+        <v>292651315</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>LÊ THỊ MỸ LOAN</t>
+          <t>Phan Thị Ánh Mỹ</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>69945287</v>
+        <v>0</v>
       </c>
       <c r="C194" t="n">
-        <v>0</v>
+        <v>240243282</v>
       </c>
       <c r="D194" t="n">
-        <v>69945287</v>
+        <v>0</v>
+      </c>
+      <c r="E194" t="n">
+        <v>240243282</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Mai Văn Tân</t>
+          <t>Hà Thị Hiếu</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>149513069</v>
+        <v>0</v>
       </c>
       <c r="C195" t="n">
-        <v>0</v>
+        <v>94706437</v>
       </c>
       <c r="D195" t="n">
-        <v>149513069</v>
+        <v>0</v>
+      </c>
+      <c r="E195" t="n">
+        <v>94706437</v>
       </c>
     </row>
     <row r="196">
@@ -3574,29 +4160,35 @@
         </is>
       </c>
       <c r="B196" t="n">
+        <v>0</v>
+      </c>
+      <c r="C196" t="n">
         <v>95596343</v>
       </c>
-      <c r="C196" t="n">
-        <v>0</v>
-      </c>
       <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="n">
         <v>95596343</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Hà Thị Hiếu</t>
+          <t>Mai Văn Tân</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>94706437</v>
+        <v>0</v>
       </c>
       <c r="C197" t="n">
-        <v>0</v>
+        <v>149513069</v>
       </c>
       <c r="D197" t="n">
-        <v>94706437</v>
+        <v>0</v>
+      </c>
+      <c r="E197" t="n">
+        <v>149513069</v>
       </c>
     </row>
     <row r="198">
@@ -3606,301 +4198,358 @@
         </is>
       </c>
       <c r="B198" t="n">
+        <v>0</v>
+      </c>
+      <c r="C198" t="n">
         <v>113695752</v>
       </c>
-      <c r="C198" t="n">
-        <v>0</v>
-      </c>
       <c r="D198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="n">
         <v>113695752</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Phạm Thị Mỹ Hạnh</t>
+          <t>LÊ THỊ MỸ LOAN</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>225080985</v>
+        <v>0</v>
       </c>
       <c r="C199" t="n">
-        <v>0</v>
+        <v>69945287</v>
       </c>
       <c r="D199" t="n">
-        <v>225080985</v>
+        <v>0</v>
+      </c>
+      <c r="E199" t="n">
+        <v>69945287</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TRẦN THỊ THU HƯƠNG</t>
+          <t>TRẦN THỊ THU HÀ</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>33034001</v>
+        <v>0</v>
       </c>
       <c r="C200" t="n">
-        <v>0</v>
+        <v>55746047</v>
       </c>
       <c r="D200" t="n">
-        <v>33034001</v>
+        <v>0</v>
+      </c>
+      <c r="E200" t="n">
+        <v>55746047</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Nhà Thuốc Linh</t>
+          <t>Phạm Thị Mỹ Hạnh</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>19459440</v>
+        <v>0</v>
       </c>
       <c r="C201" t="n">
-        <v>0</v>
+        <v>225080985</v>
       </c>
       <c r="D201" t="n">
-        <v>19459440</v>
+        <v>0</v>
+      </c>
+      <c r="E201" t="n">
+        <v>225080985</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Tạp Hóa Thùy Linh</t>
+          <t>PHẠM NGUYỄN LONG THÀNH</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>72053019</v>
+        <v>0</v>
       </c>
       <c r="C202" t="n">
-        <v>0</v>
+        <v>40290318</v>
       </c>
       <c r="D202" t="n">
-        <v>72053019</v>
+        <v>0</v>
+      </c>
+      <c r="E202" t="n">
+        <v>40290318</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Đỗ Thị Hồng Nhung</t>
+          <t>CAO MẠNH HÙNG</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>222153462</v>
+        <v>0</v>
       </c>
       <c r="C203" t="n">
-        <v>0</v>
+        <v>93965037</v>
       </c>
       <c r="D203" t="n">
-        <v>222153462</v>
+        <v>0</v>
+      </c>
+      <c r="E203" t="n">
+        <v>93965037</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Trần Minh Chung</t>
+          <t>NGUYỄN THỊ TẠO</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>55283301</v>
+        <v>0</v>
       </c>
       <c r="C204" t="n">
-        <v>0</v>
+        <v>56632668</v>
       </c>
       <c r="D204" t="n">
-        <v>55283301</v>
+        <v>0</v>
+      </c>
+      <c r="E204" t="n">
+        <v>56632668</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>TRẦN THỊ THU HÀ</t>
+          <t>Đỗ Thị Hồng Nhung</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>55746047</v>
+        <v>0</v>
       </c>
       <c r="C205" t="n">
-        <v>0</v>
+        <v>222153462</v>
       </c>
       <c r="D205" t="n">
-        <v>55746047</v>
+        <v>0</v>
+      </c>
+      <c r="E205" t="n">
+        <v>222153462</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>TRẦN TIẾN DŨNG</t>
+          <t>Trần Minh Chung</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>37058364</v>
+        <v>0</v>
       </c>
       <c r="C206" t="n">
-        <v>0</v>
+        <v>55283301</v>
       </c>
       <c r="D206" t="n">
-        <v>37058364</v>
+        <v>0</v>
+      </c>
+      <c r="E206" t="n">
+        <v>55283301</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>BÙI XUÂN NAM</t>
+          <t>Hộ Kinh Doanh Đồng Thị Thanh</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>93355244</v>
+        <v>0</v>
       </c>
       <c r="C207" t="n">
-        <v>0</v>
+        <v>75303891</v>
       </c>
       <c r="D207" t="n">
-        <v>93355244</v>
+        <v>0</v>
+      </c>
+      <c r="E207" t="n">
+        <v>75303891</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ LINH GIANG</t>
+          <t>Lại Thị Hà</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>89714754</v>
+        <v>0</v>
       </c>
       <c r="C208" t="n">
-        <v>0</v>
+        <v>91139305</v>
       </c>
       <c r="D208" t="n">
-        <v>89714754</v>
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>91139305</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Hoàng Anh Thương</t>
+          <t>Nguyễn Thị Thu</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>67529025</v>
+        <v>0</v>
       </c>
       <c r="C209" t="n">
-        <v>0</v>
+        <v>56904595</v>
       </c>
       <c r="D209" t="n">
-        <v>67529025</v>
+        <v>0</v>
+      </c>
+      <c r="E209" t="n">
+        <v>56904595</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Dương Minh Ngọc</t>
+          <t>Nguyễn Văn Trung</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>73225572</v>
+        <v>0</v>
       </c>
       <c r="C210" t="n">
-        <v>0</v>
+        <v>34317000</v>
       </c>
       <c r="D210" t="n">
-        <v>73225572</v>
+        <v>0</v>
+      </c>
+      <c r="E210" t="n">
+        <v>34317000</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Trần Thị Thu Hồng</t>
+          <t>PHẠM THỊ THU SA</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>103684279</v>
+        <v>0</v>
       </c>
       <c r="C211" t="n">
-        <v>0</v>
+        <v>72713516</v>
       </c>
       <c r="D211" t="n">
-        <v>103684279</v>
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>72713516</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>LƯU THỊ THUỲ</t>
+          <t>Trần Văn Hiệu</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>96882946</v>
+        <v>0</v>
       </c>
       <c r="C212" t="n">
-        <v>0</v>
+        <v>58075244</v>
       </c>
       <c r="D212" t="n">
-        <v>96882946</v>
+        <v>0</v>
+      </c>
+      <c r="E212" t="n">
+        <v>58075244</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Đỗ Thị Bích Hương</t>
+          <t>BÙI XUÂN NAM</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>220668611</v>
+        <v>0</v>
       </c>
       <c r="C213" t="n">
-        <v>0</v>
+        <v>93355244</v>
       </c>
       <c r="D213" t="n">
-        <v>220668611</v>
+        <v>0</v>
+      </c>
+      <c r="E213" t="n">
+        <v>93355244</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Nguyễn Đức Thiên</t>
+          <t>TRẦN TIẾN DŨNG</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>93567284</v>
+        <v>0</v>
       </c>
       <c r="C214" t="n">
-        <v>0</v>
+        <v>37058364</v>
       </c>
       <c r="D214" t="n">
-        <v>93567284</v>
+        <v>0</v>
+      </c>
+      <c r="E214" t="n">
+        <v>37058364</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Trần Thị Lan Thi</t>
+          <t>Nguyễn Thị Nương</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>93448010</v>
+        <v>0</v>
       </c>
       <c r="C215" t="n">
-        <v>0</v>
+        <v>37600124</v>
       </c>
       <c r="D215" t="n">
-        <v>93448010</v>
+        <v>0</v>
+      </c>
+      <c r="E215" t="n">
+        <v>37600124</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Lê Tiến Hậu</t>
+          <t>HỘ KINH DOANH KHIÊN LÀNH</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>130810220</v>
+        <v>0</v>
       </c>
       <c r="C216" t="n">
-        <v>0</v>
+        <v>75158369</v>
       </c>
       <c r="D216" t="n">
-        <v>130810220</v>
+        <v>0</v>
+      </c>
+      <c r="E216" t="n">
+        <v>75158369</v>
       </c>
     </row>
     <row r="217">
@@ -3910,829 +4559,985 @@
         </is>
       </c>
       <c r="B217" t="n">
+        <v>0</v>
+      </c>
+      <c r="C217" t="n">
         <v>100927438</v>
       </c>
-      <c r="C217" t="n">
-        <v>0</v>
-      </c>
       <c r="D217" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" t="n">
         <v>100927438</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Hồ Thị Thanh Hiền</t>
+          <t>LÂM MINH HOÀNG</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>72565656</v>
+        <v>0</v>
       </c>
       <c r="C218" t="n">
-        <v>0</v>
+        <v>75323336</v>
       </c>
       <c r="D218" t="n">
-        <v>72565656</v>
+        <v>0</v>
+      </c>
+      <c r="E218" t="n">
+        <v>75323336</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Đàm Đình Ngữ</t>
+          <t>HỘ KINH DOANH ĐẶNG THỊ DIỄM</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>105797354</v>
+        <v>0</v>
       </c>
       <c r="C219" t="n">
-        <v>0</v>
+        <v>75977935</v>
       </c>
       <c r="D219" t="n">
-        <v>105797354</v>
+        <v>0</v>
+      </c>
+      <c r="E219" t="n">
+        <v>75977935</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Thới Thị Bích Hà</t>
+          <t>Hộ Kinh Doanh Hồ Thị Thanh Hiền</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>96073251</v>
+        <v>0</v>
       </c>
       <c r="C220" t="n">
-        <v>0</v>
+        <v>72565656</v>
       </c>
       <c r="D220" t="n">
-        <v>96073251</v>
+        <v>0</v>
+      </c>
+      <c r="E220" t="n">
+        <v>72565656</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Võ Văn Thành</t>
+          <t>Nguyễn Đức Thiên</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>37061399</v>
+        <v>0</v>
       </c>
       <c r="C221" t="n">
-        <v>0</v>
+        <v>93567284</v>
       </c>
       <c r="D221" t="n">
-        <v>37061399</v>
+        <v>0</v>
+      </c>
+      <c r="E221" t="n">
+        <v>93567284</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Trịnh Lê Đông</t>
+          <t>Lê Tiến Hậu</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>208483355</v>
+        <v>0</v>
       </c>
       <c r="C222" t="n">
-        <v>0</v>
+        <v>130810220</v>
       </c>
       <c r="D222" t="n">
-        <v>208483355</v>
+        <v>0</v>
+      </c>
+      <c r="E222" t="n">
+        <v>130810220</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VIỄN THÔNG T&amp;T GIA LAI</t>
+          <t>Trần Thị Lan Thi</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>5148768</v>
+        <v>0</v>
       </c>
       <c r="C223" t="n">
-        <v>0</v>
+        <v>93448010</v>
       </c>
       <c r="D223" t="n">
-        <v>5148768</v>
+        <v>0</v>
+      </c>
+      <c r="E223" t="n">
+        <v>93448010</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Đặng Kim Hùng</t>
+          <t>Hoàng Thị Thanh Hương</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>72633979</v>
+        <v>0</v>
       </c>
       <c r="C224" t="n">
-        <v>0</v>
+        <v>55259900</v>
       </c>
       <c r="D224" t="n">
-        <v>72633979</v>
+        <v>0</v>
+      </c>
+      <c r="E224" t="n">
+        <v>55259900</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Tường Vi</t>
+          <t>Võ Văn Thành</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>37203656</v>
+        <v>0</v>
       </c>
       <c r="C225" t="n">
-        <v>0</v>
+        <v>37061399</v>
       </c>
       <c r="D225" t="n">
-        <v>37203656</v>
+        <v>0</v>
+      </c>
+      <c r="E225" t="n">
+        <v>37061399</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>TRỊNH HOÀNG SƠN</t>
+          <t>Trịnh Lê Đông</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>147169661</v>
+        <v>0</v>
       </c>
       <c r="C226" t="n">
-        <v>0</v>
+        <v>208483355</v>
       </c>
       <c r="D226" t="n">
-        <v>147169661</v>
+        <v>0</v>
+      </c>
+      <c r="E226" t="n">
+        <v>208483355</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Lâm Ngọc Đào</t>
+          <t>Nguyễn Thị Tường Vi</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>133099188</v>
+        <v>0</v>
       </c>
       <c r="C227" t="n">
-        <v>0</v>
+        <v>37203656</v>
       </c>
       <c r="D227" t="n">
-        <v>133099188</v>
+        <v>0</v>
+      </c>
+      <c r="E227" t="n">
+        <v>37203656</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH ĐẶNG THỊ DIỄM</t>
+          <t>Đàm Đình Ngữ</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>75977935</v>
+        <v>0</v>
       </c>
       <c r="C228" t="n">
-        <v>0</v>
+        <v>105797354</v>
       </c>
       <c r="D228" t="n">
-        <v>75977935</v>
+        <v>0</v>
+      </c>
+      <c r="E228" t="n">
+        <v>105797354</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Hoàng Thị Thanh Hương</t>
+          <t>Thới Thị Bích Hà</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>55259900</v>
+        <v>0</v>
       </c>
       <c r="C229" t="n">
-        <v>0</v>
+        <v>96073251</v>
       </c>
       <c r="D229" t="n">
-        <v>55259900</v>
+        <v>0</v>
+      </c>
+      <c r="E229" t="n">
+        <v>96073251</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH KHIÊN LÀNH</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VIỄN THÔNG T&amp;T GIA LAI</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>75158369</v>
+        <v>0</v>
       </c>
       <c r="C230" t="n">
-        <v>0</v>
+        <v>5148768</v>
       </c>
       <c r="D230" t="n">
-        <v>75158369</v>
+        <v>0</v>
+      </c>
+      <c r="E230" t="n">
+        <v>5148768</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>LÂM MINH HOÀNG</t>
+          <t>Đặng Kim Hùng</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>75323336</v>
+        <v>0</v>
       </c>
       <c r="C231" t="n">
-        <v>0</v>
+        <v>72633979</v>
       </c>
       <c r="D231" t="n">
-        <v>75323336</v>
+        <v>0</v>
+      </c>
+      <c r="E231" t="n">
+        <v>72633979</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Nương</t>
+          <t>TRỊNH HOÀNG SƠN</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>37600124</v>
+        <v>0</v>
       </c>
       <c r="C232" t="n">
-        <v>0</v>
+        <v>147169661</v>
       </c>
       <c r="D232" t="n">
-        <v>37600124</v>
+        <v>0</v>
+      </c>
+      <c r="E232" t="n">
+        <v>147169661</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ KIM LIÊN</t>
+          <t>Lâm Ngọc Đào</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>95603094</v>
+        <v>0</v>
       </c>
       <c r="C233" t="n">
-        <v>0</v>
+        <v>133099188</v>
       </c>
       <c r="D233" t="n">
-        <v>95603094</v>
+        <v>0</v>
+      </c>
+      <c r="E233" t="n">
+        <v>133099188</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Trần Bích Hả</t>
+          <t>TẠP HÓA THÙY TRANG</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>18502560</v>
+        <v>0</v>
       </c>
       <c r="C234" t="n">
-        <v>0</v>
+        <v>56131277</v>
       </c>
       <c r="D234" t="n">
-        <v>18502560</v>
+        <v>0</v>
+      </c>
+      <c r="E234" t="n">
+        <v>56131277</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>TẠP HÓA THÙY TRANG</t>
+          <t>TẠP HÓA CÚC</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>56131277</v>
+        <v>0</v>
       </c>
       <c r="C235" t="n">
-        <v>0</v>
+        <v>77778421</v>
       </c>
       <c r="D235" t="n">
-        <v>56131277</v>
+        <v>0</v>
+      </c>
+      <c r="E235" t="n">
+        <v>77778421</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Phạm Văn Minh</t>
+          <t>NGUYỄN THỊ KIM LIÊN</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>129316036</v>
+        <v>0</v>
       </c>
       <c r="C236" t="n">
-        <v>0</v>
+        <v>95603094</v>
       </c>
       <c r="D236" t="n">
-        <v>129316036</v>
+        <v>0</v>
+      </c>
+      <c r="E236" t="n">
+        <v>95603094</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>TẠP HÓA CÚC</t>
+          <t>Trần Bích Hả</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>77778421</v>
+        <v>0</v>
       </c>
       <c r="C237" t="n">
-        <v>0</v>
+        <v>18502560</v>
       </c>
       <c r="D237" t="n">
-        <v>77778421</v>
+        <v>0</v>
+      </c>
+      <c r="E237" t="n">
+        <v>18502560</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>PHOTOCOPY - VĂN PHÒNG PHẨM - TẠP HÓA MAI LAN</t>
+          <t>Phạm Văn Minh</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>59869441</v>
+        <v>0</v>
       </c>
       <c r="C238" t="n">
-        <v>0</v>
+        <v>129316036</v>
       </c>
       <c r="D238" t="n">
-        <v>59869441</v>
+        <v>0</v>
+      </c>
+      <c r="E238" t="n">
+        <v>129316036</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>HỒ TRỌNG DUY</t>
+          <t>PHOTOCOPY - VĂN PHÒNG PHẨM - TẠP HÓA MAI LAN</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>37879130</v>
+        <v>0</v>
       </c>
       <c r="C239" t="n">
-        <v>0</v>
+        <v>59869441</v>
       </c>
       <c r="D239" t="n">
-        <v>37879130</v>
+        <v>0</v>
+      </c>
+      <c r="E239" t="n">
+        <v>59869441</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH ÔNG NGỌC NHÂN</t>
+          <t>HỒ TRỌNG DUY</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>71343420</v>
+        <v>0</v>
       </c>
       <c r="C240" t="n">
-        <v>0</v>
+        <v>37879130</v>
       </c>
       <c r="D240" t="n">
-        <v>71343420</v>
+        <v>0</v>
+      </c>
+      <c r="E240" t="n">
+        <v>37879130</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Đỗ Anh Tuấn</t>
+          <t>HỘ KINH DOANH ÔNG NGỌC NHÂN</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>36114299</v>
+        <v>0</v>
       </c>
       <c r="C241" t="n">
-        <v>0</v>
+        <v>71343420</v>
       </c>
       <c r="D241" t="n">
-        <v>36114299</v>
+        <v>0</v>
+      </c>
+      <c r="E241" t="n">
+        <v>71343420</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Sui Ngọc Lan</t>
+          <t>Đỗ Anh Tuấn</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>17926173</v>
+        <v>0</v>
       </c>
       <c r="C242" t="n">
-        <v>0</v>
+        <v>36114299</v>
       </c>
       <c r="D242" t="n">
-        <v>17926173</v>
+        <v>0</v>
+      </c>
+      <c r="E242" t="n">
+        <v>36114299</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Kim Tuyến</t>
+          <t>Hoàng Thị Thu Hương</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>56971830</v>
+        <v>0</v>
       </c>
       <c r="C243" t="n">
-        <v>0</v>
+        <v>45800482</v>
       </c>
       <c r="D243" t="n">
-        <v>56971830</v>
+        <v>0</v>
+      </c>
+      <c r="E243" t="n">
+        <v>45800482</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Hoàng Thị Thu Hương</t>
+          <t>Sui Ngọc Lan</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>45800482</v>
+        <v>0</v>
       </c>
       <c r="C244" t="n">
-        <v>0</v>
+        <v>17926173</v>
       </c>
       <c r="D244" t="n">
-        <v>45800482</v>
+        <v>0</v>
+      </c>
+      <c r="E244" t="n">
+        <v>17926173</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Quách Thị Thúy Nga</t>
+          <t>Nguyễn Thị Kim Tuyến</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>37823760</v>
+        <v>0</v>
       </c>
       <c r="C245" t="n">
-        <v>0</v>
+        <v>56971830</v>
       </c>
       <c r="D245" t="n">
-        <v>37823760</v>
+        <v>0</v>
+      </c>
+      <c r="E245" t="n">
+        <v>56971830</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>BÙI QUANG DIỄN</t>
+          <t>Quách Thị Thúy Nga</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>36097078</v>
+        <v>0</v>
       </c>
       <c r="C246" t="n">
-        <v>0</v>
+        <v>37823760</v>
       </c>
       <c r="D246" t="n">
-        <v>36097078</v>
+        <v>0</v>
+      </c>
+      <c r="E246" t="n">
+        <v>37823760</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Hoàng Phát</t>
+          <t>BÙI QUANG DIỄN</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>54095774</v>
+        <v>0</v>
       </c>
       <c r="C247" t="n">
-        <v>0</v>
+        <v>36097078</v>
       </c>
       <c r="D247" t="n">
-        <v>54095774</v>
+        <v>0</v>
+      </c>
+      <c r="E247" t="n">
+        <v>36097078</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Shop Hà Thu</t>
+          <t>Hộ Kinh Doanh Hoàng Phát</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>43990020</v>
+        <v>0</v>
       </c>
       <c r="C248" t="n">
-        <v>0</v>
+        <v>54095774</v>
       </c>
       <c r="D248" t="n">
-        <v>43990020</v>
+        <v>0</v>
+      </c>
+      <c r="E248" t="n">
+        <v>54095774</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN CHERRYBLOSSOM NHA TRANG</t>
+          <t>Shop Hà Thu</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>5013051</v>
+        <v>0</v>
       </c>
       <c r="C249" t="n">
-        <v>0</v>
+        <v>43990020</v>
       </c>
       <c r="D249" t="n">
-        <v>5013051</v>
+        <v>0</v>
+      </c>
+      <c r="E249" t="n">
+        <v>43990020</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>TRƯƠNG THỊ KHUYÊN</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN CHERRYBLOSSOM NHA TRANG</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>21123415</v>
+        <v>0</v>
       </c>
       <c r="C250" t="n">
-        <v>0</v>
+        <v>5013051</v>
       </c>
       <c r="D250" t="n">
-        <v>21123415</v>
+        <v>0</v>
+      </c>
+      <c r="E250" t="n">
+        <v>5013051</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>CHI NHÁNH GIA LAI - CÔNG TY CỔ PHẦN DỊCH VỤ THƯƠNG MẠI TỔNG HỢP WINCOMMERCE</t>
+          <t>TRƯƠNG THỊ KHUYÊN</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>814320</v>
+        <v>0</v>
       </c>
       <c r="C251" t="n">
-        <v>0</v>
+        <v>21123415</v>
       </c>
       <c r="D251" t="n">
-        <v>814320</v>
+        <v>0</v>
+      </c>
+      <c r="E251" t="n">
+        <v>21123415</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ĐÀO THỊ NHUNG SÂM</t>
+          <t>CHI NHÁNH GIA LAI - CÔNG TY CỔ PHẦN DỊCH VỤ THƯƠNG MẠI TỔNG HỢP WINCOMMERCE</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>42077440</v>
+        <v>0</v>
       </c>
       <c r="C252" t="n">
-        <v>0</v>
+        <v>814320</v>
       </c>
       <c r="D252" t="n">
-        <v>42077440</v>
+        <v>0</v>
+      </c>
+      <c r="E252" t="n">
+        <v>814320</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THỰC PHẨM NHS</t>
+          <t>ĐÀO THỊ NHUNG SÂM</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>9259508</v>
+        <v>0</v>
       </c>
       <c r="C253" t="n">
-        <v>0</v>
+        <v>42077440</v>
       </c>
       <c r="D253" t="n">
-        <v>9259508</v>
+        <v>0</v>
+      </c>
+      <c r="E253" t="n">
+        <v>42077440</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>TRUNG TÂM VPP - VHP - MÁY VP - TẠP HÓA TRẦN PHÚ</t>
+          <t>CÔNG TY TNHH THỰC PHẨM NHS</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>3286473</v>
+        <v>0</v>
       </c>
       <c r="C254" t="n">
-        <v>0</v>
+        <v>9259508</v>
       </c>
       <c r="D254" t="n">
-        <v>3286473</v>
+        <v>0</v>
+      </c>
+      <c r="E254" t="n">
+        <v>9259508</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Bách Hóa Tổng Hợp Tư Tạo</t>
+          <t>TRUNG TÂM VPP - VHP - MÁY VP - TẠP HÓA TRẦN PHÚ</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>18031613</v>
+        <v>0</v>
       </c>
       <c r="C255" t="n">
-        <v>0</v>
+        <v>3286473</v>
       </c>
       <c r="D255" t="n">
-        <v>18031613</v>
+        <v>0</v>
+      </c>
+      <c r="E255" t="n">
+        <v>3286473</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh An Bình</t>
+          <t>Bách Hóa Tổng Hợp Tư Tạo</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>37425850</v>
+        <v>0</v>
       </c>
       <c r="C256" t="n">
-        <v>0</v>
+        <v>18031613</v>
       </c>
       <c r="D256" t="n">
-        <v>37425850</v>
+        <v>0</v>
+      </c>
+      <c r="E256" t="n">
+        <v>18031613</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH ĐẦU TƯ HOÀN SINH GIA LAI</t>
+          <t>Hộ Kinh Doanh An Bình</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>12389689</v>
+        <v>0</v>
       </c>
       <c r="C257" t="n">
-        <v>0</v>
+        <v>37425850</v>
       </c>
       <c r="D257" t="n">
-        <v>12389689</v>
+        <v>0</v>
+      </c>
+      <c r="E257" t="n">
+        <v>37425850</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN NƯỚC GIẢI KHÁT SANEST KHÁNH HÒA</t>
+          <t>CHI NHÁNH CÔNG TY TNHH ĐẦU TƯ HOÀN SINH GIA LAI</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>2971021</v>
+        <v>0</v>
       </c>
       <c r="C258" t="n">
-        <v>0</v>
+        <v>12389689</v>
       </c>
       <c r="D258" t="n">
-        <v>2971021</v>
+        <v>0</v>
+      </c>
+      <c r="E258" t="n">
+        <v>12389689</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>CỬA HÀNG LAN TÂM</t>
+          <t>CÔNG TY CỔ PHẦN NƯỚC GIẢI KHÁT SANEST KHÁNH HÒA</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>12302058</v>
+        <v>0</v>
       </c>
       <c r="C259" t="n">
-        <v>0</v>
+        <v>2971021</v>
       </c>
       <c r="D259" t="n">
-        <v>12302058</v>
+        <v>0</v>
+      </c>
+      <c r="E259" t="n">
+        <v>2971021</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH PHỐ NÚI RESTAURANT</t>
+          <t>CỬA HÀNG LAN TÂM</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>34735604</v>
+        <v>0</v>
       </c>
       <c r="C260" t="n">
-        <v>0</v>
+        <v>12302058</v>
       </c>
       <c r="D260" t="n">
-        <v>34735604</v>
+        <v>0</v>
+      </c>
+      <c r="E260" t="n">
+        <v>12302058</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Bùi Thành Trung</t>
+          <t>CÔNG TY TNHH PHỐ NÚI RESTAURANT</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>57172306</v>
+        <v>0</v>
       </c>
       <c r="C261" t="n">
-        <v>0</v>
+        <v>34735604</v>
       </c>
       <c r="D261" t="n">
-        <v>57172306</v>
+        <v>0</v>
+      </c>
+      <c r="E261" t="n">
+        <v>34735604</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>BÙI TRẦN THỊ LIỄU</t>
+          <t>Bùi Thành Trung</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>19416802</v>
+        <v>0</v>
       </c>
       <c r="C262" t="n">
-        <v>0</v>
+        <v>57172306</v>
       </c>
       <c r="D262" t="n">
-        <v>19416802</v>
+        <v>0</v>
+      </c>
+      <c r="E262" t="n">
+        <v>57172306</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Cửa Hàng Nhật  An</t>
+          <t>BÙI TRẦN THỊ LIỄU</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>18624060</v>
+        <v>0</v>
       </c>
       <c r="C263" t="n">
-        <v>0</v>
+        <v>19416802</v>
       </c>
       <c r="D263" t="n">
-        <v>18624060</v>
+        <v>0</v>
+      </c>
+      <c r="E263" t="n">
+        <v>19416802</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN TỨ QUÝ GIA LAI</t>
+          <t>Cửa Hàng Nhật  An</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>117288000</v>
+        <v>0</v>
       </c>
       <c r="C264" t="n">
-        <v>0</v>
+        <v>18624060</v>
       </c>
       <c r="D264" t="n">
-        <v>117288000</v>
+        <v>0</v>
+      </c>
+      <c r="E264" t="n">
+        <v>18624060</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BAMBO GIA LAI</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN TỨ QUÝ GIA LAI</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>2249569</v>
+        <v>0</v>
       </c>
       <c r="C265" t="n">
-        <v>0</v>
+        <v>117288000</v>
       </c>
       <c r="D265" t="n">
-        <v>2249569</v>
+        <v>0</v>
+      </c>
+      <c r="E265" t="n">
+        <v>117288000</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN HỆ THỐNG ẨM THỰC MIÊN DI GOURMET</t>
+          <t>CÔNG TY TNHH BAMBO GIA LAI</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>34799679</v>
+        <v>0</v>
       </c>
       <c r="C266" t="n">
-        <v>0</v>
+        <v>2249569</v>
       </c>
       <c r="D266" t="n">
-        <v>34799679</v>
+        <v>0</v>
+      </c>
+      <c r="E266" t="n">
+        <v>2249569</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Công Ty TNHH TM Ngọc Hoa</t>
+          <t>CÔNG TY CỔ PHẦN HỆ THỐNG ẨM THỰC MIÊN DI GOURMET</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>1782612</v>
+        <v>0</v>
       </c>
       <c r="C267" t="n">
-        <v>0</v>
+        <v>34799679</v>
       </c>
       <c r="D267" t="n">
-        <v>1782612</v>
+        <v>0</v>
+      </c>
+      <c r="E267" t="n">
+        <v>34799679</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Bel Việt Nam</t>
+          <t>Công Ty TNHH TM Ngọc Hoa</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>17143056</v>
+        <v>0</v>
       </c>
       <c r="C268" t="n">
-        <v>0</v>
+        <v>1782612</v>
       </c>
       <c r="D268" t="n">
-        <v>17143056</v>
+        <v>0</v>
+      </c>
+      <c r="E268" t="n">
+        <v>1782612</v>
       </c>
     </row>
     <row r="269">
@@ -4742,61 +5547,73 @@
         </is>
       </c>
       <c r="B269" t="n">
+        <v>0</v>
+      </c>
+      <c r="C269" t="n">
         <v>18981000</v>
       </c>
-      <c r="C269" t="n">
-        <v>0</v>
-      </c>
       <c r="D269" t="n">
+        <v>0</v>
+      </c>
+      <c r="E269" t="n">
         <v>18981000</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Cty TNHH MTV Lộc An Xuân</t>
+          <t>Công Ty TNHH Bel Việt Nam</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>18256590</v>
+        <v>0</v>
       </c>
       <c r="C270" t="n">
-        <v>0</v>
+        <v>17143056</v>
       </c>
       <c r="D270" t="n">
-        <v>18256590</v>
+        <v>0</v>
+      </c>
+      <c r="E270" t="n">
+        <v>17143056</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Trương Thị Mỹ Hà</t>
+          <t>Cty TNHH MTV Lộc An Xuân</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>38264775</v>
+        <v>0</v>
       </c>
       <c r="C271" t="n">
-        <v>0</v>
+        <v>18256590</v>
       </c>
       <c r="D271" t="n">
-        <v>38264775</v>
+        <v>0</v>
+      </c>
+      <c r="E271" t="n">
+        <v>18256590</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Phan Thị Ánh Lũy</t>
+          <t>Trương Thị Mỹ Hà</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>69261630</v>
+        <v>0</v>
       </c>
       <c r="C272" t="n">
-        <v>0</v>
+        <v>38264775</v>
       </c>
       <c r="D272" t="n">
-        <v>69261630</v>
+        <v>0</v>
+      </c>
+      <c r="E272" t="n">
+        <v>38264775</v>
       </c>
     </row>
     <row r="273">
@@ -4806,29 +5623,35 @@
         </is>
       </c>
       <c r="B273" t="n">
+        <v>0</v>
+      </c>
+      <c r="C273" t="n">
         <v>5400194</v>
       </c>
-      <c r="C273" t="n">
-        <v>0</v>
-      </c>
       <c r="D273" t="n">
+        <v>0</v>
+      </c>
+      <c r="E273" t="n">
         <v>5400194</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Trần Đăng Khoa</t>
+          <t>Phan Thị Ánh Lũy</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>155111160</v>
+        <v>0</v>
       </c>
       <c r="C274" t="n">
-        <v>0</v>
+        <v>69261630</v>
       </c>
       <c r="D274" t="n">
-        <v>155111160</v>
+        <v>0</v>
+      </c>
+      <c r="E274" t="n">
+        <v>69261630</v>
       </c>
     </row>
     <row r="275">
@@ -4838,221 +5661,263 @@
         </is>
       </c>
       <c r="B275" t="n">
+        <v>0</v>
+      </c>
+      <c r="C275" t="n">
         <v>114537266</v>
       </c>
-      <c r="C275" t="n">
-        <v>0</v>
-      </c>
       <c r="D275" t="n">
+        <v>0</v>
+      </c>
+      <c r="E275" t="n">
         <v>114537266</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Phạm Ngọc Lâm</t>
+          <t>Hồ Minh Ngân</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>173103828</v>
+        <v>0</v>
       </c>
       <c r="C276" t="n">
-        <v>0</v>
+        <v>71035603</v>
       </c>
       <c r="D276" t="n">
-        <v>173103828</v>
+        <v>0</v>
+      </c>
+      <c r="E276" t="n">
+        <v>71035603</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Hồ Minh Ngân</t>
+          <t>Phạm Ngọc Lâm</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>71035603</v>
+        <v>0</v>
       </c>
       <c r="C277" t="n">
-        <v>0</v>
+        <v>173103828</v>
       </c>
       <c r="D277" t="n">
-        <v>71035603</v>
+        <v>0</v>
+      </c>
+      <c r="E277" t="n">
+        <v>173103828</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN WIN FOODS GIA LAI</t>
+          <t>Trần Đăng Khoa</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>19643904</v>
+        <v>0</v>
       </c>
       <c r="C278" t="n">
-        <v>0</v>
+        <v>155111160</v>
       </c>
       <c r="D278" t="n">
-        <v>19643904</v>
+        <v>0</v>
+      </c>
+      <c r="E278" t="n">
+        <v>155111160</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Phan Thị Lâm</t>
+          <t>Nguyễn Tấn Đức</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>104212766</v>
+        <v>0</v>
       </c>
       <c r="C279" t="n">
-        <v>0</v>
+        <v>53502403</v>
       </c>
       <c r="D279" t="n">
-        <v>104212766</v>
+        <v>0</v>
+      </c>
+      <c r="E279" t="n">
+        <v>53502403</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Nguyễn Tấn Đức</t>
+          <t>Nguyễn Thành Phước</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>53502403</v>
+        <v>0</v>
       </c>
       <c r="C280" t="n">
-        <v>0</v>
+        <v>17073698</v>
       </c>
       <c r="D280" t="n">
-        <v>53502403</v>
+        <v>0</v>
+      </c>
+      <c r="E280" t="n">
+        <v>17073698</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Nguyễn Thành Phước</t>
+          <t>Phan Thị Lâm</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>17073698</v>
+        <v>0</v>
       </c>
       <c r="C281" t="n">
-        <v>0</v>
+        <v>104212766</v>
       </c>
       <c r="D281" t="n">
-        <v>17073698</v>
+        <v>0</v>
+      </c>
+      <c r="E281" t="n">
+        <v>104212766</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Trần Phương Thảo</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN WIN FOODS GIA LAI</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>146118433</v>
+        <v>0</v>
       </c>
       <c r="C282" t="n">
-        <v>0</v>
+        <v>19643904</v>
       </c>
       <c r="D282" t="n">
-        <v>146118433</v>
+        <v>0</v>
+      </c>
+      <c r="E282" t="n">
+        <v>19643904</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Thông</t>
+          <t>Trần Phương Thảo</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>138556211</v>
+        <v>0</v>
       </c>
       <c r="C283" t="n">
-        <v>0</v>
+        <v>146118433</v>
       </c>
       <c r="D283" t="n">
-        <v>138556211</v>
+        <v>0</v>
+      </c>
+      <c r="E283" t="n">
+        <v>146118433</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BAZAN FOOD</t>
+          <t>Nguyễn Văn Thông</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>2984565</v>
+        <v>0</v>
       </c>
       <c r="C284" t="n">
-        <v>0</v>
+        <v>138556211</v>
       </c>
       <c r="D284" t="n">
-        <v>2984565</v>
+        <v>0</v>
+      </c>
+      <c r="E284" t="n">
+        <v>138556211</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Cty TNHH MTV Minh Hà Gialai</t>
+          <t>CÔNG TY TNHH BAZAN FOOD</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>30879964</v>
+        <v>0</v>
       </c>
       <c r="C285" t="n">
-        <v>0</v>
+        <v>2984565</v>
       </c>
       <c r="D285" t="n">
-        <v>30879964</v>
+        <v>0</v>
+      </c>
+      <c r="E285" t="n">
+        <v>2984565</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Đoàn Thị Hồng Vân</t>
+          <t>Cty TNHH MTV Minh Hà Gialai</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>128445286</v>
+        <v>0</v>
       </c>
       <c r="C286" t="n">
-        <v>0</v>
+        <v>30879964</v>
       </c>
       <c r="D286" t="n">
-        <v>128445286</v>
+        <v>0</v>
+      </c>
+      <c r="E286" t="n">
+        <v>30879964</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Lê Thị Hồng Hà</t>
+          <t>Đoàn Thị Hồng Vân</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>88381672</v>
+        <v>0</v>
       </c>
       <c r="C287" t="n">
-        <v>0</v>
+        <v>128445286</v>
       </c>
       <c r="D287" t="n">
-        <v>88381672</v>
+        <v>0</v>
+      </c>
+      <c r="E287" t="n">
+        <v>128445286</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Văn Phòng Phẩm- Tạp Hóa Bảy</t>
+          <t>Lê Thị Hồng Hà</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>18981000</v>
+        <v>0</v>
       </c>
       <c r="C288" t="n">
-        <v>0</v>
+        <v>88381672</v>
       </c>
       <c r="D288" t="n">
-        <v>18981000</v>
+        <v>0</v>
+      </c>
+      <c r="E288" t="n">
+        <v>88381672</v>
       </c>
     </row>
     <row r="289">
@@ -5062,236 +5927,300 @@
         </is>
       </c>
       <c r="B289" t="n">
+        <v>0</v>
+      </c>
+      <c r="C289" t="n">
         <v>114003953</v>
       </c>
-      <c r="C289" t="n">
-        <v>0</v>
-      </c>
       <c r="D289" t="n">
+        <v>0</v>
+      </c>
+      <c r="E289" t="n">
         <v>114003953</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Công Ty TNHH SX Và DV TamBa</t>
+          <t>Văn Phòng Phẩm- Tạp Hóa Bảy</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>35761694</v>
+        <v>0</v>
       </c>
       <c r="C290" t="n">
-        <v>0</v>
+        <v>18981000</v>
       </c>
       <c r="D290" t="n">
-        <v>35761694</v>
+        <v>0</v>
+      </c>
+      <c r="E290" t="n">
+        <v>18981000</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Doanh Nghiệp Tư Nhân Thương Mại Thùy Dung</t>
+          <t>Công Ty TNHH SX Và DV TamBa</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>35855628</v>
+        <v>0</v>
       </c>
       <c r="C291" t="n">
-        <v>0</v>
+        <v>35761694</v>
       </c>
       <c r="D291" t="n">
-        <v>35855628</v>
+        <v>0</v>
+      </c>
+      <c r="E291" t="n">
+        <v>35761694</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN PRETZLE VIABLE</t>
+          <t>Doanh Nghiệp Tư Nhân Thương Mại Thùy Dung</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>3534369</v>
+        <v>0</v>
       </c>
       <c r="C292" t="n">
-        <v>0</v>
+        <v>35855628</v>
       </c>
       <c r="D292" t="n">
-        <v>3534369</v>
+        <v>0</v>
+      </c>
+      <c r="E292" t="n">
+        <v>35855628</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Một Thành Viên Minh Hà Gia Lai</t>
+          <t>BỆNH VIỆN ĐA KHOA TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>19212077</v>
+        <v>0</v>
       </c>
       <c r="C293" t="n">
-        <v>0</v>
+        <v>7916651</v>
       </c>
       <c r="D293" t="n">
-        <v>19212077</v>
+        <v>0</v>
+      </c>
+      <c r="E293" t="n">
+        <v>7916651</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>BỆNH VIỆN ĐA KHOA TỈNH GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN PRETZLE VIABLE</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>7916651</v>
+        <v>0</v>
       </c>
       <c r="C294" t="n">
-        <v>0</v>
+        <v>3534369</v>
       </c>
       <c r="D294" t="n">
-        <v>7916651</v>
+        <v>0</v>
+      </c>
+      <c r="E294" t="n">
+        <v>3534369</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Công Ty TNHH MTV Quỳnh Nguyên Gia Lai</t>
+          <t>Công Ty TNHH Một Thành Viên Minh Hà Gia Lai</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>403112</v>
+        <v>0</v>
       </c>
       <c r="C295" t="n">
-        <v>0</v>
+        <v>19212077</v>
       </c>
       <c r="D295" t="n">
-        <v>403112</v>
+        <v>0</v>
+      </c>
+      <c r="E295" t="n">
+        <v>19212077</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Trường THCS Nguyễn Viết Xuân</t>
+          <t>Công Ty TNHH MTV Quỳnh Nguyên Gia Lai</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>18775800</v>
+        <v>0</v>
       </c>
       <c r="C296" t="n">
-        <v>0</v>
+        <v>403112</v>
       </c>
       <c r="D296" t="n">
-        <v>18775800</v>
+        <v>0</v>
+      </c>
+      <c r="E296" t="n">
+        <v>403112</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Tứ Quý Gia Lai</t>
+          <t>Trường THCS Nguyễn Viết Xuân</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>18138600</v>
+        <v>0</v>
       </c>
       <c r="C297" t="n">
-        <v>0</v>
+        <v>18775800</v>
       </c>
       <c r="D297" t="n">
-        <v>18138600</v>
+        <v>0</v>
+      </c>
+      <c r="E297" t="n">
+        <v>18775800</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>BÙI THỊ HUYỀN</t>
+          <t>Công Ty TNHH Tứ Quý Gia Lai</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>39514581</v>
+        <v>0</v>
       </c>
       <c r="C298" t="n">
-        <v>0</v>
+        <v>18138600</v>
       </c>
       <c r="D298" t="n">
-        <v>39514581</v>
+        <v>0</v>
+      </c>
+      <c r="E298" t="n">
+        <v>18138600</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Công Ty TNHH MTV Gia Luân Gia Lai</t>
+          <t>BÙI THỊ HUYỀN</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>5471096</v>
+        <v>0</v>
       </c>
       <c r="C299" t="n">
-        <v>0</v>
+        <v>39514581</v>
       </c>
       <c r="D299" t="n">
-        <v>5471096</v>
+        <v>0</v>
+      </c>
+      <c r="E299" t="n">
+        <v>39514581</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>PHAN THỊ ÁNH MỸ</t>
+          <t>Công Ty TNHH MTV Gia Luân Gia Lai</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>5956200</v>
+        <v>0</v>
       </c>
       <c r="C300" t="n">
-        <v>0</v>
+        <v>5471096</v>
       </c>
       <c r="D300" t="n">
-        <v>5956200</v>
+        <v>0</v>
+      </c>
+      <c r="E300" t="n">
+        <v>5471096</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Đỗ Hà Trang</t>
+          <t>PHAN THỊ ÁNH MỸ</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>39601148</v>
+        <v>0</v>
       </c>
       <c r="C301" t="n">
-        <v>0</v>
+        <v>5956200</v>
       </c>
       <c r="D301" t="n">
-        <v>39601148</v>
+        <v>0</v>
+      </c>
+      <c r="E301" t="n">
+        <v>5956200</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Nguyễn Trịnh Minh Huy</t>
+          <t>Đỗ Hà Trang</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>39660336</v>
+        <v>0</v>
       </c>
       <c r="C302" t="n">
-        <v>0</v>
+        <v>39601148</v>
       </c>
       <c r="D302" t="n">
-        <v>39660336</v>
+        <v>0</v>
+      </c>
+      <c r="E302" t="n">
+        <v>39601148</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
+          <t>Nguyễn Trịnh Minh Huy</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>0</v>
+      </c>
+      <c r="C303" t="n">
+        <v>39660336</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0</v>
+      </c>
+      <c r="E303" t="n">
+        <v>39660336</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
           <t>Phường Hoa Lư. Tp Pleiku</t>
         </is>
       </c>
-      <c r="B303" t="n">
+      <c r="B304" t="n">
+        <v>0</v>
+      </c>
+      <c r="C304" t="n">
         <v>19872864</v>
       </c>
-      <c r="C303" t="n">
-        <v>0</v>
-      </c>
-      <c r="D303" t="n">
+      <c r="D304" t="n">
+        <v>0</v>
+      </c>
+      <c r="E304" t="n">
         <v>19872864</v>
       </c>
     </row>
@@ -5306,34 +6235,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Đối tượng</t>
+          <t>Nhà cung cấp</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>MUA VÀO</t>
+          <t>Số dư đầu</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ĐÃ TRẢ</t>
+          <t>Phát sinh Nợ (Trả)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DƯ CUỐI KỲ</t>
+          <t>Phát sinh Có (Mua)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Dư cuối</t>
         </is>
       </c>
     </row>
@@ -5344,7 +6279,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21791855</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -5352,6 +6287,9 @@
       <c r="D2" t="n">
         <v>21791855</v>
       </c>
+      <c r="E2" t="n">
+        <v>21791855</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5360,7 +6298,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>830567693</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -5368,133 +6306,160 @@
       <c r="D3" t="n">
         <v>830567693</v>
       </c>
+      <c r="E3" t="n">
+        <v>830567693</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BEL VIỆT NAM</t>
+          <t>Ngân hàng TMCP Ngoại thương Việt Nam</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8246551436</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>8246551436</v>
+        <v>3200627</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3200627</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Ngoại thương Việt Nam</t>
+          <t>CÔNG TY TNHH BEL VIỆT NAM</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3200627</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>3200627</v>
+        <v>8246551436</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8246551436</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN NƯỚC GIẢI KHÁT SANEST KHÁNH HÒA</t>
+          <t>sao kê Bidv 23.xls</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50214269701</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3430273365</v>
       </c>
       <c r="D6" t="n">
-        <v>50214269701</v>
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-3430273365</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THỰC PHẨM CHOLIMEX</t>
+          <t>CÔNG TY CỔ PHẦN VIỆT NAM KỸ NGHỆ SÚC SẢN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24617486040</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>24617486040</v>
+        <v>24575429136</v>
+      </c>
+      <c r="E7" t="n">
+        <v>24575429136</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN VIỆT NAM KỸ NGHỆ SÚC SẢN</t>
+          <t>CÔNG TY CỔ PHẦN THỰC PHẨM CHOLIMEX</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24575429136</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>24575429136</v>
+        <v>24617486040</v>
+      </c>
+      <c r="E8" t="n">
+        <v>24617486040</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Gia Lai </t>
+          <t>CÔNG TY CỔ PHẦN NƯỚC GIẢI KHÁT SANEST KHÁNH HÒA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1907972846</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1907972846</v>
+        <v>50214269701</v>
+      </c>
+      <c r="E9" t="n">
+        <v>50214269701</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 7 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
+          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Gia Lai </t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1559501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1559501</v>
+        <v>1907972846</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1907972846</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty CLM</t>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 7 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2023410510</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-2023410510</v>
+        <v>1559501</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1559501</v>
       </c>
     </row>
     <row r="12">
@@ -5504,7 +6469,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>241533</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -5512,6 +6477,9 @@
       <c r="D12" t="n">
         <v>241533</v>
       </c>
+      <c r="E12" t="n">
+        <v>241533</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5520,7 +6488,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>55159335</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -5528,443 +6496,527 @@
       <c r="D13" t="n">
         <v>55159335</v>
       </c>
+      <c r="E13" t="n">
+        <v>55159335</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty Yến</t>
+          <t>CÔNG TY TNHH NABATI VIỆT NAM</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10311253022</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-10311253022</v>
+        <v>14155929868</v>
+      </c>
+      <c r="E14" t="n">
+        <v>14155929868</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NABATI VIỆT NAM</t>
+          <t>Công ty Điện lực Gia Lai</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14155929868</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>14155929868</v>
+        <v>957344</v>
+      </c>
+      <c r="E15" t="n">
+        <v>957344</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty VS+NBT</t>
+          <t>CÔNG TY CỔ PHẦN TRƯỜNG XUÂN</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1047059026</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>-1047059026</v>
+        <v>12097000</v>
+      </c>
+      <c r="E16" t="n">
+        <v>12097000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Công ty Điện lực Gia Lai</t>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Gia Lai</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>957344</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>957344</v>
+        <v>1175020</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1175020</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty Vissan</t>
+          <t>NGAN HANG TMCP CONG THUONG VIET NAM - CN GIA LAI</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2675384521</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-2675384521</v>
+        <v>111352677</v>
+      </c>
+      <c r="E18" t="n">
+        <v>111352677</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN TRƯỜNG XUÂN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ÂN PHÚ KON TUM</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12097000</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>12097000</v>
+        <v>25716339</v>
+      </c>
+      <c r="E19" t="n">
+        <v>25716339</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Gia Lai</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN QUẢN LÝ NỢ VÀ KHAI THÁC TÀI SẢN NGÂN HÀNG TMCP CÔNG THƯƠNG VIỆT NAM</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1175020</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1175020</v>
+        <v>3300000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3300000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty Nbt</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>500842964</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>-500842964</v>
+        <v>33920000</v>
+      </c>
+      <c r="E21" t="n">
+        <v>33920000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NGAN HANG TMCP CONG THUONG VIET NAM - CN GIA LAI</t>
+          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Gia Lai</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>111352677</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>111352677</v>
+        <v>2888600</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2888600</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Vay VCB TT tiền hàng Cty Yến</t>
+          <t>CÔNG TY TNHH ĐĂNG KIỂM CAO NGUYÊN</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1896095709</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-1896095709</v>
+        <v>2053454</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2053454</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty VS</t>
+          <t>CÔNG TY CỔ PHẦN SOM TUM THAI</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>382900052</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-382900052</v>
+        <v>1555800</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1555800</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ÂN PHÚ KON TUM</t>
+          <t>Công Ty Cổ Phần Bệnh Viện Đa Khoa Tâm Anh TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25716339</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>25716339</v>
+        <v>31687194</v>
+      </c>
+      <c r="E25" t="n">
+        <v>31687194</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty Yến+VS+NBT</t>
+          <t>CÔNG TY TNHH HTV MẠNH PHƯƠNG F&amp;B</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>1481316545</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-1481316545</v>
+        <v>26542336</v>
+      </c>
+      <c r="E26" t="n">
+        <v>26542336</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN QUẢN LÝ NỢ VÀ KHAI THÁC TÀI SẢN NGÂN HÀNG TMCP CÔNG THƯƠNG VIỆT NAM</t>
+          <t>CHI NHÁNH CÔNG TY TNHH CHRISTIAN DIOR VIỆT NAM TẠI THÀNH PHỐ HỒ CHÍ MINH</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3300000</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>3300000</v>
+        <v>11415000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>11415000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
+          <t>CÔNG TY CỔ PHẦN QUỐC TẾ TAM SƠN - CHI NHÁNH HCM</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>33920000</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>33920000</v>
+        <v>62605000</v>
+      </c>
+      <c r="E28" t="n">
+        <v>62605000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty Nabati</t>
+          <t>Công ty TNHH Thuần Lý</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>254121566</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>-254121566</v>
+        <v>18390000</v>
+      </c>
+      <c r="E29" t="n">
+        <v>18390000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Vay Vcb tt tiền hàng Cty Clm</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DU LỊCH TÀU BẾN NGHÉ</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>526780035</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>-526780035</v>
+        <v>3061300</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3061300</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Gia Lai</t>
+          <t>CÔNG TY TNHH HAI DI LAO VIET NAM HOLDINGS - CHI NHÁNH THÀNH PHỐ HỒ CHÍ MINH</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2888600</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>2888600</v>
+        <v>1309000</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1309000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐĂNG KIỂM CAO NGUYÊN</t>
+          <t>Viettel Gia Lai- Chi nhánh Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2053454</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>2053454</v>
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN SOM TUM THAI</t>
+          <t>CÔNG TY TNHH MITRAMODE DUTA FASHINDO VIỆT NAM</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1555800</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1555800</v>
+        <v>16194000</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16194000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Công Ty Cổ Phần Bệnh Viện Đa Khoa Tâm Anh TP. Hồ Chí Minh</t>
+          <t>CÔNG TY CỔ PHẦN ĐIỆN TỬ VIỄN THÔNG ÁNH DƯƠNG</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>31687194</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>31687194</v>
+        <v>2970000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2970000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HTV MẠNH PHƯƠNG F&amp;B</t>
+          <t>CÔNG TY BẢO HIỂM BƯU ĐIỆN GIA LAI</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26542336</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>26542336</v>
+        <v>4770300</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4770300</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH CHRISTIAN DIOR VIỆT NAM TẠI THÀNH PHỐ HỒ CHÍ MINH</t>
+          <t>CÔNG TY TNHH MTV THƯƠNG MẠI &amp; DỊCH VỤ ẮC QUY DIỆN LIÊN</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>11415000</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>11415000</v>
+        <v>3300000</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3300000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN QUỐC TẾ TAM SƠN - CHI NHÁNH HCM</t>
+          <t>CÔNG TY TNHH MTV Ô TÔ TRƯỜNG HẢI GIA LAI</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>62605000</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>62605000</v>
+        <v>6418867</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6418867</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Công ty TNHH Thuần Lý</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MAY THÊU GIÀY AN PHƯỚC TẠI GIA LAI</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>18390000</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>18390000</v>
+        <v>2969400</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2969400</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DU LỊCH TÀU BẾN NGHÉ</t>
+          <t>CÔNG TY XĂNG DẦU NAM TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3061300</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>3061300</v>
+        <v>500000</v>
+      </c>
+      <c r="E39" t="n">
+        <v>500000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HAI DI LAO VIET NAM HOLDINGS - CHI NHÁNH THÀNH PHỐ HỒ CHÍ MINH</t>
+          <t>CÔNG TY CỔ PHẦN THỜI TRANG VÀ MỸ PHẨM DUY ANH</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1309000</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>1309000</v>
+        <v>35230000</v>
+      </c>
+      <c r="E40" t="n">
+        <v>35230000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Viettel Gia Lai- Chi nhánh Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+          <t>CÔNG TY TNHH MTV Ô TÔ GIA LAI</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -5974,630 +7026,237 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1817430</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1817430</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty VS= vay</t>
+          <t>TRUNG TÂM KINH DOANH VNPT - GIA LAI - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>532525085</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>-532525085</v>
+        <v>4332900</v>
+      </c>
+      <c r="E42" t="n">
+        <v>4332900</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MITRAMODE DUTA FASHINDO VIỆT NAM</t>
+          <t>CHI NHÁNH CÔNG TY TNHH TRUYỀN HÌNH CÁP SAIGONTOURIST-TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>16194000</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>16194000</v>
+        <v>1610000</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1610000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty Nabati+VS</t>
+          <t>CÔNG TY BẢO HIỂM BIDV BẮC TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>301878328</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>-301878328</v>
+        <v>3230700</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3230700</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Vay VCB tt tiền hàng Cty Bel</t>
+          <t>NGAN HANG TMCP CONG THUONG VIET NAM - 50098|CN GIA LAI</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>131227569</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>-131227569</v>
+        <v>159543182</v>
+      </c>
+      <c r="E45" t="n">
+        <v>159543182</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐIỆN TỬ VIỄN THÔNG ÁNH DƯƠNG</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HÀ ĐỨC VINH</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2970000</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>2970000</v>
+        <v>5200000</v>
+      </c>
+      <c r="E46" t="n">
+        <v>5200000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CÔNG TY BẢO HIỂM BƯU ĐIỆN GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN SÁCH VÀ THIẾT BỊ TRƯỜNG HỌC GIA LAI</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4770300</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>4770300</v>
+        <v>800000</v>
+      </c>
+      <c r="E47" t="n">
+        <v>800000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Vay Vcb tt tiền hàng Cty Yến</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN BẢO THUẬN</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>2034968400</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>-2034968400</v>
+        <v>4390000</v>
+      </c>
+      <c r="E48" t="n">
+        <v>4390000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV THƯƠNG MẠI &amp; DỊCH VỤ ẮC QUY DIỆN LIÊN</t>
+          <t>CÔNG TY TNHH THU PHÍ TỰ ĐỘNG VETC</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3300000</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>3300000</v>
+        <v>8847000</v>
+      </c>
+      <c r="E49" t="n">
+        <v>8847000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Vay VCB TT tiền hàng CTY Nabati</t>
+          <t>CÔNG TY BẢO HIỂM VIETINBANK BẮC TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>955809765</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>-955809765</v>
+        <v>1681000</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1681000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV Ô TÔ TRƯỜNG HẢI GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN AN PHÁT LỘC GIA LAI</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6418867</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>6418867</v>
+        <v>2866000</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2866000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Vay VCB TT tiền hàng CTY CLM</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THẾ HỆ MỚI GIA LAI</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>2576806319</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>-2576806319</v>
+        <v>11712950</v>
+      </c>
+      <c r="E52" t="n">
+        <v>11712950</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Vay VCB TT tiền hàng CTY Nabati VN</t>
+          <t>CN CÔNG TY CP PHÁT TRIỂN PHẦN MỀM ASIA TẠI ĐÀ NẴNG</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>725460393</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>-725460393</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Vay VCB TT tiền hàng CTY Yến SN</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" t="n">
-        <v>2700000000</v>
-      </c>
-      <c r="D54" t="n">
-        <v>-2700000000</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MAY THÊU GIÀY AN PHƯỚC TẠI GIA LAI</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>2969400</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="n">
-        <v>2969400</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Vay VCB TT tiền hàng CTY VISSAN</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" t="n">
-        <v>250151555</v>
-      </c>
-      <c r="D56" t="n">
-        <v>-250151555</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>CÔNG TY XĂNG DẦU NAM TÂY NGUYÊN</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN THỜI TRANG VÀ MỸ PHẨM DUY ANH</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>35230000</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="n">
-        <v>35230000</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MTV Ô TÔ GIA LAI</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>1817430</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" t="n">
-        <v>1817430</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Vay VCB TT tiền hàng CTY Yến</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" t="n">
-        <v>4714638720</v>
-      </c>
-      <c r="D60" t="n">
-        <v>-4714638720</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>TRUNG TÂM KINH DOANH VNPT - GIA LAI - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>4332900</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" t="n">
-        <v>4332900</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Vay VCB TT tiền hàng CTY Vissan</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" t="n">
-        <v>983516051</v>
-      </c>
-      <c r="D62" t="n">
-        <v>-983516051</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH CÔNG TY TNHH TRUYỀN HÌNH CÁP SAIGONTOURIST-TỈNH GIA LAI</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>1610000</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" t="n">
-        <v>1610000</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>CÔNG TY BẢO HIỂM BIDV BẮC TÂY NGUYÊN</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>3230700</v>
-      </c>
-      <c r="C64" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" t="n">
-        <v>3230700</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Vay VCB TT tiền hàng cty Yến SN</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>0</v>
-      </c>
-      <c r="C65" t="n">
-        <v>2755957600</v>
-      </c>
-      <c r="D65" t="n">
-        <v>-2755957600</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Vay VCB TT tiền hàng CLM</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>0</v>
-      </c>
-      <c r="C66" t="n">
-        <v>714632644</v>
-      </c>
-      <c r="D66" t="n">
-        <v>-714632644</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Vay VCB TT tiền hàng Vissan</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>0</v>
-      </c>
-      <c r="C67" t="n">
-        <v>911224575</v>
-      </c>
-      <c r="D67" t="n">
-        <v>-911224575</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>NGAN HANG TMCP CONG THUONG VIET NAM - 50098|CN GIA LAI</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>159543182</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" t="n">
-        <v>159543182</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Vay VCB TT tiền hàng CTY Visssan</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" t="n">
-        <v>240489903</v>
-      </c>
-      <c r="D69" t="n">
-        <v>-240489903</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN SÁCH VÀ THIẾT BỊ TRƯỜNG HỌC GIA LAI</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>800000</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" t="n">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HÀ ĐỨC VINH</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>5200000</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" t="n">
-        <v>5200000</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN BẢO THUẬN</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>4390000</v>
-      </c>
-      <c r="C72" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" t="n">
-        <v>4390000</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THU PHÍ TỰ ĐỘNG VETC</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>8847000</v>
-      </c>
-      <c r="C73" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" t="n">
-        <v>8847000</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>CÔNG TY BẢO HIỂM VIETINBANK BẮC TÂY NGUYÊN</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>1681000</v>
-      </c>
-      <c r="C74" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" t="n">
-        <v>1681000</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN AN PHÁT LỘC GIA LAI</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>2866000</v>
-      </c>
-      <c r="C75" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" t="n">
-        <v>2866000</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Vay VCB TT tiền hàng CTY CLM A : 272,950,420 + CLM B : 11,360,232 + VS : 167,379,844đ</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>0</v>
-      </c>
-      <c r="C76" t="n">
-        <v>451690496</v>
-      </c>
-      <c r="D76" t="n">
-        <v>-451690496</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Vay VCB TT tiền hàng CTY VS</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>0</v>
-      </c>
-      <c r="C77" t="n">
-        <v>254815217</v>
-      </c>
-      <c r="D77" t="n">
-        <v>-254815217</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THẾ HỆ MỚI GIA LAI</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>11712950</v>
-      </c>
-      <c r="C78" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" t="n">
-        <v>11712950</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Vay VCB TT tiền hàng Cty CLM</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" t="n">
-        <v>279542523</v>
-      </c>
-      <c r="D79" t="n">
-        <v>-279542523</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>CN CÔNG TY CP PHÁT TRIỂN PHẦN MỀM ASIA TẠI ĐÀ NẴNG</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
         <v>14000000</v>
       </c>
-      <c r="C80" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" t="n">
+      <c r="E53" t="n">
         <v>14000000</v>
       </c>
     </row>

--- a/docs/hoang-huy-phat/sosach2023/BAO_CAO_CONG_NO_HHP_2023.xlsx
+++ b/docs/hoang-huy-phat/sosach2023/BAO_CAO_CONG_NO_HHP_2023.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="131 - Phải thu" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="331 - Phải trả" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KHACH_HANG_131" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NHA_CUNG_CAP_331" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,58 +432,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E304"/>
+  <dimension ref="A1:D312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Khách hàng</t>
+          <t>Đối tượng</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Số dư đầu</t>
+          <t>BÁN RA</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Phát sinh Nợ (Bán)</t>
+          <t>ĐÃ THU</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Phát sinh Có (Thu)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Dư cuối</t>
+          <t>DƯ CUỐI KỲ</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>98424342419</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
+        <v>98424342419</v>
       </c>
     </row>
     <row r="3">
@@ -493,15 +486,12 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>149170604</v>
       </c>
       <c r="C3" t="n">
-        <v>149170604</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
         <v>149170604</v>
       </c>
     </row>
@@ -512,35 +502,29 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>303101385</v>
       </c>
       <c r="C4" t="n">
-        <v>303101385</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
         <v>303101385</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sao kê Bidv 23.xls</t>
+          <t>Trả gốc vay</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>66568600729</v>
       </c>
       <c r="D5" t="n">
-        <v>3428218174</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-3428218174</v>
+        <v>-66568600729</v>
       </c>
     </row>
     <row r="6">
@@ -550,15 +534,12 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>489599374</v>
       </c>
       <c r="C6" t="n">
-        <v>489599374</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
         <v>489599374</v>
       </c>
     </row>
@@ -569,15 +550,12 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>118727461</v>
       </c>
       <c r="C7" t="n">
-        <v>118727461</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
         <v>118727461</v>
       </c>
     </row>
@@ -588,15 +566,12 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>108771796</v>
       </c>
       <c r="C8" t="n">
-        <v>108771796</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
         <v>108771796</v>
       </c>
     </row>
@@ -607,15 +582,12 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>607200</v>
       </c>
       <c r="C9" t="n">
-        <v>607200</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
         <v>607200</v>
       </c>
     </row>
@@ -626,54 +598,45 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>73850617</v>
       </c>
       <c r="C10" t="n">
-        <v>73850617</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
         <v>73850617</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lê Thị Thu Ba</t>
+          <t>Nguyễn Thị Hải Thanh</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>99568668</v>
       </c>
       <c r="C11" t="n">
-        <v>120703208</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>120703208</v>
+        <v>99568668</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Hải Thanh</t>
+          <t>NHÀ SÁCH VẠN TRÍ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2548744</v>
       </c>
       <c r="C12" t="n">
-        <v>99568668</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>99568668</v>
+        <v>2548744</v>
       </c>
     </row>
     <row r="13">
@@ -683,168 +646,141 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>31301277</v>
       </c>
       <c r="C13" t="n">
-        <v>31301277</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
         <v>31301277</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NHÀ SÁCH VẠN TRÍ</t>
+          <t>Bùi Thị Dung</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>195398686</v>
       </c>
       <c r="C14" t="n">
-        <v>2548744</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2548744</v>
+        <v>195398686</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bùi Thị Dung</t>
+          <t>Lê Thị Thu Ba</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>120703208</v>
       </c>
       <c r="C15" t="n">
-        <v>195398686</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>195398686</v>
+        <v>120703208</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Khánh Hà</t>
+          <t>Đặng Thị Luyến</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>152002192</v>
       </c>
       <c r="C16" t="n">
-        <v>174239731</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>174239731</v>
+        <v>152002192</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Đặng Thị Luyến</t>
+          <t>CÔNG TY ĐIỆN LỰC GIA LAI</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>4191000</v>
       </c>
       <c r="C17" t="n">
-        <v>152002192</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>152002192</v>
+        <v>4191000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CÔNG TY ĐIỆN LỰC GIA LAI</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>53903780</v>
       </c>
       <c r="C18" t="n">
-        <v>4191000</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>4191000</v>
+        <v>53903780</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
+          <t>Cửa Hàng Nhật An</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>53345488</v>
       </c>
       <c r="C19" t="n">
-        <v>53903780</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>53903780</v>
+        <v>53345488</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cửa Hàng Nhật An</t>
+          <t>Lê Thị Chanh</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>198072703</v>
       </c>
       <c r="C20" t="n">
-        <v>53345488</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>53345488</v>
+        <v>198072703</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lê Thị Chanh</t>
+          <t>Khánh Hà</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>174239731</v>
       </c>
       <c r="C21" t="n">
-        <v>198072703</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>198072703</v>
+        <v>174239731</v>
       </c>
     </row>
     <row r="22">
@@ -854,15 +790,12 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>66979186</v>
       </c>
       <c r="C22" t="n">
-        <v>66979186</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
         <v>66979186</v>
       </c>
     </row>
@@ -873,15 +806,12 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1856854</v>
       </c>
       <c r="C23" t="n">
-        <v>1856854</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
         <v>1856854</v>
       </c>
     </row>
@@ -892,15 +822,12 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>134005420</v>
       </c>
       <c r="C24" t="n">
-        <v>134005420</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
         <v>134005420</v>
       </c>
     </row>
@@ -911,92 +838,77 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>16524465</v>
       </c>
       <c r="C25" t="n">
-        <v>16524465</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
         <v>16524465</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CHI NHÁNH KHÁCH SẠN HOÀNG ANH GIA LAI</t>
+          <t>Phạm Văn Hùng</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>114535770</v>
       </c>
       <c r="C26" t="n">
-        <v>69046765</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>69046765</v>
+        <v>114535770</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Phạm Văn Hùng</t>
+          <t>CHI NHÁNH KHÁCH SẠN HOÀNG ANH GIA LAI</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>69046765</v>
       </c>
       <c r="C27" t="n">
-        <v>114535770</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>114535770</v>
+        <v>69046765</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tống Thị Lan</t>
+          <t>Mai Thị Thủy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>92676236</v>
       </c>
       <c r="C28" t="n">
-        <v>75661056</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>75661056</v>
+        <v>92676236</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mai Thị Thủy</t>
+          <t>Tống Thị Lan</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>75661056</v>
       </c>
       <c r="C29" t="n">
-        <v>92676236</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>92676236</v>
+        <v>75661056</v>
       </c>
     </row>
     <row r="30">
@@ -1006,15 +918,12 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>73757627</v>
       </c>
       <c r="C30" t="n">
-        <v>73757627</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
         <v>73757627</v>
       </c>
     </row>
@@ -1025,15 +934,12 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>134522211</v>
       </c>
       <c r="C31" t="n">
-        <v>134522211</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
         <v>134522211</v>
       </c>
     </row>
@@ -1044,15 +950,12 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>238275640</v>
       </c>
       <c r="C32" t="n">
-        <v>238275640</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
         <v>238275640</v>
       </c>
     </row>
@@ -1063,15 +966,12 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>95699723</v>
       </c>
       <c r="C33" t="n">
-        <v>95699723</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
         <v>95699723</v>
       </c>
     </row>
@@ -1082,15 +982,12 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>68022735</v>
       </c>
       <c r="C34" t="n">
-        <v>68022735</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
         <v>68022735</v>
       </c>
     </row>
@@ -1101,396 +998,333 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>24239063</v>
       </c>
       <c r="C35" t="n">
-        <v>24239063</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
         <v>24239063</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CỬA HÀNG HỒNG NHUNG</t>
+          <t>Thanh toán tiền hàng Cty Nabati</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>57654872</v>
+        <v>600000</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>57654872</v>
+        <v>-600000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN LÊ CANG ÂN</t>
+          <t>CỬA HÀNG HỒNG NHUNG</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>57654872</v>
       </c>
       <c r="C37" t="n">
-        <v>14815563</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>14815563</v>
+        <v>57654872</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN NGUYỄN HIỆU GIA LAI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN LÊ CANG ÂN</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>14815563</v>
       </c>
       <c r="C38" t="n">
-        <v>61130160</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>61130160</v>
+        <v>14815563</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THỰC PHẨM CHOLIMEX</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN NGUYỄN HIỆU GIA LAI</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>61130160</v>
       </c>
       <c r="C39" t="n">
-        <v>776377752</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>776377752</v>
+        <v>61130160</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BEL VIỆT NAM</t>
+          <t>CÔNG TY CỔ PHẦN THỰC PHẨM CHOLIMEX</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>776377752</v>
       </c>
       <c r="C40" t="n">
-        <v>162557801</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
-        <v>162557801</v>
+        <v>776377752</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Tạp Hóa Hoàng Phát</t>
+          <t>Trả các khoản vay</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>16962352</v>
+        <v>67001000</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="n">
-        <v>16962352</v>
+        <v>-67001000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Hà Thị Thúy An</t>
+          <t>CÔNG TY TNHH BEL VIỆT NAM</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>162557801</v>
       </c>
       <c r="C42" t="n">
-        <v>77418077</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="n">
-        <v>77418077</v>
+        <v>162557801</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẢI ANH TIẾN</t>
+          <t>Trần Thanh Lương</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>77768432</v>
       </c>
       <c r="C43" t="n">
-        <v>86188966</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="n">
-        <v>86188966</v>
+        <v>77768432</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Huỳnh Văn Định</t>
+          <t>TẠP HÓA KHÁNH HÀ</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>23601721</v>
       </c>
       <c r="C44" t="n">
-        <v>77476395</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>77476395</v>
+        <v>23601721</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TẠP HÓA KHÁNH HÀ</t>
+          <t>Huỳnh Văn Định</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>77476395</v>
       </c>
       <c r="C45" t="n">
-        <v>23601721</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="n">
-        <v>23601721</v>
+        <v>77476395</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Trần Thanh Lương</t>
+          <t>Tạp Hóa Hoàng Phát</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>16962352</v>
       </c>
       <c r="C46" t="n">
-        <v>77768432</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="n">
-        <v>77768432</v>
+        <v>16962352</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>VŨ TRỌNG PHƯƠNG</t>
+          <t>Hà Thị Thúy An</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>77418077</v>
       </c>
       <c r="C47" t="n">
-        <v>57397069</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="n">
-        <v>57397069</v>
+        <v>77418077</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TẠP HÓA THÙY LINH</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HẢI ANH TIẾN</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>86188966</v>
       </c>
       <c r="C48" t="n">
-        <v>42317063</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="n">
-        <v>42317063</v>
+        <v>86188966</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HỘ KINH DOAN ĐẶNG THỊ DIỄM</t>
+          <t>VŨ TRỌNG PHƯƠNG</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>57397069</v>
       </c>
       <c r="C49" t="n">
-        <v>5578462</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="n">
-        <v>5578462</v>
+        <v>57397069</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH TRẦN VĂN THỨC</t>
+          <t>TẠP HÓA THÙY LINH</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>42317063</v>
       </c>
       <c r="C50" t="n">
-        <v>77438398</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="n">
-        <v>77438398</v>
+        <v>42317063</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TẠP PHẨM KHÁNH AN</t>
+          <t>HỘ KINH DOAN ĐẶNG THỊ DIỄM</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>5578462</v>
       </c>
       <c r="C51" t="n">
-        <v>2964343</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="n">
-        <v>2964343</v>
+        <v>5578462</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ THẢO</t>
+          <t>TẠP PHẨM KHÁNH AN</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>2964343</v>
       </c>
       <c r="C52" t="n">
-        <v>41052529</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="n">
-        <v>41052529</v>
+        <v>2964343</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Lê Thị Tuyết Anh</t>
+          <t>NGUYỄN THỊ THẢO</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>41052529</v>
       </c>
       <c r="C53" t="n">
-        <v>75481879</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="n">
-        <v>75481879</v>
+        <v>41052529</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ THANH HƯƠNG</t>
+          <t>HỘ KINH DOANH TRẦN VĂN THỨC</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>77438398</v>
       </c>
       <c r="C54" t="n">
-        <v>76418221</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="n">
-        <v>76418221</v>
+        <v>77438398</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN THỊ BÍCH THUẬN</t>
+          <t>Lê Thị Tuyết Anh</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>75481879</v>
       </c>
       <c r="C55" t="n">
-        <v>95198734</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>95198734</v>
+        <v>75481879</v>
       </c>
     </row>
     <row r="56">
@@ -1500,15 +1334,12 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>80077301</v>
       </c>
       <c r="C56" t="n">
-        <v>80077301</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="n">
         <v>80077301</v>
       </c>
     </row>
@@ -1519,725 +1350,611 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>27381529</v>
       </c>
       <c r="C57" t="n">
-        <v>27381529</v>
+        <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="n">
         <v>27381529</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ SƯƠNG</t>
+          <t>HỘ KINH DOANH NGUYỄN THỊ BÍCH THUẬN</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>95198734</v>
       </c>
       <c r="C58" t="n">
-        <v>57136188</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" t="n">
-        <v>57136188</v>
+        <v>95198734</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cửa Hàng Mua Bán Tạp Hóa Và Dụng Cụ Gia Đình Ngọc Hân</t>
+          <t>HỘ KINH DOANH NGUYỄN THỊ THANH HƯƠNG</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>76418221</v>
       </c>
       <c r="C59" t="n">
-        <v>118850900</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" t="n">
-        <v>118850900</v>
+        <v>76418221</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN MINH PHƯƠNG</t>
+          <t>Cửa Hàng Mua Bán Tạp Hóa Và Dụng Cụ Gia Đình Ngọc Hân</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>118850900</v>
       </c>
       <c r="C60" t="n">
-        <v>93016476</v>
+        <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="n">
-        <v>93016476</v>
+        <v>118850900</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ĐẶNG THỊ THỦY</t>
+          <t>NGUYỄN THỊ SƯƠNG</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>57136188</v>
       </c>
       <c r="C61" t="n">
-        <v>112695734</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="n">
-        <v>112695734</v>
+        <v>57136188</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN SẢN XUẤT THƯƠNG MẠI DỊCH VỤ MỘC GIA</t>
+          <t>HỘ KINH DOANH NGUYỄN MINH PHƯƠNG</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>93016476</v>
       </c>
       <c r="C62" t="n">
-        <v>63542833</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="n">
-        <v>63542833</v>
+        <v>93016476</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Lê Quang Vinh</t>
+          <t>ĐẶNG THỊ THỦY</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>112695734</v>
       </c>
       <c r="C63" t="n">
-        <v>144886746</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="n">
-        <v>144886746</v>
+        <v>112695734</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CÔNG TY BẢO VIỆT GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN SẢN XUẤT THƯƠNG MẠI DỊCH VỤ MỘC GIA</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>63542833</v>
       </c>
       <c r="C64" t="n">
-        <v>3661275</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="n">
-        <v>3661275</v>
+        <v>63542833</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NABATI VIỆT NAM</t>
+          <t>Nuyễn Thị Đang Loan</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>100290250</v>
+        <v>5929267000</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" t="n">
-        <v>100290250</v>
+        <v>-5929267000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ĐỒNG THỊ TUYẾT</t>
+          <t>Lê Quang Vinh</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>144886746</v>
       </c>
       <c r="C66" t="n">
-        <v>47802470</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" t="n">
-        <v>47802470</v>
+        <v>144886746</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>LÊ TUẤN HẢI</t>
+          <t>VCB luon chuyen</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>0</v>
       </c>
       <c r="C67" t="n">
-        <v>77202297</v>
+        <v>340000000</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" t="n">
-        <v>77202297</v>
+        <v>-340000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH PHẠM ĐÀO DẠ THẢO</t>
+          <t xml:space="preserve">Lý chuyển </t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>44605161</v>
+        <v>49000000</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="n">
-        <v>44605161</v>
+        <v>-49000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LÊ THỊ LINH PHƯƠNG</t>
+          <t>CÔNG TY BẢO VIỆT GIA LAI</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>3661275</v>
       </c>
       <c r="C69" t="n">
-        <v>87455197</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" t="n">
-        <v>87455197</v>
+        <v>3661275</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH PHAN THỊ ÁNH NHUNG</t>
+          <t>CÔNG TY TNHH NABATI VIỆT NAM</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>100290250</v>
       </c>
       <c r="C70" t="n">
-        <v>16661853</v>
+        <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="n">
-        <v>16661853</v>
+        <v>100290250</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN KEN</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ĐỒNG THỊ TUYẾT</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>47802470</v>
       </c>
       <c r="C71" t="n">
-        <v>3988330</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="n">
-        <v>3988330</v>
+        <v>47802470</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV HOÀNG ANH QUÂN GIA LAI</t>
+          <t>LÊ TUẤN HẢI</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>77202297</v>
       </c>
       <c r="C72" t="n">
-        <v>10917528</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>10917528</v>
+        <v>77202297</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PHAN XUÂN TUẤN</t>
+          <t>HỘ KINH DOANH PHẠM ĐÀO DẠ THẢO</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>44605161</v>
       </c>
       <c r="C73" t="n">
-        <v>32843778</v>
+        <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="n">
-        <v>32843778</v>
+        <v>44605161</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Vũ</t>
+          <t>LÊ THỊ LINH PHƯƠNG</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>87455197</v>
       </c>
       <c r="C74" t="n">
-        <v>44446971</v>
+        <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="n">
-        <v>44446971</v>
+        <v>87455197</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GIÁM SÁT TRỊNH HOÀNG SƠN</t>
+          <t>DOANH NGHIỆP TƯ NHÂN KEN</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0</v>
+        <v>3988330</v>
       </c>
       <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
+        <v>3988330</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ẨM THỰC CÔ DUYÊN</t>
+          <t>HỘ KINH DOANH PHAN THỊ ÁNH NHUNG</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0</v>
+        <v>16661853</v>
       </c>
       <c r="C76" t="n">
-        <v>18177736</v>
+        <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" t="n">
-        <v>18177736</v>
+        <v>16661853</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CÔNG TY BẢO HIỂM BIDV BẮC TÂY NGUYÊN</t>
+          <t>CÔNG TY TNHH MTV HOÀNG ANH QUÂN GIA LAI</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>10917528</v>
       </c>
       <c r="C77" t="n">
-        <v>143713599</v>
+        <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" t="n">
-        <v>143713599</v>
+        <v>10917528</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Như Ý</t>
+          <t>Nguyễn Văn Vũ</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>44446971</v>
       </c>
       <c r="C78" t="n">
-        <v>3262813</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" t="n">
-        <v>3262813</v>
+        <v>44446971</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PHẠM THỊ THU TRANG</t>
+          <t>PHAN XUÂN TUẤN</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>32843778</v>
       </c>
       <c r="C79" t="n">
-        <v>65479968</v>
+        <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" t="n">
-        <v>65479968</v>
+        <v>32843778</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TẠP HÓA SƠN THƯƠNG</t>
+          <t>GIÁM SÁT TRỊNH HOÀNG SƠN</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>0</v>
       </c>
       <c r="C80" t="n">
-        <v>137958045</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
-      </c>
-      <c r="E80" t="n">
-        <v>137958045</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ĐINH VĂN CƯỜNG</t>
+          <t>Như Ý</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>3262813</v>
       </c>
       <c r="C81" t="n">
-        <v>100594786</v>
+        <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" t="n">
-        <v>100594786</v>
+        <v>3262813</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI GIA LAI</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ẨM THỰC CÔ DUYÊN</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>18177736</v>
       </c>
       <c r="C82" t="n">
-        <v>52635998</v>
+        <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" t="n">
-        <v>52635998</v>
+        <v>18177736</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TẠP HÓA BỐN PHƯƠNG</t>
+          <t>CÔNG TY BẢO HIỂM BIDV BẮC TÂY NGUYÊN</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>143713599</v>
       </c>
       <c r="C83" t="n">
-        <v>9172417</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" t="n">
-        <v>9172417</v>
+        <v>143713599</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PHAN THỊ NGỌC OANH</t>
+          <t>PHẠM THỊ THU TRANG</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>65479968</v>
       </c>
       <c r="C84" t="n">
-        <v>81830212</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" t="n">
-        <v>81830212</v>
+        <v>65479968</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Lê Vũ Thanh Nga</t>
+          <t>ĐINH VĂN CƯỜNG</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>100594786</v>
       </c>
       <c r="C85" t="n">
-        <v>42730686</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" t="n">
-        <v>42730686</v>
+        <v>100594786</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TẠP HÓA HOÀNG PHÁT</t>
+          <t>TẠP HÓA SƠN THƯƠNG</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>137958045</v>
       </c>
       <c r="C86" t="n">
-        <v>19384101</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" t="n">
-        <v>19384101</v>
+        <v>137958045</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN NHÀ HÀNG HỒNG LUYẾN</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI GIA LAI</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>52635998</v>
       </c>
       <c r="C87" t="n">
-        <v>1351449</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" t="n">
-        <v>1351449</v>
+        <v>52635998</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PHOTOCOPY - VĂN PHÒNG PHẨM - TẠP HÓA BẢY</t>
+          <t>TẠP HÓA BỐN PHƯƠNG</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>9172417</v>
       </c>
       <c r="C88" t="n">
-        <v>35745235</v>
+        <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" t="n">
-        <v>35745235</v>
+        <v>9172417</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TRẦN THANH THỦY</t>
+          <t>PHAN THỊ NGỌC OANH</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>81830212</v>
       </c>
       <c r="C89" t="n">
-        <v>4055040</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" t="n">
-        <v>4055040</v>
+        <v>81830212</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GIÁM SÁT ĐINH VĂN VIÊN</t>
+          <t>Lê Vũ Thanh Nga</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>42730686</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0</v>
+        <v>42730686</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CỬA HÀNG NHẬT AN</t>
+          <t>TẠP HÓA HOÀNG PHÁT</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0</v>
+        <v>19384101</v>
       </c>
       <c r="C91" t="n">
-        <v>38930264</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="n">
-        <v>38930264</v>
+        <v>19384101</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV KIÊN NGUYỄN</t>
+          <t>DOANH NGHIỆP TƯ NHÂN NHÀ HÀNG HỒNG LUYẾN</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>1351449</v>
       </c>
       <c r="C92" t="n">
-        <v>2193686</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" t="n">
-        <v>2193686</v>
+        <v>1351449</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH VĨNH HIỆP</t>
+          <t>PHOTOCOPY - VĂN PHÒNG PHẨM - TẠP HÓA BẢY</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>35745235</v>
       </c>
       <c r="C93" t="n">
-        <v>58793864</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" t="n">
-        <v>58793864</v>
+        <v>35745235</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MỘT THÀNH VIÊN NGUYỄN HIỆU GIA LAI-DỊCH VỤ GIẢI TRÍ PARADISE</t>
+          <t>TRẦN THANH THỦY</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0</v>
+        <v>4055040</v>
       </c>
       <c r="C94" t="n">
-        <v>24918968</v>
+        <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" t="n">
-        <v>24918968</v>
+        <v>4055040</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GIÁM SÁT HUỲNH ĐỨC AN</t>
+          <t>GIÁM SÁT ĐINH VĂN VIÊN</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2247,428 +1964,359 @@
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Bách Hóa Tổng Hợp Sĩ Quỳnh</t>
+          <t>CỬA HÀNG NHẬT AN</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>38930264</v>
       </c>
       <c r="C96" t="n">
-        <v>121490463</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" t="n">
-        <v>121490463</v>
+        <v>38930264</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TẠP HÓA PHẠM HỒNG QUÂN</t>
+          <t>CÔNG TY TNHH MTV KIÊN NGUYỄN</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0</v>
+        <v>2193686</v>
       </c>
       <c r="C97" t="n">
-        <v>94704331</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" t="n">
-        <v>94704331</v>
+        <v>2193686</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>HỒ VĂN CÔNG</t>
+          <t>CÔNG TY TNHH VĨNH HIỆP</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>58793864</v>
       </c>
       <c r="C98" t="n">
-        <v>70075802</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" t="n">
-        <v>70075802</v>
+        <v>58793864</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TM-DV HIẾU ĐỨC</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MỘT THÀNH VIÊN NGUYỄN HIỆU GIA LAI-DỊCH VỤ GIẢI TRÍ PARADISE</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>24918968</v>
       </c>
       <c r="C99" t="n">
-        <v>15771280</v>
+        <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" t="n">
-        <v>15771280</v>
+        <v>24918968</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ĐẶC SẢN CÁ MEKONG THANH TRÚC - ĐỊA ĐIỂM KINH DOANH CÔNG TY TNHH MỘT THÀNH VIÊN VIỄN THÔNG T&amp;T GIA LAI</t>
+          <t>GIÁM SÁT HUỲNH ĐỨC AN</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>5713448</v>
+        <v>0</v>
       </c>
       <c r="D100" t="n">
         <v>0</v>
-      </c>
-      <c r="E100" t="n">
-        <v>5713448</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH THỦY HÒA</t>
+          <t>Bách Hóa Tổng Hợp Sĩ Quỳnh</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>121490463</v>
       </c>
       <c r="C101" t="n">
-        <v>16944794</v>
+        <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" t="n">
-        <v>16944794</v>
+        <v>121490463</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Lương Thị Liễu</t>
+          <t>TẠP HÓA PHẠM HỒNG QUÂN</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>94704331</v>
       </c>
       <c r="C102" t="n">
-        <v>112580783</v>
+        <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" t="n">
-        <v>112580783</v>
+        <v>94704331</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Đặng Thị Kim Liễu</t>
+          <t>HỒ VĂN CÔNG</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0</v>
+        <v>70075802</v>
       </c>
       <c r="C103" t="n">
-        <v>168991911</v>
+        <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" t="n">
-        <v>168991911</v>
+        <v>70075802</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Hà Thị Ánh Thu</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN TM-DV HIẾU ĐỨC</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>15771280</v>
       </c>
       <c r="C104" t="n">
-        <v>31768870</v>
+        <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" t="n">
-        <v>31768870</v>
+        <v>15771280</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Đàm Văn Tú</t>
+          <t>ĐẶC SẢN CÁ MEKONG THANH TRÚC - ĐỊA ĐIỂM KINH DOANH CÔNG TY TNHH MỘT THÀNH VIÊN VIỄN THÔNG T&amp;T GIA LAI</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>5713448</v>
       </c>
       <c r="C105" t="n">
-        <v>202030757</v>
+        <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" t="n">
-        <v>202030757</v>
+        <v>5713448</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TẠP HÓA HỒNG NHUNG</t>
+          <t>HỘ KINH DOANH THỦY HÒA</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>16944794</v>
       </c>
       <c r="C106" t="n">
-        <v>12402720</v>
+        <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" t="n">
-        <v>12402720</v>
+        <v>16944794</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Văn Thị Trang</t>
+          <t>TẠP HÓA HỒNG NHUNG</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0</v>
+        <v>12402720</v>
       </c>
       <c r="C107" t="n">
-        <v>64511283</v>
+        <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" t="n">
-        <v>64511283</v>
+        <v>12402720</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Đinh Văn Phúc</t>
+          <t>Lương Thị Liễu</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>112580783</v>
       </c>
       <c r="C108" t="n">
-        <v>106849534</v>
+        <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" t="n">
-        <v>106849534</v>
+        <v>112580783</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Đậu Đức Hào</t>
+          <t>Đàm Văn Tú</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0</v>
+        <v>202030757</v>
       </c>
       <c r="C109" t="n">
-        <v>238603563</v>
+        <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109" t="n">
-        <v>238603563</v>
+        <v>202030757</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TRẦN KIM HUẾ</t>
+          <t>Đặng Thị Kim Liễu</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>168991911</v>
       </c>
       <c r="C110" t="n">
-        <v>193931531</v>
+        <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" t="n">
-        <v>193931531</v>
+        <v>168991911</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Đoàn Hữu Minh</t>
+          <t>Hà Thị Ánh Thu</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>31768870</v>
       </c>
       <c r="C111" t="n">
-        <v>113495115</v>
+        <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" t="n">
-        <v>113495115</v>
+        <v>31768870</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DOANH NGHIỆP TƯ NHÂN HỒNG BIÊN</t>
+          <t>Đoàn Hữu Minh</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0</v>
+        <v>113495115</v>
       </c>
       <c r="C112" t="n">
-        <v>5741340</v>
+        <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
-      </c>
-      <c r="E112" t="n">
-        <v>5741340</v>
+        <v>113495115</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Hoàng Chí Công</t>
+          <t>Đinh Văn Phúc</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0</v>
+        <v>106849534</v>
       </c>
       <c r="C113" t="n">
-        <v>147289986</v>
+        <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" t="n">
-        <v>147289986</v>
+        <v>106849534</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Huỳnh Thị Trúc Ly</t>
+          <t>Đậu Đức Hào</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0</v>
+        <v>238603563</v>
       </c>
       <c r="C114" t="n">
-        <v>172721649</v>
+        <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" t="n">
-        <v>172721649</v>
+        <v>238603563</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Lê Văn Mẫn</t>
+          <t>TRẦN KIM HUẾ</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0</v>
+        <v>193931531</v>
       </c>
       <c r="C115" t="n">
-        <v>235395239</v>
+        <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" t="n">
-        <v>235395239</v>
+        <v>193931531</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Nguyễn Minh Tú</t>
+          <t>Văn Thị Trang</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>64511283</v>
       </c>
       <c r="C116" t="n">
-        <v>169458458</v>
+        <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" t="n">
-        <v>169458458</v>
+        <v>64511283</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN NGÓI NÂU GIA LAI</t>
+          <t>DOANH NGHIỆP TƯ NHÂN HỒNG BIÊN</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>5741340</v>
       </c>
       <c r="C117" t="n">
-        <v>62216706</v>
+        <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
-      </c>
-      <c r="E117" t="n">
-        <v>62216706</v>
+        <v>5741340</v>
       </c>
     </row>
     <row r="118">
@@ -2678,15 +2326,12 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0</v>
+        <v>289806522</v>
       </c>
       <c r="C118" t="n">
-        <v>289806522</v>
+        <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
-      </c>
-      <c r="E118" t="n">
         <v>289806522</v>
       </c>
     </row>
@@ -2697,15 +2342,12 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0</v>
+        <v>209257274</v>
       </c>
       <c r="C119" t="n">
-        <v>209257274</v>
+        <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" t="n">
         <v>209257274</v>
       </c>
     </row>
@@ -2716,54 +2358,45 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0</v>
+        <v>113593552</v>
       </c>
       <c r="C120" t="n">
-        <v>113593552</v>
+        <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
-      </c>
-      <c r="E120" t="n">
         <v>113593552</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Lê Xuân Cường</t>
+          <t>Ngô Võ Đan</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0</v>
+        <v>113453838</v>
       </c>
       <c r="C121" t="n">
-        <v>92364509</v>
+        <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" t="n">
-        <v>92364509</v>
+        <v>113453838</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Ngô Võ Đan</t>
+          <t>Lê Xuân Cường</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>92364509</v>
       </c>
       <c r="C122" t="n">
-        <v>113453838</v>
+        <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" t="n">
-        <v>113453838</v>
+        <v>92364509</v>
       </c>
     </row>
     <row r="123">
@@ -2773,73 +2406,61 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0</v>
+        <v>241451470</v>
       </c>
       <c r="C123" t="n">
-        <v>241451470</v>
+        <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" t="n">
         <v>241451470</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Lê Văn Bằng</t>
+          <t>Nguyễn Minh Tú</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0</v>
+        <v>169458458</v>
       </c>
       <c r="C124" t="n">
-        <v>132937416</v>
+        <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" t="n">
-        <v>132937416</v>
+        <v>169458458</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Nguyễn Hữu Thành</t>
+          <t>Huỳnh Thị Trúc Ly</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>172721649</v>
       </c>
       <c r="C125" t="n">
-        <v>260454151</v>
+        <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" t="n">
-        <v>260454151</v>
+        <v>172721649</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Tâm</t>
+          <t>Nguyễn Hữu Thành</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>260454151</v>
       </c>
       <c r="C126" t="n">
-        <v>167005238</v>
+        <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
-      </c>
-      <c r="E126" t="n">
-        <v>167005238</v>
+        <v>260454151</v>
       </c>
     </row>
     <row r="127">
@@ -2849,624 +2470,525 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>132486797</v>
       </c>
       <c r="C127" t="n">
-        <v>132486797</v>
+        <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
-      </c>
-      <c r="E127" t="n">
         <v>132486797</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH VÕ VĂN NGỌ</t>
+          <t>CÔNG TY CỔ PHẦN NGÓI NÂU GIA LAI</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>62216706</v>
       </c>
       <c r="C128" t="n">
-        <v>66782415</v>
+        <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" t="n">
-        <v>66782415</v>
+        <v>62216706</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TẠP HÓA NĂM THI</t>
+          <t>Nguyễn Thị Tâm</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>167005238</v>
       </c>
       <c r="C129" t="n">
-        <v>46344956</v>
+        <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" t="n">
-        <v>46344956</v>
+        <v>167005238</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thu Hằng</t>
+          <t>Lê Văn Bằng</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0</v>
+        <v>132937416</v>
       </c>
       <c r="C130" t="n">
-        <v>155155639</v>
+        <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
-      </c>
-      <c r="E130" t="n">
-        <v>155155639</v>
+        <v>132937416</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TẠP HÓA THÌN</t>
+          <t>Lê Văn Mẫn</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>235395239</v>
       </c>
       <c r="C131" t="n">
-        <v>9754668</v>
+        <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" t="n">
-        <v>9754668</v>
+        <v>235395239</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Nguyễn Nam Hồng</t>
+          <t>Hoàng Chí Công</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>147289986</v>
       </c>
       <c r="C132" t="n">
-        <v>161914097</v>
+        <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
-      </c>
-      <c r="E132" t="n">
-        <v>161914097</v>
+        <v>147289986</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Nguyễn Quốc Đạt</t>
+          <t>Nguyễn Trường Sơn</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0</v>
+        <v>107795444</v>
       </c>
       <c r="C133" t="n">
-        <v>241448995</v>
+        <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" t="n">
-        <v>241448995</v>
+        <v>107795444</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Nguyễn Trịnh Minh Hoàng</t>
+          <t>TẠP HÓA THÌN</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>9754668</v>
       </c>
       <c r="C134" t="n">
-        <v>209281321</v>
+        <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" t="n">
-        <v>209281321</v>
+        <v>9754668</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Mai Hoàng Thiện Châu</t>
+          <t>SUI NGỌC LAN</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>12232763</v>
       </c>
       <c r="C135" t="n">
-        <v>166626778</v>
+        <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
-      </c>
-      <c r="E135" t="n">
-        <v>166626778</v>
+        <v>12232763</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Đăng Loan</t>
+          <t>Mai Hoàng Thiện Châu</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>166626778</v>
       </c>
       <c r="C136" t="n">
-        <v>173086396</v>
+        <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
-      </c>
-      <c r="E136" t="n">
-        <v>173086396</v>
+        <v>166626778</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Dương</t>
+          <t>Nguyễn Thị Đăng Loan</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>173086396</v>
       </c>
       <c r="C137" t="n">
-        <v>187691183</v>
+        <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
-      </c>
-      <c r="E137" t="n">
-        <v>187691183</v>
+        <v>173086396</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SUI NGỌC LAN</t>
+          <t>Nguyễn Thị Thu Hằng</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>155155639</v>
       </c>
       <c r="C138" t="n">
-        <v>12232763</v>
+        <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
-      </c>
-      <c r="E138" t="n">
-        <v>12232763</v>
+        <v>155155639</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>QUÁCH THỊ THÚY NGA</t>
+          <t>Nguyễn Thị Minh Tâm</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>190953225</v>
       </c>
       <c r="C139" t="n">
-        <v>19762931</v>
+        <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>0</v>
-      </c>
-      <c r="E139" t="n">
-        <v>19762931</v>
+        <v>190953225</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Nguyễn Trường Sơn</t>
+          <t>Nguyễn Thị Hiền</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>153063249</v>
       </c>
       <c r="C140" t="n">
-        <v>107795444</v>
+        <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>0</v>
-      </c>
-      <c r="E140" t="n">
-        <v>107795444</v>
+        <v>153063249</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Minh Tâm</t>
+          <t>Nguyễn Quốc Đạt</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>241448995</v>
       </c>
       <c r="C141" t="n">
-        <v>190953225</v>
+        <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
-      </c>
-      <c r="E141" t="n">
-        <v>190953225</v>
+        <v>241448995</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Hiền</t>
+          <t>Nguyễn Nam Hồng</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0</v>
+        <v>161914097</v>
       </c>
       <c r="C142" t="n">
-        <v>153063249</v>
+        <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>0</v>
-      </c>
-      <c r="E142" t="n">
-        <v>153063249</v>
+        <v>161914097</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Nguyễn Hồng Ý</t>
+          <t>HỘ KINH DOANH VÕ VĂN NGỌ</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>66782415</v>
       </c>
       <c r="C143" t="n">
-        <v>225945739</v>
+        <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>0</v>
-      </c>
-      <c r="E143" t="n">
-        <v>225945739</v>
+        <v>66782415</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PHAN THỊ ÁNH LỸ</t>
+          <t>TẠP HÓA NĂM THI</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>46344956</v>
       </c>
       <c r="C144" t="n">
-        <v>18342199</v>
+        <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
-      </c>
-      <c r="E144" t="n">
-        <v>18342199</v>
+        <v>46344956</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Trịnh Tân</t>
+          <t>PHAN THỊ ÁNH LỸ</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0</v>
+        <v>18342199</v>
       </c>
       <c r="C145" t="n">
-        <v>206613852</v>
+        <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
-      </c>
-      <c r="E145" t="n">
-        <v>206613852</v>
+        <v>18342199</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Trịnh Thị Sinh</t>
+          <t>QUÁCH THỊ THÚY NGA</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0</v>
+        <v>19762931</v>
       </c>
       <c r="C146" t="n">
-        <v>152557899</v>
+        <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>0</v>
-      </c>
-      <c r="E146" t="n">
-        <v>152557899</v>
+        <v>19762931</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Võ Chí Hà</t>
+          <t>Nguyễn Trịnh Minh Hoàng</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>209281321</v>
       </c>
       <c r="C147" t="n">
-        <v>112601232</v>
+        <v>0</v>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
-      </c>
-      <c r="E147" t="n">
-        <v>112601232</v>
+        <v>209281321</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>LÊ THỊ MỸ PHƯƠNG</t>
+          <t>Nguyễn Hồng Ý</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0</v>
+        <v>225945739</v>
       </c>
       <c r="C148" t="n">
-        <v>43179190</v>
+        <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
-      </c>
-      <c r="E148" t="n">
-        <v>43179190</v>
+        <v>225945739</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Nguyễn Trịnh Tố Ngân</t>
+          <t>Nguyễn Văn Dương</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0</v>
+        <v>187691183</v>
       </c>
       <c r="C149" t="n">
-        <v>130495163</v>
+        <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
-      </c>
-      <c r="E149" t="n">
-        <v>130495163</v>
+        <v>187691183</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>TẠP HÓA BỬU HIỀN</t>
+          <t>Trần Thị Tuyết Nhung</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0</v>
+        <v>132827967</v>
       </c>
       <c r="C150" t="n">
-        <v>61435252</v>
+        <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>0</v>
-      </c>
-      <c r="E150" t="n">
-        <v>61435252</v>
+        <v>132827967</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Trần Thị Tuyết Nhung</t>
+          <t>TẠP HÓA BỬU HIỀN</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0</v>
+        <v>61435252</v>
       </c>
       <c r="C151" t="n">
-        <v>132827967</v>
+        <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
-      </c>
-      <c r="E151" t="n">
-        <v>132827967</v>
+        <v>61435252</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Trịnh Lê Hiệp</t>
+          <t>Trần Bích Hải</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0</v>
+        <v>114345439</v>
       </c>
       <c r="C152" t="n">
-        <v>260140118</v>
+        <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
-      </c>
-      <c r="E152" t="n">
-        <v>260140118</v>
+        <v>114345439</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Hoàng Tú</t>
+          <t>Nguyễn Trịnh Tố Ngân</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0</v>
+        <v>130495163</v>
       </c>
       <c r="C153" t="n">
-        <v>199955071</v>
+        <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>0</v>
-      </c>
-      <c r="E153" t="n">
-        <v>199955071</v>
+        <v>130495163</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Bùi Văn Lực</t>
+          <t>Võ Chí Hà</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0</v>
+        <v>112601232</v>
       </c>
       <c r="C154" t="n">
-        <v>243611717</v>
+        <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>0</v>
-      </c>
-      <c r="E154" t="n">
-        <v>243611717</v>
+        <v>112601232</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Vương Trường Giang</t>
+          <t>Trịnh Thị Sinh</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0</v>
+        <v>152557899</v>
       </c>
       <c r="C155" t="n">
-        <v>111832426</v>
+        <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>0</v>
-      </c>
-      <c r="E155" t="n">
-        <v>111832426</v>
+        <v>152557899</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Võ Văn Vũ</t>
+          <t>Phan Thanh Hoàng</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0</v>
+        <v>116130899</v>
       </c>
       <c r="C156" t="n">
-        <v>112039110</v>
+        <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
-      </c>
-      <c r="E156" t="n">
-        <v>112039110</v>
+        <v>116130899</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Vũ Thị Việt Hằng</t>
+          <t>Trịnh Tân</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0</v>
+        <v>206613852</v>
       </c>
       <c r="C157" t="n">
-        <v>165336925</v>
+        <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>0</v>
-      </c>
-      <c r="E157" t="n">
-        <v>165336925</v>
+        <v>206613852</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Đỗ Trịnh Công</t>
+          <t>Trịnh Lê Hiệp</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0</v>
+        <v>260140118</v>
       </c>
       <c r="C158" t="n">
-        <v>152180951</v>
+        <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
-      </c>
-      <c r="E158" t="n">
-        <v>152180951</v>
+        <v>260140118</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Phan Thanh Hoàng</t>
+          <t>Trần Quý Đức</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0</v>
+        <v>169963096</v>
       </c>
       <c r="C159" t="n">
-        <v>116130899</v>
+        <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>0</v>
-      </c>
-      <c r="E159" t="n">
-        <v>116130899</v>
+        <v>169963096</v>
       </c>
     </row>
     <row r="160">
@@ -3476,1213 +2998,1021 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0</v>
+        <v>130483375</v>
       </c>
       <c r="C160" t="n">
-        <v>130483375</v>
+        <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
-      </c>
-      <c r="E160" t="n">
         <v>130483375</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Trần Bích Hải</t>
+          <t>LÊ THỊ MỸ PHƯƠNG</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0</v>
+        <v>43179190</v>
       </c>
       <c r="C161" t="n">
-        <v>114345439</v>
+        <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
-      </c>
-      <c r="E161" t="n">
-        <v>114345439</v>
+        <v>43179190</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Trần Quý Đức</t>
+          <t>Đỗ Trịnh Công</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0</v>
+        <v>152180951</v>
       </c>
       <c r="C162" t="n">
-        <v>169963096</v>
+        <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>0</v>
-      </c>
-      <c r="E162" t="n">
-        <v>169963096</v>
+        <v>152180951</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Kpă Vũ Mạnh Long</t>
+          <t>Vũ Thị Việt Hằng</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0</v>
+        <v>165336925</v>
       </c>
       <c r="C163" t="n">
-        <v>109286964</v>
+        <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>0</v>
-      </c>
-      <c r="E163" t="n">
-        <v>109286964</v>
+        <v>165336925</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Ngô Văn Bằng</t>
+          <t>Võ Văn Vũ</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0</v>
+        <v>112039110</v>
       </c>
       <c r="C164" t="n">
-        <v>111936480</v>
+        <v>0</v>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
-      </c>
-      <c r="E164" t="n">
-        <v>111936480</v>
+        <v>112039110</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>HUỲNH ĐỨC AN</t>
+          <t>Vương Trường Giang</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0</v>
+        <v>111832426</v>
       </c>
       <c r="C165" t="n">
-        <v>54719280</v>
+        <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
-      </c>
-      <c r="E165" t="n">
-        <v>54719280</v>
+        <v>111832426</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Huỳnh Thị Cúc</t>
+          <t>Bùi Văn Lực</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0</v>
+        <v>243611717</v>
       </c>
       <c r="C166" t="n">
-        <v>248582520</v>
+        <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
-      </c>
-      <c r="E166" t="n">
-        <v>248582520</v>
+        <v>243611717</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Nguyễn Thúc Bảo</t>
+          <t>Hoàng Tú</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0</v>
+        <v>199955071</v>
       </c>
       <c r="C167" t="n">
-        <v>111954346</v>
+        <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>0</v>
-      </c>
-      <c r="E167" t="n">
-        <v>111954346</v>
+        <v>199955071</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Phan Công Thiện</t>
+          <t>Trịnh Thị Luận</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0</v>
+        <v>168619647</v>
       </c>
       <c r="C168" t="n">
-        <v>112632349</v>
+        <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>0</v>
-      </c>
-      <c r="E168" t="n">
-        <v>112632349</v>
+        <v>168619647</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Nguyễn Lê Hậu</t>
+          <t>Huỳnh Thị Cúc</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0</v>
+        <v>248582520</v>
       </c>
       <c r="C169" t="n">
-        <v>260476999</v>
+        <v>0</v>
       </c>
       <c r="D169" t="n">
-        <v>0</v>
-      </c>
-      <c r="E169" t="n">
-        <v>260476999</v>
+        <v>248582520</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>NGUYỄN VĂN CÔNG</t>
+          <t>Kpă Vũ Mạnh Long</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0</v>
+        <v>109286964</v>
       </c>
       <c r="C170" t="n">
-        <v>94306512</v>
+        <v>0</v>
       </c>
       <c r="D170" t="n">
-        <v>0</v>
-      </c>
-      <c r="E170" t="n">
-        <v>94306512</v>
+        <v>109286964</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Dương Thị Thông</t>
+          <t>HUỲNH ĐỨC AN</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0</v>
+        <v>54719280</v>
       </c>
       <c r="C171" t="n">
-        <v>243833248</v>
+        <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
-      </c>
-      <c r="E171" t="n">
-        <v>243833248</v>
+        <v>54719280</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Trịnh Thị Luận</t>
+          <t>Phan Thị Thùy Mỵ</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0</v>
+        <v>113837653</v>
       </c>
       <c r="C172" t="n">
-        <v>168619647</v>
+        <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
-      </c>
-      <c r="E172" t="n">
-        <v>168619647</v>
+        <v>113837653</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Phan Thị Thùy Mỵ</t>
+          <t>Ngô Văn Bằng</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0</v>
+        <v>111936480</v>
       </c>
       <c r="C173" t="n">
-        <v>113837653</v>
+        <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>0</v>
-      </c>
-      <c r="E173" t="n">
-        <v>113837653</v>
+        <v>111936480</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Mai Thị Kim Loan</t>
+          <t>LTG</t>
         </is>
       </c>
       <c r="B174" t="n">
         <v>0</v>
       </c>
       <c r="C174" t="n">
-        <v>144859608</v>
+        <v>4662130</v>
       </c>
       <c r="D174" t="n">
-        <v>0</v>
-      </c>
-      <c r="E174" t="n">
-        <v>144859608</v>
+        <v>-4662130</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Dương Nô</t>
+          <t>Dương Thị Thông</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0</v>
+        <v>243833248</v>
       </c>
       <c r="C175" t="n">
-        <v>111439059</v>
+        <v>0</v>
       </c>
       <c r="D175" t="n">
-        <v>0</v>
-      </c>
-      <c r="E175" t="n">
-        <v>111439059</v>
+        <v>243833248</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Ngô Đức Thuận</t>
+          <t>Nguyễn Lê Hậu</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0</v>
+        <v>260476999</v>
       </c>
       <c r="C176" t="n">
-        <v>131567122</v>
+        <v>0</v>
       </c>
       <c r="D176" t="n">
-        <v>0</v>
-      </c>
-      <c r="E176" t="n">
-        <v>131567122</v>
+        <v>260476999</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Theo</t>
+          <t>Phan Công Thiện</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0</v>
+        <v>112632349</v>
       </c>
       <c r="C177" t="n">
-        <v>93332200</v>
+        <v>0</v>
       </c>
       <c r="D177" t="n">
-        <v>0</v>
-      </c>
-      <c r="E177" t="n">
-        <v>93332200</v>
+        <v>112632349</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ĐINH VĂN VIÊN</t>
+          <t>Nguyễn Thúc Bảo</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0</v>
+        <v>111954346</v>
       </c>
       <c r="C178" t="n">
-        <v>51415511</v>
+        <v>0</v>
       </c>
       <c r="D178" t="n">
-        <v>0</v>
-      </c>
-      <c r="E178" t="n">
-        <v>51415511</v>
+        <v>111954346</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Đinh Thiện Ân</t>
+          <t>NGUYỄN VĂN CÔNG</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0</v>
+        <v>94306512</v>
       </c>
       <c r="C179" t="n">
-        <v>114697559</v>
+        <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>0</v>
-      </c>
-      <c r="E179" t="n">
-        <v>114697559</v>
+        <v>94306512</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Trần Trung Hiếu</t>
+          <t>Ngô Đức Thuận</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0</v>
+        <v>131567122</v>
       </c>
       <c r="C180" t="n">
-        <v>19665288</v>
+        <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
-      </c>
-      <c r="E180" t="n">
-        <v>19665288</v>
+        <v>131567122</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Đinh Biên Thùy</t>
+          <t>ĐINH VĂN VIÊN</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0</v>
+        <v>51415511</v>
       </c>
       <c r="C181" t="n">
-        <v>142784458</v>
+        <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>0</v>
-      </c>
-      <c r="E181" t="n">
-        <v>142784458</v>
+        <v>51415511</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Trịnh Lê Hưng</t>
+          <t>Mai Thị Kim Loan</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0</v>
+        <v>144859608</v>
       </c>
       <c r="C182" t="n">
-        <v>208830345</v>
+        <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>0</v>
-      </c>
-      <c r="E182" t="n">
-        <v>208830345</v>
+        <v>144859608</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ LINH GIANG</t>
+          <t>Dương Nô</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0</v>
+        <v>111439059</v>
       </c>
       <c r="C183" t="n">
-        <v>89714754</v>
+        <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>0</v>
-      </c>
-      <c r="E183" t="n">
-        <v>89714754</v>
+        <v>111439059</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TRẦN THỊ THU HƯƠNG</t>
+          <t>Nguyễn Văn Theo</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0</v>
+        <v>93332200</v>
       </c>
       <c r="C184" t="n">
-        <v>33034001</v>
+        <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
-      </c>
-      <c r="E184" t="n">
-        <v>33034001</v>
+        <v>93332200</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Hoàng Anh Thương</t>
+          <t>Trịnh Lê Hưng</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0</v>
+        <v>208830345</v>
       </c>
       <c r="C185" t="n">
-        <v>67529025</v>
+        <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>0</v>
-      </c>
-      <c r="E185" t="n">
-        <v>67529025</v>
+        <v>208830345</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Trần Thị Thu Hồng</t>
+          <t>Đinh Biên Thùy</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0</v>
+        <v>142784458</v>
       </c>
       <c r="C186" t="n">
-        <v>103684279</v>
+        <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>0</v>
-      </c>
-      <c r="E186" t="n">
-        <v>103684279</v>
+        <v>142784458</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Dương Minh Ngọc</t>
+          <t>Trần Trung Hiếu</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0</v>
+        <v>19665288</v>
       </c>
       <c r="C187" t="n">
-        <v>73225572</v>
+        <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>0</v>
-      </c>
-      <c r="E187" t="n">
-        <v>73225572</v>
+        <v>19665288</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Nhà Thuốc Linh</t>
+          <t>Đinh Thiện Ân</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0</v>
+        <v>114697559</v>
       </c>
       <c r="C188" t="n">
-        <v>19459440</v>
+        <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>0</v>
-      </c>
-      <c r="E188" t="n">
-        <v>19459440</v>
+        <v>114697559</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Tạp Hóa Thùy Linh</t>
+          <t>Nguyễn Thị Thanh Hương</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>0</v>
+        <v>292651315</v>
       </c>
       <c r="C189" t="n">
-        <v>72053019</v>
+        <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>0</v>
-      </c>
-      <c r="E189" t="n">
-        <v>72053019</v>
+        <v>292651315</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Đỗ Thị Bích Hương</t>
+          <t>CAO MẠNH HÙNG</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0</v>
+        <v>93965037</v>
       </c>
       <c r="C190" t="n">
-        <v>220668611</v>
+        <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>0</v>
-      </c>
-      <c r="E190" t="n">
-        <v>220668611</v>
+        <v>93965037</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>TẠP HÓA NHƯ THỦY</t>
+          <t>NGUYỄN THỊ TẠO</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0</v>
+        <v>56632668</v>
       </c>
       <c r="C191" t="n">
-        <v>57550578</v>
+        <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>0</v>
-      </c>
-      <c r="E191" t="n">
-        <v>57550578</v>
+        <v>56632668</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>LƯU THỊ THUỲ</t>
+          <t>Đỗ Thành Vinh</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0</v>
+        <v>113695752</v>
       </c>
       <c r="C192" t="n">
-        <v>96882946</v>
+        <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>0</v>
-      </c>
-      <c r="E192" t="n">
-        <v>96882946</v>
+        <v>113695752</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thanh Hương</t>
+          <t>Phạm Thị Mỹ Hạnh</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0</v>
+        <v>225080985</v>
       </c>
       <c r="C193" t="n">
-        <v>292651315</v>
+        <v>0</v>
       </c>
       <c r="D193" t="n">
-        <v>0</v>
-      </c>
-      <c r="E193" t="n">
-        <v>292651315</v>
+        <v>225080985</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Phan Thị Ánh Mỹ</t>
+          <t>TẠP HÓA NHƯ THỦY</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0</v>
+        <v>57550578</v>
       </c>
       <c r="C194" t="n">
-        <v>240243282</v>
+        <v>0</v>
       </c>
       <c r="D194" t="n">
-        <v>0</v>
-      </c>
-      <c r="E194" t="n">
-        <v>240243282</v>
+        <v>57550578</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Hà Thị Hiếu</t>
+          <t>TRẦN THỊ THU HƯƠNG</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0</v>
+        <v>33034001</v>
       </c>
       <c r="C195" t="n">
-        <v>94706437</v>
+        <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>0</v>
-      </c>
-      <c r="E195" t="n">
-        <v>94706437</v>
+        <v>33034001</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Lê Văn Hưng</t>
+          <t>Phan Thị Ánh Mỹ</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0</v>
+        <v>240243282</v>
       </c>
       <c r="C196" t="n">
-        <v>95596343</v>
+        <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>0</v>
-      </c>
-      <c r="E196" t="n">
-        <v>95596343</v>
+        <v>240243282</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Mai Văn Tân</t>
+          <t>PHẠM NGUYỄN LONG THÀNH</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0</v>
+        <v>40290318</v>
       </c>
       <c r="C197" t="n">
-        <v>149513069</v>
+        <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>0</v>
-      </c>
-      <c r="E197" t="n">
-        <v>149513069</v>
+        <v>40290318</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Đỗ Thành Vinh</t>
+          <t>Hà Thị Hiếu</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0</v>
+        <v>94706437</v>
       </c>
       <c r="C198" t="n">
-        <v>113695752</v>
+        <v>0</v>
       </c>
       <c r="D198" t="n">
-        <v>0</v>
-      </c>
-      <c r="E198" t="n">
-        <v>113695752</v>
+        <v>94706437</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>LÊ THỊ MỸ LOAN</t>
+          <t>NGUYỄN THỊ LINH GIANG</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0</v>
+        <v>89714754</v>
       </c>
       <c r="C199" t="n">
-        <v>69945287</v>
+        <v>0</v>
       </c>
       <c r="D199" t="n">
-        <v>0</v>
-      </c>
-      <c r="E199" t="n">
-        <v>69945287</v>
+        <v>89714754</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TRẦN THỊ THU HÀ</t>
+          <t>Lê Văn Hưng</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0</v>
+        <v>95596343</v>
       </c>
       <c r="C200" t="n">
-        <v>55746047</v>
+        <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>0</v>
-      </c>
-      <c r="E200" t="n">
-        <v>55746047</v>
+        <v>95596343</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Phạm Thị Mỹ Hạnh</t>
+          <t>Hộ Kinh Doanh Đồng Thị Thanh</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0</v>
+        <v>75303891</v>
       </c>
       <c r="C201" t="n">
-        <v>225080985</v>
+        <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>0</v>
-      </c>
-      <c r="E201" t="n">
-        <v>225080985</v>
+        <v>75303891</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PHẠM NGUYỄN LONG THÀNH</t>
+          <t>Lại Thị Hà</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0</v>
+        <v>91139305</v>
       </c>
       <c r="C202" t="n">
-        <v>40290318</v>
+        <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>0</v>
-      </c>
-      <c r="E202" t="n">
-        <v>40290318</v>
+        <v>91139305</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>CAO MẠNH HÙNG</t>
+          <t>Nguyễn Thị Thu</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0</v>
+        <v>56904595</v>
       </c>
       <c r="C203" t="n">
-        <v>93965037</v>
+        <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>0</v>
-      </c>
-      <c r="E203" t="n">
-        <v>93965037</v>
+        <v>56904595</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ TẠO</t>
+          <t>Nguyễn Văn Trung</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0</v>
+        <v>34317000</v>
       </c>
       <c r="C204" t="n">
-        <v>56632668</v>
+        <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>0</v>
-      </c>
-      <c r="E204" t="n">
-        <v>56632668</v>
+        <v>34317000</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Đỗ Thị Hồng Nhung</t>
+          <t>PHẠM THỊ THU SA</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0</v>
+        <v>72713516</v>
       </c>
       <c r="C205" t="n">
-        <v>222153462</v>
+        <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>0</v>
-      </c>
-      <c r="E205" t="n">
-        <v>222153462</v>
+        <v>72713516</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Trần Minh Chung</t>
+          <t>Trần Văn Hiệu</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0</v>
+        <v>58075244</v>
       </c>
       <c r="C206" t="n">
-        <v>55283301</v>
+        <v>0</v>
       </c>
       <c r="D206" t="n">
-        <v>0</v>
-      </c>
-      <c r="E206" t="n">
-        <v>55283301</v>
+        <v>58075244</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Đồng Thị Thanh</t>
+          <t>LÊ THỊ MỸ LOAN</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0</v>
+        <v>69945287</v>
       </c>
       <c r="C207" t="n">
-        <v>75303891</v>
+        <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>0</v>
-      </c>
-      <c r="E207" t="n">
-        <v>75303891</v>
+        <v>69945287</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Lại Thị Hà</t>
+          <t>Mai Văn Tân</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0</v>
+        <v>149513069</v>
       </c>
       <c r="C208" t="n">
-        <v>91139305</v>
+        <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>0</v>
-      </c>
-      <c r="E208" t="n">
-        <v>91139305</v>
+        <v>149513069</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Thu</t>
+          <t>Dương Minh Ngọc</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0</v>
+        <v>73225572</v>
       </c>
       <c r="C209" t="n">
-        <v>56904595</v>
+        <v>0</v>
       </c>
       <c r="D209" t="n">
-        <v>0</v>
-      </c>
-      <c r="E209" t="n">
-        <v>56904595</v>
+        <v>73225572</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Trung</t>
+          <t>Trần Thị Thu Hồng</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0</v>
+        <v>103684279</v>
       </c>
       <c r="C210" t="n">
-        <v>34317000</v>
+        <v>0</v>
       </c>
       <c r="D210" t="n">
-        <v>0</v>
-      </c>
-      <c r="E210" t="n">
-        <v>34317000</v>
+        <v>103684279</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>PHẠM THỊ THU SA</t>
+          <t>LƯU THỊ THUỲ</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0</v>
+        <v>96882946</v>
       </c>
       <c r="C211" t="n">
-        <v>72713516</v>
+        <v>0</v>
       </c>
       <c r="D211" t="n">
-        <v>0</v>
-      </c>
-      <c r="E211" t="n">
-        <v>72713516</v>
+        <v>96882946</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Trần Văn Hiệu</t>
+          <t>Đỗ Thị Bích Hương</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0</v>
+        <v>220668611</v>
       </c>
       <c r="C212" t="n">
-        <v>58075244</v>
+        <v>0</v>
       </c>
       <c r="D212" t="n">
-        <v>0</v>
-      </c>
-      <c r="E212" t="n">
-        <v>58075244</v>
+        <v>220668611</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>BÙI XUÂN NAM</t>
+          <t>Nhà Thuốc Linh</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0</v>
+        <v>19459440</v>
       </c>
       <c r="C213" t="n">
-        <v>93355244</v>
+        <v>0</v>
       </c>
       <c r="D213" t="n">
-        <v>0</v>
-      </c>
-      <c r="E213" t="n">
-        <v>93355244</v>
+        <v>19459440</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TRẦN TIẾN DŨNG</t>
+          <t>Tạp Hóa Thùy Linh</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0</v>
+        <v>72053019</v>
       </c>
       <c r="C214" t="n">
-        <v>37058364</v>
+        <v>0</v>
       </c>
       <c r="D214" t="n">
-        <v>0</v>
-      </c>
-      <c r="E214" t="n">
-        <v>37058364</v>
+        <v>72053019</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Nương</t>
+          <t>Trần Minh Chung</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0</v>
+        <v>55283301</v>
       </c>
       <c r="C215" t="n">
-        <v>37600124</v>
+        <v>0</v>
       </c>
       <c r="D215" t="n">
-        <v>0</v>
-      </c>
-      <c r="E215" t="n">
-        <v>37600124</v>
+        <v>55283301</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH KHIÊN LÀNH</t>
+          <t>TRẦN THỊ THU HÀ</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0</v>
+        <v>55746047</v>
       </c>
       <c r="C216" t="n">
-        <v>75158369</v>
+        <v>0</v>
       </c>
       <c r="D216" t="n">
-        <v>0</v>
-      </c>
-      <c r="E216" t="n">
-        <v>75158369</v>
+        <v>55746047</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Vũ Thị Thu Hường</t>
+          <t>Hoàng Anh Thương</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0</v>
+        <v>67529025</v>
       </c>
       <c r="C217" t="n">
-        <v>100927438</v>
+        <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>0</v>
-      </c>
-      <c r="E217" t="n">
-        <v>100927438</v>
+        <v>67529025</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>LÂM MINH HOÀNG</t>
+          <t>Đỗ Thị Hồng Nhung</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0</v>
+        <v>222153462</v>
       </c>
       <c r="C218" t="n">
-        <v>75323336</v>
+        <v>0</v>
       </c>
       <c r="D218" t="n">
-        <v>0</v>
-      </c>
-      <c r="E218" t="n">
-        <v>75323336</v>
+        <v>222153462</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH ĐẶNG THỊ DIỄM</t>
+          <t>TRẦN TIẾN DŨNG</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0</v>
+        <v>37058364</v>
       </c>
       <c r="C219" t="n">
-        <v>75977935</v>
+        <v>0</v>
       </c>
       <c r="D219" t="n">
-        <v>0</v>
-      </c>
-      <c r="E219" t="n">
-        <v>75977935</v>
+        <v>37058364</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Hồ Thị Thanh Hiền</t>
+          <t>BÙI XUÂN NAM</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0</v>
+        <v>93355244</v>
       </c>
       <c r="C220" t="n">
-        <v>72565656</v>
+        <v>0</v>
       </c>
       <c r="D220" t="n">
-        <v>0</v>
-      </c>
-      <c r="E220" t="n">
-        <v>72565656</v>
+        <v>93355244</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Nguyễn Đức Thiên</t>
+          <t>HỘ KINH DOANH ĐẶNG THỊ DIỄM</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0</v>
+        <v>75977935</v>
       </c>
       <c r="C221" t="n">
-        <v>93567284</v>
+        <v>0</v>
       </c>
       <c r="D221" t="n">
-        <v>0</v>
-      </c>
-      <c r="E221" t="n">
-        <v>93567284</v>
+        <v>75977935</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Lê Tiến Hậu</t>
+          <t>HỘ KINH DOANH KHIÊN LÀNH</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0</v>
+        <v>75158369</v>
       </c>
       <c r="C222" t="n">
-        <v>130810220</v>
+        <v>0</v>
       </c>
       <c r="D222" t="n">
-        <v>0</v>
-      </c>
-      <c r="E222" t="n">
-        <v>130810220</v>
+        <v>75158369</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Trần Thị Lan Thi</t>
+          <t>Nguyễn Thị Nương</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0</v>
+        <v>37600124</v>
       </c>
       <c r="C223" t="n">
-        <v>93448010</v>
+        <v>0</v>
       </c>
       <c r="D223" t="n">
-        <v>0</v>
-      </c>
-      <c r="E223" t="n">
-        <v>93448010</v>
+        <v>37600124</v>
       </c>
     </row>
     <row r="224">
@@ -4692,1535 +4022,1420 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0</v>
+        <v>55259900</v>
       </c>
       <c r="C224" t="n">
-        <v>55259900</v>
+        <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>0</v>
-      </c>
-      <c r="E224" t="n">
         <v>55259900</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Võ Văn Thành</t>
+          <t>Trần Thị Lan Thi</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0</v>
+        <v>93448010</v>
       </c>
       <c r="C225" t="n">
-        <v>37061399</v>
+        <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>0</v>
-      </c>
-      <c r="E225" t="n">
-        <v>37061399</v>
+        <v>93448010</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Trịnh Lê Đông</t>
+          <t>Lê Tiến Hậu</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0</v>
+        <v>130810220</v>
       </c>
       <c r="C226" t="n">
-        <v>208483355</v>
+        <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>0</v>
-      </c>
-      <c r="E226" t="n">
-        <v>208483355</v>
+        <v>130810220</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Tường Vi</t>
+          <t>Nguyễn Đức Thiên</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0</v>
+        <v>93567284</v>
       </c>
       <c r="C227" t="n">
-        <v>37203656</v>
+        <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>0</v>
-      </c>
-      <c r="E227" t="n">
-        <v>37203656</v>
+        <v>93567284</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Đàm Đình Ngữ</t>
+          <t>Hộ Kinh Doanh Hồ Thị Thanh Hiền</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0</v>
+        <v>72565656</v>
       </c>
       <c r="C228" t="n">
-        <v>105797354</v>
+        <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>0</v>
-      </c>
-      <c r="E228" t="n">
-        <v>105797354</v>
+        <v>72565656</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Thới Thị Bích Hà</t>
+          <t>LÂM MINH HOÀNG</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0</v>
+        <v>75323336</v>
       </c>
       <c r="C229" t="n">
-        <v>96073251</v>
+        <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>0</v>
-      </c>
-      <c r="E229" t="n">
-        <v>96073251</v>
+        <v>75323336</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VIỄN THÔNG T&amp;T GIA LAI</t>
+          <t>Lâm Ngọc Đào</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0</v>
+        <v>133099188</v>
       </c>
       <c r="C230" t="n">
-        <v>5148768</v>
+        <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>0</v>
-      </c>
-      <c r="E230" t="n">
-        <v>5148768</v>
+        <v>133099188</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Đặng Kim Hùng</t>
+          <t>TRỊNH HOÀNG SƠN</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0</v>
+        <v>147169661</v>
       </c>
       <c r="C231" t="n">
-        <v>72633979</v>
+        <v>0</v>
       </c>
       <c r="D231" t="n">
-        <v>0</v>
-      </c>
-      <c r="E231" t="n">
-        <v>72633979</v>
+        <v>147169661</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>TRỊNH HOÀNG SƠN</t>
+          <t>Vũ Thị Thu Hường</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0</v>
+        <v>100927438</v>
       </c>
       <c r="C232" t="n">
-        <v>147169661</v>
+        <v>0</v>
       </c>
       <c r="D232" t="n">
-        <v>0</v>
-      </c>
-      <c r="E232" t="n">
-        <v>147169661</v>
+        <v>100927438</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Lâm Ngọc Đào</t>
+          <t>Nguyễn Thị Tường Vi</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>0</v>
+        <v>37203656</v>
       </c>
       <c r="C233" t="n">
-        <v>133099188</v>
+        <v>0</v>
       </c>
       <c r="D233" t="n">
-        <v>0</v>
-      </c>
-      <c r="E233" t="n">
-        <v>133099188</v>
+        <v>37203656</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>TẠP HÓA THÙY TRANG</t>
+          <t>Đặng Kim Hùng</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>0</v>
+        <v>72633979</v>
       </c>
       <c r="C234" t="n">
-        <v>56131277</v>
+        <v>0</v>
       </c>
       <c r="D234" t="n">
-        <v>0</v>
-      </c>
-      <c r="E234" t="n">
-        <v>56131277</v>
+        <v>72633979</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>TẠP HÓA CÚC</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VIỄN THÔNG T&amp;T GIA LAI</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0</v>
+        <v>5148768</v>
       </c>
       <c r="C235" t="n">
-        <v>77778421</v>
+        <v>0</v>
       </c>
       <c r="D235" t="n">
-        <v>0</v>
-      </c>
-      <c r="E235" t="n">
-        <v>77778421</v>
+        <v>5148768</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>NGUYỄN THỊ KIM LIÊN</t>
+          <t>Trịnh Lê Đông</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0</v>
+        <v>208483355</v>
       </c>
       <c r="C236" t="n">
-        <v>95603094</v>
+        <v>0</v>
       </c>
       <c r="D236" t="n">
-        <v>0</v>
-      </c>
-      <c r="E236" t="n">
-        <v>95603094</v>
+        <v>208483355</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Trần Bích Hả</t>
+          <t>Đàm Đình Ngữ</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0</v>
+        <v>105797354</v>
       </c>
       <c r="C237" t="n">
-        <v>18502560</v>
+        <v>0</v>
       </c>
       <c r="D237" t="n">
-        <v>0</v>
-      </c>
-      <c r="E237" t="n">
-        <v>18502560</v>
+        <v>105797354</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Phạm Văn Minh</t>
+          <t>Thới Thị Bích Hà</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0</v>
+        <v>96073251</v>
       </c>
       <c r="C238" t="n">
-        <v>129316036</v>
+        <v>0</v>
       </c>
       <c r="D238" t="n">
-        <v>0</v>
-      </c>
-      <c r="E238" t="n">
-        <v>129316036</v>
+        <v>96073251</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>PHOTOCOPY - VĂN PHÒNG PHẨM - TẠP HÓA MAI LAN</t>
+          <t>Võ Văn Thành</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0</v>
+        <v>37061399</v>
       </c>
       <c r="C239" t="n">
-        <v>59869441</v>
+        <v>0</v>
       </c>
       <c r="D239" t="n">
-        <v>0</v>
-      </c>
-      <c r="E239" t="n">
-        <v>59869441</v>
+        <v>37061399</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>HỒ TRỌNG DUY</t>
+          <t>Trần Bích Hả</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0</v>
+        <v>18502560</v>
       </c>
       <c r="C240" t="n">
-        <v>37879130</v>
+        <v>0</v>
       </c>
       <c r="D240" t="n">
-        <v>0</v>
-      </c>
-      <c r="E240" t="n">
-        <v>37879130</v>
+        <v>18502560</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH ÔNG NGỌC NHÂN</t>
+          <t>TẠP HÓA CÚC</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0</v>
+        <v>77778421</v>
       </c>
       <c r="C241" t="n">
-        <v>71343420</v>
+        <v>0</v>
       </c>
       <c r="D241" t="n">
-        <v>0</v>
-      </c>
-      <c r="E241" t="n">
-        <v>71343420</v>
+        <v>77778421</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Đỗ Anh Tuấn</t>
+          <t>TẠP HÓA THÙY TRANG</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0</v>
+        <v>56131277</v>
       </c>
       <c r="C242" t="n">
-        <v>36114299</v>
+        <v>0</v>
       </c>
       <c r="D242" t="n">
-        <v>0</v>
-      </c>
-      <c r="E242" t="n">
-        <v>36114299</v>
+        <v>56131277</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Hoàng Thị Thu Hương</t>
+          <t>NGUYỄN THỊ KIM LIÊN</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0</v>
+        <v>95603094</v>
       </c>
       <c r="C243" t="n">
-        <v>45800482</v>
+        <v>0</v>
       </c>
       <c r="D243" t="n">
-        <v>0</v>
-      </c>
-      <c r="E243" t="n">
-        <v>45800482</v>
+        <v>95603094</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Sui Ngọc Lan</t>
+          <t>Phạm Văn Minh</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0</v>
+        <v>129316036</v>
       </c>
       <c r="C244" t="n">
-        <v>17926173</v>
+        <v>0</v>
       </c>
       <c r="D244" t="n">
-        <v>0</v>
-      </c>
-      <c r="E244" t="n">
-        <v>17926173</v>
+        <v>129316036</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Kim Tuyến</t>
+          <t>PHOTOCOPY - VĂN PHÒNG PHẨM - TẠP HÓA MAI LAN</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0</v>
+        <v>59869441</v>
       </c>
       <c r="C245" t="n">
-        <v>56971830</v>
+        <v>0</v>
       </c>
       <c r="D245" t="n">
-        <v>0</v>
-      </c>
-      <c r="E245" t="n">
-        <v>56971830</v>
+        <v>59869441</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Quách Thị Thúy Nga</t>
+          <t>HỒ TRỌNG DUY</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0</v>
+        <v>37879130</v>
       </c>
       <c r="C246" t="n">
-        <v>37823760</v>
+        <v>0</v>
       </c>
       <c r="D246" t="n">
-        <v>0</v>
-      </c>
-      <c r="E246" t="n">
-        <v>37823760</v>
+        <v>37879130</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>BÙI QUANG DIỄN</t>
+          <t>HỘ KINH DOANH ÔNG NGỌC NHÂN</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0</v>
+        <v>71343420</v>
       </c>
       <c r="C247" t="n">
-        <v>36097078</v>
+        <v>0</v>
       </c>
       <c r="D247" t="n">
-        <v>0</v>
-      </c>
-      <c r="E247" t="n">
-        <v>36097078</v>
+        <v>71343420</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Hoàng Phát</t>
+          <t>Đỗ Anh Tuấn</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0</v>
+        <v>36114299</v>
       </c>
       <c r="C248" t="n">
-        <v>54095774</v>
+        <v>0</v>
       </c>
       <c r="D248" t="n">
-        <v>0</v>
-      </c>
-      <c r="E248" t="n">
-        <v>54095774</v>
+        <v>36114299</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Shop Hà Thu</t>
+          <t>Sui Ngọc Lan</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0</v>
+        <v>17926173</v>
       </c>
       <c r="C249" t="n">
-        <v>43990020</v>
+        <v>0</v>
       </c>
       <c r="D249" t="n">
-        <v>0</v>
-      </c>
-      <c r="E249" t="n">
-        <v>43990020</v>
+        <v>17926173</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN CHERRYBLOSSOM NHA TRANG</t>
+          <t>Nguyễn Thị Kim Tuyến</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0</v>
+        <v>56971830</v>
       </c>
       <c r="C250" t="n">
-        <v>5013051</v>
+        <v>0</v>
       </c>
       <c r="D250" t="n">
-        <v>0</v>
-      </c>
-      <c r="E250" t="n">
-        <v>5013051</v>
+        <v>56971830</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>TRƯƠNG THỊ KHUYÊN</t>
+          <t>Hoàng Thị Thu Hương</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0</v>
+        <v>45800482</v>
       </c>
       <c r="C251" t="n">
-        <v>21123415</v>
+        <v>0</v>
       </c>
       <c r="D251" t="n">
-        <v>0</v>
-      </c>
-      <c r="E251" t="n">
-        <v>21123415</v>
+        <v>45800482</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>CHI NHÁNH GIA LAI - CÔNG TY CỔ PHẦN DỊCH VỤ THƯƠNG MẠI TỔNG HỢP WINCOMMERCE</t>
+          <t>Quách Thị Thúy Nga</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0</v>
+        <v>37823760</v>
       </c>
       <c r="C252" t="n">
-        <v>814320</v>
+        <v>0</v>
       </c>
       <c r="D252" t="n">
-        <v>0</v>
-      </c>
-      <c r="E252" t="n">
-        <v>814320</v>
+        <v>37823760</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ĐÀO THỊ NHUNG SÂM</t>
+          <t>BÙI QUANG DIỄN</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0</v>
+        <v>36097078</v>
       </c>
       <c r="C253" t="n">
-        <v>42077440</v>
+        <v>0</v>
       </c>
       <c r="D253" t="n">
-        <v>0</v>
-      </c>
-      <c r="E253" t="n">
-        <v>42077440</v>
+        <v>36097078</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THỰC PHẨM NHS</t>
+          <t>Hộ Kinh Doanh Hoàng Phát</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0</v>
+        <v>54095774</v>
       </c>
       <c r="C254" t="n">
-        <v>9259508</v>
+        <v>0</v>
       </c>
       <c r="D254" t="n">
-        <v>0</v>
-      </c>
-      <c r="E254" t="n">
-        <v>9259508</v>
+        <v>54095774</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>TRUNG TÂM VPP - VHP - MÁY VP - TẠP HÓA TRẦN PHÚ</t>
+          <t>Shop Hà Thu</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0</v>
+        <v>43990020</v>
       </c>
       <c r="C255" t="n">
-        <v>3286473</v>
+        <v>0</v>
       </c>
       <c r="D255" t="n">
-        <v>0</v>
-      </c>
-      <c r="E255" t="n">
-        <v>3286473</v>
+        <v>43990020</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Bách Hóa Tổng Hợp Tư Tạo</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN CHERRYBLOSSOM NHA TRANG</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0</v>
+        <v>5013051</v>
       </c>
       <c r="C256" t="n">
-        <v>18031613</v>
+        <v>0</v>
       </c>
       <c r="D256" t="n">
-        <v>0</v>
-      </c>
-      <c r="E256" t="n">
-        <v>18031613</v>
+        <v>5013051</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh An Bình</t>
+          <t>TRƯƠNG THỊ KHUYÊN</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0</v>
+        <v>21123415</v>
       </c>
       <c r="C257" t="n">
-        <v>37425850</v>
+        <v>0</v>
       </c>
       <c r="D257" t="n">
-        <v>0</v>
-      </c>
-      <c r="E257" t="n">
-        <v>37425850</v>
+        <v>21123415</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH ĐẦU TƯ HOÀN SINH GIA LAI</t>
+          <t>CHI NHÁNH GIA LAI - CÔNG TY CỔ PHẦN DỊCH VỤ THƯƠNG MẠI TỔNG HỢP WINCOMMERCE</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0</v>
+        <v>814320</v>
       </c>
       <c r="C258" t="n">
-        <v>12389689</v>
+        <v>0</v>
       </c>
       <c r="D258" t="n">
-        <v>0</v>
-      </c>
-      <c r="E258" t="n">
-        <v>12389689</v>
+        <v>814320</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN NƯỚC GIẢI KHÁT SANEST KHÁNH HÒA</t>
+          <t>ĐÀO THỊ NHUNG SÂM</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0</v>
+        <v>42077440</v>
       </c>
       <c r="C259" t="n">
-        <v>2971021</v>
+        <v>0</v>
       </c>
       <c r="D259" t="n">
-        <v>0</v>
-      </c>
-      <c r="E259" t="n">
-        <v>2971021</v>
+        <v>42077440</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>CỬA HÀNG LAN TÂM</t>
+          <t>CÔNG TY TNHH THỰC PHẨM NHS</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0</v>
+        <v>9259508</v>
       </c>
       <c r="C260" t="n">
-        <v>12302058</v>
+        <v>0</v>
       </c>
       <c r="D260" t="n">
-        <v>0</v>
-      </c>
-      <c r="E260" t="n">
-        <v>12302058</v>
+        <v>9259508</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH PHỐ NÚI RESTAURANT</t>
+          <t>TRUNG TÂM VPP - VHP - MÁY VP - TẠP HÓA TRẦN PHÚ</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0</v>
+        <v>3286473</v>
       </c>
       <c r="C261" t="n">
-        <v>34735604</v>
+        <v>0</v>
       </c>
       <c r="D261" t="n">
-        <v>0</v>
-      </c>
-      <c r="E261" t="n">
-        <v>34735604</v>
+        <v>3286473</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Bùi Thành Trung</t>
+          <t>Hộ Kinh Doanh An Bình</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0</v>
+        <v>37425850</v>
       </c>
       <c r="C262" t="n">
-        <v>57172306</v>
+        <v>0</v>
       </c>
       <c r="D262" t="n">
-        <v>0</v>
-      </c>
-      <c r="E262" t="n">
-        <v>57172306</v>
+        <v>37425850</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>BÙI TRẦN THỊ LIỄU</t>
+          <t>Bách Hóa Tổng Hợp Tư Tạo</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>0</v>
+        <v>18031613</v>
       </c>
       <c r="C263" t="n">
-        <v>19416802</v>
+        <v>0</v>
       </c>
       <c r="D263" t="n">
-        <v>0</v>
-      </c>
-      <c r="E263" t="n">
-        <v>19416802</v>
+        <v>18031613</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Cửa Hàng Nhật  An</t>
+          <t>LNH</t>
         </is>
       </c>
       <c r="B264" t="n">
         <v>0</v>
       </c>
       <c r="C264" t="n">
-        <v>18624060</v>
+        <v>3124917</v>
       </c>
       <c r="D264" t="n">
-        <v>0</v>
-      </c>
-      <c r="E264" t="n">
-        <v>18624060</v>
+        <v>-3124917</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN TỨ QUÝ GIA LAI</t>
+          <t>CHI NHÁNH CÔNG TY TNHH ĐẦU TƯ HOÀN SINH GIA LAI</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>0</v>
+        <v>12389689</v>
       </c>
       <c r="C265" t="n">
-        <v>117288000</v>
+        <v>0</v>
       </c>
       <c r="D265" t="n">
-        <v>0</v>
-      </c>
-      <c r="E265" t="n">
-        <v>117288000</v>
+        <v>12389689</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BAMBO GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN NƯỚC GIẢI KHÁT SANEST KHÁNH HÒA</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>0</v>
+        <v>2971021</v>
       </c>
       <c r="C266" t="n">
-        <v>2249569</v>
+        <v>0</v>
       </c>
       <c r="D266" t="n">
-        <v>0</v>
-      </c>
-      <c r="E266" t="n">
-        <v>2249569</v>
+        <v>2971021</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN HỆ THỐNG ẨM THỰC MIÊN DI GOURMET</t>
+          <t>CỬA HÀNG LAN TÂM</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>0</v>
+        <v>12302058</v>
       </c>
       <c r="C267" t="n">
-        <v>34799679</v>
+        <v>0</v>
       </c>
       <c r="D267" t="n">
-        <v>0</v>
-      </c>
-      <c r="E267" t="n">
-        <v>34799679</v>
+        <v>12302058</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Công Ty TNHH TM Ngọc Hoa</t>
+          <t>CÔNG TY TNHH PHỐ NÚI RESTAURANT</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>0</v>
+        <v>34735604</v>
       </c>
       <c r="C268" t="n">
-        <v>1782612</v>
+        <v>0</v>
       </c>
       <c r="D268" t="n">
-        <v>0</v>
-      </c>
-      <c r="E268" t="n">
-        <v>1782612</v>
+        <v>34735604</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Cty TNHH MTV SXTMDV Nhật Vĩnh</t>
+          <t>Bùi Thành Trung</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>0</v>
+        <v>57172306</v>
       </c>
       <c r="C269" t="n">
-        <v>18981000</v>
+        <v>0</v>
       </c>
       <c r="D269" t="n">
-        <v>0</v>
-      </c>
-      <c r="E269" t="n">
-        <v>18981000</v>
+        <v>57172306</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Bel Việt Nam</t>
+          <t>BÙI TRẦN THỊ LIỄU</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>0</v>
+        <v>19416802</v>
       </c>
       <c r="C270" t="n">
-        <v>17143056</v>
+        <v>0</v>
       </c>
       <c r="D270" t="n">
-        <v>0</v>
-      </c>
-      <c r="E270" t="n">
-        <v>17143056</v>
+        <v>19416802</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Cty TNHH MTV Lộc An Xuân</t>
+          <t>Cửa Hàng Nhật  An</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>0</v>
+        <v>18624060</v>
       </c>
       <c r="C271" t="n">
-        <v>18256590</v>
+        <v>0</v>
       </c>
       <c r="D271" t="n">
-        <v>0</v>
-      </c>
-      <c r="E271" t="n">
-        <v>18256590</v>
+        <v>18624060</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Trương Thị Mỹ Hà</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN TỨ QUÝ GIA LAI</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>0</v>
+        <v>117288000</v>
       </c>
       <c r="C272" t="n">
-        <v>38264775</v>
+        <v>0</v>
       </c>
       <c r="D272" t="n">
-        <v>0</v>
-      </c>
-      <c r="E272" t="n">
-        <v>38264775</v>
+        <v>117288000</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Tổng Công Ty Hàng Không Việt Nam- CTCP- Chi Nhánh Việt Nam</t>
+          <t>CÔNG TY TNHH BAMBO GIA LAI</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>0</v>
+        <v>2249569</v>
       </c>
       <c r="C273" t="n">
-        <v>5400194</v>
+        <v>0</v>
       </c>
       <c r="D273" t="n">
-        <v>0</v>
-      </c>
-      <c r="E273" t="n">
-        <v>5400194</v>
+        <v>2249569</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Phan Thị Ánh Lũy</t>
+          <t>CÔNG TY CỔ PHẦN HỆ THỐNG ẨM THỰC MIÊN DI GOURMET</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>0</v>
+        <v>34799679</v>
       </c>
       <c r="C274" t="n">
-        <v>69261630</v>
+        <v>0</v>
       </c>
       <c r="D274" t="n">
-        <v>0</v>
-      </c>
-      <c r="E274" t="n">
-        <v>69261630</v>
+        <v>34799679</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Nguyễn Mạnh</t>
+          <t>Công Ty TNHH TM Ngọc Hoa</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>0</v>
+        <v>1782612</v>
       </c>
       <c r="C275" t="n">
-        <v>114537266</v>
+        <v>0</v>
       </c>
       <c r="D275" t="n">
-        <v>0</v>
-      </c>
-      <c r="E275" t="n">
-        <v>114537266</v>
+        <v>1782612</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Hồ Minh Ngân</t>
+          <t>Cty TNHH MTV SXTMDV Nhật Vĩnh</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>0</v>
+        <v>18981000</v>
       </c>
       <c r="C276" t="n">
-        <v>71035603</v>
+        <v>0</v>
       </c>
       <c r="D276" t="n">
-        <v>0</v>
-      </c>
-      <c r="E276" t="n">
-        <v>71035603</v>
+        <v>18981000</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Phạm Ngọc Lâm</t>
+          <t>Công Ty TNHH Bel Việt Nam</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>0</v>
+        <v>17143056</v>
       </c>
       <c r="C277" t="n">
-        <v>173103828</v>
+        <v>0</v>
       </c>
       <c r="D277" t="n">
-        <v>0</v>
-      </c>
-      <c r="E277" t="n">
-        <v>173103828</v>
+        <v>17143056</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Trần Đăng Khoa</t>
+          <t>Cty TNHH MTV Lộc An Xuân</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>0</v>
+        <v>18256590</v>
       </c>
       <c r="C278" t="n">
-        <v>155111160</v>
+        <v>0</v>
       </c>
       <c r="D278" t="n">
-        <v>0</v>
-      </c>
-      <c r="E278" t="n">
-        <v>155111160</v>
+        <v>18256590</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Nguyễn Tấn Đức</t>
+          <t>Trương Thị Mỹ Hà</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>0</v>
+        <v>38264775</v>
       </c>
       <c r="C279" t="n">
-        <v>53502403</v>
+        <v>0</v>
       </c>
       <c r="D279" t="n">
-        <v>0</v>
-      </c>
-      <c r="E279" t="n">
-        <v>53502403</v>
+        <v>38264775</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Nguyễn Thành Phước</t>
+          <t>Tổng Công Ty Hàng Không Việt Nam- CTCP- Chi Nhánh Việt Nam</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>0</v>
+        <v>5400194</v>
       </c>
       <c r="C280" t="n">
-        <v>17073698</v>
+        <v>0</v>
       </c>
       <c r="D280" t="n">
-        <v>0</v>
-      </c>
-      <c r="E280" t="n">
-        <v>17073698</v>
+        <v>5400194</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Phan Thị Lâm</t>
+          <t>Phan Thị Ánh Lũy</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>0</v>
+        <v>69261630</v>
       </c>
       <c r="C281" t="n">
-        <v>104212766</v>
+        <v>0</v>
       </c>
       <c r="D281" t="n">
-        <v>0</v>
-      </c>
-      <c r="E281" t="n">
-        <v>104212766</v>
+        <v>69261630</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN WIN FOODS GIA LAI</t>
+          <t>Phạm Ngọc Lâm</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>0</v>
+        <v>173103828</v>
       </c>
       <c r="C282" t="n">
-        <v>19643904</v>
+        <v>0</v>
       </c>
       <c r="D282" t="n">
-        <v>0</v>
-      </c>
-      <c r="E282" t="n">
-        <v>19643904</v>
+        <v>173103828</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Trần Phương Thảo</t>
+          <t>Nguyễn Mạnh</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>0</v>
+        <v>114537266</v>
       </c>
       <c r="C283" t="n">
-        <v>146118433</v>
+        <v>0</v>
       </c>
       <c r="D283" t="n">
-        <v>0</v>
-      </c>
-      <c r="E283" t="n">
-        <v>146118433</v>
+        <v>114537266</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Nguyễn Văn Thông</t>
+          <t>Hồ Minh Ngân</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>0</v>
+        <v>71035603</v>
       </c>
       <c r="C284" t="n">
-        <v>138556211</v>
+        <v>0</v>
       </c>
       <c r="D284" t="n">
-        <v>0</v>
-      </c>
-      <c r="E284" t="n">
-        <v>138556211</v>
+        <v>71035603</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH BAZAN FOOD</t>
+          <t>Trần Đăng Khoa</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>0</v>
+        <v>155111160</v>
       </c>
       <c r="C285" t="n">
-        <v>2984565</v>
+        <v>0</v>
       </c>
       <c r="D285" t="n">
-        <v>0</v>
-      </c>
-      <c r="E285" t="n">
-        <v>2984565</v>
+        <v>155111160</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Cty TNHH MTV Minh Hà Gialai</t>
+          <t>Trần Phương Thảo</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>0</v>
+        <v>146118433</v>
       </c>
       <c r="C286" t="n">
-        <v>30879964</v>
+        <v>0</v>
       </c>
       <c r="D286" t="n">
-        <v>0</v>
-      </c>
-      <c r="E286" t="n">
-        <v>30879964</v>
+        <v>146118433</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Đoàn Thị Hồng Vân</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN WIN FOODS GIA LAI</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>0</v>
+        <v>19643904</v>
       </c>
       <c r="C287" t="n">
-        <v>128445286</v>
+        <v>0</v>
       </c>
       <c r="D287" t="n">
-        <v>0</v>
-      </c>
-      <c r="E287" t="n">
-        <v>128445286</v>
+        <v>19643904</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Lê Thị Hồng Hà</t>
+          <t>Nguyễn Tấn Đức</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>0</v>
+        <v>53502403</v>
       </c>
       <c r="C288" t="n">
-        <v>88381672</v>
+        <v>0</v>
       </c>
       <c r="D288" t="n">
-        <v>0</v>
-      </c>
-      <c r="E288" t="n">
-        <v>88381672</v>
+        <v>53502403</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Phạm Thị Thu Sương</t>
+          <t>Nguyễn Thành Phước</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>0</v>
+        <v>17073698</v>
       </c>
       <c r="C289" t="n">
-        <v>114003953</v>
+        <v>0</v>
       </c>
       <c r="D289" t="n">
-        <v>0</v>
-      </c>
-      <c r="E289" t="n">
-        <v>114003953</v>
+        <v>17073698</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Văn Phòng Phẩm- Tạp Hóa Bảy</t>
+          <t>Phan Thị Lâm</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>0</v>
+        <v>104212766</v>
       </c>
       <c r="C290" t="n">
-        <v>18981000</v>
+        <v>0</v>
       </c>
       <c r="D290" t="n">
-        <v>0</v>
-      </c>
-      <c r="E290" t="n">
-        <v>18981000</v>
+        <v>104212766</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Công Ty TNHH SX Và DV TamBa</t>
+          <t>Nguyễn Văn Thông</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>0</v>
+        <v>138556211</v>
       </c>
       <c r="C291" t="n">
-        <v>35761694</v>
+        <v>0</v>
       </c>
       <c r="D291" t="n">
-        <v>0</v>
-      </c>
-      <c r="E291" t="n">
-        <v>35761694</v>
+        <v>138556211</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Doanh Nghiệp Tư Nhân Thương Mại Thùy Dung</t>
+          <t>CÔNG TY TNHH BAZAN FOOD</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>0</v>
+        <v>2984565</v>
       </c>
       <c r="C292" t="n">
-        <v>35855628</v>
+        <v>0</v>
       </c>
       <c r="D292" t="n">
-        <v>0</v>
-      </c>
-      <c r="E292" t="n">
-        <v>35855628</v>
+        <v>2984565</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>BỆNH VIỆN ĐA KHOA TỈNH GIA LAI</t>
+          <t>Cty TNHH MTV Minh Hà Gialai</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>0</v>
+        <v>30879964</v>
       </c>
       <c r="C293" t="n">
-        <v>7916651</v>
+        <v>0</v>
       </c>
       <c r="D293" t="n">
-        <v>0</v>
-      </c>
-      <c r="E293" t="n">
-        <v>7916651</v>
+        <v>30879964</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN PRETZLE VIABLE</t>
+          <t>Đoàn Thị Hồng Vân</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0</v>
+        <v>128445286</v>
       </c>
       <c r="C294" t="n">
-        <v>3534369</v>
+        <v>0</v>
       </c>
       <c r="D294" t="n">
-        <v>0</v>
-      </c>
-      <c r="E294" t="n">
-        <v>3534369</v>
+        <v>128445286</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Một Thành Viên Minh Hà Gia Lai</t>
+          <t>Lê Thị Hồng Hà</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>0</v>
+        <v>88381672</v>
       </c>
       <c r="C295" t="n">
-        <v>19212077</v>
+        <v>0</v>
       </c>
       <c r="D295" t="n">
-        <v>0</v>
-      </c>
-      <c r="E295" t="n">
-        <v>19212077</v>
+        <v>88381672</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Công Ty TNHH MTV Quỳnh Nguyên Gia Lai</t>
+          <t>Phạm Thị Thu Sương</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>0</v>
+        <v>114003953</v>
       </c>
       <c r="C296" t="n">
-        <v>403112</v>
+        <v>0</v>
       </c>
       <c r="D296" t="n">
-        <v>0</v>
-      </c>
-      <c r="E296" t="n">
-        <v>403112</v>
+        <v>114003953</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Trường THCS Nguyễn Viết Xuân</t>
+          <t>Văn Phòng Phẩm- Tạp Hóa Bảy</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>0</v>
+        <v>18981000</v>
       </c>
       <c r="C297" t="n">
-        <v>18775800</v>
+        <v>0</v>
       </c>
       <c r="D297" t="n">
-        <v>0</v>
-      </c>
-      <c r="E297" t="n">
-        <v>18775800</v>
+        <v>18981000</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Tứ Quý Gia Lai</t>
+          <t>Công Ty TNHH SX Và DV TamBa</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>0</v>
+        <v>35761694</v>
       </c>
       <c r="C298" t="n">
-        <v>18138600</v>
+        <v>0</v>
       </c>
       <c r="D298" t="n">
-        <v>0</v>
-      </c>
-      <c r="E298" t="n">
-        <v>18138600</v>
+        <v>35761694</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>BÙI THỊ HUYỀN</t>
+          <t>Doanh Nghiệp Tư Nhân Thương Mại Thùy Dung</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>0</v>
+        <v>35855628</v>
       </c>
       <c r="C299" t="n">
-        <v>39514581</v>
+        <v>0</v>
       </c>
       <c r="D299" t="n">
-        <v>0</v>
-      </c>
-      <c r="E299" t="n">
-        <v>39514581</v>
+        <v>35855628</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Công Ty TNHH MTV Gia Luân Gia Lai</t>
+          <t>TKM CHOLIME</t>
         </is>
       </c>
       <c r="B300" t="n">
         <v>0</v>
       </c>
       <c r="C300" t="n">
-        <v>5471096</v>
+        <v>3534400</v>
       </c>
       <c r="D300" t="n">
-        <v>0</v>
-      </c>
-      <c r="E300" t="n">
-        <v>5471096</v>
+        <v>-3534400</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>PHAN THỊ ÁNH MỸ</t>
+          <t>CÔNG TY CỔ PHẦN PRETZLE VIABLE</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>0</v>
+        <v>3534369</v>
       </c>
       <c r="C301" t="n">
-        <v>5956200</v>
+        <v>0</v>
       </c>
       <c r="D301" t="n">
-        <v>0</v>
-      </c>
-      <c r="E301" t="n">
-        <v>5956200</v>
+        <v>3534369</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Đỗ Hà Trang</t>
+          <t>BỆNH VIỆN ĐA KHOA TỈNH GIA LAI</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>0</v>
+        <v>7916651</v>
       </c>
       <c r="C302" t="n">
-        <v>39601148</v>
+        <v>0</v>
       </c>
       <c r="D302" t="n">
-        <v>0</v>
-      </c>
-      <c r="E302" t="n">
-        <v>39601148</v>
+        <v>7916651</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Nguyễn Trịnh Minh Huy</t>
+          <t>Công Ty TNHH Một Thành Viên Minh Hà Gia Lai</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>0</v>
+        <v>19212077</v>
       </c>
       <c r="C303" t="n">
-        <v>39660336</v>
+        <v>0</v>
       </c>
       <c r="D303" t="n">
-        <v>0</v>
-      </c>
-      <c r="E303" t="n">
-        <v>39660336</v>
+        <v>19212077</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
+          <t>Công Ty TNHH MTV Quỳnh Nguyên Gia Lai</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>403112</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0</v>
+      </c>
+      <c r="D304" t="n">
+        <v>403112</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Trường THCS Nguyễn Viết Xuân</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>18775800</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0</v>
+      </c>
+      <c r="D305" t="n">
+        <v>18775800</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH Tứ Quý Gia Lai</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>18138600</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0</v>
+      </c>
+      <c r="D306" t="n">
+        <v>18138600</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>BÙI THỊ HUYỀN</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>39514581</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0</v>
+      </c>
+      <c r="D307" t="n">
+        <v>39514581</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH MTV Gia Luân Gia Lai</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>5471096</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0</v>
+      </c>
+      <c r="D308" t="n">
+        <v>5471096</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Nguyễn Trịnh Minh Huy</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>39660336</v>
+      </c>
+      <c r="C309" t="n">
+        <v>0</v>
+      </c>
+      <c r="D309" t="n">
+        <v>39660336</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>PHAN THỊ ÁNH MỸ</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>5956200</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0</v>
+      </c>
+      <c r="D310" t="n">
+        <v>5956200</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Đỗ Hà Trang</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>39601148</v>
+      </c>
+      <c r="C311" t="n">
+        <v>0</v>
+      </c>
+      <c r="D311" t="n">
+        <v>39601148</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
           <t>Phường Hoa Lư. Tp Pleiku</t>
         </is>
       </c>
-      <c r="B304" t="n">
-        <v>0</v>
-      </c>
-      <c r="C304" t="n">
+      <c r="B312" t="n">
         <v>19872864</v>
       </c>
-      <c r="D304" t="n">
-        <v>0</v>
-      </c>
-      <c r="E304" t="n">
+      <c r="C312" t="n">
+        <v>0</v>
+      </c>
+      <c r="D312" t="n">
         <v>19872864</v>
       </c>
     </row>
@@ -6235,40 +5450,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nhà cung cấp</t>
+          <t>Đối tượng</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Số dư đầu</t>
+          <t>MUA VÀO</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Phát sinh Nợ (Trả)</t>
+          <t>ĐÃ TRẢ</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Phát sinh Có (Mua)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Dư cuối</t>
+          <t>DƯ CUỐI KỲ</t>
         </is>
       </c>
     </row>
@@ -6279,7 +5488,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>21791855</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -6287,9 +5496,6 @@
       <c r="D2" t="n">
         <v>21791855</v>
       </c>
-      <c r="E2" t="n">
-        <v>21791855</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6298,7 +5504,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>830567693</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -6306,9 +5512,6 @@
       <c r="D3" t="n">
         <v>830567693</v>
       </c>
-      <c r="E3" t="n">
-        <v>830567693</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6317,7 +5520,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>3200627</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -6325,9 +5528,6 @@
       <c r="D4" t="n">
         <v>3200627</v>
       </c>
-      <c r="E4" t="n">
-        <v>3200627</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6336,7 +5536,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>8246551436</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -6344,27 +5544,21 @@
       <c r="D5" t="n">
         <v>8246551436</v>
       </c>
-      <c r="E5" t="n">
-        <v>8246551436</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sao kê Bidv 23.xls</t>
+          <t>CÔNG TY CỔ PHẦN NƯỚC GIẢI KHÁT SANEST KHÁNH HÒA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>50214269701</v>
       </c>
       <c r="C6" t="n">
-        <v>3430273365</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-3430273365</v>
+        <v>50214269701</v>
       </c>
     </row>
     <row r="7">
@@ -6374,7 +5568,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>24575429136</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -6382,9 +5576,6 @@
       <c r="D7" t="n">
         <v>24575429136</v>
       </c>
-      <c r="E7" t="n">
-        <v>24575429136</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6393,7 +5584,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>24617486040</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -6401,65 +5592,53 @@
       <c r="D8" t="n">
         <v>24617486040</v>
       </c>
-      <c r="E8" t="n">
-        <v>24617486040</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN NƯỚC GIẢI KHÁT SANEST KHÁNH HÒA</t>
+          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Gia Lai </t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1907972846</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>50214269701</v>
-      </c>
-      <c r="E9" t="n">
-        <v>50214269701</v>
+        <v>1907972846</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ngân hàng TMCP Ngoại thương Việt Nam - Chi nhánh Gia Lai </t>
+          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 7 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1559501</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1907972846</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1907972846</v>
+        <v>1559501</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CÔNG TY DỊCH VỤ MOBIFONE KHU VỰC 7 - CHI NHÁNH TỔNG CÔNG TY VIỄN THÔNG MOBIFONE</t>
+          <t>Vay VCB tt tiền hàng Cty CLM</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2023410510</v>
       </c>
       <c r="D11" t="n">
-        <v>1559501</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1559501</v>
+        <v>-2023410510</v>
       </c>
     </row>
     <row r="12">
@@ -6469,7 +5648,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>241533</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -6477,546 +5656,459 @@
       <c r="D12" t="n">
         <v>241533</v>
       </c>
-      <c r="E12" t="n">
-        <v>241533</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH SẢN XUẤT - THƯƠNG MẠI VÀ DỊCH VỤ HỒNG AN</t>
+          <t>Vay VCB tt tiền hàng Cty Yến</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>10311253022</v>
       </c>
       <c r="D13" t="n">
-        <v>55159335</v>
-      </c>
-      <c r="E13" t="n">
-        <v>55159335</v>
+        <v>-10311253022</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NABATI VIỆT NAM</t>
+          <t>CÔNG TY TNHH SẢN XUẤT - THƯƠNG MẠI VÀ DỊCH VỤ HỒNG AN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>55159335</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>14155929868</v>
-      </c>
-      <c r="E14" t="n">
-        <v>14155929868</v>
+        <v>55159335</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Công ty Điện lực Gia Lai</t>
+          <t>Vay VCB tt tiền hàng Cty VS+NBT</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1047059026</v>
       </c>
       <c r="D15" t="n">
-        <v>957344</v>
-      </c>
-      <c r="E15" t="n">
-        <v>957344</v>
+        <v>-1047059026</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN TRƯỜNG XUÂN</t>
+          <t>CÔNG TY TNHH NABATI VIỆT NAM</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>14155929868</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>12097000</v>
-      </c>
-      <c r="E16" t="n">
-        <v>12097000</v>
+        <v>14155929868</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Gia Lai</t>
+          <t>Vay VCB tt tiền hàng Cty Vissan</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>2675384521</v>
       </c>
       <c r="D17" t="n">
-        <v>1175020</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1175020</v>
+        <v>-2675384521</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NGAN HANG TMCP CONG THUONG VIET NAM - CN GIA LAI</t>
+          <t>Công ty Điện lực Gia Lai</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>957344</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>111352677</v>
-      </c>
-      <c r="E18" t="n">
-        <v>111352677</v>
+        <v>957344</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ÂN PHÚ KON TUM</t>
+          <t>CÔNG TY CỔ PHẦN TRƯỜNG XUÂN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>12097000</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>25716339</v>
-      </c>
-      <c r="E19" t="n">
-        <v>25716339</v>
+        <v>12097000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN QUẢN LÝ NỢ VÀ KHAI THÁC TÀI SẢN NGÂN HÀNG TMCP CÔNG THƯƠNG VIỆT NAM</t>
+          <t>Ngân hàng TMCP Sài Gòn Thương Tín - Chi nhánh Gia Lai</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1175020</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="E20" t="n">
-        <v>3300000</v>
+        <v>1175020</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
+          <t>Vay VCB tt tiền hàng Cty Nbt</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>500842964</v>
       </c>
       <c r="D21" t="n">
-        <v>33920000</v>
-      </c>
-      <c r="E21" t="n">
-        <v>33920000</v>
+        <v>-500842964</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Gia Lai</t>
+          <t>NGAN HANG TMCP CONG THUONG VIET NAM - CN GIA LAI</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>111352677</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>2888600</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2888600</v>
+        <v>111352677</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐĂNG KIỂM CAO NGUYÊN</t>
+          <t>Vay VCB TT tiền hàng Cty Yến</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1896095709</v>
       </c>
       <c r="D23" t="n">
-        <v>2053454</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2053454</v>
+        <v>-1896095709</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN SOM TUM THAI</t>
+          <t>Vay VCB tt tiền hàng Cty VS</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>382900052</v>
       </c>
       <c r="D24" t="n">
-        <v>1555800</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1555800</v>
+        <v>-382900052</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Công Ty Cổ Phần Bệnh Viện Đa Khoa Tâm Anh TP. Hồ Chí Minh</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ÂN PHÚ KON TUM</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>25716339</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>31687194</v>
-      </c>
-      <c r="E25" t="n">
-        <v>31687194</v>
+        <v>25716339</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HTV MẠNH PHƯƠNG F&amp;B</t>
+          <t>Vay VCB tt tiền hàng Cty Yến+VS+NBT</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1481316545</v>
       </c>
       <c r="D26" t="n">
-        <v>26542336</v>
-      </c>
-      <c r="E26" t="n">
-        <v>26542336</v>
+        <v>-1481316545</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH CHRISTIAN DIOR VIỆT NAM TẠI THÀNH PHỐ HỒ CHÍ MINH</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN QUẢN LÝ NỢ VÀ KHAI THÁC TÀI SẢN NGÂN HÀNG TMCP CÔNG THƯƠNG VIỆT NAM</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>3300000</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>11415000</v>
-      </c>
-      <c r="E27" t="n">
-        <v>11415000</v>
+        <v>3300000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN QUỐC TẾ TAM SƠN - CHI NHÁNH HCM</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN THIÊN THANH G.A</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>33920000</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>62605000</v>
-      </c>
-      <c r="E28" t="n">
-        <v>62605000</v>
+        <v>33920000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Công ty TNHH Thuần Lý</t>
+          <t>Vay VCB tt tiền hàng Cty Nabati</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>254121566</v>
       </c>
       <c r="D29" t="n">
-        <v>18390000</v>
-      </c>
-      <c r="E29" t="n">
-        <v>18390000</v>
+        <v>-254121566</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DU LỊCH TÀU BẾN NGHÉ</t>
+          <t>Vay Vcb tt tiền hàng Cty Clm</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>526780035</v>
       </c>
       <c r="D30" t="n">
-        <v>3061300</v>
-      </c>
-      <c r="E30" t="n">
-        <v>3061300</v>
+        <v>-526780035</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH HAI DI LAO VIET NAM HOLDINGS - CHI NHÁNH THÀNH PHỐ HỒ CHÍ MINH</t>
+          <t>Ngân hàng Thương mại Cổ phần Đầu tư và Phát triển Việt Nam - Chi nhánh Gia Lai</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>2888600</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>1309000</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1309000</v>
+        <v>2888600</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Viettel Gia Lai- Chi nhánh Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
+          <t>CÔNG TY TNHH ĐĂNG KIỂM CAO NGUYÊN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>2053454</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
+        <v>2053454</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MITRAMODE DUTA FASHINDO VIỆT NAM</t>
+          <t>CÔNG TY CỔ PHẦN SOM TUM THAI</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>1555800</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>16194000</v>
-      </c>
-      <c r="E33" t="n">
-        <v>16194000</v>
+        <v>1555800</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐIỆN TỬ VIỄN THÔNG ÁNH DƯƠNG</t>
+          <t>Công Ty Cổ Phần Bệnh Viện Đa Khoa Tâm Anh TP. Hồ Chí Minh</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>31687194</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>2970000</v>
-      </c>
-      <c r="E34" t="n">
-        <v>2970000</v>
+        <v>31687194</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CÔNG TY BẢO HIỂM BƯU ĐIỆN GIA LAI</t>
+          <t>CÔNG TY TNHH HTV MẠNH PHƯƠNG F&amp;B</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>26542336</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>4770300</v>
-      </c>
-      <c r="E35" t="n">
-        <v>4770300</v>
+        <v>26542336</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV THƯƠNG MẠI &amp; DỊCH VỤ ẮC QUY DIỆN LIÊN</t>
+          <t>CÔNG TY CỔ PHẦN QUỐC TẾ TAM SƠN - CHI NHÁNH HCM</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>62605000</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>3300000</v>
-      </c>
-      <c r="E36" t="n">
-        <v>3300000</v>
+        <v>62605000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV Ô TÔ TRƯỜNG HẢI GIA LAI</t>
+          <t>CHI NHÁNH CÔNG TY TNHH CHRISTIAN DIOR VIỆT NAM TẠI THÀNH PHỐ HỒ CHÍ MINH</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>11415000</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>6418867</v>
-      </c>
-      <c r="E37" t="n">
-        <v>6418867</v>
+        <v>11415000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MAY THÊU GIÀY AN PHƯỚC TẠI GIA LAI</t>
+          <t>Công ty TNHH Thuần Lý</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>18390000</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>2969400</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2969400</v>
+        <v>18390000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CÔNG TY XĂNG DẦU NAM TÂY NGUYÊN</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DU LỊCH TÀU BẾN NGHÉ</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>3061300</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>500000</v>
-      </c>
-      <c r="E39" t="n">
-        <v>500000</v>
+        <v>3061300</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN THỜI TRANG VÀ MỸ PHẨM DUY ANH</t>
+          <t>CÔNG TY TNHH HAI DI LAO VIET NAM HOLDINGS - CHI NHÁNH THÀNH PHỐ HỒ CHÍ MINH</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>1309000</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>35230000</v>
-      </c>
-      <c r="E40" t="n">
-        <v>35230000</v>
+        <v>1309000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MTV Ô TÔ GIA LAI</t>
+          <t>Viettel Gia Lai- Chi nhánh Tập đoàn Công nghiệp - Viễn thông Quân đội</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -7026,238 +6118,663 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1817430</v>
-      </c>
-      <c r="E41" t="n">
-        <v>1817430</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TRUNG TÂM KINH DOANH VNPT - GIA LAI - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
+          <t>CÔNG TY TNHH MITRAMODE DUTA FASHINDO VIỆT NAM</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>16194000</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>4332900</v>
-      </c>
-      <c r="E42" t="n">
-        <v>4332900</v>
+        <v>16194000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH TRUYỀN HÌNH CÁP SAIGONTOURIST-TỈNH GIA LAI</t>
+          <t>Vay VCB tt tiền hàng Cty Nabati+VS</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>301878328</v>
       </c>
       <c r="D43" t="n">
-        <v>1610000</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1610000</v>
+        <v>-301878328</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CÔNG TY BẢO HIỂM BIDV BẮC TÂY NGUYÊN</t>
+          <t>Vay VCB tt tiền hàng Cty Bel</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>131227569</v>
       </c>
       <c r="D44" t="n">
-        <v>3230700</v>
-      </c>
-      <c r="E44" t="n">
-        <v>3230700</v>
+        <v>-131227569</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NGAN HANG TMCP CONG THUONG VIET NAM - 50098|CN GIA LAI</t>
+          <t>CÔNG TY CỔ PHẦN ĐIỆN TỬ VIỄN THÔNG ÁNH DƯƠNG</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>2970000</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>159543182</v>
-      </c>
-      <c r="E45" t="n">
-        <v>159543182</v>
+        <v>2970000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HÀ ĐỨC VINH</t>
+          <t>CÔNG TY BẢO HIỂM BƯU ĐIỆN GIA LAI</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>4770300</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>5200000</v>
-      </c>
-      <c r="E46" t="n">
-        <v>5200000</v>
+        <v>4770300</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN SÁCH VÀ THIẾT BỊ TRƯỜNG HỌC GIA LAI</t>
+          <t>Vay Vcb tt tiền hàng Cty Yến</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>2034968400</v>
       </c>
       <c r="D47" t="n">
-        <v>800000</v>
-      </c>
-      <c r="E47" t="n">
-        <v>800000</v>
+        <v>-2034968400</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN BẢO THUẬN</t>
+          <t>CÔNG TY TNHH MTV THƯƠNG MẠI &amp; DỊCH VỤ ẮC QUY DIỆN LIÊN</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>3300000</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>4390000</v>
-      </c>
-      <c r="E48" t="n">
-        <v>4390000</v>
+        <v>3300000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THU PHÍ TỰ ĐỘNG VETC</t>
+          <t>Vay VCB TT tiền hàng CTY Nabati</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>955809765</v>
       </c>
       <c r="D49" t="n">
-        <v>8847000</v>
-      </c>
-      <c r="E49" t="n">
-        <v>8847000</v>
+        <v>-955809765</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CÔNG TY BẢO HIỂM VIETINBANK BẮC TÂY NGUYÊN</t>
+          <t>CÔNG TY TNHH MTV Ô TÔ TRƯỜNG HẢI GIA LAI</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>6418867</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>1681000</v>
-      </c>
-      <c r="E50" t="n">
-        <v>1681000</v>
+        <v>6418867</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN AN PHÁT LỘC GIA LAI</t>
+          <t>Vay VCB TT tiền hàng CTY CLM</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>2903837550</v>
       </c>
       <c r="D51" t="n">
-        <v>2866000</v>
-      </c>
-      <c r="E51" t="n">
-        <v>2866000</v>
+        <v>-2903837550</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THẾ HỆ MỚI GIA LAI</t>
+          <t>Vay VCB TT tiền hàng CTY Yến SN</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>2700000000</v>
       </c>
       <c r="D52" t="n">
-        <v>11712950</v>
-      </c>
-      <c r="E52" t="n">
-        <v>11712950</v>
+        <v>-2700000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>CHI NHÁNH CÔNG TY TNHH MAY THÊU GIÀY AN PHƯỚC TẠI GIA LAI</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2969400</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2969400</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CÔNG TY XĂNG DẦU NAM TÂY NGUYÊN</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MTV Ô TÔ GIA LAI</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1817430</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1817430</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THỜI TRANG VÀ MỸ PHẨM DUY ANH</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>35230000</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>35230000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Vay VCB TT tiền hàng CTY Yến</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" t="n">
+        <v>4714638720</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-4714638720</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TRUNG TÂM KINH DOANH VNPT - GIA LAI - CHI NHÁNH TỔNG CÔNG TY DỊCH VỤ VIỄN THÔNG</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>4332900</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4332900</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Vay VCB TT tiền hàng CTY Vissan</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" t="n">
+        <v>985192901</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-985192901</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TNHH TRUYỀN HÌNH CÁP SAIGONTOURIST-TỈNH GIA LAI</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1610000</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1610000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CÔNG TY BẢO HIỂM BIDV BẮC TÂY NGUYÊN</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>3230700</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>3230700</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Vay VCB TT tiền hàng cty Yến SN</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2755957600</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-2755957600</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Vay VCB TT tiền hàng CLM</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" t="n">
+        <v>714632644</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-714632644</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Vay VCB TT tiền hàng Vissan</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" t="n">
+        <v>911224575</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-911224575</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HUY VŨ</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>3480000</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>3480000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>NGAN HANG TMCP CONG THUONG VIET NAM - 50098|CN GIA LAI</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>159543182</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>159543182</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Vay VCB TT tiền hàng CTY Visssan</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" t="n">
+        <v>240489903</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-240489903</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN HÀ ĐỨC VINH</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>5200000</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN SÁCH VÀ THIẾT BỊ TRƯỜNG HỌC GIA LAI</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>800000</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN BẢO THUẬN</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>4390000</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>4390000</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THU PHÍ TỰ ĐỘNG VETC</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>8847000</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>8847000</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Vay VCB TT tiền hàng CTY Nabati VN</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" t="n">
+        <v>415459768</v>
+      </c>
+      <c r="D72" t="n">
+        <v>-415459768</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>CÔNG TY BẢO HIỂM VIETINBANK BẮC TÂY NGUYÊN</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1681000</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1681000</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN AN PHÁT LỘC GIA LAI</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>2866000</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>2866000</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Vay VCB TT tiền hàng CTY CLM A : 272,950,420 + CLM B : 11,360,232 + VS : 167,379,844đ</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" t="n">
+        <v>451690496</v>
+      </c>
+      <c r="D75" t="n">
+        <v>-451690496</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN THẾ HỆ MỚI GIA LAI</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>11712950</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>11712950</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Vay VCB TT tiền hàng CTY VS</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" t="n">
+        <v>254815217</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-254815217</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Vay VCB TT tiền hàng Cty CLM</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>279542523</v>
+      </c>
+      <c r="D78" t="n">
+        <v>-279542523</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>CN CÔNG TY CP PHÁT TRIỂN PHẦN MỀM ASIA TẠI ĐÀ NẴNG</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" t="n">
+      <c r="B79" t="n">
         <v>14000000</v>
       </c>
-      <c r="E53" t="n">
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
         <v>14000000</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Vay VCB TT tiền hàng Cty CLM Chư Sê</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="n">
+        <v>174852169</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-174852169</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Vay VCB TT tiền hàng CTY Bêl</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" t="n">
+        <v>247840258</v>
+      </c>
+      <c r="D81" t="n">
+        <v>-247840258</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Vay VCB TT tiền hàng CTY CLM Phố</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" t="n">
+        <v>859127044</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-859127044</v>
       </c>
     </row>
   </sheetData>
